--- a/public/data/データ管理用.xlsx
+++ b/public/data/データ管理用.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\world_map_project\world-map-news-app\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D9A15D-9E1A-4996-9B97-D07DFE1756F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B2C7623-654A-4995-B66A-C066D229DE78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{17EB953A-2661-4049-9616-0D3098A3DA36}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{17EB953A-2661-4049-9616-0D3098A3DA36}"/>
   </bookViews>
   <sheets>
     <sheet name="events-入力用" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="248">
   <si>
     <t>country_iso3</t>
   </si>
@@ -521,13 +521,686 @@
       <t>ゴウイ</t>
     </rPh>
     <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>イスラエル</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>イスラエル閣僚がレバノン南部を併合宣言</t>
+    <rPh sb="12" eb="14">
+      <t>ナンブ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>財務相スモトリッヒ氏がレバノン南部リタニ川まで国境拡大を主張、空爆で民間被害。</t>
+    <rPh sb="9" eb="10">
+      <t>ウジ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ナンブ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>紛争</t>
+    <rPh sb="0" eb="2">
+      <t>フンソウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>レバノン</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>軍事的緊張が高まる</t>
+  </si>
+  <si>
+    <t>Reuters</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/middle-east/israeli-minister-calls-annexation-southern-lebanon-2026-03-23/</t>
+  </si>
+  <si>
+    <t>スロベニア</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>スロベニア総選挙</t>
+    <rPh sb="5" eb="8">
+      <t>ソウセンキョ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>自由派とポピュリスト右派が接戦、過半数獲得できず小党が連立の鍵に。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>選挙</t>
+    <rPh sb="0" eb="2">
+      <t>センキョ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>国内政治に影響</t>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/europe/slovenians-vote-tight-race-between-liberals-populist-right-2026-03-22/</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>イタリア</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>イタリアの司法改革案が国民投票にて否決</t>
+    <rPh sb="5" eb="10">
+      <t>シホウカイカクアン</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>コクミントウヒョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ヒケツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メローニの司法改正案が僅差で否決、支持基盤に大打撃。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>国内政治</t>
+    <rPh sb="0" eb="4">
+      <t>コクナイセイジ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/europe/exit-polls-suggest-italys-meloni-has-narrowly-lost-justice-referendum-vote-2026-03-23/</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>キューバ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ロシア原油がキューバに到着</t>
+    <rPh sb="11" eb="13">
+      <t>トウチャク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>トランプ大統領がキューバへの輸送を容認、ロシア産原油でキューバの燃料不足が一時緩和</t>
+    <rPh sb="4" eb="7">
+      <t>ダイトウリョウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ユソウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>エネルギー</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ロシア</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>アメリカ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>国際関係に影響</t>
+  </si>
+  <si>
+    <t>エネルギー</t>
+  </si>
+  <si>
+    <t>Bloomberg</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.bloomberg.com/news/articles/2026-03-30/russian-oil-shipment-buys-us-and-cuba-time-as-crisis-festers</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>パラグアイ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>パラグアイ、財務相が交代</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>暫定の財務相が就任、後任選定へ</t>
+    <rPh sb="0" eb="2">
+      <t>ザンテイ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ザイムショウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シュウニン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>コウニン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>センテイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.bloomberg.com/news/articles/2026-03-31/paraguay-names-interim-finance-chief-after-fernandez-resigns</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>アメリカ、3隻目の空母を中東海域へ派遣</t>
+    <rPh sb="12" eb="16">
+      <t>チュウトウカイイキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>第3空母戦闘群を中東へ増派、イランとの緊張続く。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>イラン</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.bloomberg.com/news/articles/2026-03-31/third-us-aircraft-carrier-heads-to-mideast-as-iran-war-continues</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>レバノン南部で国連平和維持軍3名が死亡</t>
+    <rPh sb="4" eb="6">
+      <t>ナンブ</t>
+    </rPh>
+    <rPh sb="7" eb="14">
+      <t>コクレンヘイワイジグン</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シボウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>イスラエルによるレバノン南部攻撃による</t>
+    <rPh sb="12" eb="14">
+      <t>ナンブ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/middle-east/unifil-says-one-peacekeeper-killed-one-critically-injured-southern-lebanon-2026-03-29/</t>
+  </si>
+  <si>
+    <t>イギリス</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>イギリスとシリアの首脳会談</t>
+    <rPh sb="9" eb="13">
+      <t>シュノウカイダン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>移民問題と国境警備問題が議題に</t>
+    <rPh sb="0" eb="4">
+      <t>イミンモンダイ</t>
+    </rPh>
+    <rPh sb="5" eb="11">
+      <t>コッキョウケイビモンダイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ギダイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>国際関係</t>
+    <rPh sb="0" eb="4">
+      <t>コクサイカンケイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>シリア</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/middle-east/uk-pm-starmer-raises-migration-border-security-talks-with-syrias-president-2026-03-31/</t>
+  </si>
+  <si>
+    <t>イスラエルがレバノン南部に緩衝地帯設置を表明</t>
+    <rPh sb="10" eb="12">
+      <t>ナンブ</t>
+    </rPh>
+    <rPh sb="13" eb="19">
+      <t>カンショウチタイセッチ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ヒョウメイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>イスラエル国防相、レバノン南部リタ川までを緩衝地帯にすると発言</t>
+    <rPh sb="5" eb="8">
+      <t>コクボウショウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ナンブ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>カワ</t>
+    </rPh>
+    <rPh sb="21" eb="25">
+      <t>カンショウチタイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ハツゲン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/middle-east/israel-establish-buffer-zone-south-lebanon-up-litani-river-defence-minister-says-2026-03-31/</t>
+  </si>
+  <si>
+    <t>ウクライナ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ゼレンスキー大統領のヨルダン訪問</t>
+    <rPh sb="6" eb="9">
+      <t>ダイトウリョウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ホウモン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>アブドラ国王と安全保障協力について協議</t>
+    <rPh sb="4" eb="6">
+      <t>コクオウ</t>
+    </rPh>
+    <rPh sb="7" eb="13">
+      <t>アンゼンホショウキョウリョク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>キョウギ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ヨルダン</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/business/aerospace-defense/ukraines-zelenskiy-arrives-jordan-next-leg-gulf-tour-2026-03-29/</t>
+  </si>
+  <si>
+    <t>ロシアがスパイ容疑で英外交官を追放</t>
+    <rPh sb="7" eb="9">
+      <t>ヨウギ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>エイ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ガイコウカン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ツイホウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>スパイ容疑で外交官を国外退去処分と発表。英政府は抗議。</t>
+    <rPh sb="20" eb="21">
+      <t>エイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/russia-expels-british-diplomat-over-espionage-fsb-says-2026-03-30/</t>
+  </si>
+  <si>
+    <t>イタリア、米軍機のシチリア基地利用を拒否と発表</t>
+    <rPh sb="5" eb="8">
+      <t>ベイグンキ</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>キチリヨウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>キョヒ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ハッピョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>イタリアが中東に向かう米軍航空機の基地使用を拒否</t>
+    <rPh sb="5" eb="7">
+      <t>チュウトウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="11" eb="16">
+      <t>ベイグンコウクウキ</t>
+    </rPh>
+    <rPh sb="17" eb="21">
+      <t>キチシヨウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>キョヒ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/business/aerospace-defense/italy-refuses-us-aircraft-use-sicily-base-middle-east-operations-source-says-2026-03-31/</t>
+  </si>
+  <si>
+    <t>フランス</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>フランスがイスラエルの領空通過を拒否</t>
+    <rPh sb="11" eb="13">
+      <t>リョウクウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ツウカ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>キョヒ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>イラン攻撃用の米国製兵器輸送において自国領空通過を拒否した。</t>
+    <rPh sb="3" eb="5">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ベイコク</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヘイキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ユソウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジコク</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>リョウクウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ツウカ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>キョヒ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/china/france-refused-israel-use-its-air-space-transfer-us-weapons-iran-war-sources-2026-03-31/</t>
+  </si>
+  <si>
+    <t>ネパール</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ネパールの前首相が逮捕される</t>
+    <rPh sb="5" eb="8">
+      <t>ゼンシュショウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>タイホ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>2025年9月の抗議活動への弾圧に関連した逮捕</t>
+    <rPh sb="4" eb="5">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>コウギカツドウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ダンアツ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カンレン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>タイホ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/asia-pacific/nepals-ex-pm-oli-held-over-deaths-during-gen-z-protests-2026-03-28/</t>
+  </si>
+  <si>
+    <t>アフガニスタン</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>アフガニスタンとパキスタンで豪雨被害</t>
+    <rPh sb="16" eb="18">
+      <t>ヒガイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>両国で合計45名が死亡したとされる</t>
+    <rPh sb="0" eb="2">
+      <t>リョウコク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ゴウケイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シボウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>災害</t>
+    <rPh sb="0" eb="2">
+      <t>サイガイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>パキスタン</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>人道問題に影響</t>
+  </si>
+  <si>
+    <t>人道</t>
+  </si>
+  <si>
+    <t>https://www.reuters.com/sustainability/climate-energy/heavy-rain-floods-kill-22-people-afghanistan-2026-03-30/</t>
+  </si>
+  <si>
+    <t>コソボ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>コソボがガザ地区への部隊派遣を承認</t>
+    <rPh sb="6" eb="8">
+      <t>チク</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>ブタイハケン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ショウニン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>米国主導の国際安定化部隊へ参加表明、派遣規模は未公表。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>パレスチナ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/asia-pacific/kosovo-approves-troops-gaza-under-us-backed-scheme-2026-03-30/</t>
+  </si>
+  <si>
+    <t>パキスタンとアフガニスタンが再衝突</t>
+    <rPh sb="14" eb="17">
+      <t>サイショウトツ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>両国国境で砲撃があり民間人被害報告。</t>
+    <rPh sb="0" eb="2">
+      <t>リョウコク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/asia-pacific/pakistan-afghanistan-trade-fire-islamabad-prepares-host-us-iran-talks-2026-03-30/</t>
+  </si>
+  <si>
+    <t>タイ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>タイにて新内閣が承認される</t>
+    <rPh sb="4" eb="7">
+      <t>シンナイカク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ショウニン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>アヌティン新内閣が承認される</t>
+    <rPh sb="9" eb="11">
+      <t>ショウニン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/asia-pacific/thai-king-approves-pm-anutins-cabinet-royal-gazette-says-2026-03-31/</t>
+  </si>
+  <si>
+    <t>韓国</t>
+    <rPh sb="0" eb="2">
+      <t>カンコク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>韓国にて株価の大暴落と通貨の急落が発生</t>
+    <rPh sb="0" eb="2">
+      <t>カンコク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カブカ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>ダイボウラク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ツウカ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>キュウラク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ハッセイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>2008年以来の下がり幅を記録。</t>
+    <rPh sb="4" eb="5">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>イライ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ハバ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>キロク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>経済</t>
+    <rPh sb="0" eb="2">
+      <t>ケイザイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>金融市場に影響</t>
+  </si>
+  <si>
+    <t>金融</t>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/asia-pacific/south-korea-hit-by-steepest-stocks-selloff-since-2008-currency-tumbles-2026-03-31/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -692,6 +1365,23 @@
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
@@ -997,7 +1687,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1124,8 +1814,11 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1138,8 +1831,15 @@
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="42">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - アクセント 1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - アクセント 2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - アクセント 3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -1167,6 +1867,7 @@
     <cellStyle name="タイトル" xfId="1" builtinId="15" customBuiltin="1"/>
     <cellStyle name="チェック セル" xfId="13" builtinId="23" customBuiltin="1"/>
     <cellStyle name="どちらでもない" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="ハイパーリンク" xfId="42" builtinId="8"/>
     <cellStyle name="メモ" xfId="15" builtinId="10" customBuiltin="1"/>
     <cellStyle name="リンク セル" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="悪い" xfId="7" builtinId="27" customBuiltin="1"/>
@@ -3944,6 +4645,17 @@
           </cell>
           <cell r="C249" t="str">
             <v>EU</v>
+          </cell>
+        </row>
+        <row r="250">
+          <cell r="A250" t="str">
+            <v>コソボ</v>
+          </cell>
+          <cell r="B250" t="str">
+            <v>XKK</v>
+          </cell>
+          <cell r="C250" t="str">
+            <v>Kosovo</v>
           </cell>
         </row>
       </sheetData>
@@ -4340,30 +5052,27 @@
     <row r="2" spans="1:19">
       <c r="A2" s="2" t="str">
         <f>IF(C2="","",VLOOKUP(C2,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>TCD</v>
+        <v>SVN</v>
       </c>
       <c r="B2" s="3" t="str">
         <f>IF(C2="","",VLOOKUP(C2,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Chad</v>
+        <v>Slovenia</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>161</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>162</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>163</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" t="s">
-        <v>23</v>
+        <v>164</v>
       </c>
       <c r="J2" s="2" t="str">
         <f>IF(G2="","",VLOOKUP(G2,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>SDN</v>
+        <v/>
       </c>
       <c r="K2" s="2" t="str">
         <f>IF(H2="","",VLOOKUP(H2,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -4375,54 +5084,54 @@
       </c>
       <c r="M2" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J2:L2)</f>
-        <v>SDN</v>
+        <v/>
       </c>
       <c r="N2" t="s">
-        <v>24</v>
+        <v>165</v>
       </c>
       <c r="O2" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="P2" s="1">
-        <v>46104</v>
+        <v>46103</v>
       </c>
       <c r="Q2" t="s">
-        <v>26</v>
+        <v>159</v>
       </c>
       <c r="R2" t="s">
-        <v>27</v>
+        <v>166</v>
       </c>
       <c r="S2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="2" t="str">
         <f>IF(C3="","",VLOOKUP(C3,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>CRI</v>
+        <v>TCD</v>
       </c>
       <c r="B3" s="3" t="str">
         <f>IF(C3="","",VLOOKUP(C3,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Costa Rica</v>
+        <v>Chad</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J3" s="2" t="str">
         <f>IF(G3="","",VLOOKUP(G3,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>USA</v>
+        <v>SDN</v>
       </c>
       <c r="K3" s="2" t="str">
         <f>IF(H3="","",VLOOKUP(H3,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -4434,13 +5143,13 @@
       </c>
       <c r="M3" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J3:L3)</f>
-        <v>USA</v>
+        <v>SDN</v>
       </c>
       <c r="N3" t="s">
         <v>24</v>
       </c>
       <c r="O3" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="P3" s="1">
         <v>46104</v>
@@ -4449,36 +5158,39 @@
         <v>26</v>
       </c>
       <c r="R3" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="S3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="2" t="str">
         <f>IF(C4="","",VLOOKUP(C4,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>CHN</v>
+        <v>CRI</v>
       </c>
       <c r="B4" s="3" t="str">
         <f>IF(C4="","",VLOOKUP(C4,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>China</v>
+        <v>Costa Rica</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>107</v>
+        <v>61</v>
       </c>
       <c r="F4" t="s">
-        <v>79</v>
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
       </c>
       <c r="J4" s="2" t="str">
         <f>IF(G4="","",VLOOKUP(G4,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>USA</v>
       </c>
       <c r="K4" s="2" t="str">
         <f>IF(H4="","",VLOOKUP(H4,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -4490,13 +5202,13 @@
       </c>
       <c r="M4" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J4:L4)</f>
-        <v/>
+        <v>USA</v>
       </c>
       <c r="N4" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="O4" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="P4" s="1">
         <v>46104</v>
@@ -4505,39 +5217,36 @@
         <v>26</v>
       </c>
       <c r="R4" t="s">
-        <v>108</v>
+        <v>62</v>
       </c>
       <c r="S4">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="2" t="str">
         <f>IF(C5="","",VLOOKUP(C5,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>JPN</v>
+        <v>CHN</v>
       </c>
       <c r="B5" s="3" t="str">
         <f>IF(C5="","",VLOOKUP(C5,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Japan</v>
+        <v>China</v>
       </c>
       <c r="C5" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="J5" s="2" t="str">
         <f>IF(G5="","",VLOOKUP(G5,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>CHN</v>
+        <v/>
       </c>
       <c r="K5" s="2" t="str">
         <f>IF(H5="","",VLOOKUP(H5,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -4549,22 +5258,22 @@
       </c>
       <c r="M5" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J5:L5)</f>
-        <v>CHN</v>
+        <v/>
       </c>
       <c r="N5" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="O5" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="P5" s="1">
-        <v>46105</v>
+        <v>46104</v>
       </c>
       <c r="Q5" t="s">
         <v>26</v>
       </c>
       <c r="R5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="S5">
         <v>5</v>
@@ -4580,19 +5289,19 @@
         <v>Israel</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>153</v>
       </c>
       <c r="D6" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="E6" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="F6" t="s">
-        <v>69</v>
+        <v>156</v>
       </c>
       <c r="G6" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="J6" s="2" t="str">
         <f>IF(G6="","",VLOOKUP(G6,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -4611,48 +5320,48 @@
         <v>LBN</v>
       </c>
       <c r="N6" t="s">
-        <v>68</v>
+        <v>158</v>
       </c>
       <c r="O6" t="s">
         <v>69</v>
       </c>
       <c r="P6" s="1">
-        <v>46105</v>
+        <v>46104</v>
       </c>
       <c r="Q6" t="s">
-        <v>26</v>
-      </c>
-      <c r="R6" t="s">
-        <v>134</v>
+        <v>159</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>160</v>
       </c>
       <c r="S6">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="2" t="str">
         <f>IF(C7="","",VLOOKUP(C7,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>EU</v>
+        <v>ITA</v>
       </c>
       <c r="B7" s="3" t="str">
         <f>IF(C7="","",VLOOKUP(C7,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>EU</v>
+        <v>Italy</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>167</v>
       </c>
       <c r="D7" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="E7" t="s">
-        <v>148</v>
-      </c>
-      <c r="G7" t="s">
-        <v>149</v>
+        <v>169</v>
+      </c>
+      <c r="F7" t="s">
+        <v>170</v>
       </c>
       <c r="J7" s="2" t="str">
         <f>IF(G7="","",VLOOKUP(G7,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>AUS</v>
+        <v/>
       </c>
       <c r="K7" s="2" t="str">
         <f>IF(H7="","",VLOOKUP(H7,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -4664,22 +5373,22 @@
       </c>
       <c r="M7" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J7:L7)</f>
-        <v>AUS</v>
+        <v/>
       </c>
       <c r="N7" t="s">
-        <v>24</v>
+        <v>165</v>
       </c>
       <c r="O7" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="P7" s="1">
-        <v>46105</v>
+        <v>46104</v>
       </c>
       <c r="Q7" t="s">
-        <v>26</v>
-      </c>
-      <c r="R7" t="s">
-        <v>150</v>
+        <v>159</v>
+      </c>
+      <c r="R7" s="5" t="s">
+        <v>171</v>
       </c>
       <c r="S7">
         <v>5</v>
@@ -4688,30 +5397,30 @@
     <row r="8" spans="1:19">
       <c r="A8" s="2" t="str">
         <f>IF(C8="","",VLOOKUP(C8,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>MEX</v>
+        <v>JPN</v>
       </c>
       <c r="B8" s="3" t="str">
         <f>IF(C8="","",VLOOKUP(C8,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Mexico</v>
+        <v>Japan</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="F8" t="s">
         <v>24</v>
       </c>
       <c r="G8" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="J8" s="2" t="str">
         <f>IF(G8="","",VLOOKUP(G8,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>CUB</v>
+        <v>CHN</v>
       </c>
       <c r="K8" s="2" t="str">
         <f>IF(H8="","",VLOOKUP(H8,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -4723,7 +5432,7 @@
       </c>
       <c r="M8" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J8:L8)</f>
-        <v>CUB</v>
+        <v>CHN</v>
       </c>
       <c r="N8" t="s">
         <v>24</v>
@@ -4732,45 +5441,45 @@
         <v>53</v>
       </c>
       <c r="P8" s="1">
-        <v>46106</v>
+        <v>46105</v>
       </c>
       <c r="Q8" t="s">
         <v>26</v>
       </c>
       <c r="R8" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="S8">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" s="2" t="str">
         <f>IF(C9="","",VLOOKUP(C9,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>CYP</v>
+        <v>ISR</v>
       </c>
       <c r="B9" s="3" t="str">
         <f>IF(C9="","",VLOOKUP(C9,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Cyprus</v>
+        <v>Israel</v>
       </c>
       <c r="C9" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="E9" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="G9" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="J9" s="2" t="str">
         <f>IF(G9="","",VLOOKUP(G9,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>GBR</v>
+        <v>LBN</v>
       </c>
       <c r="K9" s="2" t="str">
         <f>IF(H9="","",VLOOKUP(H9,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -4782,51 +5491,51 @@
       </c>
       <c r="M9" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J9:L9)</f>
-        <v>GBR</v>
+        <v>LBN</v>
       </c>
       <c r="N9" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="O9" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="P9" s="1">
-        <v>46106</v>
+        <v>46105</v>
       </c>
       <c r="Q9" t="s">
         <v>26</v>
       </c>
       <c r="R9" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="S9">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" s="2" t="str">
         <f>IF(C10="","",VLOOKUP(C10,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>DNK</v>
+        <v>EU</v>
       </c>
       <c r="B10" s="3" t="str">
         <f>IF(C10="","",VLOOKUP(C10,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Denmark</v>
+        <v>EU</v>
       </c>
       <c r="C10" t="s">
-        <v>122</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="E10" t="s">
-        <v>124</v>
-      </c>
-      <c r="F10" t="s">
-        <v>79</v>
+        <v>148</v>
+      </c>
+      <c r="G10" t="s">
+        <v>149</v>
       </c>
       <c r="J10" s="2" t="str">
         <f>IF(G10="","",VLOOKUP(G10,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>AUS</v>
       </c>
       <c r="K10" s="2" t="str">
         <f>IF(H10="","",VLOOKUP(H10,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -4838,54 +5547,54 @@
       </c>
       <c r="M10" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J10:L10)</f>
-        <v/>
+        <v>AUS</v>
       </c>
       <c r="N10" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="O10" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="P10" s="1">
-        <v>46106</v>
+        <v>46105</v>
       </c>
       <c r="Q10" t="s">
         <v>26</v>
       </c>
       <c r="R10" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="S10">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" s="2" t="str">
         <f>IF(C11="","",VLOOKUP(C11,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>GBR</v>
+        <v>MEX</v>
       </c>
       <c r="B11" s="3" t="str">
         <f>IF(C11="","",VLOOKUP(C11,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Britain</v>
+        <v>Mexico</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>135</v>
+        <v>51</v>
       </c>
       <c r="E11" t="s">
-        <v>136</v>
+        <v>52</v>
       </c>
       <c r="F11" t="s">
         <v>24</v>
       </c>
       <c r="G11" t="s">
-        <v>137</v>
+        <v>31</v>
       </c>
       <c r="J11" s="2" t="str">
         <f>IF(G11="","",VLOOKUP(G11,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>TUR</v>
+        <v>CUB</v>
       </c>
       <c r="K11" s="2" t="str">
         <f>IF(H11="","",VLOOKUP(H11,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -4897,13 +5606,13 @@
       </c>
       <c r="M11" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J11:L11)</f>
-        <v>TUR</v>
+        <v>CUB</v>
       </c>
       <c r="N11" t="s">
         <v>24</v>
       </c>
       <c r="O11" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="P11" s="1">
         <v>46106</v>
@@ -4912,39 +5621,39 @@
         <v>26</v>
       </c>
       <c r="R11" t="s">
-        <v>138</v>
+        <v>54</v>
       </c>
       <c r="S11">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:19">
       <c r="A12" s="2" t="str">
         <f>IF(C12="","",VLOOKUP(C12,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>KEN</v>
+        <v>CYP</v>
       </c>
       <c r="B12" s="3" t="str">
         <f>IF(C12="","",VLOOKUP(C12,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Kenya</v>
+        <v>Cyprus</v>
       </c>
       <c r="C12" t="s">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="D12" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="E12" t="s">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="F12" t="s">
         <v>24</v>
       </c>
       <c r="G12" t="s">
-        <v>71</v>
+        <v>120</v>
       </c>
       <c r="J12" s="2" t="str">
         <f>IF(G12="","",VLOOKUP(G12,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>CHN</v>
+        <v>GBR</v>
       </c>
       <c r="K12" s="2" t="str">
         <f>IF(H12="","",VLOOKUP(H12,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -4956,13 +5665,13 @@
       </c>
       <c r="M12" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J12:L12)</f>
-        <v>CHN</v>
+        <v>GBR</v>
       </c>
       <c r="N12" t="s">
         <v>24</v>
       </c>
       <c r="O12" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="P12" s="1">
         <v>46106</v>
@@ -4971,39 +5680,36 @@
         <v>26</v>
       </c>
       <c r="R12" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="S12">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:19">
       <c r="A13" s="2" t="str">
         <f>IF(C13="","",VLOOKUP(C13,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>USA</v>
+        <v>DNK</v>
       </c>
       <c r="B13" s="3" t="str">
         <f>IF(C13="","",VLOOKUP(C13,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>America</v>
+        <v>Denmark</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>122</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>123</v>
       </c>
       <c r="E13" t="s">
-        <v>56</v>
+        <v>124</v>
       </c>
       <c r="F13" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="J13" s="2" t="str">
         <f>IF(G13="","",VLOOKUP(G13,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>VEN</v>
+        <v/>
       </c>
       <c r="K13" s="2" t="str">
         <f>IF(H13="","",VLOOKUP(H13,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -5015,22 +5721,22 @@
       </c>
       <c r="M13" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J13:L13)</f>
-        <v>VEN</v>
+        <v/>
       </c>
       <c r="N13" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="O13" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="P13" s="1">
-        <v>46107</v>
+        <v>46106</v>
       </c>
       <c r="Q13" t="s">
         <v>26</v>
       </c>
       <c r="R13" t="s">
-        <v>58</v>
+        <v>125</v>
       </c>
       <c r="S13">
         <v>3</v>
@@ -5039,30 +5745,30 @@
     <row r="14" spans="1:19">
       <c r="A14" s="2" t="str">
         <f>IF(C14="","",VLOOKUP(C14,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>PAK</v>
+        <v>GBR</v>
       </c>
       <c r="B14" s="3" t="str">
         <f>IF(C14="","",VLOOKUP(C14,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Pakistan</v>
+        <v>Britain</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="D14" t="s">
-        <v>92</v>
+        <v>135</v>
       </c>
       <c r="E14" t="s">
-        <v>93</v>
+        <v>136</v>
       </c>
       <c r="F14" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G14" t="s">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="J14" s="2" t="str">
         <f>IF(G14="","",VLOOKUP(G14,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>AFG</v>
+        <v>TUR</v>
       </c>
       <c r="K14" s="2" t="str">
         <f>IF(H14="","",VLOOKUP(H14,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -5074,54 +5780,54 @@
       </c>
       <c r="M14" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J14:L14)</f>
-        <v>AFG</v>
+        <v>TUR</v>
       </c>
       <c r="N14" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="O14" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="P14" s="1">
-        <v>46107</v>
+        <v>46106</v>
       </c>
       <c r="Q14" t="s">
         <v>26</v>
       </c>
       <c r="R14" t="s">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="S14">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:19">
       <c r="A15" s="2" t="str">
         <f>IF(C15="","",VLOOKUP(C15,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>USA</v>
+        <v>KEN</v>
       </c>
       <c r="B15" s="3" t="str">
         <f>IF(C15="","",VLOOKUP(C15,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>America</v>
+        <v>Kenya</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>143</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="E15" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="F15" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G15" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J15" s="2" t="str">
         <f>IF(G15="","",VLOOKUP(G15,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>IRN</v>
+        <v>CHN</v>
       </c>
       <c r="K15" s="2" t="str">
         <f>IF(H15="","",VLOOKUP(H15,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -5133,61 +5839,58 @@
       </c>
       <c r="M15" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J15:L15)</f>
-        <v>IRN</v>
+        <v>CHN</v>
       </c>
       <c r="N15" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="O15" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="P15" s="1">
-        <v>46107</v>
+        <v>46106</v>
       </c>
       <c r="Q15" t="s">
         <v>26</v>
       </c>
       <c r="R15" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="S15">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:19">
       <c r="A16" s="2" t="str">
         <f>IF(C16="","",VLOOKUP(C16,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>IRN</v>
+        <v>USA</v>
       </c>
       <c r="B16" s="3" t="str">
         <f>IF(C16="","",VLOOKUP(C16,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Iran</v>
+        <v>America</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="D16" t="s">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="E16" t="s">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="F16" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G16" t="s">
-        <v>28</v>
-      </c>
-      <c r="H16" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="J16" s="2" t="str">
         <f>IF(G16="","",VLOOKUP(G16,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>USA</v>
+        <v>VEN</v>
       </c>
       <c r="K16" s="2" t="str">
         <f>IF(H16="","",VLOOKUP(H16,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>PAK</v>
+        <v/>
       </c>
       <c r="L16" s="2" t="str">
         <f>IF(I16="","",VLOOKUP(I16,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -5195,13 +5898,13 @@
       </c>
       <c r="M16" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J16:L16)</f>
-        <v>USA;PAK</v>
+        <v>VEN</v>
       </c>
       <c r="N16" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="O16" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="P16" s="1">
         <v>46107</v>
@@ -5210,39 +5913,39 @@
         <v>26</v>
       </c>
       <c r="R16" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="S16">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:19">
       <c r="A17" s="2" t="str">
         <f>IF(C17="","",VLOOKUP(C17,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>UKR</v>
+        <v>PAK</v>
       </c>
       <c r="B17" s="3" t="str">
         <f>IF(C17="","",VLOOKUP(C17,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Ukraine</v>
+        <v>Pakistan</v>
       </c>
       <c r="C17" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="D17" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="E17" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="F17" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="G17" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="J17" s="2" t="str">
         <f>IF(G17="","",VLOOKUP(G17,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>RUS</v>
+        <v>AFG</v>
       </c>
       <c r="K17" s="2" t="str">
         <f>IF(H17="","",VLOOKUP(H17,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -5254,7 +5957,7 @@
       </c>
       <c r="M17" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J17:L17)</f>
-        <v>RUS</v>
+        <v>AFG</v>
       </c>
       <c r="N17" t="s">
         <v>68</v>
@@ -5269,7 +5972,7 @@
         <v>26</v>
       </c>
       <c r="R17" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="S17">
         <v>5</v>
@@ -5288,20 +5991,20 @@
         <v>28</v>
       </c>
       <c r="D18" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="E18" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="F18" t="s">
         <v>22</v>
       </c>
       <c r="G18" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="J18" s="2" t="str">
         <f>IF(G18="","",VLOOKUP(G18,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>CUB</v>
+        <v>IRN</v>
       </c>
       <c r="K18" s="2" t="str">
         <f>IF(H18="","",VLOOKUP(H18,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -5313,119 +6016,116 @@
       </c>
       <c r="M18" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J18:L18)</f>
-        <v>CUB</v>
+        <v>IRN</v>
       </c>
       <c r="N18" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="O18" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="P18" s="1">
-        <v>46108</v>
+        <v>46107</v>
       </c>
       <c r="Q18" t="s">
         <v>26</v>
       </c>
       <c r="R18" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="S18">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:19">
       <c r="A19" s="2" t="str">
         <f>IF(C19="","",VLOOKUP(C19,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>CAN</v>
+        <v>IRN</v>
       </c>
       <c r="B19" s="3" t="str">
         <f>IF(C19="","",VLOOKUP(C19,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Canada</v>
+        <v>Iran</v>
       </c>
       <c r="C19" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="D19" t="s">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="E19" t="s">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="F19" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="G19" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H19" t="s">
-        <v>38</v>
-      </c>
-      <c r="I19" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="J19" s="2" t="str">
         <f>IF(G19="","",VLOOKUP(G19,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>BRA</v>
+        <v>USA</v>
       </c>
       <c r="K19" s="2" t="str">
         <f>IF(H19="","",VLOOKUP(H19,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>ARG</v>
+        <v>PAK</v>
       </c>
       <c r="L19" s="2" t="str">
         <f>IF(I19="","",VLOOKUP(I19,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>PRY</v>
+        <v/>
       </c>
       <c r="M19" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J19:L19)</f>
-        <v>BRA;ARG;PRY</v>
+        <v>USA;PAK</v>
       </c>
       <c r="N19" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="O19" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="P19" s="1">
-        <v>46108</v>
+        <v>46107</v>
       </c>
       <c r="Q19" t="s">
         <v>26</v>
       </c>
       <c r="R19" t="s">
-        <v>41</v>
+        <v>101</v>
       </c>
       <c r="S19">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:19">
       <c r="A20" s="2" t="str">
         <f>IF(C20="","",VLOOKUP(C20,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>EU</v>
+        <v>UKR</v>
       </c>
       <c r="B20" s="3" t="str">
         <f>IF(C20="","",VLOOKUP(C20,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>EU</v>
+        <v>Ukraine</v>
       </c>
       <c r="C20" t="s">
-        <v>42</v>
+        <v>109</v>
       </c>
       <c r="D20" t="s">
-        <v>43</v>
+        <v>113</v>
       </c>
       <c r="E20" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="F20" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="G20" t="s">
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="J20" s="2" t="str">
         <f>IF(G20="","",VLOOKUP(G20,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>CPTPP</v>
+        <v>RUS</v>
       </c>
       <c r="K20" s="2" t="str">
         <f>IF(H20="","",VLOOKUP(H20,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -5437,22 +6137,22 @@
       </c>
       <c r="M20" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J20:L20)</f>
-        <v>CPTPP</v>
+        <v>RUS</v>
       </c>
       <c r="N20" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="O20" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="P20" s="1">
-        <v>46108</v>
+        <v>46107</v>
       </c>
       <c r="Q20" t="s">
         <v>26</v>
       </c>
       <c r="R20" t="s">
-        <v>46</v>
+        <v>116</v>
       </c>
       <c r="S20">
         <v>5</v>
@@ -5461,54 +6161,48 @@
     <row r="21" spans="1:19">
       <c r="A21" s="2" t="str">
         <f>IF(C21="","",VLOOKUP(C21,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>CAN</v>
+        <v>USA</v>
       </c>
       <c r="B21" s="3" t="str">
         <f>IF(C21="","",VLOOKUP(C21,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Canada</v>
+        <v>America</v>
       </c>
       <c r="C21" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D21" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="E21" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="F21" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="G21" t="s">
-        <v>37</v>
-      </c>
-      <c r="H21" t="s">
-        <v>38</v>
-      </c>
-      <c r="I21" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="J21" s="2" t="str">
         <f>IF(G21="","",VLOOKUP(G21,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>BRA</v>
+        <v>CUB</v>
       </c>
       <c r="K21" s="2" t="str">
         <f>IF(H21="","",VLOOKUP(H21,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>ARG</v>
+        <v/>
       </c>
       <c r="L21" s="2" t="str">
         <f>IF(I21="","",VLOOKUP(I21,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>PRY</v>
+        <v/>
       </c>
       <c r="M21" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J21:L21)</f>
-        <v>BRA;ARG;PRY</v>
+        <v>CUB</v>
       </c>
       <c r="N21" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="O21" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="P21" s="1">
         <v>46108</v>
@@ -5517,7 +6211,7 @@
         <v>26</v>
       </c>
       <c r="R21" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="S21">
         <v>4</v>
@@ -5526,45 +6220,54 @@
     <row r="22" spans="1:19">
       <c r="A22" s="2" t="str">
         <f>IF(C22="","",VLOOKUP(C22,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>NPL</v>
+        <v>CAN</v>
       </c>
       <c r="B22" s="3" t="str">
         <f>IF(C22="","",VLOOKUP(C22,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Nepal</v>
+        <v>Canada</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="E22" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="F22" t="s">
-        <v>79</v>
+        <v>36</v>
+      </c>
+      <c r="G22" t="s">
+        <v>37</v>
+      </c>
+      <c r="H22" t="s">
+        <v>38</v>
+      </c>
+      <c r="I22" t="s">
+        <v>39</v>
       </c>
       <c r="J22" s="2" t="str">
         <f>IF(G22="","",VLOOKUP(G22,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>BRA</v>
       </c>
       <c r="K22" s="2" t="str">
         <f>IF(H22="","",VLOOKUP(H22,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>ARG</v>
       </c>
       <c r="L22" s="2" t="str">
         <f>IF(I22="","",VLOOKUP(I22,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>PRY</v>
       </c>
       <c r="M22" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J22:L22)</f>
-        <v/>
+        <v>BRA;ARG;PRY</v>
       </c>
       <c r="N22" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="O22" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="P22" s="1">
         <v>46108</v>
@@ -5573,39 +6276,39 @@
         <v>26</v>
       </c>
       <c r="R22" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="S22">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:19">
       <c r="A23" s="2" t="str">
         <f>IF(C23="","",VLOOKUP(C23,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>PRK</v>
+        <v>EU</v>
       </c>
       <c r="B23" s="3" t="str">
         <f>IF(C23="","",VLOOKUP(C23,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>North Korea</v>
+        <v>EU</v>
       </c>
       <c r="C23" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="E23" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F23" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="G23" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="J23" s="2" t="str">
         <f>IF(G23="","",VLOOKUP(G23,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>BLR</v>
+        <v>CPTPP</v>
       </c>
       <c r="K23" s="2" t="str">
         <f>IF(H23="","",VLOOKUP(H23,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -5617,13 +6320,13 @@
       </c>
       <c r="M23" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J23:L23)</f>
-        <v>BLR</v>
+        <v>CPTPP</v>
       </c>
       <c r="N23" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="O23" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="P23" s="1">
         <v>46108</v>
@@ -5632,7 +6335,7 @@
         <v>26</v>
       </c>
       <c r="R23" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="S23">
         <v>5</v>
@@ -5641,48 +6344,54 @@
     <row r="24" spans="1:19">
       <c r="A24" s="2" t="str">
         <f>IF(C24="","",VLOOKUP(C24,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>UKR</v>
+        <v>CAN</v>
       </c>
       <c r="B24" s="3" t="str">
         <f>IF(C24="","",VLOOKUP(C24,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Ukraine</v>
+        <v>Canada</v>
       </c>
       <c r="C24" t="s">
-        <v>109</v>
+        <v>33</v>
       </c>
       <c r="D24" t="s">
-        <v>110</v>
+        <v>47</v>
       </c>
       <c r="E24" t="s">
-        <v>152</v>
+        <v>48</v>
       </c>
       <c r="F24" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="G24" t="s">
-        <v>111</v>
+        <v>37</v>
+      </c>
+      <c r="H24" t="s">
+        <v>38</v>
+      </c>
+      <c r="I24" t="s">
+        <v>39</v>
       </c>
       <c r="J24" s="2" t="str">
         <f>IF(G24="","",VLOOKUP(G24,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>SAU</v>
+        <v>BRA</v>
       </c>
       <c r="K24" s="2" t="str">
         <f>IF(H24="","",VLOOKUP(H24,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>ARG</v>
       </c>
       <c r="L24" s="2" t="str">
         <f>IF(I24="","",VLOOKUP(I24,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>PRY</v>
       </c>
       <c r="M24" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J24:L24)</f>
-        <v>SAU</v>
+        <v>BRA;ARG;PRY</v>
       </c>
       <c r="N24" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="O24" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="P24" s="1">
         <v>46108</v>
@@ -5691,39 +6400,36 @@
         <v>26</v>
       </c>
       <c r="R24" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="S24">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:19">
       <c r="A25" s="2" t="str">
         <f>IF(C25="","",VLOOKUP(C25,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>COD</v>
+        <v>NPL</v>
       </c>
       <c r="B25" s="3" t="str">
         <f>IF(C25="","",VLOOKUP(C25,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Democratic Republic of the Congo</v>
+        <v>Nepal</v>
       </c>
       <c r="C25" t="s">
-        <v>139</v>
+        <v>76</v>
       </c>
       <c r="D25" t="s">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="E25" t="s">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="F25" t="s">
-        <v>24</v>
-      </c>
-      <c r="G25" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="J25" s="2" t="str">
         <f>IF(G25="","",VLOOKUP(G25,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>CHN</v>
+        <v/>
       </c>
       <c r="K25" s="2" t="str">
         <f>IF(H25="","",VLOOKUP(H25,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -5735,13 +6441,13 @@
       </c>
       <c r="M25" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J25:L25)</f>
-        <v>CHN</v>
+        <v/>
       </c>
       <c r="N25" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="O25" t="s">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="P25" s="1">
         <v>46108</v>
@@ -5750,39 +6456,39 @@
         <v>26</v>
       </c>
       <c r="R25" t="s">
-        <v>142</v>
+        <v>81</v>
       </c>
       <c r="S25">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:19">
       <c r="A26" s="2" t="str">
         <f>IF(C26="","",VLOOKUP(C26,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>CHN</v>
+        <v>PRK</v>
       </c>
       <c r="B26" s="3" t="str">
         <f>IF(C26="","",VLOOKUP(C26,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>China</v>
+        <v>North Korea</v>
       </c>
       <c r="C26" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="D26" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="E26" t="s">
-        <v>151</v>
+        <v>88</v>
       </c>
       <c r="F26" t="s">
         <v>24</v>
       </c>
       <c r="G26" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="J26" s="2" t="str">
         <f>IF(G26="","",VLOOKUP(G26,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>PHL</v>
+        <v>BLR</v>
       </c>
       <c r="K26" s="2" t="str">
         <f>IF(H26="","",VLOOKUP(H26,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -5794,51 +6500,54 @@
       </c>
       <c r="M26" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J26:L26)</f>
-        <v>PHL</v>
+        <v>BLR</v>
       </c>
       <c r="N26" t="s">
         <v>24</v>
       </c>
       <c r="O26" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="P26" s="1">
-        <v>46109</v>
+        <v>46108</v>
       </c>
       <c r="Q26" t="s">
         <v>26</v>
       </c>
       <c r="R26" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="S26">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:19">
       <c r="A27" s="2" t="str">
         <f>IF(C27="","",VLOOKUP(C27,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>IDN</v>
+        <v>UKR</v>
       </c>
       <c r="B27" s="3" t="str">
         <f>IF(C27="","",VLOOKUP(C27,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Indonesia</v>
+        <v>Ukraine</v>
       </c>
       <c r="C27" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="D27" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="E27" t="s">
-        <v>84</v>
+        <v>152</v>
       </c>
       <c r="F27" t="s">
-        <v>79</v>
+        <v>24</v>
+      </c>
+      <c r="G27" t="s">
+        <v>111</v>
       </c>
       <c r="J27" s="2" t="str">
         <f>IF(G27="","",VLOOKUP(G27,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>SAU</v>
       </c>
       <c r="K27" s="2" t="str">
         <f>IF(H27="","",VLOOKUP(H27,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -5850,61 +6559,58 @@
       </c>
       <c r="M27" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J27:L27)</f>
-        <v/>
+        <v>SAU</v>
       </c>
       <c r="N27" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="O27" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="P27" s="1">
-        <v>46109</v>
+        <v>46108</v>
       </c>
       <c r="Q27" t="s">
         <v>26</v>
       </c>
       <c r="R27" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="S27">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:19">
       <c r="A28" s="2" t="str">
         <f>IF(C28="","",VLOOKUP(C28,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>UKR</v>
+        <v>COD</v>
       </c>
       <c r="B28" s="3" t="str">
         <f>IF(C28="","",VLOOKUP(C28,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Ukraine</v>
+        <v>Democratic Republic of the Congo</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="D28" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E28" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="F28" t="s">
         <v>24</v>
       </c>
       <c r="G28" t="s">
-        <v>128</v>
-      </c>
-      <c r="H28" t="s">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="J28" s="2" t="str">
         <f>IF(G28="","",VLOOKUP(G28,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>ARE</v>
+        <v>CHN</v>
       </c>
       <c r="K28" s="2" t="str">
         <f>IF(H28="","",VLOOKUP(H28,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>QAT</v>
+        <v/>
       </c>
       <c r="L28" s="2" t="str">
         <f>IF(I28="","",VLOOKUP(I28,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -5912,100 +6618,106 @@
       </c>
       <c r="M28" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J28:L28)</f>
-        <v>ARE;QAT</v>
+        <v>CHN</v>
       </c>
       <c r="N28" t="s">
         <v>24</v>
       </c>
       <c r="O28" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="P28" s="1">
-        <v>46109</v>
+        <v>46108</v>
       </c>
       <c r="Q28" t="s">
         <v>26</v>
       </c>
       <c r="R28" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="S28">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:19">
       <c r="A29" s="2" t="str">
         <f>IF(C29="","",VLOOKUP(C29,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>YEM</v>
+        <v>CHN</v>
       </c>
       <c r="B29" s="3" t="str">
         <f>IF(C29="","",VLOOKUP(C29,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Yemen</v>
+        <v>China</v>
       </c>
       <c r="C29" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D29" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E29" t="s">
-        <v>65</v>
+        <v>151</v>
       </c>
       <c r="F29" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G29" t="s">
-        <v>66</v>
-      </c>
-      <c r="H29" t="s">
-        <v>28</v>
-      </c>
-      <c r="I29" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="J29" s="2" t="str">
         <f>IF(G29="","",VLOOKUP(G29,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>IRN</v>
+        <v>PHL</v>
       </c>
       <c r="K29" s="2" t="str">
         <f>IF(H29="","",VLOOKUP(H29,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>USA</v>
+        <v/>
       </c>
       <c r="L29" s="2" t="str">
         <f>IF(I29="","",VLOOKUP(I29,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>ISR</v>
+        <v/>
       </c>
       <c r="M29" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J29:L29)</f>
-        <v>IRN;USA;ISR</v>
+        <v>PHL</v>
       </c>
       <c r="N29" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="O29" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="P29" s="1">
-        <v>46110</v>
+        <v>46109</v>
       </c>
       <c r="Q29" t="s">
         <v>26</v>
       </c>
       <c r="R29" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="S29">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:19">
       <c r="A30" s="2" t="str">
         <f>IF(C30="","",VLOOKUP(C30,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>IDN</v>
       </c>
       <c r="B30" s="3" t="str">
         <f>IF(C30="","",VLOOKUP(C30,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Indonesia</v>
+      </c>
+      <c r="C30" t="s">
+        <v>82</v>
+      </c>
+      <c r="D30" t="s">
+        <v>83</v>
+      </c>
+      <c r="E30" t="s">
+        <v>84</v>
+      </c>
+      <c r="F30" t="s">
+        <v>79</v>
       </c>
       <c r="J30" s="2" t="str">
         <f>IF(G30="","",VLOOKUP(G30,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -6022,24 +6734,60 @@
       <c r="M30" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J30:L30)</f>
         <v/>
+      </c>
+      <c r="N30" t="s">
+        <v>80</v>
+      </c>
+      <c r="O30" t="s">
+        <v>80</v>
+      </c>
+      <c r="P30" s="1">
+        <v>46109</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>26</v>
+      </c>
+      <c r="R30" t="s">
+        <v>85</v>
+      </c>
+      <c r="S30">
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:19">
       <c r="A31" s="2" t="str">
         <f>IF(C31="","",VLOOKUP(C31,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>UKR</v>
       </c>
       <c r="B31" s="3" t="str">
         <f>IF(C31="","",VLOOKUP(C31,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Ukraine</v>
+      </c>
+      <c r="C31" t="s">
+        <v>109</v>
+      </c>
+      <c r="D31" t="s">
+        <v>126</v>
+      </c>
+      <c r="E31" t="s">
+        <v>127</v>
+      </c>
+      <c r="F31" t="s">
+        <v>24</v>
+      </c>
+      <c r="G31" t="s">
+        <v>128</v>
+      </c>
+      <c r="H31" t="s">
+        <v>129</v>
       </c>
       <c r="J31" s="2" t="str">
         <f>IF(G31="","",VLOOKUP(G31,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>ARE</v>
       </c>
       <c r="K31" s="2" t="str">
         <f>IF(H31="","",VLOOKUP(H31,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>QAT</v>
       </c>
       <c r="L31" s="2" t="str">
         <f>IF(I31="","",VLOOKUP(I31,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -6047,17 +6795,47 @@
       </c>
       <c r="M31" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J31:L31)</f>
-        <v/>
+        <v>ARE;QAT</v>
+      </c>
+      <c r="N31" t="s">
+        <v>24</v>
+      </c>
+      <c r="O31" t="s">
+        <v>74</v>
+      </c>
+      <c r="P31" s="1">
+        <v>46109</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>26</v>
+      </c>
+      <c r="R31" t="s">
+        <v>130</v>
+      </c>
+      <c r="S31">
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:19">
       <c r="A32" s="2" t="str">
         <f>IF(C32="","",VLOOKUP(C32,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>NPL</v>
       </c>
       <c r="B32" s="3" t="str">
         <f>IF(C32="","",VLOOKUP(C32,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Nepal</v>
+      </c>
+      <c r="C32" t="s">
+        <v>217</v>
+      </c>
+      <c r="D32" t="s">
+        <v>218</v>
+      </c>
+      <c r="E32" t="s">
+        <v>219</v>
+      </c>
+      <c r="F32" t="s">
+        <v>170</v>
       </c>
       <c r="J32" s="2" t="str">
         <f>IF(G32="","",VLOOKUP(G32,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -6075,45 +6853,117 @@
         <f>_xlfn.TEXTJOIN(";",TRUE,J32:L32)</f>
         <v/>
       </c>
+      <c r="N32" t="s">
+        <v>165</v>
+      </c>
+      <c r="O32" t="s">
+        <v>79</v>
+      </c>
+      <c r="P32" s="1">
+        <v>46109</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>159</v>
+      </c>
+      <c r="R32" t="s">
+        <v>220</v>
+      </c>
+      <c r="S32">
+        <v>2</v>
+      </c>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:19">
       <c r="A33" s="2" t="str">
         <f>IF(C33="","",VLOOKUP(C33,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>YEM</v>
       </c>
       <c r="B33" s="3" t="str">
         <f>IF(C33="","",VLOOKUP(C33,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Yemen</v>
+      </c>
+      <c r="C33" t="s">
+        <v>63</v>
+      </c>
+      <c r="D33" t="s">
+        <v>64</v>
+      </c>
+      <c r="E33" t="s">
+        <v>65</v>
+      </c>
+      <c r="F33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G33" t="s">
+        <v>66</v>
+      </c>
+      <c r="H33" t="s">
+        <v>28</v>
+      </c>
+      <c r="I33" t="s">
+        <v>67</v>
       </c>
       <c r="J33" s="2" t="str">
         <f>IF(G33="","",VLOOKUP(G33,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>IRN</v>
       </c>
       <c r="K33" s="2" t="str">
         <f>IF(H33="","",VLOOKUP(H33,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>USA</v>
       </c>
       <c r="L33" s="2" t="str">
         <f>IF(I33="","",VLOOKUP(I33,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>ISR</v>
       </c>
       <c r="M33" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J33:L33)</f>
-        <v/>
+        <v>IRN;USA;ISR</v>
+      </c>
+      <c r="N33" t="s">
+        <v>68</v>
+      </c>
+      <c r="O33" t="s">
+        <v>69</v>
+      </c>
+      <c r="P33" s="1">
+        <v>46110</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>26</v>
+      </c>
+      <c r="R33" t="s">
+        <v>70</v>
+      </c>
+      <c r="S33">
+        <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:19">
       <c r="A34" s="2" t="str">
         <f>IF(C34="","",VLOOKUP(C34,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>UKR</v>
       </c>
       <c r="B34" s="3" t="str">
         <f>IF(C34="","",VLOOKUP(C34,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Ukraine</v>
+      </c>
+      <c r="C34" t="s">
+        <v>202</v>
+      </c>
+      <c r="D34" t="s">
+        <v>203</v>
+      </c>
+      <c r="E34" t="s">
+        <v>204</v>
+      </c>
+      <c r="F34" t="s">
+        <v>196</v>
+      </c>
+      <c r="G34" t="s">
+        <v>205</v>
       </c>
       <c r="J34" s="2" t="str">
         <f>IF(G34="","",VLOOKUP(G34,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>JOR</v>
       </c>
       <c r="K34" s="2" t="str">
         <f>IF(H34="","",VLOOKUP(H34,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -6125,25 +6975,61 @@
       </c>
       <c r="M34" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J34:L34)</f>
-        <v/>
+        <v>JOR</v>
+      </c>
+      <c r="N34" t="s">
+        <v>178</v>
+      </c>
+      <c r="O34" t="s">
+        <v>53</v>
+      </c>
+      <c r="P34" s="1">
+        <v>46110</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>159</v>
+      </c>
+      <c r="R34" t="s">
+        <v>206</v>
+      </c>
+      <c r="S34">
+        <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:19">
       <c r="A35" s="2" t="str">
         <f>IF(C35="","",VLOOKUP(C35,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>CUB</v>
       </c>
       <c r="B35" s="3" t="str">
         <f>IF(C35="","",VLOOKUP(C35,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Cuba</v>
+      </c>
+      <c r="C35" t="s">
+        <v>172</v>
+      </c>
+      <c r="D35" t="s">
+        <v>173</v>
+      </c>
+      <c r="E35" t="s">
+        <v>174</v>
+      </c>
+      <c r="F35" t="s">
+        <v>175</v>
+      </c>
+      <c r="G35" t="s">
+        <v>176</v>
+      </c>
+      <c r="H35" t="s">
+        <v>177</v>
       </c>
       <c r="J35" s="2" t="str">
         <f>IF(G35="","",VLOOKUP(G35,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>RUS</v>
       </c>
       <c r="K35" s="2" t="str">
         <f>IF(H35="","",VLOOKUP(H35,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>USA</v>
       </c>
       <c r="L35" s="2" t="str">
         <f>IF(I35="","",VLOOKUP(I35,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -6151,21 +7037,54 @@
       </c>
       <c r="M35" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J35:L35)</f>
-        <v/>
+        <v>RUS;USA</v>
+      </c>
+      <c r="N35" t="s">
+        <v>178</v>
+      </c>
+      <c r="O35" t="s">
+        <v>179</v>
+      </c>
+      <c r="P35" s="1">
+        <v>46111</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>180</v>
+      </c>
+      <c r="R35" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="S35">
+        <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:19">
       <c r="A36" s="2" t="str">
         <f>IF(C36="","",VLOOKUP(C36,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>LBN</v>
       </c>
       <c r="B36" s="3" t="str">
         <f>IF(C36="","",VLOOKUP(C36,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Lebanon</v>
+      </c>
+      <c r="C36" t="s">
+        <v>157</v>
+      </c>
+      <c r="D36" t="s">
+        <v>190</v>
+      </c>
+      <c r="E36" t="s">
+        <v>191</v>
+      </c>
+      <c r="F36" t="s">
+        <v>156</v>
+      </c>
+      <c r="G36" t="s">
+        <v>153</v>
       </c>
       <c r="J36" s="2" t="str">
         <f>IF(G36="","",VLOOKUP(G36,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>ISR</v>
       </c>
       <c r="K36" s="2" t="str">
         <f>IF(H36="","",VLOOKUP(H36,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -6177,21 +7096,54 @@
       </c>
       <c r="M36" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J36:L36)</f>
-        <v/>
+        <v>ISR</v>
+      </c>
+      <c r="N36" t="s">
+        <v>158</v>
+      </c>
+      <c r="O36" t="s">
+        <v>69</v>
+      </c>
+      <c r="P36" s="1">
+        <v>46111</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>159</v>
+      </c>
+      <c r="R36" t="s">
+        <v>192</v>
+      </c>
+      <c r="S36">
+        <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:19">
       <c r="A37" s="2" t="str">
         <f>IF(C37="","",VLOOKUP(C37,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>RUS</v>
       </c>
       <c r="B37" s="3" t="str">
         <f>IF(C37="","",VLOOKUP(C37,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Russian Federation</v>
+      </c>
+      <c r="C37" t="s">
+        <v>176</v>
+      </c>
+      <c r="D37" t="s">
+        <v>207</v>
+      </c>
+      <c r="E37" t="s">
+        <v>208</v>
+      </c>
+      <c r="F37" t="s">
+        <v>196</v>
+      </c>
+      <c r="G37" t="s">
+        <v>193</v>
       </c>
       <c r="J37" s="2" t="str">
         <f>IF(G37="","",VLOOKUP(G37,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>GBR</v>
       </c>
       <c r="K37" s="2" t="str">
         <f>IF(H37="","",VLOOKUP(H37,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -6203,21 +7155,54 @@
       </c>
       <c r="M37" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J37:L37)</f>
-        <v/>
+        <v>GBR</v>
+      </c>
+      <c r="N37" t="s">
+        <v>178</v>
+      </c>
+      <c r="O37" t="s">
+        <v>53</v>
+      </c>
+      <c r="P37" s="1">
+        <v>46111</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>159</v>
+      </c>
+      <c r="R37" t="s">
+        <v>209</v>
+      </c>
+      <c r="S37">
+        <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:19">
       <c r="A38" s="2" t="str">
         <f>IF(C38="","",VLOOKUP(C38,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>AFG</v>
       </c>
       <c r="B38" s="3" t="str">
         <f>IF(C38="","",VLOOKUP(C38,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Afghanistan</v>
+      </c>
+      <c r="C38" t="s">
+        <v>221</v>
+      </c>
+      <c r="D38" t="s">
+        <v>222</v>
+      </c>
+      <c r="E38" t="s">
+        <v>223</v>
+      </c>
+      <c r="F38" t="s">
+        <v>224</v>
+      </c>
+      <c r="G38" t="s">
+        <v>225</v>
       </c>
       <c r="J38" s="2" t="str">
         <f>IF(G38="","",VLOOKUP(G38,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>PAK</v>
       </c>
       <c r="K38" s="2" t="str">
         <f>IF(H38="","",VLOOKUP(H38,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -6229,47 +7214,119 @@
       </c>
       <c r="M38" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J38:L38)</f>
-        <v/>
+        <v>PAK</v>
+      </c>
+      <c r="N38" t="s">
+        <v>226</v>
+      </c>
+      <c r="O38" t="s">
+        <v>227</v>
+      </c>
+      <c r="P38" s="1">
+        <v>46111</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>159</v>
+      </c>
+      <c r="R38" t="s">
+        <v>228</v>
+      </c>
+      <c r="S38">
+        <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:19">
       <c r="A39" s="2" t="str">
         <f>IF(C39="","",VLOOKUP(C39,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>XKK</v>
       </c>
       <c r="B39" s="3" t="str">
         <f>IF(C39="","",VLOOKUP(C39,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Kosovo</v>
+      </c>
+      <c r="C39" t="s">
+        <v>229</v>
+      </c>
+      <c r="D39" t="s">
+        <v>230</v>
+      </c>
+      <c r="E39" t="s">
+        <v>231</v>
+      </c>
+      <c r="F39" t="s">
+        <v>156</v>
+      </c>
+      <c r="G39" t="s">
+        <v>177</v>
+      </c>
+      <c r="H39" t="s">
+        <v>153</v>
+      </c>
+      <c r="I39" t="s">
+        <v>232</v>
       </c>
       <c r="J39" s="2" t="str">
         <f>IF(G39="","",VLOOKUP(G39,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>USA</v>
       </c>
       <c r="K39" s="2" t="str">
         <f>IF(H39="","",VLOOKUP(H39,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>ISR</v>
       </c>
       <c r="L39" s="2" t="str">
         <f>IF(I39="","",VLOOKUP(I39,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>PSE</v>
       </c>
       <c r="M39" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J39:L39)</f>
-        <v/>
+        <v>USA;ISR;PSE</v>
+      </c>
+      <c r="N39" t="s">
+        <v>178</v>
+      </c>
+      <c r="O39" t="s">
+        <v>69</v>
+      </c>
+      <c r="P39" s="1">
+        <v>46111</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>159</v>
+      </c>
+      <c r="R39" t="s">
+        <v>233</v>
+      </c>
+      <c r="S39">
+        <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" spans="1:19">
       <c r="A40" s="2" t="str">
         <f>IF(C40="","",VLOOKUP(C40,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>PAK</v>
       </c>
       <c r="B40" s="3" t="str">
         <f>IF(C40="","",VLOOKUP(C40,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Pakistan</v>
+      </c>
+      <c r="C40" t="s">
+        <v>225</v>
+      </c>
+      <c r="D40" t="s">
+        <v>234</v>
+      </c>
+      <c r="E40" t="s">
+        <v>235</v>
+      </c>
+      <c r="F40" t="s">
+        <v>156</v>
+      </c>
+      <c r="G40" t="s">
+        <v>221</v>
       </c>
       <c r="J40" s="2" t="str">
         <f>IF(G40="","",VLOOKUP(G40,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>AFG</v>
       </c>
       <c r="K40" s="2" t="str">
         <f>IF(H40="","",VLOOKUP(H40,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -6281,17 +7338,47 @@
       </c>
       <c r="M40" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J40:L40)</f>
-        <v/>
+        <v>AFG</v>
+      </c>
+      <c r="N40" t="s">
+        <v>158</v>
+      </c>
+      <c r="O40" t="s">
+        <v>69</v>
+      </c>
+      <c r="P40" s="1">
+        <v>46111</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>159</v>
+      </c>
+      <c r="R40" t="s">
+        <v>236</v>
+      </c>
+      <c r="S40">
+        <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" spans="1:19">
       <c r="A41" s="2" t="str">
         <f>IF(C41="","",VLOOKUP(C41,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>PRY</v>
       </c>
       <c r="B41" s="3" t="str">
         <f>IF(C41="","",VLOOKUP(C41,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Paraguay</v>
+      </c>
+      <c r="C41" t="s">
+        <v>182</v>
+      </c>
+      <c r="D41" t="s">
+        <v>183</v>
+      </c>
+      <c r="E41" t="s">
+        <v>184</v>
+      </c>
+      <c r="F41" t="s">
+        <v>170</v>
       </c>
       <c r="J41" s="2" t="str">
         <f>IF(G41="","",VLOOKUP(G41,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -6309,19 +7396,52 @@
         <f>_xlfn.TEXTJOIN(";",TRUE,J41:L41)</f>
         <v/>
       </c>
+      <c r="N41" t="s">
+        <v>165</v>
+      </c>
+      <c r="O41" t="s">
+        <v>79</v>
+      </c>
+      <c r="P41" s="1">
+        <v>46112</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>180</v>
+      </c>
+      <c r="R41" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="S41">
+        <v>1</v>
+      </c>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" spans="1:19">
       <c r="A42" s="2" t="str">
         <f>IF(C42="","",VLOOKUP(C42,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>USA</v>
       </c>
       <c r="B42" s="3" t="str">
         <f>IF(C42="","",VLOOKUP(C42,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>America</v>
+      </c>
+      <c r="C42" t="s">
+        <v>177</v>
+      </c>
+      <c r="D42" t="s">
+        <v>186</v>
+      </c>
+      <c r="E42" t="s">
+        <v>187</v>
+      </c>
+      <c r="F42" t="s">
+        <v>156</v>
+      </c>
+      <c r="G42" t="s">
+        <v>188</v>
       </c>
       <c r="J42" s="2" t="str">
         <f>IF(G42="","",VLOOKUP(G42,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>IRN</v>
       </c>
       <c r="K42" s="2" t="str">
         <f>IF(H42="","",VLOOKUP(H42,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -6333,21 +7453,54 @@
       </c>
       <c r="M42" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J42:L42)</f>
-        <v/>
+        <v>IRN</v>
+      </c>
+      <c r="N42" t="s">
+        <v>158</v>
+      </c>
+      <c r="O42" t="s">
+        <v>69</v>
+      </c>
+      <c r="P42" s="1">
+        <v>46112</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>180</v>
+      </c>
+      <c r="R42" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="S42">
+        <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" spans="1:19">
       <c r="A43" s="2" t="str">
         <f>IF(C43="","",VLOOKUP(C43,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>GBR</v>
       </c>
       <c r="B43" s="3" t="str">
         <f>IF(C43="","",VLOOKUP(C43,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Britain</v>
+      </c>
+      <c r="C43" t="s">
+        <v>193</v>
+      </c>
+      <c r="D43" t="s">
+        <v>194</v>
+      </c>
+      <c r="E43" t="s">
+        <v>195</v>
+      </c>
+      <c r="F43" t="s">
+        <v>196</v>
+      </c>
+      <c r="G43" t="s">
+        <v>197</v>
       </c>
       <c r="J43" s="2" t="str">
         <f>IF(G43="","",VLOOKUP(G43,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>SYR</v>
       </c>
       <c r="K43" s="2" t="str">
         <f>IF(H43="","",VLOOKUP(H43,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -6359,21 +7512,54 @@
       </c>
       <c r="M43" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J43:L43)</f>
-        <v/>
+        <v>SYR</v>
+      </c>
+      <c r="N43" t="s">
+        <v>178</v>
+      </c>
+      <c r="O43" t="s">
+        <v>53</v>
+      </c>
+      <c r="P43" s="1">
+        <v>46112</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>159</v>
+      </c>
+      <c r="R43" t="s">
+        <v>198</v>
+      </c>
+      <c r="S43">
+        <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:13">
+    <row r="44" spans="1:19">
       <c r="A44" s="2" t="str">
         <f>IF(C44="","",VLOOKUP(C44,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>ISR</v>
       </c>
       <c r="B44" s="3" t="str">
         <f>IF(C44="","",VLOOKUP(C44,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Israel</v>
+      </c>
+      <c r="C44" t="s">
+        <v>153</v>
+      </c>
+      <c r="D44" t="s">
+        <v>199</v>
+      </c>
+      <c r="E44" t="s">
+        <v>200</v>
+      </c>
+      <c r="F44" t="s">
+        <v>156</v>
+      </c>
+      <c r="G44" t="s">
+        <v>157</v>
       </c>
       <c r="J44" s="2" t="str">
         <f>IF(G44="","",VLOOKUP(G44,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>LBN</v>
       </c>
       <c r="K44" s="2" t="str">
         <f>IF(H44="","",VLOOKUP(H44,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -6385,21 +7571,54 @@
       </c>
       <c r="M44" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J44:L44)</f>
-        <v/>
+        <v>LBN</v>
+      </c>
+      <c r="N44" t="s">
+        <v>158</v>
+      </c>
+      <c r="O44" t="s">
+        <v>69</v>
+      </c>
+      <c r="P44" s="1">
+        <v>46112</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>159</v>
+      </c>
+      <c r="R44" t="s">
+        <v>201</v>
+      </c>
+      <c r="S44">
+        <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:13">
+    <row r="45" spans="1:19">
       <c r="A45" s="2" t="str">
         <f>IF(C45="","",VLOOKUP(C45,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>ITA</v>
       </c>
       <c r="B45" s="3" t="str">
         <f>IF(C45="","",VLOOKUP(C45,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Italy</v>
+      </c>
+      <c r="C45" t="s">
+        <v>167</v>
+      </c>
+      <c r="D45" t="s">
+        <v>210</v>
+      </c>
+      <c r="E45" t="s">
+        <v>211</v>
+      </c>
+      <c r="F45" t="s">
+        <v>196</v>
+      </c>
+      <c r="G45" t="s">
+        <v>177</v>
       </c>
       <c r="J45" s="2" t="str">
         <f>IF(G45="","",VLOOKUP(G45,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>USA</v>
       </c>
       <c r="K45" s="2" t="str">
         <f>IF(H45="","",VLOOKUP(H45,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -6411,25 +7630,61 @@
       </c>
       <c r="M45" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J45:L45)</f>
-        <v/>
+        <v>USA</v>
+      </c>
+      <c r="N45" t="s">
+        <v>178</v>
+      </c>
+      <c r="O45" t="s">
+        <v>53</v>
+      </c>
+      <c r="P45" s="1">
+        <v>46112</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>159</v>
+      </c>
+      <c r="R45" t="s">
+        <v>212</v>
+      </c>
+      <c r="S45">
+        <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:13">
+    <row r="46" spans="1:19">
       <c r="A46" s="2" t="str">
         <f>IF(C46="","",VLOOKUP(C46,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>FRA</v>
       </c>
       <c r="B46" s="3" t="str">
         <f>IF(C46="","",VLOOKUP(C46,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>France</v>
+      </c>
+      <c r="C46" t="s">
+        <v>213</v>
+      </c>
+      <c r="D46" t="s">
+        <v>214</v>
+      </c>
+      <c r="E46" t="s">
+        <v>215</v>
+      </c>
+      <c r="F46" t="s">
+        <v>196</v>
+      </c>
+      <c r="G46" t="s">
+        <v>153</v>
+      </c>
+      <c r="H46" t="s">
+        <v>177</v>
       </c>
       <c r="J46" s="2" t="str">
         <f>IF(G46="","",VLOOKUP(G46,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>ISR</v>
       </c>
       <c r="K46" s="2" t="str">
         <f>IF(H46="","",VLOOKUP(H46,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>USA</v>
       </c>
       <c r="L46" s="2" t="str">
         <f>IF(I46="","",VLOOKUP(I46,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -6437,17 +7692,47 @@
       </c>
       <c r="M46" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J46:L46)</f>
-        <v/>
+        <v>ISR;USA</v>
+      </c>
+      <c r="N46" t="s">
+        <v>178</v>
+      </c>
+      <c r="O46" t="s">
+        <v>53</v>
+      </c>
+      <c r="P46" s="1">
+        <v>46112</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>159</v>
+      </c>
+      <c r="R46" t="s">
+        <v>216</v>
+      </c>
+      <c r="S46">
+        <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" spans="1:19">
       <c r="A47" s="2" t="str">
         <f>IF(C47="","",VLOOKUP(C47,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>THA</v>
       </c>
       <c r="B47" s="3" t="str">
         <f>IF(C47="","",VLOOKUP(C47,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Thailand</v>
+      </c>
+      <c r="C47" t="s">
+        <v>237</v>
+      </c>
+      <c r="D47" t="s">
+        <v>238</v>
+      </c>
+      <c r="E47" t="s">
+        <v>239</v>
+      </c>
+      <c r="F47" t="s">
+        <v>170</v>
       </c>
       <c r="J47" s="2" t="str">
         <f>IF(G47="","",VLOOKUP(G47,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -6465,15 +7750,45 @@
         <f>_xlfn.TEXTJOIN(";",TRUE,J47:L47)</f>
         <v/>
       </c>
+      <c r="N47" t="s">
+        <v>165</v>
+      </c>
+      <c r="O47" t="s">
+        <v>79</v>
+      </c>
+      <c r="P47" s="1">
+        <v>46112</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>159</v>
+      </c>
+      <c r="R47" t="s">
+        <v>240</v>
+      </c>
+      <c r="S47">
+        <v>2</v>
+      </c>
     </row>
-    <row r="48" spans="1:13">
+    <row r="48" spans="1:19">
       <c r="A48" s="2" t="str">
         <f>IF(C48="","",VLOOKUP(C48,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>KOR</v>
       </c>
       <c r="B48" s="3" t="str">
         <f>IF(C48="","",VLOOKUP(C48,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Korea</v>
+      </c>
+      <c r="C48" t="s">
+        <v>241</v>
+      </c>
+      <c r="D48" t="s">
+        <v>242</v>
+      </c>
+      <c r="E48" t="s">
+        <v>243</v>
+      </c>
+      <c r="F48" t="s">
+        <v>244</v>
       </c>
       <c r="J48" s="2" t="str">
         <f>IF(G48="","",VLOOKUP(G48,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -6490,6 +7805,24 @@
       <c r="M48" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J48:L48)</f>
         <v/>
+      </c>
+      <c r="N48" t="s">
+        <v>245</v>
+      </c>
+      <c r="O48" t="s">
+        <v>246</v>
+      </c>
+      <c r="P48" s="1">
+        <v>46112</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>159</v>
+      </c>
+      <c r="R48" t="s">
+        <v>247</v>
+      </c>
+      <c r="S48">
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -6981,6 +8314,12 @@
     </sortState>
   </autoFilter>
   <phoneticPr fontId="18"/>
+  <hyperlinks>
+    <hyperlink ref="R7" r:id="rId1" xr:uid="{B2B6E0E5-9387-475B-9F4B-ACDF1B43A472}"/>
+    <hyperlink ref="R35" r:id="rId2" xr:uid="{986F3D43-7B5A-48C0-A47B-A7E7119BCBD9}"/>
+    <hyperlink ref="R41" r:id="rId3" xr:uid="{CAB2C613-E685-436C-AA62-7678804484F9}"/>
+    <hyperlink ref="R42" r:id="rId4" xr:uid="{B735F61B-7109-4112-8AD5-8A0DE0EE4130}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/public/data/データ管理用.xlsx
+++ b/public/data/データ管理用.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\world_map_project\world-map-news-app\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B2C7623-654A-4995-B66A-C066D229DE78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{578BB216-20D3-48D9-B8D3-C4422A3022A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{17EB953A-2661-4049-9616-0D3098A3DA36}"/>
+    <workbookView xWindow="29850" yWindow="1515" windowWidth="25935" windowHeight="8880" xr2:uid="{17EB953A-2661-4049-9616-0D3098A3DA36}"/>
   </bookViews>
   <sheets>
     <sheet name="events-入力用" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'events-入力用'!$A$1:$S$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'events-入力用'!$A$1:$S$77</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="356">
   <si>
     <t>country_iso3</t>
   </si>
@@ -1194,6 +1194,791 @@
   </si>
   <si>
     <t>https://www.reuters.com/world/asia-pacific/south-korea-hit-by-steepest-stocks-selloff-since-2008-currency-tumbles-2026-03-31/</t>
+  </si>
+  <si>
+    <t>メキシコ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>メキシコにて新たな外相が就任</t>
+    <rPh sb="6" eb="7">
+      <t>アラ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ガイショウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シュウニン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.bloomberg.com/news/articles/2026-04-01/roberto-velasco-poised-to-be-mexico-s-top-diplomat-after-de-la-fuente-resigns</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>モンゴル</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>モンゴルにて新首相が承認される</t>
+    <rPh sb="6" eb="9">
+      <t>シンシュショウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ショウニン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/china/mongolia-names-new-prime-minister-following-stalemate-parliament-2026-03-31/</t>
+  </si>
+  <si>
+    <t>アメリカがベネズエラの大使館を再開</t>
+    <rPh sb="11" eb="14">
+      <t>タイシカン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>サイカイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ベネズエラ首都カラカスの大使館業務が再開、段階的な外交関係回復へ</t>
+    <rPh sb="5" eb="7">
+      <t>シュト</t>
+    </rPh>
+    <rPh sb="12" eb="17">
+      <t>タイシカンギョウム</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>サイカイ</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>ダンカイテキ</t>
+    </rPh>
+    <rPh sb="25" eb="31">
+      <t>ガイコウカンケイカイフク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ベネズエラ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>外交関係が改善</t>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/americas/us-resumes-embassy-operations-venezuela-2026-03-30/</t>
+  </si>
+  <si>
+    <t>エジプト</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>アラブ連盟の事務総長にエジプト外交官が指名される</t>
+    <rPh sb="3" eb="5">
+      <t>レンメイ</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>ジムソウチョウ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>ガイコウカン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>シメイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/business/media-telecom/arab-foreign-ministers-name-nabil-fahmy-arab-league-chief-2026-03-29/</t>
+  </si>
+  <si>
+    <t>エジプトとキプロス、天然ガス協力協定に署名</t>
+    <rPh sb="16" eb="18">
+      <t>キョウテイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ショメイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>キプロス</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>エネルギー市場に影響</t>
+  </si>
+  <si>
+    <t>https://www.reuters.com/business/energy/egypt-cyprus-sign-framework-agreement-cooperation-gas-2026-03-30/</t>
+  </si>
+  <si>
+    <t>ソマリア</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ソマリア軍が南西部主要都市を制圧</t>
+    <rPh sb="4" eb="5">
+      <t>グン</t>
+    </rPh>
+    <rPh sb="6" eb="13">
+      <t>ナンセイブシュヨウトシ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>セイアツ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>政府との関係遮断を宣言していた州政府首都を制圧</t>
+    <rPh sb="0" eb="2">
+      <t>セイフ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カンケイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シャダン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>センゲン</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>シュウセイフ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>シュト</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>セイアツ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/africa/somali-national-army-takes-control-part-biggest-city-south-west-state-2026-03-30/</t>
+  </si>
+  <si>
+    <t>イラン海軍司令官の死亡が発表される</t>
+    <rPh sb="3" eb="8">
+      <t>カイグンシレイカン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シボウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ハッピョウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>イスラエルの攻撃により死亡したもの</t>
+    <rPh sb="6" eb="8">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シボウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/middle-east/iran-confirms-death-revolutionary-guards-navy-commander-tangsiri-statement-says-2026-03-30/</t>
+  </si>
+  <si>
+    <t>ドイツ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ドイツ極右政党、ロシアとの関係修復を主張</t>
+    <rPh sb="3" eb="7">
+      <t>キョクウセイトウ</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>カンケイシュウフク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>シュチョウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>極右「ドイツのための選択肢」がロシアからのエネルギー調達を再主張</t>
+    <rPh sb="0" eb="2">
+      <t>キョクウ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>センタクシ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>チョウタツ</t>
+    </rPh>
+    <rPh sb="29" eb="32">
+      <t>サイシュチョウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/business/soaring-fuel-prices-drive-german-far-right-calls-turn-back-russia-2026-03-31/</t>
+  </si>
+  <si>
+    <t>ウクライナとトルコの首脳会談</t>
+    <rPh sb="10" eb="14">
+      <t>シュノウカイダン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>両国の安全保障協力の強化やエネルギー調達分野での連携を確認。</t>
+    <rPh sb="0" eb="2">
+      <t>リョウコク</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>アンゼンホショウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>チョウタツ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>国際関係</t>
+    <rPh sb="0" eb="2">
+      <t>コクサイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンケイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>トルコ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/business/aerospace-defense/zelenskiy-arrives-istanbul-talks-with-erdogan-2026-04-04/</t>
+  </si>
+  <si>
+    <t>伊メローニ首相の中東訪問</t>
+    <rPh sb="0" eb="1">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シュショウ</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>チュウトウホウモン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>湾岸諸国訪問にてエネルギー供給確保と安全支援の強化を協議</t>
+    <rPh sb="2" eb="4">
+      <t>ショコク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>サウジアラビア</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>カタール</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>UAE</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/europe/italys-meloni-flies-gulf-region-energy-security-push-2026-04-03/</t>
+  </si>
+  <si>
+    <t>韓国とフランスの首脳会談</t>
+    <rPh sb="0" eb="2">
+      <t>カンコク</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>シュノウカイダン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>防衛協力と経済エネルギー連携を確認</t>
+    <rPh sb="0" eb="4">
+      <t>ボウエイキョウリョク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ケイザイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>レンケイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/asia-pacific/south-korea-france-upgrade-ties-strategic-partnership-blue-house-says-2026-04-03/</t>
+  </si>
+  <si>
+    <t>ロ軍がハリコフへドローン攻撃を継続</t>
+    <rPh sb="1" eb="2">
+      <t>グン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ケイゾク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/russian-forces-maintain-day-long-drone-barrage-ukraines-kharkiv-2026-04-02/</t>
+  </si>
+  <si>
+    <t>ホルムズ海峡封鎖問題に40カ国が協議</t>
+    <rPh sb="4" eb="6">
+      <t>カイキョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>フウサ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>コク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>キョウギ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>40カ国がイランによるホルムズ海峡封鎖問題について連合を結成し協議</t>
+    <rPh sb="17" eb="21">
+      <t>フウサモンダイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/business/energy/dozens-countries-discuss-coalition-secure-passage-through-strait-hormuz-2026-04-02/</t>
+  </si>
+  <si>
+    <t>米トランプ大統領がNATO脱退を仄めかす</t>
+    <rPh sb="0" eb="1">
+      <t>ベイ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ダイトウリョウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ダッタイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ホノ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>欧州の支援拒否を理由にNATO離脱を示唆、各国が強く反発</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>外交関係が悪化</t>
+  </si>
+  <si>
+    <t>https://www.reuters.com/business/aerospace-defense/trump-threatens-nato-exit-scaling-up-tensions-with-allies-2026-04-01/</t>
+  </si>
+  <si>
+    <t>セルビア</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>セルビア首都での大規模抗議活動</t>
+    <rPh sb="4" eb="6">
+      <t>シュト</t>
+    </rPh>
+    <rPh sb="8" eb="13">
+      <t>ダイキボコウギ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カツドウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>市内で学生らがデモ中に衝突、複数負傷・数人逮捕と報告。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/serbian-students-protesters-clash-with-police-belgrade-2026-03-31/</t>
+  </si>
+  <si>
+    <t>イラン政府が反体制派関係者2名を処刑と発表</t>
+    <rPh sb="3" eb="5">
+      <t>セイフ</t>
+    </rPh>
+    <rPh sb="6" eb="13">
+      <t>ハンタイセイハカンケイシャ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ショケイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ハッピョウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/middle-east/iran-executes-two-linked-opposition-group-media-say-2026-04-04/</t>
+  </si>
+  <si>
+    <t>インド</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>インドが約7年ぶりにイラン産原油を調達</t>
+    <rPh sb="4" eb="5">
+      <t>ヤク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>サンゲンユ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>チョウタツ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/business/energy/india-says-crude-oil-supplies-secured-no-payment-issues-iran-imports-2026-04-04/</t>
+  </si>
+  <si>
+    <t>ロシアとトルコ首脳の電話会談</t>
+    <rPh sb="7" eb="9">
+      <t>シュノウ</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>デンワカイダン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>両首脳が中東情勢を協議、地域安定へ情報共有と調整で一致を確認</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/middle-east/putin-holds-call-with-turkeys-erdogan-discuss-middle-east-2026-04-03/</t>
+  </si>
+  <si>
+    <t>日本</t>
+    <rPh sb="0" eb="2">
+      <t>ニホン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>オマーン</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/business/energy/japanese-owned-lng-tanker-crosses-strait-hormuz-2026-04-03/</t>
+  </si>
+  <si>
+    <t>イスラエル空爆でヒズボラ最高司令官が死亡</t>
+    <rPh sb="5" eb="7">
+      <t>クウバク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>サイコウ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>シレイカン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>シボウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/middle-east/israeli-military-says-strike-beirut-killed-hezbollah-southern-front-commander-2026-04-01/</t>
+  </si>
+  <si>
+    <t>シリア暫定大統領がイラン紛争不干渉を表明</t>
+    <rPh sb="3" eb="8">
+      <t>ザンテイダイトウリョウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>フンソウ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>フカンショウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヒョウメイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>「攻撃されない限り参戦せず」と表明、国境強化と外交重視を強調</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/europe/syria-will-stay-out-iran-conflict-unless-it-faces-aggression-president-says-2026-03-31/</t>
+  </si>
+  <si>
+    <t>アルゼンチン</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>アルゼンチンがイラン革命防衛隊をテロ組織に指定</t>
+    <rPh sb="10" eb="15">
+      <t>カクメイボウエイタイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ソシキ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>シテイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>アメリカと歩調を合わせ、金融制裁適用が可能に</t>
+    <rPh sb="8" eb="9">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/middle-east/argentina-designates-irans-irgc-terrorist-organization-aligning-with-us-2026-04-01/</t>
+  </si>
+  <si>
+    <t>ブルキナファソ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ブルキナファソ軍による民間人犠牲増報告</t>
+    <rPh sb="17" eb="19">
+      <t>ホウコク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>同国とマリにて軍事政権が民間人を多数殺害と人権団体が発表</t>
+    <rPh sb="0" eb="2">
+      <t>ドウコク</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>グンジセイケン</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ミンカンジン</t>
+    </rPh>
+    <rPh sb="16" eb="20">
+      <t>タスウサツガイ</t>
+    </rPh>
+    <rPh sb="21" eb="25">
+      <t>ジンケンダンタイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ハッピョウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>マリ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/africa/burkina-mali-troops-kill-more-civilians-than-jihadists-do-data-shows-2026-04-02/</t>
+  </si>
+  <si>
+    <t>エチオピア</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>エチオピアと中国が債務問題で合意</t>
+    <rPh sb="11" eb="13">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ゴウイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>G20の共通枠組みで債務処理に両国が合意、再編と新融資も協議。</t>
+    <rPh sb="15" eb="17">
+      <t>リョウコク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>中国</t>
+    <rPh sb="0" eb="2">
+      <t>チュウゴク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>経済に影響</t>
+  </si>
+  <si>
+    <t>経済</t>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/africa/ethiopia-says-reaches-resolution-with-china-debt-treatment-2026-04-03/</t>
+  </si>
+  <si>
+    <t>コンゴ民主共和国</t>
+    <rPh sb="3" eb="8">
+      <t>ミンシュキョウワコク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>DRコンゴ東部でIS系反乱が15人殺害</t>
+    <rPh sb="5" eb="7">
+      <t>トウブ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>地域情勢が不安定化</t>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/africa/islamic-state-linked-rebels-kill-15-eastern-congo-officials-say-2026-04-02/</t>
+  </si>
+  <si>
+    <t>アメリカがベネズエラ暫定大統領への制裁を解除</t>
+    <rPh sb="10" eb="15">
+      <t>ザンテイダイトウリョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>セイサイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>カイジョ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>制裁解除で資産管理や大使館再開の道が開き、国際取引再開に弾み。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/americas/us-lifts-sanctions-venezuelas-interim-president-2026-04-01/</t>
+  </si>
+  <si>
+    <t>欧州連合</t>
+    <rPh sb="0" eb="4">
+      <t>オウシュウレンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>EUがキューバへ230万ドルを人道支援として拠出</t>
+    <rPh sb="11" eb="12">
+      <t>マン</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>ジンドウシエン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>キョシュツ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>電力危機と物資不足を受け、食料と飲料水で最大200万人支援を実施へ。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/americas/eu-announces-further-23-million-humanitarian-aid-cuba-2026-04-01/</t>
+  </si>
+  <si>
+    <t>中国がデジタルヒューマンへの規制を強化</t>
+    <rPh sb="17" eb="19">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>デジタルヒューマンへの明示表示を義務化、未成年への中毒性のあるサービス提供を禁止</t>
+    <rPh sb="25" eb="28">
+      <t>チュウドクセイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/china/china-moves-regulate-digital-humans-bans-addictive-services-children-2026-04-03/</t>
+  </si>
+  <si>
+    <t>ニュージーランド</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ニュージーランドとクック諸島が安全保障宣言に署名</t>
+    <rPh sb="15" eb="19">
+      <t>アンゼンホショウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>センゲン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ショメイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>安全保障協力を深化させ、領域防衛・海上監視・災害支援で連携強化、制度的枠組みも構築へ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>クック諸島</t>
+    <rPh sb="3" eb="5">
+      <t>ショトウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/asia-pacific/new-zealand-cook-islands-sign-defence-security-declaration-2026-04-01/</t>
+  </si>
+  <si>
+    <t>日本等3カ国の船舶がホルムズ海峡を通過</t>
+    <rPh sb="0" eb="2">
+      <t>ニホン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ナド</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>コク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>センパク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カイキョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ツウカ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
   </si>
 </sst>
 </file>
@@ -1384,7 +2169,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1567,6 +2352,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1818,7 +2609,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1836,6 +2627,9 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="42">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1884,7 +2678,16 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="良い" xfId="6" builtinId="26" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC0E6F5"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -4981,7 +5784,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11153815-6F7F-462F-8165-5CE05A98A928}">
-  <dimension ref="A1:S69"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:S77"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="2" width="8.796875" style="2"/>
@@ -5049,7 +5853,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" hidden="1">
       <c r="A2" s="2" t="str">
         <f>IF(C2="","",VLOOKUP(C2,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>SVN</v>
@@ -5105,7 +5909,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" hidden="1">
       <c r="A3" s="2" t="str">
         <f>IF(C3="","",VLOOKUP(C3,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>TCD</v>
@@ -5164,7 +5968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" hidden="1">
       <c r="A4" s="2" t="str">
         <f>IF(C4="","",VLOOKUP(C4,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>CRI</v>
@@ -5223,7 +6027,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" hidden="1">
       <c r="A5" s="2" t="str">
         <f>IF(C5="","",VLOOKUP(C5,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>CHN</v>
@@ -5279,7 +6083,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" hidden="1">
       <c r="A6" s="2" t="str">
         <f>IF(C6="","",VLOOKUP(C6,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>ISR</v>
@@ -5338,7 +6142,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:19" hidden="1">
       <c r="A7" s="2" t="str">
         <f>IF(C7="","",VLOOKUP(C7,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>ITA</v>
@@ -5394,7 +6198,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:19" hidden="1">
       <c r="A8" s="2" t="str">
         <f>IF(C8="","",VLOOKUP(C8,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>JPN</v>
@@ -5453,7 +6257,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:19" hidden="1">
       <c r="A9" s="2" t="str">
         <f>IF(C9="","",VLOOKUP(C9,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>ISR</v>
@@ -5512,7 +6316,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:19" hidden="1">
       <c r="A10" s="2" t="str">
         <f>IF(C10="","",VLOOKUP(C10,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>EU</v>
@@ -5568,7 +6372,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:19" hidden="1">
       <c r="A11" s="2" t="str">
         <f>IF(C11="","",VLOOKUP(C11,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>MEX</v>
@@ -5627,7 +6431,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:19" hidden="1">
       <c r="A12" s="2" t="str">
         <f>IF(C12="","",VLOOKUP(C12,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>CYP</v>
@@ -5686,7 +6490,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:19" hidden="1">
       <c r="A13" s="2" t="str">
         <f>IF(C13="","",VLOOKUP(C13,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>DNK</v>
@@ -5742,7 +6546,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:19" hidden="1">
       <c r="A14" s="2" t="str">
         <f>IF(C14="","",VLOOKUP(C14,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>GBR</v>
@@ -5801,7 +6605,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:19" hidden="1">
       <c r="A15" s="2" t="str">
         <f>IF(C15="","",VLOOKUP(C15,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>KEN</v>
@@ -5860,7 +6664,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:19" hidden="1">
       <c r="A16" s="2" t="str">
         <f>IF(C16="","",VLOOKUP(C16,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>USA</v>
@@ -5919,7 +6723,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:19" hidden="1">
       <c r="A17" s="2" t="str">
         <f>IF(C17="","",VLOOKUP(C17,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>PAK</v>
@@ -5978,7 +6782,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:19" hidden="1">
       <c r="A18" s="2" t="str">
         <f>IF(C18="","",VLOOKUP(C18,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>USA</v>
@@ -6037,7 +6841,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:19" hidden="1">
       <c r="A19" s="2" t="str">
         <f>IF(C19="","",VLOOKUP(C19,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>IRN</v>
@@ -6099,7 +6903,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:19" hidden="1">
       <c r="A20" s="2" t="str">
         <f>IF(C20="","",VLOOKUP(C20,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>UKR</v>
@@ -6158,7 +6962,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:19" hidden="1">
       <c r="A21" s="2" t="str">
         <f>IF(C21="","",VLOOKUP(C21,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>USA</v>
@@ -6217,7 +7021,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:19" hidden="1">
       <c r="A22" s="2" t="str">
         <f>IF(C22="","",VLOOKUP(C22,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>CAN</v>
@@ -6282,7 +7086,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:19" hidden="1">
       <c r="A23" s="2" t="str">
         <f>IF(C23="","",VLOOKUP(C23,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>EU</v>
@@ -6341,7 +7145,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:19" hidden="1">
       <c r="A24" s="2" t="str">
         <f>IF(C24="","",VLOOKUP(C24,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>CAN</v>
@@ -6406,7 +7210,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:19" hidden="1">
       <c r="A25" s="2" t="str">
         <f>IF(C25="","",VLOOKUP(C25,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>NPL</v>
@@ -6462,7 +7266,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:19" hidden="1">
       <c r="A26" s="2" t="str">
         <f>IF(C26="","",VLOOKUP(C26,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>PRK</v>
@@ -6521,7 +7325,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:19" hidden="1">
       <c r="A27" s="2" t="str">
         <f>IF(C27="","",VLOOKUP(C27,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>UKR</v>
@@ -6580,7 +7384,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:19" hidden="1">
       <c r="A28" s="2" t="str">
         <f>IF(C28="","",VLOOKUP(C28,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>COD</v>
@@ -6639,7 +7443,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:19" hidden="1">
       <c r="A29" s="2" t="str">
         <f>IF(C29="","",VLOOKUP(C29,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>CHN</v>
@@ -6698,7 +7502,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:19" hidden="1">
       <c r="A30" s="2" t="str">
         <f>IF(C30="","",VLOOKUP(C30,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>IDN</v>
@@ -6754,7 +7558,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:19" hidden="1">
       <c r="A31" s="2" t="str">
         <f>IF(C31="","",VLOOKUP(C31,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>UKR</v>
@@ -6816,7 +7620,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:19" hidden="1">
       <c r="A32" s="2" t="str">
         <f>IF(C32="","",VLOOKUP(C32,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>NPL</v>
@@ -6872,7 +7676,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:19">
+    <row r="33" spans="1:19" hidden="1">
       <c r="A33" s="2" t="str">
         <f>IF(C33="","",VLOOKUP(C33,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>YEM</v>
@@ -6937,7 +7741,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:19" hidden="1">
       <c r="A34" s="2" t="str">
         <f>IF(C34="","",VLOOKUP(C34,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>UKR</v>
@@ -6996,40 +7800,31 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" spans="1:19" hidden="1">
       <c r="A35" s="2" t="str">
         <f>IF(C35="","",VLOOKUP(C35,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>CUB</v>
+        <v>EGY</v>
       </c>
       <c r="B35" s="3" t="str">
         <f>IF(C35="","",VLOOKUP(C35,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Cuba</v>
+        <v>Egypt</v>
       </c>
       <c r="C35" t="s">
-        <v>172</v>
+        <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>173</v>
-      </c>
-      <c r="E35" t="s">
-        <v>174</v>
+        <v>260</v>
       </c>
       <c r="F35" t="s">
-        <v>175</v>
-      </c>
-      <c r="G35" t="s">
-        <v>176</v>
-      </c>
-      <c r="H35" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="J35" s="2" t="str">
         <f>IF(G35="","",VLOOKUP(G35,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>RUS</v>
+        <v/>
       </c>
       <c r="K35" s="2" t="str">
         <f>IF(H35="","",VLOOKUP(H35,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>USA</v>
+        <v/>
       </c>
       <c r="L35" s="2" t="str">
         <f>IF(I35="","",VLOOKUP(I35,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -7037,58 +7832,61 @@
       </c>
       <c r="M35" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J35:L35)</f>
-        <v>RUS;USA</v>
+        <v/>
       </c>
       <c r="N35" t="s">
-        <v>178</v>
+        <v>257</v>
       </c>
       <c r="O35" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="P35" s="1">
-        <v>46111</v>
+        <v>46110</v>
       </c>
       <c r="Q35" t="s">
-        <v>180</v>
-      </c>
-      <c r="R35" s="5" t="s">
-        <v>181</v>
+        <v>159</v>
+      </c>
+      <c r="R35" t="s">
+        <v>261</v>
       </c>
       <c r="S35">
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:19">
+    <row r="36" spans="1:19" hidden="1">
       <c r="A36" s="2" t="str">
         <f>IF(C36="","",VLOOKUP(C36,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>LBN</v>
+        <v>CUB</v>
       </c>
       <c r="B36" s="3" t="str">
         <f>IF(C36="","",VLOOKUP(C36,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Lebanon</v>
+        <v>Cuba</v>
       </c>
       <c r="C36" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="D36" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="E36" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="F36" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="G36" t="s">
-        <v>153</v>
+        <v>176</v>
+      </c>
+      <c r="H36" t="s">
+        <v>177</v>
       </c>
       <c r="J36" s="2" t="str">
         <f>IF(G36="","",VLOOKUP(G36,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>ISR</v>
+        <v>RUS</v>
       </c>
       <c r="K36" s="2" t="str">
         <f>IF(H36="","",VLOOKUP(H36,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>USA</v>
       </c>
       <c r="L36" s="2" t="str">
         <f>IF(I36="","",VLOOKUP(I36,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -7096,54 +7894,54 @@
       </c>
       <c r="M36" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J36:L36)</f>
-        <v>ISR</v>
+        <v>RUS;USA</v>
       </c>
       <c r="N36" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="O36" t="s">
-        <v>69</v>
+        <v>179</v>
       </c>
       <c r="P36" s="1">
         <v>46111</v>
       </c>
       <c r="Q36" t="s">
-        <v>159</v>
-      </c>
-      <c r="R36" t="s">
-        <v>192</v>
+        <v>180</v>
+      </c>
+      <c r="R36" s="5" t="s">
+        <v>181</v>
       </c>
       <c r="S36">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:19">
+    <row r="37" spans="1:19" hidden="1">
       <c r="A37" s="2" t="str">
         <f>IF(C37="","",VLOOKUP(C37,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>RUS</v>
+        <v>LBN</v>
       </c>
       <c r="B37" s="3" t="str">
         <f>IF(C37="","",VLOOKUP(C37,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Russian Federation</v>
+        <v>Lebanon</v>
       </c>
       <c r="C37" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="D37" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="E37" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="F37" t="s">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="G37" t="s">
-        <v>193</v>
+        <v>153</v>
       </c>
       <c r="J37" s="2" t="str">
         <f>IF(G37="","",VLOOKUP(G37,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>GBR</v>
+        <v>ISR</v>
       </c>
       <c r="K37" s="2" t="str">
         <f>IF(H37="","",VLOOKUP(H37,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -7155,13 +7953,13 @@
       </c>
       <c r="M37" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J37:L37)</f>
-        <v>GBR</v>
+        <v>ISR</v>
       </c>
       <c r="N37" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="O37" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="P37" s="1">
         <v>46111</v>
@@ -7170,39 +7968,39 @@
         <v>159</v>
       </c>
       <c r="R37" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="S37">
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:19">
+    <row r="38" spans="1:19" hidden="1">
       <c r="A38" s="2" t="str">
         <f>IF(C38="","",VLOOKUP(C38,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>AFG</v>
+        <v>RUS</v>
       </c>
       <c r="B38" s="3" t="str">
         <f>IF(C38="","",VLOOKUP(C38,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Afghanistan</v>
+        <v>Russian Federation</v>
       </c>
       <c r="C38" t="s">
-        <v>221</v>
+        <v>176</v>
       </c>
       <c r="D38" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="E38" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F38" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="G38" t="s">
-        <v>225</v>
+        <v>193</v>
       </c>
       <c r="J38" s="2" t="str">
         <f>IF(G38="","",VLOOKUP(G38,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>PAK</v>
+        <v>GBR</v>
       </c>
       <c r="K38" s="2" t="str">
         <f>IF(H38="","",VLOOKUP(H38,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -7214,13 +8012,13 @@
       </c>
       <c r="M38" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J38:L38)</f>
-        <v>PAK</v>
+        <v>GBR</v>
       </c>
       <c r="N38" t="s">
-        <v>226</v>
+        <v>178</v>
       </c>
       <c r="O38" t="s">
-        <v>227</v>
+        <v>53</v>
       </c>
       <c r="P38" s="1">
         <v>46111</v>
@@ -7229,63 +8027,57 @@
         <v>159</v>
       </c>
       <c r="R38" t="s">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="S38">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:19">
+    <row r="39" spans="1:19" hidden="1">
       <c r="A39" s="2" t="str">
         <f>IF(C39="","",VLOOKUP(C39,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>XKK</v>
+        <v>AFG</v>
       </c>
       <c r="B39" s="3" t="str">
         <f>IF(C39="","",VLOOKUP(C39,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Kosovo</v>
+        <v>Afghanistan</v>
       </c>
       <c r="C39" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="D39" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="E39" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="F39" t="s">
-        <v>156</v>
+        <v>224</v>
       </c>
       <c r="G39" t="s">
-        <v>177</v>
-      </c>
-      <c r="H39" t="s">
-        <v>153</v>
-      </c>
-      <c r="I39" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="J39" s="2" t="str">
         <f>IF(G39="","",VLOOKUP(G39,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>USA</v>
+        <v>PAK</v>
       </c>
       <c r="K39" s="2" t="str">
         <f>IF(H39="","",VLOOKUP(H39,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>ISR</v>
+        <v/>
       </c>
       <c r="L39" s="2" t="str">
         <f>IF(I39="","",VLOOKUP(I39,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>PSE</v>
+        <v/>
       </c>
       <c r="M39" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J39:L39)</f>
-        <v>USA;ISR;PSE</v>
+        <v>PAK</v>
       </c>
       <c r="N39" t="s">
-        <v>178</v>
+        <v>226</v>
       </c>
       <c r="O39" t="s">
-        <v>69</v>
+        <v>227</v>
       </c>
       <c r="P39" s="1">
         <v>46111</v>
@@ -7294,54 +8086,60 @@
         <v>159</v>
       </c>
       <c r="R39" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="S39">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:19">
+    <row r="40" spans="1:19" hidden="1">
       <c r="A40" s="2" t="str">
         <f>IF(C40="","",VLOOKUP(C40,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>PAK</v>
+        <v>XKK</v>
       </c>
       <c r="B40" s="3" t="str">
         <f>IF(C40="","",VLOOKUP(C40,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Pakistan</v>
+        <v>Kosovo</v>
       </c>
       <c r="C40" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D40" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E40" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F40" t="s">
         <v>156</v>
       </c>
       <c r="G40" t="s">
-        <v>221</v>
+        <v>177</v>
+      </c>
+      <c r="H40" t="s">
+        <v>153</v>
+      </c>
+      <c r="I40" t="s">
+        <v>232</v>
       </c>
       <c r="J40" s="2" t="str">
         <f>IF(G40="","",VLOOKUP(G40,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>AFG</v>
+        <v>USA</v>
       </c>
       <c r="K40" s="2" t="str">
         <f>IF(H40="","",VLOOKUP(H40,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>ISR</v>
       </c>
       <c r="L40" s="2" t="str">
         <f>IF(I40="","",VLOOKUP(I40,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>PSE</v>
       </c>
       <c r="M40" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J40:L40)</f>
-        <v>AFG</v>
+        <v>USA;ISR;PSE</v>
       </c>
       <c r="N40" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="O40" t="s">
         <v>69</v>
@@ -7353,36 +8151,39 @@
         <v>159</v>
       </c>
       <c r="R40" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="S40">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:19">
       <c r="A41" s="2" t="str">
         <f>IF(C41="","",VLOOKUP(C41,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>PRY</v>
+        <v>PAK</v>
       </c>
       <c r="B41" s="3" t="str">
         <f>IF(C41="","",VLOOKUP(C41,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Paraguay</v>
+        <v>Pakistan</v>
       </c>
       <c r="C41" t="s">
-        <v>182</v>
-      </c>
-      <c r="D41" t="s">
-        <v>183</v>
+        <v>225</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>234</v>
       </c>
       <c r="E41" t="s">
-        <v>184</v>
+        <v>235</v>
       </c>
       <c r="F41" t="s">
-        <v>170</v>
+        <v>156</v>
+      </c>
+      <c r="G41" t="s">
+        <v>221</v>
       </c>
       <c r="J41" s="2" t="str">
         <f>IF(G41="","",VLOOKUP(G41,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>AFG</v>
       </c>
       <c r="K41" s="2" t="str">
         <f>IF(H41="","",VLOOKUP(H41,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -7394,28 +8195,28 @@
       </c>
       <c r="M41" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J41:L41)</f>
-        <v/>
+        <v>AFG</v>
       </c>
       <c r="N41" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="O41" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="P41" s="1">
-        <v>46112</v>
+        <v>46111</v>
       </c>
       <c r="Q41" t="s">
-        <v>180</v>
-      </c>
-      <c r="R41" s="5" t="s">
-        <v>185</v>
+        <v>159</v>
+      </c>
+      <c r="R41" t="s">
+        <v>236</v>
       </c>
       <c r="S41">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:19">
+    <row r="42" spans="1:19" hidden="1">
       <c r="A42" s="2" t="str">
         <f>IF(C42="","",VLOOKUP(C42,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>USA</v>
@@ -7428,20 +8229,20 @@
         <v>177</v>
       </c>
       <c r="D42" t="s">
-        <v>186</v>
+        <v>254</v>
       </c>
       <c r="E42" t="s">
-        <v>187</v>
+        <v>255</v>
       </c>
       <c r="F42" t="s">
-        <v>156</v>
+        <v>196</v>
       </c>
       <c r="G42" t="s">
-        <v>188</v>
+        <v>256</v>
       </c>
       <c r="J42" s="2" t="str">
         <f>IF(G42="","",VLOOKUP(G42,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>IRN</v>
+        <v>VEN</v>
       </c>
       <c r="K42" s="2" t="str">
         <f>IF(H42="","",VLOOKUP(H42,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -7453,54 +8254,51 @@
       </c>
       <c r="M42" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J42:L42)</f>
-        <v>IRN</v>
+        <v>VEN</v>
       </c>
       <c r="N42" t="s">
-        <v>158</v>
+        <v>257</v>
       </c>
       <c r="O42" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="P42" s="1">
-        <v>46112</v>
+        <v>46111</v>
       </c>
       <c r="Q42" t="s">
-        <v>180</v>
-      </c>
-      <c r="R42" s="5" t="s">
-        <v>189</v>
+        <v>159</v>
+      </c>
+      <c r="R42" t="s">
+        <v>258</v>
       </c>
       <c r="S42">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:19">
       <c r="A43" s="2" t="str">
         <f>IF(C43="","",VLOOKUP(C43,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>GBR</v>
+        <v>EGY</v>
       </c>
       <c r="B43" s="3" t="str">
         <f>IF(C43="","",VLOOKUP(C43,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Britain</v>
+        <v>Egypt</v>
       </c>
       <c r="C43" t="s">
-        <v>193</v>
-      </c>
-      <c r="D43" t="s">
-        <v>194</v>
-      </c>
-      <c r="E43" t="s">
-        <v>195</v>
+        <v>259</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>262</v>
       </c>
       <c r="F43" t="s">
         <v>196</v>
       </c>
       <c r="G43" t="s">
-        <v>197</v>
+        <v>263</v>
       </c>
       <c r="J43" s="2" t="str">
         <f>IF(G43="","",VLOOKUP(G43,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>SYR</v>
+        <v>CYP</v>
       </c>
       <c r="K43" s="2" t="str">
         <f>IF(H43="","",VLOOKUP(H43,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -7512,54 +8310,51 @@
       </c>
       <c r="M43" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J43:L43)</f>
-        <v>SYR</v>
+        <v>CYP</v>
       </c>
       <c r="N43" t="s">
-        <v>178</v>
+        <v>264</v>
       </c>
       <c r="O43" t="s">
-        <v>53</v>
+        <v>179</v>
       </c>
       <c r="P43" s="1">
-        <v>46112</v>
+        <v>46111</v>
       </c>
       <c r="Q43" t="s">
         <v>159</v>
       </c>
       <c r="R43" t="s">
-        <v>198</v>
+        <v>265</v>
       </c>
       <c r="S43">
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:19">
+    <row r="44" spans="1:19" hidden="1">
       <c r="A44" s="2" t="str">
         <f>IF(C44="","",VLOOKUP(C44,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>ISR</v>
+        <v>SOM</v>
       </c>
       <c r="B44" s="3" t="str">
         <f>IF(C44="","",VLOOKUP(C44,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Israel</v>
+        <v>Somalia</v>
       </c>
       <c r="C44" t="s">
-        <v>153</v>
+        <v>266</v>
       </c>
       <c r="D44" t="s">
-        <v>199</v>
+        <v>267</v>
       </c>
       <c r="E44" t="s">
-        <v>200</v>
+        <v>268</v>
       </c>
       <c r="F44" t="s">
-        <v>156</v>
-      </c>
-      <c r="G44" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="J44" s="2" t="str">
         <f>IF(G44="","",VLOOKUP(G44,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>LBN</v>
+        <v/>
       </c>
       <c r="K44" s="2" t="str">
         <f>IF(H44="","",VLOOKUP(H44,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -7571,54 +8366,54 @@
       </c>
       <c r="M44" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J44:L44)</f>
-        <v>LBN</v>
+        <v/>
       </c>
       <c r="N44" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="O44" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="P44" s="1">
-        <v>46112</v>
+        <v>46111</v>
       </c>
       <c r="Q44" t="s">
         <v>159</v>
       </c>
       <c r="R44" t="s">
-        <v>201</v>
+        <v>269</v>
       </c>
       <c r="S44">
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:19">
+    <row r="45" spans="1:19" hidden="1">
       <c r="A45" s="2" t="str">
         <f>IF(C45="","",VLOOKUP(C45,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>ITA</v>
+        <v>IRN</v>
       </c>
       <c r="B45" s="3" t="str">
         <f>IF(C45="","",VLOOKUP(C45,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Italy</v>
+        <v>Iran</v>
       </c>
       <c r="C45" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="D45" t="s">
-        <v>210</v>
+        <v>270</v>
       </c>
       <c r="E45" t="s">
-        <v>211</v>
+        <v>271</v>
       </c>
       <c r="F45" t="s">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="G45" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="J45" s="2" t="str">
         <f>IF(G45="","",VLOOKUP(G45,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>USA</v>
+        <v>ISR</v>
       </c>
       <c r="K45" s="2" t="str">
         <f>IF(H45="","",VLOOKUP(H45,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -7630,61 +8425,55 @@
       </c>
       <c r="M45" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J45:L45)</f>
-        <v>USA</v>
+        <v>ISR</v>
       </c>
       <c r="N45" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="O45" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="P45" s="1">
-        <v>46112</v>
+        <v>46111</v>
       </c>
       <c r="Q45" t="s">
         <v>159</v>
       </c>
       <c r="R45" t="s">
-        <v>212</v>
+        <v>272</v>
       </c>
       <c r="S45">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:19">
+    <row r="46" spans="1:19" hidden="1">
       <c r="A46" s="2" t="str">
         <f>IF(C46="","",VLOOKUP(C46,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>FRA</v>
+        <v>PRY</v>
       </c>
       <c r="B46" s="3" t="str">
         <f>IF(C46="","",VLOOKUP(C46,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>France</v>
+        <v>Paraguay</v>
       </c>
       <c r="C46" t="s">
-        <v>213</v>
+        <v>182</v>
       </c>
       <c r="D46" t="s">
-        <v>214</v>
+        <v>183</v>
       </c>
       <c r="E46" t="s">
-        <v>215</v>
+        <v>184</v>
       </c>
       <c r="F46" t="s">
-        <v>196</v>
-      </c>
-      <c r="G46" t="s">
-        <v>153</v>
-      </c>
-      <c r="H46" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="J46" s="2" t="str">
         <f>IF(G46="","",VLOOKUP(G46,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>ISR</v>
+        <v/>
       </c>
       <c r="K46" s="2" t="str">
         <f>IF(H46="","",VLOOKUP(H46,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>USA</v>
+        <v/>
       </c>
       <c r="L46" s="2" t="str">
         <f>IF(I46="","",VLOOKUP(I46,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -7692,51 +8481,54 @@
       </c>
       <c r="M46" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J46:L46)</f>
-        <v>ISR;USA</v>
+        <v/>
       </c>
       <c r="N46" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="O46" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="P46" s="1">
         <v>46112</v>
       </c>
       <c r="Q46" t="s">
-        <v>159</v>
-      </c>
-      <c r="R46" t="s">
-        <v>216</v>
+        <v>180</v>
+      </c>
+      <c r="R46" s="5" t="s">
+        <v>185</v>
       </c>
       <c r="S46">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:19">
       <c r="A47" s="2" t="str">
         <f>IF(C47="","",VLOOKUP(C47,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>THA</v>
+        <v>USA</v>
       </c>
       <c r="B47" s="3" t="str">
         <f>IF(C47="","",VLOOKUP(C47,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Thailand</v>
+        <v>America</v>
       </c>
       <c r="C47" t="s">
-        <v>237</v>
-      </c>
-      <c r="D47" t="s">
-        <v>238</v>
+        <v>177</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>186</v>
       </c>
       <c r="E47" t="s">
-        <v>239</v>
+        <v>187</v>
       </c>
       <c r="F47" t="s">
-        <v>170</v>
+        <v>156</v>
+      </c>
+      <c r="G47" t="s">
+        <v>188</v>
       </c>
       <c r="J47" s="2" t="str">
         <f>IF(G47="","",VLOOKUP(G47,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>IRN</v>
       </c>
       <c r="K47" s="2" t="str">
         <f>IF(H47="","",VLOOKUP(H47,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -7748,51 +8540,54 @@
       </c>
       <c r="M47" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J47:L47)</f>
-        <v/>
+        <v>IRN</v>
       </c>
       <c r="N47" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="O47" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="P47" s="1">
         <v>46112</v>
       </c>
       <c r="Q47" t="s">
-        <v>159</v>
-      </c>
-      <c r="R47" t="s">
-        <v>240</v>
+        <v>180</v>
+      </c>
+      <c r="R47" s="5" t="s">
+        <v>189</v>
       </c>
       <c r="S47">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:19">
+    <row r="48" spans="1:19" hidden="1">
       <c r="A48" s="2" t="str">
         <f>IF(C48="","",VLOOKUP(C48,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>KOR</v>
+        <v>GBR</v>
       </c>
       <c r="B48" s="3" t="str">
         <f>IF(C48="","",VLOOKUP(C48,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Korea</v>
+        <v>Britain</v>
       </c>
       <c r="C48" t="s">
-        <v>241</v>
+        <v>193</v>
       </c>
       <c r="D48" t="s">
-        <v>242</v>
+        <v>194</v>
       </c>
       <c r="E48" t="s">
-        <v>243</v>
+        <v>195</v>
       </c>
       <c r="F48" t="s">
-        <v>244</v>
+        <v>196</v>
+      </c>
+      <c r="G48" t="s">
+        <v>197</v>
       </c>
       <c r="J48" s="2" t="str">
         <f>IF(G48="","",VLOOKUP(G48,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>SYR</v>
       </c>
       <c r="K48" s="2" t="str">
         <f>IF(H48="","",VLOOKUP(H48,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -7804,13 +8599,13 @@
       </c>
       <c r="M48" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J48:L48)</f>
-        <v/>
+        <v>SYR</v>
       </c>
       <c r="N48" t="s">
-        <v>245</v>
+        <v>178</v>
       </c>
       <c r="O48" t="s">
-        <v>246</v>
+        <v>53</v>
       </c>
       <c r="P48" s="1">
         <v>46112</v>
@@ -7819,24 +8614,39 @@
         <v>159</v>
       </c>
       <c r="R48" t="s">
-        <v>247</v>
+        <v>198</v>
       </c>
       <c r="S48">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:13">
+    <row r="49" spans="1:19" hidden="1">
       <c r="A49" s="2" t="str">
         <f>IF(C49="","",VLOOKUP(C49,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>ISR</v>
       </c>
       <c r="B49" s="3" t="str">
         <f>IF(C49="","",VLOOKUP(C49,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Israel</v>
+      </c>
+      <c r="C49" t="s">
+        <v>153</v>
+      </c>
+      <c r="D49" t="s">
+        <v>199</v>
+      </c>
+      <c r="E49" t="s">
+        <v>200</v>
+      </c>
+      <c r="F49" t="s">
+        <v>156</v>
+      </c>
+      <c r="G49" t="s">
+        <v>157</v>
       </c>
       <c r="J49" s="2" t="str">
         <f>IF(G49="","",VLOOKUP(G49,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>LBN</v>
       </c>
       <c r="K49" s="2" t="str">
         <f>IF(H49="","",VLOOKUP(H49,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -7848,21 +8658,54 @@
       </c>
       <c r="M49" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J49:L49)</f>
-        <v/>
+        <v>LBN</v>
+      </c>
+      <c r="N49" t="s">
+        <v>158</v>
+      </c>
+      <c r="O49" t="s">
+        <v>69</v>
+      </c>
+      <c r="P49" s="1">
+        <v>46112</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>159</v>
+      </c>
+      <c r="R49" t="s">
+        <v>201</v>
+      </c>
+      <c r="S49">
+        <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:13">
+    <row r="50" spans="1:19">
       <c r="A50" s="2" t="str">
         <f>IF(C50="","",VLOOKUP(C50,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>ITA</v>
       </c>
       <c r="B50" s="3" t="str">
         <f>IF(C50="","",VLOOKUP(C50,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Italy</v>
+      </c>
+      <c r="C50" t="s">
+        <v>167</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="E50" t="s">
+        <v>211</v>
+      </c>
+      <c r="F50" t="s">
+        <v>196</v>
+      </c>
+      <c r="G50" t="s">
+        <v>177</v>
       </c>
       <c r="J50" s="2" t="str">
         <f>IF(G50="","",VLOOKUP(G50,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>USA</v>
       </c>
       <c r="K50" s="2" t="str">
         <f>IF(H50="","",VLOOKUP(H50,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -7874,25 +8717,61 @@
       </c>
       <c r="M50" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J50:L50)</f>
-        <v/>
+        <v>USA</v>
+      </c>
+      <c r="N50" t="s">
+        <v>178</v>
+      </c>
+      <c r="O50" t="s">
+        <v>53</v>
+      </c>
+      <c r="P50" s="1">
+        <v>46112</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>159</v>
+      </c>
+      <c r="R50" t="s">
+        <v>212</v>
+      </c>
+      <c r="S50">
+        <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:13">
+    <row r="51" spans="1:19">
       <c r="A51" s="2" t="str">
         <f>IF(C51="","",VLOOKUP(C51,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>FRA</v>
       </c>
       <c r="B51" s="3" t="str">
         <f>IF(C51="","",VLOOKUP(C51,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>France</v>
+      </c>
+      <c r="C51" t="s">
+        <v>213</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="E51" t="s">
+        <v>215</v>
+      </c>
+      <c r="F51" t="s">
+        <v>196</v>
+      </c>
+      <c r="G51" t="s">
+        <v>153</v>
+      </c>
+      <c r="H51" t="s">
+        <v>177</v>
       </c>
       <c r="J51" s="2" t="str">
         <f>IF(G51="","",VLOOKUP(G51,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>ISR</v>
       </c>
       <c r="K51" s="2" t="str">
         <f>IF(H51="","",VLOOKUP(H51,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>USA</v>
       </c>
       <c r="L51" s="2" t="str">
         <f>IF(I51="","",VLOOKUP(I51,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -7900,17 +8779,47 @@
       </c>
       <c r="M51" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J51:L51)</f>
-        <v/>
+        <v>ISR;USA</v>
+      </c>
+      <c r="N51" t="s">
+        <v>178</v>
+      </c>
+      <c r="O51" t="s">
+        <v>53</v>
+      </c>
+      <c r="P51" s="1">
+        <v>46112</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>159</v>
+      </c>
+      <c r="R51" t="s">
+        <v>216</v>
+      </c>
+      <c r="S51">
+        <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:13">
+    <row r="52" spans="1:19" hidden="1">
       <c r="A52" s="2" t="str">
         <f>IF(C52="","",VLOOKUP(C52,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>THA</v>
       </c>
       <c r="B52" s="3" t="str">
         <f>IF(C52="","",VLOOKUP(C52,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Thailand</v>
+      </c>
+      <c r="C52" t="s">
+        <v>237</v>
+      </c>
+      <c r="D52" t="s">
+        <v>238</v>
+      </c>
+      <c r="E52" t="s">
+        <v>239</v>
+      </c>
+      <c r="F52" t="s">
+        <v>170</v>
       </c>
       <c r="J52" s="2" t="str">
         <f>IF(G52="","",VLOOKUP(G52,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -7928,15 +8837,45 @@
         <f>_xlfn.TEXTJOIN(";",TRUE,J52:L52)</f>
         <v/>
       </c>
+      <c r="N52" t="s">
+        <v>165</v>
+      </c>
+      <c r="O52" t="s">
+        <v>79</v>
+      </c>
+      <c r="P52" s="1">
+        <v>46112</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>159</v>
+      </c>
+      <c r="R52" t="s">
+        <v>240</v>
+      </c>
+      <c r="S52">
+        <v>2</v>
+      </c>
     </row>
-    <row r="53" spans="1:13">
+    <row r="53" spans="1:19">
       <c r="A53" s="2" t="str">
         <f>IF(C53="","",VLOOKUP(C53,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>KOR</v>
       </c>
       <c r="B53" s="3" t="str">
         <f>IF(C53="","",VLOOKUP(C53,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Korea</v>
+      </c>
+      <c r="C53" t="s">
+        <v>241</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="E53" t="s">
+        <v>243</v>
+      </c>
+      <c r="F53" t="s">
+        <v>244</v>
       </c>
       <c r="J53" s="2" t="str">
         <f>IF(G53="","",VLOOKUP(G53,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -7954,15 +8893,42 @@
         <f>_xlfn.TEXTJOIN(";",TRUE,J53:L53)</f>
         <v/>
       </c>
+      <c r="N53" t="s">
+        <v>245</v>
+      </c>
+      <c r="O53" t="s">
+        <v>246</v>
+      </c>
+      <c r="P53" s="1">
+        <v>46112</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>159</v>
+      </c>
+      <c r="R53" t="s">
+        <v>247</v>
+      </c>
+      <c r="S53">
+        <v>4</v>
+      </c>
     </row>
-    <row r="54" spans="1:13">
+    <row r="54" spans="1:19" hidden="1">
       <c r="A54" s="2" t="str">
         <f>IF(C54="","",VLOOKUP(C54,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>MNG</v>
       </c>
       <c r="B54" s="3" t="str">
         <f>IF(C54="","",VLOOKUP(C54,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Mongolia</v>
+      </c>
+      <c r="C54" t="s">
+        <v>251</v>
+      </c>
+      <c r="D54" t="s">
+        <v>252</v>
+      </c>
+      <c r="F54" t="s">
+        <v>170</v>
       </c>
       <c r="J54" s="2" t="str">
         <f>IF(G54="","",VLOOKUP(G54,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -7980,15 +8946,45 @@
         <f>_xlfn.TEXTJOIN(";",TRUE,J54:L54)</f>
         <v/>
       </c>
+      <c r="N54" t="s">
+        <v>165</v>
+      </c>
+      <c r="O54" t="s">
+        <v>79</v>
+      </c>
+      <c r="P54" s="1">
+        <v>46112</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>159</v>
+      </c>
+      <c r="R54" t="s">
+        <v>253</v>
+      </c>
+      <c r="S54">
+        <v>1</v>
+      </c>
     </row>
-    <row r="55" spans="1:13">
+    <row r="55" spans="1:19">
       <c r="A55" s="2" t="str">
         <f>IF(C55="","",VLOOKUP(C55,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>DEU</v>
       </c>
       <c r="B55" s="3" t="str">
         <f>IF(C55="","",VLOOKUP(C55,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Germany</v>
+      </c>
+      <c r="C55" t="s">
+        <v>273</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="E55" t="s">
+        <v>275</v>
+      </c>
+      <c r="F55" t="s">
+        <v>170</v>
       </c>
       <c r="J55" s="2" t="str">
         <f>IF(G55="","",VLOOKUP(G55,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -8006,15 +9002,45 @@
         <f>_xlfn.TEXTJOIN(";",TRUE,J55:L55)</f>
         <v/>
       </c>
+      <c r="N55" t="s">
+        <v>165</v>
+      </c>
+      <c r="O55" t="s">
+        <v>79</v>
+      </c>
+      <c r="P55" s="1">
+        <v>46112</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>159</v>
+      </c>
+      <c r="R55" t="s">
+        <v>276</v>
+      </c>
+      <c r="S55">
+        <v>3</v>
+      </c>
     </row>
-    <row r="56" spans="1:13">
+    <row r="56" spans="1:19" hidden="1">
       <c r="A56" s="2" t="str">
         <f>IF(C56="","",VLOOKUP(C56,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>SRB</v>
       </c>
       <c r="B56" s="3" t="str">
         <f>IF(C56="","",VLOOKUP(C56,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Serbia</v>
+      </c>
+      <c r="C56" t="s">
+        <v>300</v>
+      </c>
+      <c r="D56" t="s">
+        <v>301</v>
+      </c>
+      <c r="E56" t="s">
+        <v>302</v>
+      </c>
+      <c r="F56" t="s">
+        <v>170</v>
       </c>
       <c r="J56" s="2" t="str">
         <f>IF(G56="","",VLOOKUP(G56,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -8032,41 +9058,107 @@
         <f>_xlfn.TEXTJOIN(";",TRUE,J56:L56)</f>
         <v/>
       </c>
+      <c r="N56" t="s">
+        <v>165</v>
+      </c>
+      <c r="O56" t="s">
+        <v>79</v>
+      </c>
+      <c r="P56" s="1">
+        <v>46112</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>159</v>
+      </c>
+      <c r="R56" t="s">
+        <v>303</v>
+      </c>
+      <c r="S56">
+        <v>3</v>
+      </c>
     </row>
-    <row r="57" spans="1:13">
+    <row r="57" spans="1:19" hidden="1">
       <c r="A57" s="2" t="str">
         <f>IF(C57="","",VLOOKUP(C57,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>SYR</v>
       </c>
       <c r="B57" s="3" t="str">
         <f>IF(C57="","",VLOOKUP(C57,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Syrian Arab Republic</v>
+      </c>
+      <c r="C57" t="s">
+        <v>197</v>
+      </c>
+      <c r="D57" t="s">
+        <v>317</v>
+      </c>
+      <c r="E57" t="s">
+        <v>318</v>
+      </c>
+      <c r="F57" t="s">
+        <v>279</v>
+      </c>
+      <c r="G57" t="s">
+        <v>188</v>
+      </c>
+      <c r="H57" t="s">
+        <v>177</v>
+      </c>
+      <c r="I57" t="s">
+        <v>153</v>
       </c>
       <c r="J57" s="2" t="str">
         <f>IF(G57="","",VLOOKUP(G57,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>IRN</v>
       </c>
       <c r="K57" s="2" t="str">
         <f>IF(H57="","",VLOOKUP(H57,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>USA</v>
       </c>
       <c r="L57" s="2" t="str">
         <f>IF(I57="","",VLOOKUP(I57,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>ISR</v>
       </c>
       <c r="M57" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J57:L57)</f>
-        <v/>
+        <v>IRN;USA;ISR</v>
+      </c>
+      <c r="N57" t="s">
+        <v>178</v>
+      </c>
+      <c r="O57" t="s">
+        <v>53</v>
+      </c>
+      <c r="P57" s="1">
+        <v>46112</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>159</v>
+      </c>
+      <c r="R57" t="s">
+        <v>319</v>
+      </c>
+      <c r="S57">
+        <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:13">
+    <row r="58" spans="1:19" hidden="1">
       <c r="A58" s="2" t="str">
         <f>IF(C58="","",VLOOKUP(C58,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>MEX</v>
       </c>
       <c r="B58" s="3" t="str">
         <f>IF(C58="","",VLOOKUP(C58,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Mexico</v>
+      </c>
+      <c r="C58" t="s">
+        <v>248</v>
+      </c>
+      <c r="D58" t="s">
+        <v>249</v>
+      </c>
+      <c r="F58" t="s">
+        <v>170</v>
       </c>
       <c r="J58" s="2" t="str">
         <f>IF(G58="","",VLOOKUP(G58,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -8084,15 +9176,45 @@
         <f>_xlfn.TEXTJOIN(";",TRUE,J58:L58)</f>
         <v/>
       </c>
+      <c r="N58" t="s">
+        <v>165</v>
+      </c>
+      <c r="O58" t="s">
+        <v>79</v>
+      </c>
+      <c r="P58" s="1">
+        <v>46113</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>159</v>
+      </c>
+      <c r="R58" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="S58">
+        <v>1</v>
+      </c>
     </row>
-    <row r="59" spans="1:13">
+    <row r="59" spans="1:19" hidden="1">
       <c r="A59" s="2" t="str">
         <f>IF(C59="","",VLOOKUP(C59,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>USA</v>
       </c>
       <c r="B59" s="3" t="str">
         <f>IF(C59="","",VLOOKUP(C59,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>America</v>
+      </c>
+      <c r="C59" t="s">
+        <v>177</v>
+      </c>
+      <c r="D59" t="s">
+        <v>296</v>
+      </c>
+      <c r="E59" t="s">
+        <v>297</v>
+      </c>
+      <c r="F59" t="s">
+        <v>279</v>
       </c>
       <c r="J59" s="2" t="str">
         <f>IF(G59="","",VLOOKUP(G59,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -8110,15 +9232,46 @@
         <f>_xlfn.TEXTJOIN(";",TRUE,J59:L59)</f>
         <v/>
       </c>
+      <c r="N59" t="s">
+        <v>298</v>
+      </c>
+      <c r="P59" s="1">
+        <v>46113</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>159</v>
+      </c>
+      <c r="R59" t="s">
+        <v>299</v>
+      </c>
+      <c r="S59">
+        <v>4</v>
+      </c>
     </row>
-    <row r="60" spans="1:13">
+    <row r="60" spans="1:19">
       <c r="A60" s="2" t="str">
         <f>IF(C60="","",VLOOKUP(C60,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>LBN</v>
+      </c>
+      <c r="B60" s="3" t="str">
+        <f>IF(C60="","",VLOOKUP(C60,[1]ISO辞書!A:C,3,FALSE))</f>
+        <v>Lebanon</v>
+      </c>
+      <c r="C60" t="s">
+        <v>157</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="F60" t="s">
+        <v>156</v>
+      </c>
+      <c r="G60" t="s">
+        <v>153</v>
       </c>
       <c r="J60" s="2" t="str">
         <f>IF(G60="","",VLOOKUP(G60,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>ISR</v>
       </c>
       <c r="K60" s="2" t="str">
         <f>IF(H60="","",VLOOKUP(H60,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -8130,17 +9283,54 @@
       </c>
       <c r="M60" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J60:L60)</f>
-        <v/>
+        <v>ISR</v>
+      </c>
+      <c r="N60" t="s">
+        <v>158</v>
+      </c>
+      <c r="O60" t="s">
+        <v>69</v>
+      </c>
+      <c r="P60" s="1">
+        <v>46113</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>159</v>
+      </c>
+      <c r="R60" t="s">
+        <v>316</v>
+      </c>
+      <c r="S60">
+        <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:13">
+    <row r="61" spans="1:19" hidden="1">
       <c r="A61" s="2" t="str">
         <f>IF(C61="","",VLOOKUP(C61,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>ARG</v>
+      </c>
+      <c r="B61" s="3" t="str">
+        <f>IF(C61="","",VLOOKUP(C61,[1]ISO辞書!A:C,3,FALSE))</f>
+        <v>Argentina</v>
+      </c>
+      <c r="C61" t="s">
+        <v>320</v>
+      </c>
+      <c r="D61" t="s">
+        <v>321</v>
+      </c>
+      <c r="E61" t="s">
+        <v>322</v>
+      </c>
+      <c r="F61" t="s">
+        <v>279</v>
+      </c>
+      <c r="G61" t="s">
+        <v>188</v>
       </c>
       <c r="J61" s="2" t="str">
         <f>IF(G61="","",VLOOKUP(G61,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>IRN</v>
       </c>
       <c r="K61" s="2" t="str">
         <f>IF(H61="","",VLOOKUP(H61,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -8152,17 +9342,54 @@
       </c>
       <c r="M61" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J61:L61)</f>
-        <v/>
+        <v>IRN</v>
+      </c>
+      <c r="N61" t="s">
+        <v>178</v>
+      </c>
+      <c r="O61" t="s">
+        <v>53</v>
+      </c>
+      <c r="P61" s="1">
+        <v>46113</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>159</v>
+      </c>
+      <c r="R61" t="s">
+        <v>323</v>
+      </c>
+      <c r="S61">
+        <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:13">
+    <row r="62" spans="1:19" hidden="1">
       <c r="A62" s="2" t="str">
         <f>IF(C62="","",VLOOKUP(C62,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>EU</v>
+      </c>
+      <c r="B62" s="3" t="str">
+        <f>IF(C62="","",VLOOKUP(C62,[1]ISO辞書!A:C,3,FALSE))</f>
+        <v>EU</v>
+      </c>
+      <c r="C62" t="s">
+        <v>343</v>
+      </c>
+      <c r="D62" t="s">
+        <v>344</v>
+      </c>
+      <c r="E62" t="s">
+        <v>345</v>
+      </c>
+      <c r="F62" t="s">
+        <v>279</v>
+      </c>
+      <c r="G62" t="s">
+        <v>172</v>
       </c>
       <c r="J62" s="2" t="str">
         <f>IF(G62="","",VLOOKUP(G62,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>CUB</v>
       </c>
       <c r="K62" s="2" t="str">
         <f>IF(H62="","",VLOOKUP(H62,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -8174,17 +9401,51 @@
       </c>
       <c r="M62" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J62:L62)</f>
-        <v/>
+        <v>CUB</v>
+      </c>
+      <c r="N62" t="s">
+        <v>178</v>
+      </c>
+      <c r="O62" t="s">
+        <v>53</v>
+      </c>
+      <c r="P62" s="1">
+        <v>46113</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>159</v>
+      </c>
+      <c r="R62" t="s">
+        <v>346</v>
+      </c>
+      <c r="S62">
+        <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:13">
+    <row r="63" spans="1:19" hidden="1">
       <c r="A63" s="2" t="str">
         <f>IF(C63="","",VLOOKUP(C63,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>RUS</v>
+      </c>
+      <c r="B63" s="3" t="str">
+        <f>IF(C63="","",VLOOKUP(C63,[1]ISO辞書!A:C,3,FALSE))</f>
+        <v>Russian Federation</v>
+      </c>
+      <c r="C63" t="s">
+        <v>176</v>
+      </c>
+      <c r="D63" t="s">
+        <v>291</v>
+      </c>
+      <c r="F63" t="s">
+        <v>156</v>
+      </c>
+      <c r="G63" t="s">
+        <v>202</v>
       </c>
       <c r="J63" s="2" t="str">
         <f>IF(G63="","",VLOOKUP(G63,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>UKR</v>
       </c>
       <c r="K63" s="2" t="str">
         <f>IF(H63="","",VLOOKUP(H63,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -8196,31 +9457,119 @@
       </c>
       <c r="M63" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J63:L63)</f>
-        <v/>
+        <v>UKR</v>
+      </c>
+      <c r="N63" t="s">
+        <v>158</v>
+      </c>
+      <c r="O63" t="s">
+        <v>69</v>
+      </c>
+      <c r="P63" s="1">
+        <v>46114</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>159</v>
+      </c>
+      <c r="R63" t="s">
+        <v>292</v>
+      </c>
+      <c r="S63">
+        <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:13">
+    <row r="64" spans="1:19">
+      <c r="A64" s="2" t="str">
+        <f>IF(C64="","",VLOOKUP(C64,[1]ISO辞書!A:C,2,FALSE))</f>
+        <v>GBR</v>
+      </c>
+      <c r="B64" s="3" t="str">
+        <f>IF(C64="","",VLOOKUP(C64,[1]ISO辞書!A:C,3,FALSE))</f>
+        <v>Britain</v>
+      </c>
+      <c r="C64" t="s">
+        <v>193</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="E64" t="s">
+        <v>294</v>
+      </c>
+      <c r="F64" t="s">
+        <v>279</v>
+      </c>
+      <c r="G64" t="s">
+        <v>273</v>
+      </c>
+      <c r="H64" t="s">
+        <v>213</v>
+      </c>
+      <c r="I64" t="s">
+        <v>286</v>
+      </c>
       <c r="J64" s="2" t="str">
         <f>IF(G64="","",VLOOKUP(G64,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>DEU</v>
       </c>
       <c r="K64" s="2" t="str">
         <f>IF(H64="","",VLOOKUP(H64,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>FRA</v>
       </c>
       <c r="L64" s="2" t="str">
         <f>IF(I64="","",VLOOKUP(I64,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>ARE</v>
       </c>
       <c r="M64" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J64:L64)</f>
-        <v/>
+        <v>DEU;FRA;ARE</v>
+      </c>
+      <c r="N64" t="s">
+        <v>264</v>
+      </c>
+      <c r="O64" t="s">
+        <v>179</v>
+      </c>
+      <c r="P64" s="1">
+        <v>46114</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>159</v>
+      </c>
+      <c r="R64" t="s">
+        <v>295</v>
+      </c>
+      <c r="S64">
+        <v>5</v>
       </c>
     </row>
-    <row r="65" spans="10:13">
+    <row r="65" spans="1:19" hidden="1">
+      <c r="A65" s="2" t="str">
+        <f>IF(C65="","",VLOOKUP(C65,[1]ISO辞書!A:C,2,FALSE))</f>
+        <v>BFA</v>
+      </c>
+      <c r="B65" s="3" t="str">
+        <f>IF(C65="","",VLOOKUP(C65,[1]ISO辞書!A:C,3,FALSE))</f>
+        <v>Burkina Faso</v>
+      </c>
+      <c r="C65" t="s">
+        <v>324</v>
+      </c>
+      <c r="D65" t="s">
+        <v>325</v>
+      </c>
+      <c r="E65" t="s">
+        <v>326</v>
+      </c>
+      <c r="F65" t="s">
+        <v>279</v>
+      </c>
+      <c r="G65" t="s">
+        <v>327</v>
+      </c>
       <c r="J65" s="2" t="str">
         <f>IF(G65="","",VLOOKUP(G65,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>MLI</v>
       </c>
       <c r="K65" s="2" t="str">
         <f>IF(H65="","",VLOOKUP(H65,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -8232,10 +9581,45 @@
       </c>
       <c r="M65" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J65:L65)</f>
-        <v/>
+        <v>MLI</v>
+      </c>
+      <c r="N65" t="s">
+        <v>158</v>
+      </c>
+      <c r="O65" t="s">
+        <v>69</v>
+      </c>
+      <c r="P65" s="1">
+        <v>46114</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>159</v>
+      </c>
+      <c r="R65" t="s">
+        <v>328</v>
+      </c>
+      <c r="S65">
+        <v>3</v>
       </c>
     </row>
-    <row r="66" spans="10:13">
+    <row r="66" spans="1:19" hidden="1">
+      <c r="A66" s="2" t="str">
+        <f>IF(C66="","",VLOOKUP(C66,[1]ISO辞書!A:C,2,FALSE))</f>
+        <v>COD</v>
+      </c>
+      <c r="B66" s="3" t="str">
+        <f>IF(C66="","",VLOOKUP(C66,[1]ISO辞書!A:C,3,FALSE))</f>
+        <v>Democratic Republic of the Congo</v>
+      </c>
+      <c r="C66" t="s">
+        <v>336</v>
+      </c>
+      <c r="D66" t="s">
+        <v>337</v>
+      </c>
+      <c r="F66" t="s">
+        <v>156</v>
+      </c>
       <c r="J66" s="2" t="str">
         <f>IF(G66="","",VLOOKUP(G66,[1]ISO辞書!A:B,2,FALSE))</f>
         <v/>
@@ -8252,11 +9636,52 @@
         <f>_xlfn.TEXTJOIN(";",TRUE,J66:L66)</f>
         <v/>
       </c>
+      <c r="N66" t="s">
+        <v>338</v>
+      </c>
+      <c r="O66" t="s">
+        <v>69</v>
+      </c>
+      <c r="P66" s="1">
+        <v>46114</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>159</v>
+      </c>
+      <c r="R66" t="s">
+        <v>339</v>
+      </c>
+      <c r="S66">
+        <v>2</v>
+      </c>
     </row>
-    <row r="67" spans="10:13">
+    <row r="67" spans="1:19" hidden="1">
+      <c r="A67" s="2" t="str">
+        <f>IF(C67="","",VLOOKUP(C67,[1]ISO辞書!A:C,2,FALSE))</f>
+        <v>USA</v>
+      </c>
+      <c r="B67" s="3" t="str">
+        <f>IF(C67="","",VLOOKUP(C67,[1]ISO辞書!A:C,3,FALSE))</f>
+        <v>America</v>
+      </c>
+      <c r="C67" t="s">
+        <v>177</v>
+      </c>
+      <c r="D67" t="s">
+        <v>340</v>
+      </c>
+      <c r="E67" t="s">
+        <v>341</v>
+      </c>
+      <c r="F67" t="s">
+        <v>279</v>
+      </c>
+      <c r="G67" t="s">
+        <v>256</v>
+      </c>
       <c r="J67" s="2" t="str">
         <f>IF(G67="","",VLOOKUP(G67,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>VEN</v>
       </c>
       <c r="K67" s="2" t="str">
         <f>IF(H67="","",VLOOKUP(H67,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -8268,13 +9693,54 @@
       </c>
       <c r="M67" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J67:L67)</f>
-        <v/>
+        <v>VEN</v>
+      </c>
+      <c r="N67" t="s">
+        <v>257</v>
+      </c>
+      <c r="O67" t="s">
+        <v>53</v>
+      </c>
+      <c r="P67" s="1">
+        <v>46114</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>159</v>
+      </c>
+      <c r="R67" t="s">
+        <v>342</v>
+      </c>
+      <c r="S67">
+        <v>4</v>
       </c>
     </row>
-    <row r="68" spans="10:13">
+    <row r="68" spans="1:19">
+      <c r="A68" s="2" t="str">
+        <f>IF(C68="","",VLOOKUP(C68,[1]ISO辞書!A:C,2,FALSE))</f>
+        <v>NZL</v>
+      </c>
+      <c r="B68" s="3" t="str">
+        <f>IF(C68="","",VLOOKUP(C68,[1]ISO辞書!A:C,3,FALSE))</f>
+        <v>New Zealand</v>
+      </c>
+      <c r="C68" t="s">
+        <v>350</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="E68" t="s">
+        <v>352</v>
+      </c>
+      <c r="F68" t="s">
+        <v>279</v>
+      </c>
+      <c r="G68" t="s">
+        <v>353</v>
+      </c>
       <c r="J68" s="2" t="str">
         <f>IF(G68="","",VLOOKUP(G68,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>COK</v>
       </c>
       <c r="K68" s="2" t="str">
         <f>IF(H68="","",VLOOKUP(H68,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -8286,39 +9752,568 @@
       </c>
       <c r="M68" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J68:L68)</f>
-        <v/>
+        <v>COK</v>
+      </c>
+      <c r="N68" t="s">
+        <v>257</v>
+      </c>
+      <c r="O68" t="s">
+        <v>53</v>
+      </c>
+      <c r="P68" s="1">
+        <v>46114</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>159</v>
+      </c>
+      <c r="R68" t="s">
+        <v>354</v>
+      </c>
+      <c r="S68">
+        <v>4</v>
       </c>
     </row>
-    <row r="69" spans="10:13">
+    <row r="69" spans="1:19" hidden="1">
+      <c r="A69" s="2" t="str">
+        <f>IF(C69="","",VLOOKUP(C69,[1]ISO辞書!A:C,2,FALSE))</f>
+        <v>ITA</v>
+      </c>
+      <c r="B69" s="3" t="str">
+        <f>IF(C69="","",VLOOKUP(C69,[1]ISO辞書!A:C,3,FALSE))</f>
+        <v>Italy</v>
+      </c>
+      <c r="C69" t="s">
+        <v>167</v>
+      </c>
+      <c r="D69" t="s">
+        <v>282</v>
+      </c>
+      <c r="E69" t="s">
+        <v>283</v>
+      </c>
+      <c r="G69" t="s">
+        <v>284</v>
+      </c>
+      <c r="H69" t="s">
+        <v>285</v>
+      </c>
+      <c r="I69" t="s">
+        <v>286</v>
+      </c>
       <c r="J69" s="2" t="str">
         <f>IF(G69="","",VLOOKUP(G69,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>SAU</v>
       </c>
       <c r="K69" s="2" t="str">
         <f>IF(H69="","",VLOOKUP(H69,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>QAT</v>
       </c>
       <c r="L69" s="2" t="str">
         <f>IF(I69="","",VLOOKUP(I69,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>ARE</v>
       </c>
       <c r="M69" s="3" t="str">
         <f>_xlfn.TEXTJOIN(";",TRUE,J69:L69)</f>
-        <v/>
+        <v>SAU;QAT;ARE</v>
+      </c>
+      <c r="N69" t="s">
+        <v>257</v>
+      </c>
+      <c r="O69" t="s">
+        <v>53</v>
+      </c>
+      <c r="P69" s="1">
+        <v>46115</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>159</v>
+      </c>
+      <c r="R69" t="s">
+        <v>287</v>
+      </c>
+      <c r="S69">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" hidden="1">
+      <c r="A70" s="2" t="str">
+        <f>IF(C70="","",VLOOKUP(C70,[1]ISO辞書!A:C,2,FALSE))</f>
+        <v>KOR</v>
+      </c>
+      <c r="B70" s="3" t="str">
+        <f>IF(C70="","",VLOOKUP(C70,[1]ISO辞書!A:C,3,FALSE))</f>
+        <v>Korea</v>
+      </c>
+      <c r="C70" t="s">
+        <v>241</v>
+      </c>
+      <c r="D70" t="s">
+        <v>288</v>
+      </c>
+      <c r="E70" t="s">
+        <v>289</v>
+      </c>
+      <c r="F70" t="s">
+        <v>279</v>
+      </c>
+      <c r="G70" t="s">
+        <v>213</v>
+      </c>
+      <c r="J70" s="2" t="str">
+        <f>IF(G70="","",VLOOKUP(G70,[1]ISO辞書!A:B,2,FALSE))</f>
+        <v>FRA</v>
+      </c>
+      <c r="K70" s="2" t="str">
+        <f>IF(H70="","",VLOOKUP(H70,[1]ISO辞書!A:B,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="L70" s="2" t="str">
+        <f>IF(I70="","",VLOOKUP(I70,[1]ISO辞書!A:B,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="M70" s="3" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,J70:L70)</f>
+        <v>FRA</v>
+      </c>
+      <c r="N70" t="s">
+        <v>257</v>
+      </c>
+      <c r="O70" t="s">
+        <v>53</v>
+      </c>
+      <c r="P70" s="1">
+        <v>46115</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>159</v>
+      </c>
+      <c r="R70" t="s">
+        <v>290</v>
+      </c>
+      <c r="S70">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" hidden="1">
+      <c r="A71" s="2" t="str">
+        <f>IF(C71="","",VLOOKUP(C71,[1]ISO辞書!A:C,2,FALSE))</f>
+        <v>RUS</v>
+      </c>
+      <c r="B71" s="3" t="str">
+        <f>IF(C71="","",VLOOKUP(C71,[1]ISO辞書!A:C,3,FALSE))</f>
+        <v>Russian Federation</v>
+      </c>
+      <c r="C71" t="s">
+        <v>176</v>
+      </c>
+      <c r="D71" t="s">
+        <v>309</v>
+      </c>
+      <c r="E71" t="s">
+        <v>310</v>
+      </c>
+      <c r="F71" t="s">
+        <v>279</v>
+      </c>
+      <c r="G71" t="s">
+        <v>280</v>
+      </c>
+      <c r="J71" s="2" t="str">
+        <f>IF(G71="","",VLOOKUP(G71,[1]ISO辞書!A:B,2,FALSE))</f>
+        <v>TUR</v>
+      </c>
+      <c r="K71" s="2" t="str">
+        <f>IF(H71="","",VLOOKUP(H71,[1]ISO辞書!A:B,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="L71" s="2" t="str">
+        <f>IF(I71="","",VLOOKUP(I71,[1]ISO辞書!A:B,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="M71" s="3" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,J71:L71)</f>
+        <v>TUR</v>
+      </c>
+      <c r="N71" t="s">
+        <v>178</v>
+      </c>
+      <c r="O71" t="s">
+        <v>53</v>
+      </c>
+      <c r="P71" s="1">
+        <v>46115</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>159</v>
+      </c>
+      <c r="R71" t="s">
+        <v>311</v>
+      </c>
+      <c r="S71">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19">
+      <c r="A72" s="2" t="str">
+        <f>IF(C72="","",VLOOKUP(C72,[1]ISO辞書!A:C,2,FALSE))</f>
+        <v>JPN</v>
+      </c>
+      <c r="B72" s="3" t="str">
+        <f>IF(C72="","",VLOOKUP(C72,[1]ISO辞書!A:C,3,FALSE))</f>
+        <v>Japan</v>
+      </c>
+      <c r="C72" t="s">
+        <v>312</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="F72" t="s">
+        <v>279</v>
+      </c>
+      <c r="G72" t="s">
+        <v>213</v>
+      </c>
+      <c r="H72" t="s">
+        <v>313</v>
+      </c>
+      <c r="I72" t="s">
+        <v>188</v>
+      </c>
+      <c r="J72" s="2" t="str">
+        <f>IF(G72="","",VLOOKUP(G72,[1]ISO辞書!A:B,2,FALSE))</f>
+        <v>FRA</v>
+      </c>
+      <c r="K72" s="2" t="str">
+        <f>IF(H72="","",VLOOKUP(H72,[1]ISO辞書!A:B,2,FALSE))</f>
+        <v>OMN</v>
+      </c>
+      <c r="L72" s="2" t="str">
+        <f>IF(I72="","",VLOOKUP(I72,[1]ISO辞書!A:B,2,FALSE))</f>
+        <v>IRN</v>
+      </c>
+      <c r="M72" s="3" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,J72:L72)</f>
+        <v>FRA;OMN;IRN</v>
+      </c>
+      <c r="N72" t="s">
+        <v>264</v>
+      </c>
+      <c r="O72" t="s">
+        <v>179</v>
+      </c>
+      <c r="P72" s="1">
+        <v>46115</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>159</v>
+      </c>
+      <c r="R72" t="s">
+        <v>314</v>
+      </c>
+      <c r="S72">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" hidden="1">
+      <c r="A73" s="2" t="str">
+        <f>IF(C73="","",VLOOKUP(C73,[1]ISO辞書!A:C,2,FALSE))</f>
+        <v>ETH</v>
+      </c>
+      <c r="B73" s="3" t="str">
+        <f>IF(C73="","",VLOOKUP(C73,[1]ISO辞書!A:C,3,FALSE))</f>
+        <v>Ethiopia</v>
+      </c>
+      <c r="C73" t="s">
+        <v>329</v>
+      </c>
+      <c r="D73" t="s">
+        <v>330</v>
+      </c>
+      <c r="E73" t="s">
+        <v>331</v>
+      </c>
+      <c r="F73" t="s">
+        <v>279</v>
+      </c>
+      <c r="G73" t="s">
+        <v>332</v>
+      </c>
+      <c r="J73" s="2" t="str">
+        <f>IF(G73="","",VLOOKUP(G73,[1]ISO辞書!A:B,2,FALSE))</f>
+        <v>CHN</v>
+      </c>
+      <c r="K73" s="2" t="str">
+        <f>IF(H73="","",VLOOKUP(H73,[1]ISO辞書!A:B,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="L73" s="2" t="str">
+        <f>IF(I73="","",VLOOKUP(I73,[1]ISO辞書!A:B,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="M73" s="3" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,J73:L73)</f>
+        <v>CHN</v>
+      </c>
+      <c r="N73" t="s">
+        <v>333</v>
+      </c>
+      <c r="O73" t="s">
+        <v>334</v>
+      </c>
+      <c r="P73" s="1">
+        <v>46115</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>159</v>
+      </c>
+      <c r="R73" t="s">
+        <v>335</v>
+      </c>
+      <c r="S73">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" hidden="1">
+      <c r="A74" s="2" t="str">
+        <f>IF(C74="","",VLOOKUP(C74,[1]ISO辞書!A:C,2,FALSE))</f>
+        <v>CHN</v>
+      </c>
+      <c r="B74" s="3" t="str">
+        <f>IF(C74="","",VLOOKUP(C74,[1]ISO辞書!A:C,3,FALSE))</f>
+        <v>China</v>
+      </c>
+      <c r="C74" t="s">
+        <v>332</v>
+      </c>
+      <c r="D74" t="s">
+        <v>347</v>
+      </c>
+      <c r="E74" t="s">
+        <v>348</v>
+      </c>
+      <c r="F74" t="s">
+        <v>170</v>
+      </c>
+      <c r="J74" s="2" t="str">
+        <f>IF(G74="","",VLOOKUP(G74,[1]ISO辞書!A:B,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="K74" s="2" t="str">
+        <f>IF(H74="","",VLOOKUP(H74,[1]ISO辞書!A:B,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="L74" s="2" t="str">
+        <f>IF(I74="","",VLOOKUP(I74,[1]ISO辞書!A:B,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="M74" s="3" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,J74:L74)</f>
+        <v/>
+      </c>
+      <c r="N74" t="s">
+        <v>165</v>
+      </c>
+      <c r="O74" t="s">
+        <v>79</v>
+      </c>
+      <c r="P74" s="1">
+        <v>46115</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>159</v>
+      </c>
+      <c r="R74" t="s">
+        <v>349</v>
+      </c>
+      <c r="S74">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" hidden="1">
+      <c r="A75" s="2" t="str">
+        <f>IF(C75="","",VLOOKUP(C75,[1]ISO辞書!A:C,2,FALSE))</f>
+        <v>UKR</v>
+      </c>
+      <c r="B75" s="3" t="str">
+        <f>IF(C75="","",VLOOKUP(C75,[1]ISO辞書!A:C,3,FALSE))</f>
+        <v>Ukraine</v>
+      </c>
+      <c r="C75" t="s">
+        <v>202</v>
+      </c>
+      <c r="D75" t="s">
+        <v>277</v>
+      </c>
+      <c r="E75" t="s">
+        <v>278</v>
+      </c>
+      <c r="F75" t="s">
+        <v>279</v>
+      </c>
+      <c r="G75" t="s">
+        <v>280</v>
+      </c>
+      <c r="J75" s="2" t="str">
+        <f>IF(G75="","",VLOOKUP(G75,[1]ISO辞書!A:B,2,FALSE))</f>
+        <v>TUR</v>
+      </c>
+      <c r="K75" s="2" t="str">
+        <f>IF(H75="","",VLOOKUP(H75,[1]ISO辞書!A:B,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="L75" s="2" t="str">
+        <f>IF(I75="","",VLOOKUP(I75,[1]ISO辞書!A:B,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="M75" s="3" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,J75:L75)</f>
+        <v>TUR</v>
+      </c>
+      <c r="N75" t="s">
+        <v>257</v>
+      </c>
+      <c r="O75" t="s">
+        <v>74</v>
+      </c>
+      <c r="P75" s="1">
+        <v>46116</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>159</v>
+      </c>
+      <c r="R75" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="S75">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" hidden="1">
+      <c r="A76" s="2" t="str">
+        <f>IF(C76="","",VLOOKUP(C76,[1]ISO辞書!A:C,2,FALSE))</f>
+        <v>IRN</v>
+      </c>
+      <c r="B76" s="3" t="str">
+        <f>IF(C76="","",VLOOKUP(C76,[1]ISO辞書!A:C,3,FALSE))</f>
+        <v>Iran</v>
+      </c>
+      <c r="C76" t="s">
+        <v>188</v>
+      </c>
+      <c r="D76" t="s">
+        <v>304</v>
+      </c>
+      <c r="F76" t="s">
+        <v>170</v>
+      </c>
+      <c r="J76" s="2" t="str">
+        <f>IF(G76="","",VLOOKUP(G76,[1]ISO辞書!A:B,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="K76" s="2" t="str">
+        <f>IF(H76="","",VLOOKUP(H76,[1]ISO辞書!A:B,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="L76" s="2" t="str">
+        <f>IF(I76="","",VLOOKUP(I76,[1]ISO辞書!A:B,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="M76" s="3" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,J76:L76)</f>
+        <v/>
+      </c>
+      <c r="N76" t="s">
+        <v>165</v>
+      </c>
+      <c r="O76" t="s">
+        <v>79</v>
+      </c>
+      <c r="P76" s="1">
+        <v>46116</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>159</v>
+      </c>
+      <c r="R76" t="s">
+        <v>305</v>
+      </c>
+      <c r="S76">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19">
+      <c r="A77" s="2" t="str">
+        <f>IF(C77="","",VLOOKUP(C77,[1]ISO辞書!A:C,2,FALSE))</f>
+        <v>IND</v>
+      </c>
+      <c r="B77" s="3" t="str">
+        <f>IF(C77="","",VLOOKUP(C77,[1]ISO辞書!A:C,3,FALSE))</f>
+        <v>India</v>
+      </c>
+      <c r="C77" t="s">
+        <v>306</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="F77" t="s">
+        <v>279</v>
+      </c>
+      <c r="G77" t="s">
+        <v>188</v>
+      </c>
+      <c r="J77" s="2" t="str">
+        <f>IF(G77="","",VLOOKUP(G77,[1]ISO辞書!A:B,2,FALSE))</f>
+        <v>IRN</v>
+      </c>
+      <c r="K77" s="2" t="str">
+        <f>IF(H77="","",VLOOKUP(H77,[1]ISO辞書!A:B,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="L77" s="2" t="str">
+        <f>IF(I77="","",VLOOKUP(I77,[1]ISO辞書!A:B,2,FALSE))</f>
+        <v/>
+      </c>
+      <c r="M77" s="3" t="str">
+        <f>_xlfn.TEXTJOIN(";",TRUE,J77:L77)</f>
+        <v>IRN</v>
+      </c>
+      <c r="N77" t="s">
+        <v>264</v>
+      </c>
+      <c r="O77" t="s">
+        <v>179</v>
+      </c>
+      <c r="P77" s="1">
+        <v>46116</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>159</v>
+      </c>
+      <c r="R77" t="s">
+        <v>308</v>
+      </c>
+      <c r="S77">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S1" xr:uid="{11153815-6F7F-462F-8165-5CE05A98A928}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S69">
+  <autoFilter ref="A1:S77" xr:uid="{11153815-6F7F-462F-8165-5CE05A98A928}">
+    <filterColumn colId="3">
+      <colorFilter dxfId="0"/>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S77">
       <sortCondition ref="P1"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="18"/>
   <hyperlinks>
     <hyperlink ref="R7" r:id="rId1" xr:uid="{B2B6E0E5-9387-475B-9F4B-ACDF1B43A472}"/>
-    <hyperlink ref="R35" r:id="rId2" xr:uid="{986F3D43-7B5A-48C0-A47B-A7E7119BCBD9}"/>
-    <hyperlink ref="R41" r:id="rId3" xr:uid="{CAB2C613-E685-436C-AA62-7678804484F9}"/>
-    <hyperlink ref="R42" r:id="rId4" xr:uid="{B735F61B-7109-4112-8AD5-8A0DE0EE4130}"/>
+    <hyperlink ref="R36" r:id="rId2" xr:uid="{986F3D43-7B5A-48C0-A47B-A7E7119BCBD9}"/>
+    <hyperlink ref="R46" r:id="rId3" xr:uid="{CAB2C613-E685-436C-AA62-7678804484F9}"/>
+    <hyperlink ref="R47" r:id="rId4" xr:uid="{B735F61B-7109-4112-8AD5-8A0DE0EE4130}"/>
+    <hyperlink ref="R58" r:id="rId5" xr:uid="{26955398-EA42-49E0-8883-3400EA7BDFE3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/データ管理用.xlsx
+++ b/public/data/データ管理用.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\world_map_project\world-map-news-app\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C18AB1-483A-4D9E-AF8A-3A66B3D77D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC9F65A-D081-4E94-8CF6-CA5AFB3AA2A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1344" yWindow="1032" windowWidth="21540" windowHeight="12012" xr2:uid="{17EB953A-2661-4049-9616-0D3098A3DA36}"/>
+    <workbookView xWindow="1272" yWindow="828" windowWidth="21540" windowHeight="12012" xr2:uid="{17EB953A-2661-4049-9616-0D3098A3DA36}"/>
   </bookViews>
   <sheets>
     <sheet name="events-入力用" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'events-入力用'!$A$1:$S$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'events-入力用'!$A$1:$S$373</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2613,22 +2613,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>イギリスがロシアセンス間に対し接近禁止を警告</t>
-    <rPh sb="11" eb="12">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>タイ</t>
-    </rPh>
-    <rPh sb="15" eb="19">
-      <t>セッキンキンシ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ケイコク</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>海底ケーブルやパイプラインの保護として警告</t>
     <rPh sb="0" eb="2">
       <t>カイテイ</t>
@@ -3240,6 +3224,22 @@
   </si>
   <si>
     <t>https://www.reuters.com/world/middle-east/israel-approves-dozens-new-settlements-west-bank-watchdog-says-2026-04-09/</t>
+  </si>
+  <si>
+    <t>イギリスがロシア潜水艦に対し接近禁止を警告</t>
+    <rPh sb="8" eb="11">
+      <t>センスイカン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="14" eb="18">
+      <t>セッキンキンシ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ケイコク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
   </si>
 </sst>
 </file>
@@ -3870,7 +3870,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3891,6 +3891,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3939,7 +3942,16 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="良い" xfId="6" builtinId="26" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC0E6F5"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -7036,11 +7048,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11153815-6F7F-462F-8165-5CE05A98A928}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:S373"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="2" width="0" style="2" hidden="1" customWidth="1"/>
-    <col min="4" max="5" width="34.19921875" customWidth="1"/>
+    <col min="4" max="4" width="34.19921875" style="7" customWidth="1"/>
+    <col min="5" max="5" width="34.19921875" customWidth="1"/>
     <col min="10" max="12" width="8.796875" style="2" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="8.796875" style="2"/>
     <col min="16" max="16" width="10.3984375" bestFit="1" customWidth="1"/>
@@ -7056,7 +7070,7 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
@@ -7105,7 +7119,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" hidden="1">
       <c r="A2" s="2" t="str">
         <f>IF(C2="","",VLOOKUP(C2,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>SVN</v>
@@ -7117,7 +7131,7 @@
       <c r="C2" t="s">
         <v>161</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="7" t="s">
         <v>162</v>
       </c>
       <c r="E2" t="s">
@@ -7139,7 +7153,7 @@
         <v/>
       </c>
       <c r="M2" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J2:L2)</f>
+        <f t="shared" ref="M2:M65" si="0">_xlfn.TEXTJOIN(";",TRUE,J2:L2)</f>
         <v/>
       </c>
       <c r="N2" t="s">
@@ -7161,7 +7175,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" hidden="1">
       <c r="A3" s="2" t="str">
         <f>IF(C3="","",VLOOKUP(C3,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>TCD</v>
@@ -7173,7 +7187,7 @@
       <c r="C3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E3" t="s">
@@ -7198,7 +7212,7 @@
         <v/>
       </c>
       <c r="M3" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J3:L3)</f>
+        <f t="shared" si="0"/>
         <v>SDN</v>
       </c>
       <c r="N3" t="s">
@@ -7220,7 +7234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" hidden="1">
       <c r="A4" s="2" t="str">
         <f>IF(C4="","",VLOOKUP(C4,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>CRI</v>
@@ -7232,7 +7246,7 @@
       <c r="C4" t="s">
         <v>59</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="7" t="s">
         <v>60</v>
       </c>
       <c r="E4" t="s">
@@ -7257,7 +7271,7 @@
         <v/>
       </c>
       <c r="M4" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J4:L4)</f>
+        <f t="shared" si="0"/>
         <v>USA</v>
       </c>
       <c r="N4" t="s">
@@ -7279,7 +7293,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" hidden="1">
       <c r="A5" s="2" t="str">
         <f>IF(C5="","",VLOOKUP(C5,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>CHN</v>
@@ -7291,7 +7305,7 @@
       <c r="C5" t="s">
         <v>71</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="7" t="s">
         <v>106</v>
       </c>
       <c r="E5" t="s">
@@ -7313,7 +7327,7 @@
         <v/>
       </c>
       <c r="M5" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J5:L5)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="N5" t="s">
@@ -7335,7 +7349,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" hidden="1">
       <c r="A6" s="2" t="str">
         <f>IF(C6="","",VLOOKUP(C6,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>ISR</v>
@@ -7347,7 +7361,7 @@
       <c r="C6" t="s">
         <v>153</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="7" t="s">
         <v>154</v>
       </c>
       <c r="E6" t="s">
@@ -7372,7 +7386,7 @@
         <v/>
       </c>
       <c r="M6" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J6:L6)</f>
+        <f t="shared" si="0"/>
         <v>LBN</v>
       </c>
       <c r="N6" t="s">
@@ -7394,7 +7408,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:19" hidden="1">
       <c r="A7" s="2" t="str">
         <f>IF(C7="","",VLOOKUP(C7,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>ITA</v>
@@ -7406,7 +7420,7 @@
       <c r="C7" t="s">
         <v>167</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="7" t="s">
         <v>168</v>
       </c>
       <c r="E7" t="s">
@@ -7428,7 +7442,7 @@
         <v/>
       </c>
       <c r="M7" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J7:L7)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="N7" t="s">
@@ -7450,7 +7464,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:19" hidden="1">
       <c r="A8" s="2" t="str">
         <f>IF(C8="","",VLOOKUP(C8,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>JPN</v>
@@ -7462,7 +7476,7 @@
       <c r="C8" t="s">
         <v>102</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="7" t="s">
         <v>103</v>
       </c>
       <c r="E8" t="s">
@@ -7487,7 +7501,7 @@
         <v/>
       </c>
       <c r="M8" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J8:L8)</f>
+        <f t="shared" si="0"/>
         <v>CHN</v>
       </c>
       <c r="N8" t="s">
@@ -7509,7 +7523,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:19" hidden="1">
       <c r="A9" s="2" t="str">
         <f>IF(C9="","",VLOOKUP(C9,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>ISR</v>
@@ -7521,7 +7535,7 @@
       <c r="C9" t="s">
         <v>67</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="7" t="s">
         <v>131</v>
       </c>
       <c r="E9" t="s">
@@ -7546,7 +7560,7 @@
         <v/>
       </c>
       <c r="M9" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J9:L9)</f>
+        <f t="shared" si="0"/>
         <v>LBN</v>
       </c>
       <c r="N9" t="s">
@@ -7568,7 +7582,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:19" hidden="1">
       <c r="A10" s="2" t="str">
         <f>IF(C10="","",VLOOKUP(C10,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>EU</v>
@@ -7580,7 +7594,7 @@
       <c r="C10" t="s">
         <v>42</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="7" t="s">
         <v>147</v>
       </c>
       <c r="E10" t="s">
@@ -7602,7 +7616,7 @@
         <v/>
       </c>
       <c r="M10" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J10:L10)</f>
+        <f t="shared" si="0"/>
         <v>AUS</v>
       </c>
       <c r="N10" t="s">
@@ -7624,7 +7638,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:19" hidden="1">
       <c r="A11" s="2" t="str">
         <f>IF(C11="","",VLOOKUP(C11,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>MEX</v>
@@ -7636,7 +7650,7 @@
       <c r="C11" t="s">
         <v>50</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="7" t="s">
         <v>51</v>
       </c>
       <c r="E11" t="s">
@@ -7661,7 +7675,7 @@
         <v/>
       </c>
       <c r="M11" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J11:L11)</f>
+        <f t="shared" si="0"/>
         <v>CUB</v>
       </c>
       <c r="N11" t="s">
@@ -7683,7 +7697,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:19" hidden="1">
       <c r="A12" s="2" t="str">
         <f>IF(C12="","",VLOOKUP(C12,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>CYP</v>
@@ -7695,7 +7709,7 @@
       <c r="C12" t="s">
         <v>117</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="7" t="s">
         <v>118</v>
       </c>
       <c r="E12" t="s">
@@ -7720,7 +7734,7 @@
         <v/>
       </c>
       <c r="M12" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J12:L12)</f>
+        <f t="shared" si="0"/>
         <v>GBR</v>
       </c>
       <c r="N12" t="s">
@@ -7742,7 +7756,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:19" hidden="1">
       <c r="A13" s="2" t="str">
         <f>IF(C13="","",VLOOKUP(C13,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>DNK</v>
@@ -7754,7 +7768,7 @@
       <c r="C13" t="s">
         <v>122</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="7" t="s">
         <v>123</v>
       </c>
       <c r="E13" t="s">
@@ -7776,7 +7790,7 @@
         <v/>
       </c>
       <c r="M13" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J13:L13)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="N13" t="s">
@@ -7798,7 +7812,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:19" hidden="1">
       <c r="A14" s="2" t="str">
         <f>IF(C14="","",VLOOKUP(C14,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>GBR</v>
@@ -7810,7 +7824,7 @@
       <c r="C14" t="s">
         <v>120</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="7" t="s">
         <v>135</v>
       </c>
       <c r="E14" t="s">
@@ -7835,7 +7849,7 @@
         <v/>
       </c>
       <c r="M14" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J14:L14)</f>
+        <f t="shared" si="0"/>
         <v>TUR</v>
       </c>
       <c r="N14" t="s">
@@ -7857,7 +7871,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:19" hidden="1">
       <c r="A15" s="2" t="str">
         <f>IF(C15="","",VLOOKUP(C15,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>KEN</v>
@@ -7869,7 +7883,7 @@
       <c r="C15" t="s">
         <v>143</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="7" t="s">
         <v>144</v>
       </c>
       <c r="E15" t="s">
@@ -7894,7 +7908,7 @@
         <v/>
       </c>
       <c r="M15" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J15:L15)</f>
+        <f t="shared" si="0"/>
         <v>CHN</v>
       </c>
       <c r="N15" t="s">
@@ -7916,7 +7930,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:19" hidden="1">
       <c r="A16" s="2" t="str">
         <f>IF(C16="","",VLOOKUP(C16,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>USA</v>
@@ -7928,7 +7942,7 @@
       <c r="C16" t="s">
         <v>28</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="7" t="s">
         <v>55</v>
       </c>
       <c r="E16" t="s">
@@ -7953,7 +7967,7 @@
         <v/>
       </c>
       <c r="M16" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J16:L16)</f>
+        <f t="shared" si="0"/>
         <v>VEN</v>
       </c>
       <c r="N16" t="s">
@@ -7975,7 +7989,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:19" hidden="1">
       <c r="A17" s="2" t="str">
         <f>IF(C17="","",VLOOKUP(C17,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>PAK</v>
@@ -7987,7 +8001,7 @@
       <c r="C17" t="s">
         <v>91</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="7" t="s">
         <v>92</v>
       </c>
       <c r="E17" t="s">
@@ -8012,7 +8026,7 @@
         <v/>
       </c>
       <c r="M17" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J17:L17)</f>
+        <f t="shared" si="0"/>
         <v>AFG</v>
       </c>
       <c r="N17" t="s">
@@ -8034,7 +8048,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:19" hidden="1">
       <c r="A18" s="2" t="str">
         <f>IF(C18="","",VLOOKUP(C18,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>USA</v>
@@ -8046,7 +8060,7 @@
       <c r="C18" t="s">
         <v>28</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="7" t="s">
         <v>96</v>
       </c>
       <c r="E18" t="s">
@@ -8071,7 +8085,7 @@
         <v/>
       </c>
       <c r="M18" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J18:L18)</f>
+        <f t="shared" si="0"/>
         <v>IRN</v>
       </c>
       <c r="N18" t="s">
@@ -8093,7 +8107,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:19" hidden="1">
       <c r="A19" s="2" t="str">
         <f>IF(C19="","",VLOOKUP(C19,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>IRN</v>
@@ -8105,7 +8119,7 @@
       <c r="C19" t="s">
         <v>66</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="7" t="s">
         <v>99</v>
       </c>
       <c r="E19" t="s">
@@ -8133,7 +8147,7 @@
         <v/>
       </c>
       <c r="M19" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J19:L19)</f>
+        <f t="shared" si="0"/>
         <v>USA;PAK</v>
       </c>
       <c r="N19" t="s">
@@ -8155,7 +8169,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:19" hidden="1">
       <c r="A20" s="2" t="str">
         <f>IF(C20="","",VLOOKUP(C20,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>UKR</v>
@@ -8167,7 +8181,7 @@
       <c r="C20" t="s">
         <v>109</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="7" t="s">
         <v>113</v>
       </c>
       <c r="E20" t="s">
@@ -8192,7 +8206,7 @@
         <v/>
       </c>
       <c r="M20" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J20:L20)</f>
+        <f t="shared" si="0"/>
         <v>RUS</v>
       </c>
       <c r="N20" t="s">
@@ -8214,7 +8228,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:19" hidden="1">
       <c r="A21" s="2" t="str">
         <f>IF(C21="","",VLOOKUP(C21,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>USA</v>
@@ -8226,7 +8240,7 @@
       <c r="C21" t="s">
         <v>28</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="7" t="s">
         <v>29</v>
       </c>
       <c r="E21" t="s">
@@ -8251,7 +8265,7 @@
         <v/>
       </c>
       <c r="M21" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J21:L21)</f>
+        <f t="shared" si="0"/>
         <v>CUB</v>
       </c>
       <c r="N21" t="s">
@@ -8273,7 +8287,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:19" hidden="1">
       <c r="A22" s="2" t="str">
         <f>IF(C22="","",VLOOKUP(C22,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>CAN</v>
@@ -8285,7 +8299,7 @@
       <c r="C22" t="s">
         <v>33</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="7" t="s">
         <v>34</v>
       </c>
       <c r="E22" t="s">
@@ -8316,7 +8330,7 @@
         <v>PRY</v>
       </c>
       <c r="M22" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J22:L22)</f>
+        <f t="shared" si="0"/>
         <v>BRA;ARG;PRY</v>
       </c>
       <c r="N22" t="s">
@@ -8338,7 +8352,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:19" hidden="1">
       <c r="A23" s="2" t="str">
         <f>IF(C23="","",VLOOKUP(C23,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>EU</v>
@@ -8350,7 +8364,7 @@
       <c r="C23" t="s">
         <v>42</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="7" t="s">
         <v>43</v>
       </c>
       <c r="E23" t="s">
@@ -8375,7 +8389,7 @@
         <v/>
       </c>
       <c r="M23" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J23:L23)</f>
+        <f t="shared" si="0"/>
         <v>CPTPP</v>
       </c>
       <c r="N23" t="s">
@@ -8397,7 +8411,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:19" hidden="1">
       <c r="A24" s="2" t="str">
         <f>IF(C24="","",VLOOKUP(C24,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>CAN</v>
@@ -8409,7 +8423,7 @@
       <c r="C24" t="s">
         <v>33</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="7" t="s">
         <v>47</v>
       </c>
       <c r="E24" t="s">
@@ -8440,7 +8454,7 @@
         <v>PRY</v>
       </c>
       <c r="M24" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J24:L24)</f>
+        <f t="shared" si="0"/>
         <v>BRA;ARG;PRY</v>
       </c>
       <c r="N24" t="s">
@@ -8462,7 +8476,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:19" hidden="1">
       <c r="A25" s="2" t="str">
         <f>IF(C25="","",VLOOKUP(C25,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>NPL</v>
@@ -8474,7 +8488,7 @@
       <c r="C25" t="s">
         <v>76</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="7" t="s">
         <v>77</v>
       </c>
       <c r="E25" t="s">
@@ -8496,7 +8510,7 @@
         <v/>
       </c>
       <c r="M25" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J25:L25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="N25" t="s">
@@ -8518,7 +8532,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:19" hidden="1">
       <c r="A26" s="2" t="str">
         <f>IF(C26="","",VLOOKUP(C26,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>PRK</v>
@@ -8530,7 +8544,7 @@
       <c r="C26" t="s">
         <v>86</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="7" t="s">
         <v>87</v>
       </c>
       <c r="E26" t="s">
@@ -8555,7 +8569,7 @@
         <v/>
       </c>
       <c r="M26" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J26:L26)</f>
+        <f t="shared" si="0"/>
         <v>BLR</v>
       </c>
       <c r="N26" t="s">
@@ -8577,7 +8591,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:19" hidden="1">
       <c r="A27" s="2" t="str">
         <f>IF(C27="","",VLOOKUP(C27,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>UKR</v>
@@ -8589,7 +8603,7 @@
       <c r="C27" t="s">
         <v>109</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="7" t="s">
         <v>110</v>
       </c>
       <c r="E27" t="s">
@@ -8614,7 +8628,7 @@
         <v/>
       </c>
       <c r="M27" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J27:L27)</f>
+        <f t="shared" si="0"/>
         <v>SAU</v>
       </c>
       <c r="N27" t="s">
@@ -8636,7 +8650,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:19" hidden="1">
       <c r="A28" s="2" t="str">
         <f>IF(C28="","",VLOOKUP(C28,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>COD</v>
@@ -8648,7 +8662,7 @@
       <c r="C28" t="s">
         <v>139</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="7" t="s">
         <v>140</v>
       </c>
       <c r="E28" t="s">
@@ -8673,7 +8687,7 @@
         <v/>
       </c>
       <c r="M28" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J28:L28)</f>
+        <f t="shared" si="0"/>
         <v>CHN</v>
       </c>
       <c r="N28" t="s">
@@ -8695,7 +8709,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:19" hidden="1">
       <c r="A29" s="2" t="str">
         <f>IF(C29="","",VLOOKUP(C29,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>CHN</v>
@@ -8707,7 +8721,7 @@
       <c r="C29" t="s">
         <v>71</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="7" t="s">
         <v>72</v>
       </c>
       <c r="E29" t="s">
@@ -8732,7 +8746,7 @@
         <v/>
       </c>
       <c r="M29" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J29:L29)</f>
+        <f t="shared" si="0"/>
         <v>PHL</v>
       </c>
       <c r="N29" t="s">
@@ -8754,7 +8768,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:19" hidden="1">
       <c r="A30" s="2" t="str">
         <f>IF(C30="","",VLOOKUP(C30,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>IDN</v>
@@ -8766,7 +8780,7 @@
       <c r="C30" t="s">
         <v>82</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="7" t="s">
         <v>83</v>
       </c>
       <c r="E30" t="s">
@@ -8788,7 +8802,7 @@
         <v/>
       </c>
       <c r="M30" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J30:L30)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="N30" t="s">
@@ -8810,7 +8824,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:19" hidden="1">
       <c r="A31" s="2" t="str">
         <f>IF(C31="","",VLOOKUP(C31,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>UKR</v>
@@ -8822,7 +8836,7 @@
       <c r="C31" t="s">
         <v>109</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="7" t="s">
         <v>126</v>
       </c>
       <c r="E31" t="s">
@@ -8850,7 +8864,7 @@
         <v/>
       </c>
       <c r="M31" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J31:L31)</f>
+        <f t="shared" si="0"/>
         <v>ARE;QAT</v>
       </c>
       <c r="N31" t="s">
@@ -8872,7 +8886,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:19" hidden="1">
       <c r="A32" s="2" t="str">
         <f>IF(C32="","",VLOOKUP(C32,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>NPL</v>
@@ -8884,7 +8898,7 @@
       <c r="C32" t="s">
         <v>217</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="7" t="s">
         <v>218</v>
       </c>
       <c r="E32" t="s">
@@ -8906,7 +8920,7 @@
         <v/>
       </c>
       <c r="M32" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J32:L32)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="N32" t="s">
@@ -8928,7 +8942,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:19">
+    <row r="33" spans="1:19" hidden="1">
       <c r="A33" s="2" t="str">
         <f>IF(C33="","",VLOOKUP(C33,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>YEM</v>
@@ -8940,7 +8954,7 @@
       <c r="C33" t="s">
         <v>63</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="7" t="s">
         <v>64</v>
       </c>
       <c r="E33" t="s">
@@ -8971,7 +8985,7 @@
         <v>ISR</v>
       </c>
       <c r="M33" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J33:L33)</f>
+        <f t="shared" si="0"/>
         <v>IRN;USA;ISR</v>
       </c>
       <c r="N33" t="s">
@@ -8993,7 +9007,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:19" hidden="1">
       <c r="A34" s="2" t="str">
         <f>IF(C34="","",VLOOKUP(C34,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>UKR</v>
@@ -9005,7 +9019,7 @@
       <c r="C34" t="s">
         <v>202</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="7" t="s">
         <v>203</v>
       </c>
       <c r="E34" t="s">
@@ -9030,7 +9044,7 @@
         <v/>
       </c>
       <c r="M34" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J34:L34)</f>
+        <f t="shared" si="0"/>
         <v>JOR</v>
       </c>
       <c r="N34" t="s">
@@ -9052,7 +9066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" spans="1:19" hidden="1">
       <c r="A35" s="2" t="str">
         <f>IF(C35="","",VLOOKUP(C35,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>EGY</v>
@@ -9064,7 +9078,7 @@
       <c r="C35" t="s">
         <v>259</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="7" t="s">
         <v>260</v>
       </c>
       <c r="F35" t="s">
@@ -9083,7 +9097,7 @@
         <v/>
       </c>
       <c r="M35" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J35:L35)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="N35" t="s">
@@ -9105,7 +9119,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:19">
+    <row r="36" spans="1:19" hidden="1">
       <c r="A36" s="2" t="str">
         <f>IF(C36="","",VLOOKUP(C36,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>CUB</v>
@@ -9117,7 +9131,7 @@
       <c r="C36" t="s">
         <v>172</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="7" t="s">
         <v>173</v>
       </c>
       <c r="E36" t="s">
@@ -9145,7 +9159,7 @@
         <v/>
       </c>
       <c r="M36" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J36:L36)</f>
+        <f t="shared" si="0"/>
         <v>RUS;USA</v>
       </c>
       <c r="N36" t="s">
@@ -9167,7 +9181,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:19">
+    <row r="37" spans="1:19" hidden="1">
       <c r="A37" s="2" t="str">
         <f>IF(C37="","",VLOOKUP(C37,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>LBN</v>
@@ -9179,7 +9193,7 @@
       <c r="C37" t="s">
         <v>157</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="7" t="s">
         <v>190</v>
       </c>
       <c r="E37" t="s">
@@ -9204,7 +9218,7 @@
         <v/>
       </c>
       <c r="M37" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J37:L37)</f>
+        <f t="shared" si="0"/>
         <v>ISR</v>
       </c>
       <c r="N37" t="s">
@@ -9226,7 +9240,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:19">
+    <row r="38" spans="1:19" hidden="1">
       <c r="A38" s="2" t="str">
         <f>IF(C38="","",VLOOKUP(C38,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>RUS</v>
@@ -9238,7 +9252,7 @@
       <c r="C38" t="s">
         <v>176</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="7" t="s">
         <v>207</v>
       </c>
       <c r="E38" t="s">
@@ -9263,7 +9277,7 @@
         <v/>
       </c>
       <c r="M38" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J38:L38)</f>
+        <f t="shared" si="0"/>
         <v>GBR</v>
       </c>
       <c r="N38" t="s">
@@ -9285,7 +9299,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:19">
+    <row r="39" spans="1:19" hidden="1">
       <c r="A39" s="2" t="str">
         <f>IF(C39="","",VLOOKUP(C39,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>AFG</v>
@@ -9297,7 +9311,7 @@
       <c r="C39" t="s">
         <v>221</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="7" t="s">
         <v>222</v>
       </c>
       <c r="E39" t="s">
@@ -9322,7 +9336,7 @@
         <v/>
       </c>
       <c r="M39" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J39:L39)</f>
+        <f t="shared" si="0"/>
         <v>PAK</v>
       </c>
       <c r="N39" t="s">
@@ -9344,7 +9358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:19">
+    <row r="40" spans="1:19" hidden="1">
       <c r="A40" s="2" t="str">
         <f>IF(C40="","",VLOOKUP(C40,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>XKK</v>
@@ -9356,7 +9370,7 @@
       <c r="C40" t="s">
         <v>229</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="7" t="s">
         <v>230</v>
       </c>
       <c r="E40" t="s">
@@ -9387,7 +9401,7 @@
         <v>PSE</v>
       </c>
       <c r="M40" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J40:L40)</f>
+        <f t="shared" si="0"/>
         <v>USA;ISR;PSE</v>
       </c>
       <c r="N40" t="s">
@@ -9409,7 +9423,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:19">
+    <row r="41" spans="1:19" hidden="1">
       <c r="A41" s="2" t="str">
         <f>IF(C41="","",VLOOKUP(C41,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>PAK</v>
@@ -9421,7 +9435,7 @@
       <c r="C41" t="s">
         <v>225</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D41" s="7" t="s">
         <v>234</v>
       </c>
       <c r="E41" t="s">
@@ -9446,7 +9460,7 @@
         <v/>
       </c>
       <c r="M41" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J41:L41)</f>
+        <f t="shared" si="0"/>
         <v>AFG</v>
       </c>
       <c r="N41" t="s">
@@ -9468,7 +9482,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:19">
+    <row r="42" spans="1:19" hidden="1">
       <c r="A42" s="2" t="str">
         <f>IF(C42="","",VLOOKUP(C42,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>USA</v>
@@ -9480,7 +9494,7 @@
       <c r="C42" t="s">
         <v>177</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="7" t="s">
         <v>254</v>
       </c>
       <c r="E42" t="s">
@@ -9505,7 +9519,7 @@
         <v/>
       </c>
       <c r="M42" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J42:L42)</f>
+        <f t="shared" si="0"/>
         <v>VEN</v>
       </c>
       <c r="N42" t="s">
@@ -9527,7 +9541,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:19">
+    <row r="43" spans="1:19" hidden="1">
       <c r="A43" s="2" t="str">
         <f>IF(C43="","",VLOOKUP(C43,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>EGY</v>
@@ -9539,7 +9553,7 @@
       <c r="C43" t="s">
         <v>259</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D43" s="7" t="s">
         <v>262</v>
       </c>
       <c r="F43" t="s">
@@ -9561,7 +9575,7 @@
         <v/>
       </c>
       <c r="M43" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J43:L43)</f>
+        <f t="shared" si="0"/>
         <v>CYP</v>
       </c>
       <c r="N43" t="s">
@@ -9583,7 +9597,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:19">
+    <row r="44" spans="1:19" hidden="1">
       <c r="A44" s="2" t="str">
         <f>IF(C44="","",VLOOKUP(C44,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>SOM</v>
@@ -9595,7 +9609,7 @@
       <c r="C44" t="s">
         <v>266</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="7" t="s">
         <v>267</v>
       </c>
       <c r="E44" t="s">
@@ -9617,7 +9631,7 @@
         <v/>
       </c>
       <c r="M44" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J44:L44)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="N44" t="s">
@@ -9639,7 +9653,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:19">
+    <row r="45" spans="1:19" hidden="1">
       <c r="A45" s="2" t="str">
         <f>IF(C45="","",VLOOKUP(C45,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>IRN</v>
@@ -9651,7 +9665,7 @@
       <c r="C45" t="s">
         <v>188</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="7" t="s">
         <v>270</v>
       </c>
       <c r="E45" t="s">
@@ -9676,7 +9690,7 @@
         <v/>
       </c>
       <c r="M45" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J45:L45)</f>
+        <f t="shared" si="0"/>
         <v>ISR</v>
       </c>
       <c r="N45" t="s">
@@ -9698,7 +9712,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:19">
+    <row r="46" spans="1:19" hidden="1">
       <c r="A46" s="2" t="str">
         <f>IF(C46="","",VLOOKUP(C46,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>PRY</v>
@@ -9710,7 +9724,7 @@
       <c r="C46" t="s">
         <v>182</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="7" t="s">
         <v>183</v>
       </c>
       <c r="E46" t="s">
@@ -9732,7 +9746,7 @@
         <v/>
       </c>
       <c r="M46" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J46:L46)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="N46" t="s">
@@ -9754,7 +9768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:19">
+    <row r="47" spans="1:19" hidden="1">
       <c r="A47" s="2" t="str">
         <f>IF(C47="","",VLOOKUP(C47,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>USA</v>
@@ -9766,7 +9780,7 @@
       <c r="C47" t="s">
         <v>177</v>
       </c>
-      <c r="D47" s="6" t="s">
+      <c r="D47" s="7" t="s">
         <v>186</v>
       </c>
       <c r="E47" t="s">
@@ -9791,7 +9805,7 @@
         <v/>
       </c>
       <c r="M47" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J47:L47)</f>
+        <f t="shared" si="0"/>
         <v>IRN</v>
       </c>
       <c r="N47" t="s">
@@ -9813,7 +9827,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:19">
+    <row r="48" spans="1:19" hidden="1">
       <c r="A48" s="2" t="str">
         <f>IF(C48="","",VLOOKUP(C48,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>GBR</v>
@@ -9825,7 +9839,7 @@
       <c r="C48" t="s">
         <v>193</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="7" t="s">
         <v>194</v>
       </c>
       <c r="E48" t="s">
@@ -9850,7 +9864,7 @@
         <v/>
       </c>
       <c r="M48" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J48:L48)</f>
+        <f t="shared" si="0"/>
         <v>SYR</v>
       </c>
       <c r="N48" t="s">
@@ -9872,7 +9886,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:19">
+    <row r="49" spans="1:19" hidden="1">
       <c r="A49" s="2" t="str">
         <f>IF(C49="","",VLOOKUP(C49,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>ISR</v>
@@ -9884,7 +9898,7 @@
       <c r="C49" t="s">
         <v>153</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="7" t="s">
         <v>199</v>
       </c>
       <c r="E49" t="s">
@@ -9909,7 +9923,7 @@
         <v/>
       </c>
       <c r="M49" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J49:L49)</f>
+        <f t="shared" si="0"/>
         <v>LBN</v>
       </c>
       <c r="N49" t="s">
@@ -9931,7 +9945,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:19">
+    <row r="50" spans="1:19" hidden="1">
       <c r="A50" s="2" t="str">
         <f>IF(C50="","",VLOOKUP(C50,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>ITA</v>
@@ -9943,7 +9957,7 @@
       <c r="C50" t="s">
         <v>167</v>
       </c>
-      <c r="D50" s="6" t="s">
+      <c r="D50" s="7" t="s">
         <v>210</v>
       </c>
       <c r="E50" t="s">
@@ -9968,7 +9982,7 @@
         <v/>
       </c>
       <c r="M50" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J50:L50)</f>
+        <f t="shared" si="0"/>
         <v>USA</v>
       </c>
       <c r="N50" t="s">
@@ -9990,7 +10004,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:19">
+    <row r="51" spans="1:19" hidden="1">
       <c r="A51" s="2" t="str">
         <f>IF(C51="","",VLOOKUP(C51,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>FRA</v>
@@ -10002,7 +10016,7 @@
       <c r="C51" t="s">
         <v>213</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="D51" s="7" t="s">
         <v>214</v>
       </c>
       <c r="E51" t="s">
@@ -10030,7 +10044,7 @@
         <v/>
       </c>
       <c r="M51" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J51:L51)</f>
+        <f t="shared" si="0"/>
         <v>ISR;USA</v>
       </c>
       <c r="N51" t="s">
@@ -10052,7 +10066,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:19">
+    <row r="52" spans="1:19" hidden="1">
       <c r="A52" s="2" t="str">
         <f>IF(C52="","",VLOOKUP(C52,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>THA</v>
@@ -10064,7 +10078,7 @@
       <c r="C52" t="s">
         <v>237</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D52" s="7" t="s">
         <v>238</v>
       </c>
       <c r="E52" t="s">
@@ -10086,7 +10100,7 @@
         <v/>
       </c>
       <c r="M52" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J52:L52)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="N52" t="s">
@@ -10108,7 +10122,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:19">
+    <row r="53" spans="1:19" hidden="1">
       <c r="A53" s="2" t="str">
         <f>IF(C53="","",VLOOKUP(C53,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>KOR</v>
@@ -10120,7 +10134,7 @@
       <c r="C53" t="s">
         <v>241</v>
       </c>
-      <c r="D53" s="6" t="s">
+      <c r="D53" s="7" t="s">
         <v>242</v>
       </c>
       <c r="E53" t="s">
@@ -10142,7 +10156,7 @@
         <v/>
       </c>
       <c r="M53" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J53:L53)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="N53" t="s">
@@ -10164,7 +10178,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:19">
+    <row r="54" spans="1:19" hidden="1">
       <c r="A54" s="2" t="str">
         <f>IF(C54="","",VLOOKUP(C54,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>MNG</v>
@@ -10176,7 +10190,7 @@
       <c r="C54" t="s">
         <v>251</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" s="7" t="s">
         <v>252</v>
       </c>
       <c r="F54" t="s">
@@ -10195,7 +10209,7 @@
         <v/>
       </c>
       <c r="M54" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J54:L54)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="N54" t="s">
@@ -10217,7 +10231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:19">
+    <row r="55" spans="1:19" hidden="1">
       <c r="A55" s="2" t="str">
         <f>IF(C55="","",VLOOKUP(C55,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>DEU</v>
@@ -10229,7 +10243,7 @@
       <c r="C55" t="s">
         <v>273</v>
       </c>
-      <c r="D55" s="6" t="s">
+      <c r="D55" s="7" t="s">
         <v>274</v>
       </c>
       <c r="E55" t="s">
@@ -10251,7 +10265,7 @@
         <v/>
       </c>
       <c r="M55" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J55:L55)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="N55" t="s">
@@ -10273,7 +10287,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:19">
+    <row r="56" spans="1:19" hidden="1">
       <c r="A56" s="2" t="str">
         <f>IF(C56="","",VLOOKUP(C56,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>SRB</v>
@@ -10285,7 +10299,7 @@
       <c r="C56" t="s">
         <v>300</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D56" s="7" t="s">
         <v>301</v>
       </c>
       <c r="E56" t="s">
@@ -10307,7 +10321,7 @@
         <v/>
       </c>
       <c r="M56" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J56:L56)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="N56" t="s">
@@ -10329,7 +10343,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:19">
+    <row r="57" spans="1:19" hidden="1">
       <c r="A57" s="2" t="str">
         <f>IF(C57="","",VLOOKUP(C57,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>SYR</v>
@@ -10341,7 +10355,7 @@
       <c r="C57" t="s">
         <v>197</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D57" s="7" t="s">
         <v>317</v>
       </c>
       <c r="E57" t="s">
@@ -10372,7 +10386,7 @@
         <v>ISR</v>
       </c>
       <c r="M57" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J57:L57)</f>
+        <f t="shared" si="0"/>
         <v>IRN;USA;ISR</v>
       </c>
       <c r="N57" t="s">
@@ -10394,7 +10408,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:19">
+    <row r="58" spans="1:19" hidden="1">
       <c r="A58" s="2" t="str">
         <f>IF(C58="","",VLOOKUP(C58,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>MEX</v>
@@ -10406,7 +10420,7 @@
       <c r="C58" t="s">
         <v>248</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D58" s="7" t="s">
         <v>249</v>
       </c>
       <c r="F58" t="s">
@@ -10425,7 +10439,7 @@
         <v/>
       </c>
       <c r="M58" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J58:L58)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="N58" t="s">
@@ -10447,7 +10461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:19">
+    <row r="59" spans="1:19" hidden="1">
       <c r="A59" s="2" t="str">
         <f>IF(C59="","",VLOOKUP(C59,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>USA</v>
@@ -10459,7 +10473,7 @@
       <c r="C59" t="s">
         <v>177</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D59" s="7" t="s">
         <v>296</v>
       </c>
       <c r="E59" t="s">
@@ -10481,7 +10495,7 @@
         <v/>
       </c>
       <c r="M59" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J59:L59)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="N59" t="s">
@@ -10500,7 +10514,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:19">
+    <row r="60" spans="1:19" hidden="1">
       <c r="A60" s="2" t="str">
         <f>IF(C60="","",VLOOKUP(C60,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>LBN</v>
@@ -10512,7 +10526,7 @@
       <c r="C60" t="s">
         <v>157</v>
       </c>
-      <c r="D60" s="6" t="s">
+      <c r="D60" s="7" t="s">
         <v>315</v>
       </c>
       <c r="F60" t="s">
@@ -10534,7 +10548,7 @@
         <v/>
       </c>
       <c r="M60" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J60:L60)</f>
+        <f t="shared" si="0"/>
         <v>ISR</v>
       </c>
       <c r="N60" t="s">
@@ -10556,7 +10570,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:19">
+    <row r="61" spans="1:19" hidden="1">
       <c r="A61" s="2" t="str">
         <f>IF(C61="","",VLOOKUP(C61,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>ARG</v>
@@ -10568,7 +10582,7 @@
       <c r="C61" t="s">
         <v>320</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D61" s="7" t="s">
         <v>321</v>
       </c>
       <c r="E61" t="s">
@@ -10593,7 +10607,7 @@
         <v/>
       </c>
       <c r="M61" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J61:L61)</f>
+        <f t="shared" si="0"/>
         <v>IRN</v>
       </c>
       <c r="N61" t="s">
@@ -10615,7 +10629,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:19">
+    <row r="62" spans="1:19" hidden="1">
       <c r="A62" s="2" t="str">
         <f>IF(C62="","",VLOOKUP(C62,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>EU</v>
@@ -10627,7 +10641,7 @@
       <c r="C62" t="s">
         <v>343</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D62" s="7" t="s">
         <v>344</v>
       </c>
       <c r="E62" t="s">
@@ -10652,7 +10666,7 @@
         <v/>
       </c>
       <c r="M62" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J62:L62)</f>
+        <f t="shared" si="0"/>
         <v>CUB</v>
       </c>
       <c r="N62" t="s">
@@ -10674,7 +10688,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:19">
+    <row r="63" spans="1:19" hidden="1">
       <c r="A63" s="2" t="str">
         <f>IF(C63="","",VLOOKUP(C63,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>TCD</v>
@@ -10686,7 +10700,7 @@
       <c r="C63" t="s">
         <v>407</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="7" t="s">
         <v>408</v>
       </c>
       <c r="F63" t="s">
@@ -10708,7 +10722,7 @@
         <v/>
       </c>
       <c r="M63" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J63:L63)</f>
+        <f t="shared" si="0"/>
         <v>HTI</v>
       </c>
       <c r="N63" t="s">
@@ -10730,7 +10744,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:19">
+    <row r="64" spans="1:19" hidden="1">
       <c r="A64" s="2" t="str">
         <f>IF(C64="","",VLOOKUP(C64,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>RUS</v>
@@ -10742,7 +10756,7 @@
       <c r="C64" t="s">
         <v>176</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D64" s="7" t="s">
         <v>291</v>
       </c>
       <c r="F64" t="s">
@@ -10764,7 +10778,7 @@
         <v/>
       </c>
       <c r="M64" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J64:L64)</f>
+        <f t="shared" si="0"/>
         <v>UKR</v>
       </c>
       <c r="N64" t="s">
@@ -10786,7 +10800,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:19">
+    <row r="65" spans="1:19" hidden="1">
       <c r="A65" s="2" t="str">
         <f>IF(C65="","",VLOOKUP(C65,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>GBR</v>
@@ -10798,7 +10812,7 @@
       <c r="C65" t="s">
         <v>193</v>
       </c>
-      <c r="D65" s="6" t="s">
+      <c r="D65" s="7" t="s">
         <v>293</v>
       </c>
       <c r="E65" t="s">
@@ -10829,7 +10843,7 @@
         <v>ARE</v>
       </c>
       <c r="M65" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J65:L65)</f>
+        <f t="shared" si="0"/>
         <v>DEU;FRA;ARE</v>
       </c>
       <c r="N65" t="s">
@@ -10851,7 +10865,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:19">
+    <row r="66" spans="1:19" hidden="1">
       <c r="A66" s="2" t="str">
         <f>IF(C66="","",VLOOKUP(C66,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>BFA</v>
@@ -10863,7 +10877,7 @@
       <c r="C66" t="s">
         <v>324</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D66" s="7" t="s">
         <v>325</v>
       </c>
       <c r="E66" t="s">
@@ -10888,7 +10902,7 @@
         <v/>
       </c>
       <c r="M66" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J66:L66)</f>
+        <f t="shared" ref="M66:M129" si="1">_xlfn.TEXTJOIN(";",TRUE,J66:L66)</f>
         <v>MLI</v>
       </c>
       <c r="N66" t="s">
@@ -10910,7 +10924,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:19">
+    <row r="67" spans="1:19" hidden="1">
       <c r="A67" s="2" t="str">
         <f>IF(C67="","",VLOOKUP(C67,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>COD</v>
@@ -10922,7 +10936,7 @@
       <c r="C67" t="s">
         <v>336</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D67" s="7" t="s">
         <v>337</v>
       </c>
       <c r="F67" t="s">
@@ -10941,7 +10955,7 @@
         <v/>
       </c>
       <c r="M67" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J67:L67)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N67" t="s">
@@ -10963,7 +10977,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:19">
+    <row r="68" spans="1:19" hidden="1">
       <c r="A68" s="2" t="str">
         <f>IF(C68="","",VLOOKUP(C68,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>USA</v>
@@ -10975,7 +10989,7 @@
       <c r="C68" t="s">
         <v>177</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D68" s="7" t="s">
         <v>340</v>
       </c>
       <c r="E68" t="s">
@@ -11000,7 +11014,7 @@
         <v/>
       </c>
       <c r="M68" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J68:L68)</f>
+        <f t="shared" si="1"/>
         <v>VEN</v>
       </c>
       <c r="N68" t="s">
@@ -11022,7 +11036,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:19">
+    <row r="69" spans="1:19" hidden="1">
       <c r="A69" s="2" t="str">
         <f>IF(C69="","",VLOOKUP(C69,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>NZL</v>
@@ -11034,7 +11048,7 @@
       <c r="C69" t="s">
         <v>350</v>
       </c>
-      <c r="D69" s="6" t="s">
+      <c r="D69" s="7" t="s">
         <v>351</v>
       </c>
       <c r="E69" t="s">
@@ -11059,7 +11073,7 @@
         <v/>
       </c>
       <c r="M69" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J69:L69)</f>
+        <f t="shared" si="1"/>
         <v>COK</v>
       </c>
       <c r="N69" t="s">
@@ -11081,7 +11095,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:19">
+    <row r="70" spans="1:19" hidden="1">
       <c r="A70" s="2" t="str">
         <f>IF(C70="","",VLOOKUP(C70,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>IND</v>
@@ -11093,7 +11107,7 @@
       <c r="C70" t="s">
         <v>395</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D70" s="7" t="s">
         <v>396</v>
       </c>
       <c r="F70" t="s">
@@ -11118,7 +11132,7 @@
         <v/>
       </c>
       <c r="M70" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J70:L70)</f>
+        <f t="shared" si="1"/>
         <v>GBR;IRN</v>
       </c>
       <c r="N70" t="s">
@@ -11140,7 +11154,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:19">
+    <row r="71" spans="1:19" hidden="1">
       <c r="A71" s="2" t="str">
         <f>IF(C71="","",VLOOKUP(C71,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>RUS</v>
@@ -11152,7 +11166,7 @@
       <c r="C71" t="s">
         <v>388</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D71" s="7" t="s">
         <v>399</v>
       </c>
       <c r="F71" t="s">
@@ -11174,7 +11188,7 @@
         <v/>
       </c>
       <c r="M71" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J71:L71)</f>
+        <f t="shared" si="1"/>
         <v>MDG</v>
       </c>
       <c r="N71" t="s">
@@ -11196,7 +11210,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:19">
+    <row r="72" spans="1:19" hidden="1">
       <c r="A72" s="2" t="str">
         <f>IF(C72="","",VLOOKUP(C72,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>ITA</v>
@@ -11208,7 +11222,7 @@
       <c r="C72" t="s">
         <v>167</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D72" s="7" t="s">
         <v>282</v>
       </c>
       <c r="E72" t="s">
@@ -11236,7 +11250,7 @@
         <v>ARE</v>
       </c>
       <c r="M72" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J72:L72)</f>
+        <f t="shared" si="1"/>
         <v>SAU;QAT;ARE</v>
       </c>
       <c r="N72" t="s">
@@ -11258,7 +11272,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:19">
+    <row r="73" spans="1:19" hidden="1">
       <c r="A73" s="2" t="str">
         <f>IF(C73="","",VLOOKUP(C73,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>KOR</v>
@@ -11270,7 +11284,7 @@
       <c r="C73" t="s">
         <v>241</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D73" s="7" t="s">
         <v>288</v>
       </c>
       <c r="E73" t="s">
@@ -11295,7 +11309,7 @@
         <v/>
       </c>
       <c r="M73" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J73:L73)</f>
+        <f t="shared" si="1"/>
         <v>FRA</v>
       </c>
       <c r="N73" t="s">
@@ -11317,7 +11331,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:19">
+    <row r="74" spans="1:19" hidden="1">
       <c r="A74" s="2" t="str">
         <f>IF(C74="","",VLOOKUP(C74,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>RUS</v>
@@ -11329,7 +11343,7 @@
       <c r="C74" t="s">
         <v>176</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D74" s="7" t="s">
         <v>309</v>
       </c>
       <c r="E74" t="s">
@@ -11354,7 +11368,7 @@
         <v/>
       </c>
       <c r="M74" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J74:L74)</f>
+        <f t="shared" si="1"/>
         <v>TUR</v>
       </c>
       <c r="N74" t="s">
@@ -11376,7 +11390,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:19">
+    <row r="75" spans="1:19" hidden="1">
       <c r="A75" s="2" t="str">
         <f>IF(C75="","",VLOOKUP(C75,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>JPN</v>
@@ -11388,7 +11402,7 @@
       <c r="C75" t="s">
         <v>312</v>
       </c>
-      <c r="D75" s="6" t="s">
+      <c r="D75" s="7" t="s">
         <v>355</v>
       </c>
       <c r="F75" t="s">
@@ -11416,7 +11430,7 @@
         <v>IRN</v>
       </c>
       <c r="M75" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J75:L75)</f>
+        <f t="shared" si="1"/>
         <v>FRA;OMN;IRN</v>
       </c>
       <c r="N75" t="s">
@@ -11438,7 +11452,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:19">
+    <row r="76" spans="1:19" hidden="1">
       <c r="A76" s="2" t="str">
         <f>IF(C76="","",VLOOKUP(C76,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>ETH</v>
@@ -11450,7 +11464,7 @@
       <c r="C76" t="s">
         <v>329</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D76" s="7" t="s">
         <v>330</v>
       </c>
       <c r="E76" t="s">
@@ -11475,7 +11489,7 @@
         <v/>
       </c>
       <c r="M76" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J76:L76)</f>
+        <f t="shared" si="1"/>
         <v>CHN</v>
       </c>
       <c r="N76" t="s">
@@ -11497,7 +11511,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="1:19">
+    <row r="77" spans="1:19" hidden="1">
       <c r="A77" s="2" t="str">
         <f>IF(C77="","",VLOOKUP(C77,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>CHN</v>
@@ -11509,7 +11523,7 @@
       <c r="C77" t="s">
         <v>332</v>
       </c>
-      <c r="D77" t="s">
+      <c r="D77" s="7" t="s">
         <v>347</v>
       </c>
       <c r="E77" t="s">
@@ -11531,7 +11545,7 @@
         <v/>
       </c>
       <c r="M77" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J77:L77)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N77" t="s">
@@ -11553,7 +11567,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:19">
+    <row r="78" spans="1:19" hidden="1">
       <c r="A78" s="2" t="str">
         <f>IF(C78="","",VLOOKUP(C78,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>RUS</v>
@@ -11565,7 +11579,7 @@
       <c r="C78" t="s">
         <v>388</v>
       </c>
-      <c r="D78" t="s">
+      <c r="D78" s="7" t="s">
         <v>389</v>
       </c>
       <c r="F78" t="s">
@@ -11590,7 +11604,7 @@
         <v/>
       </c>
       <c r="M78" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J78:L78)</f>
+        <f t="shared" si="1"/>
         <v>IRN;USA</v>
       </c>
       <c r="N78" t="s">
@@ -11612,7 +11626,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:19">
+    <row r="79" spans="1:19" hidden="1">
       <c r="A79" s="2" t="str">
         <f>IF(C79="","",VLOOKUP(C79,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>MMR</v>
@@ -11624,7 +11638,7 @@
       <c r="C79" t="s">
         <v>391</v>
       </c>
-      <c r="D79" t="s">
+      <c r="D79" s="7" t="s">
         <v>392</v>
       </c>
       <c r="E79" t="s">
@@ -11646,7 +11660,7 @@
         <v/>
       </c>
       <c r="M79" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J79:L79)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N79" t="s">
@@ -11668,7 +11682,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:19">
+    <row r="80" spans="1:19" hidden="1">
       <c r="A80" s="2" t="str">
         <f>IF(C80="","",VLOOKUP(C80,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>AFG</v>
@@ -11680,7 +11694,7 @@
       <c r="C80" t="s">
         <v>411</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D80" s="7" t="s">
         <v>412</v>
       </c>
       <c r="F80" t="s">
@@ -11699,7 +11713,7 @@
         <v/>
       </c>
       <c r="M80" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J80:L80)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N80" t="s">
@@ -11721,7 +11735,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:19">
+    <row r="81" spans="1:19" hidden="1">
       <c r="A81" s="2" t="str">
         <f>IF(C81="","",VLOOKUP(C81,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>GRC</v>
@@ -11733,7 +11747,7 @@
       <c r="C81" t="s">
         <v>415</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D81" s="7" t="s">
         <v>416</v>
       </c>
       <c r="F81" t="s">
@@ -11752,7 +11766,7 @@
         <v/>
       </c>
       <c r="M81" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J81:L81)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N81" t="s">
@@ -11774,7 +11788,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:19">
+    <row r="82" spans="1:19" hidden="1">
       <c r="A82" s="2" t="str">
         <f>IF(C82="","",VLOOKUP(C82,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>UKR</v>
@@ -11786,7 +11800,7 @@
       <c r="C82" t="s">
         <v>202</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D82" s="7" t="s">
         <v>277</v>
       </c>
       <c r="E82" t="s">
@@ -11811,7 +11825,7 @@
         <v/>
       </c>
       <c r="M82" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J82:L82)</f>
+        <f t="shared" si="1"/>
         <v>TUR</v>
       </c>
       <c r="N82" t="s">
@@ -11833,7 +11847,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:19">
+    <row r="83" spans="1:19" hidden="1">
       <c r="A83" s="2" t="str">
         <f>IF(C83="","",VLOOKUP(C83,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>IRN</v>
@@ -11845,7 +11859,7 @@
       <c r="C83" t="s">
         <v>188</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D83" s="7" t="s">
         <v>304</v>
       </c>
       <c r="F83" t="s">
@@ -11864,7 +11878,7 @@
         <v/>
       </c>
       <c r="M83" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J83:L83)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N83" t="s">
@@ -11920,7 +11934,7 @@
         <v/>
       </c>
       <c r="M84" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J84:L84)</f>
+        <f t="shared" si="1"/>
         <v>IRN</v>
       </c>
       <c r="N84" t="s">
@@ -11942,7 +11956,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="1:19">
+    <row r="85" spans="1:19" hidden="1">
       <c r="A85" s="2" t="str">
         <f>IF(C85="","",VLOOKUP(C85,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>COD</v>
@@ -11954,7 +11968,7 @@
       <c r="C85" t="s">
         <v>376</v>
       </c>
-      <c r="D85" t="s">
+      <c r="D85" s="7" t="s">
         <v>377</v>
       </c>
       <c r="E85" t="s">
@@ -11979,7 +11993,7 @@
         <v/>
       </c>
       <c r="M85" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J85:L85)</f>
+        <f t="shared" si="1"/>
         <v>USA</v>
       </c>
       <c r="N85" t="s">
@@ -12001,7 +12015,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:19">
+    <row r="86" spans="1:19" hidden="1">
       <c r="A86" s="2" t="str">
         <f>IF(C86="","",VLOOKUP(C86,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>IRN</v>
@@ -12013,7 +12027,7 @@
       <c r="C86" t="s">
         <v>367</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D86" s="7" t="s">
         <v>381</v>
       </c>
       <c r="E86" t="s">
@@ -12038,7 +12052,7 @@
         <v/>
       </c>
       <c r="M86" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J86:L86)</f>
+        <f t="shared" si="1"/>
         <v>ARE</v>
       </c>
       <c r="N86" t="s">
@@ -12060,7 +12074,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:19">
+    <row r="87" spans="1:19" hidden="1">
       <c r="A87" s="2" t="str">
         <f>IF(C87="","",VLOOKUP(C87,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>USA</v>
@@ -12072,7 +12086,7 @@
       <c r="C87" t="s">
         <v>368</v>
       </c>
-      <c r="D87" t="s">
+      <c r="D87" s="7" t="s">
         <v>385</v>
       </c>
       <c r="E87" t="s">
@@ -12097,7 +12111,7 @@
         <v/>
       </c>
       <c r="M87" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J87:L87)</f>
+        <f t="shared" si="1"/>
         <v>IRN</v>
       </c>
       <c r="N87" t="s">
@@ -12119,7 +12133,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:19">
+    <row r="88" spans="1:19" hidden="1">
       <c r="A88" s="2" t="str">
         <f>IF(C88="","",VLOOKUP(C88,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>UKR</v>
@@ -12131,7 +12145,7 @@
       <c r="C88" t="s">
         <v>418</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D88" s="7" t="s">
         <v>419</v>
       </c>
       <c r="E88" t="s">
@@ -12156,7 +12170,7 @@
         <v/>
       </c>
       <c r="M88" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J88:L88)</f>
+        <f t="shared" si="1"/>
         <v>RUS</v>
       </c>
       <c r="N88" t="s">
@@ -12190,7 +12204,7 @@
       <c r="C89" t="s">
         <v>418</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D89" s="6" t="s">
         <v>433</v>
       </c>
       <c r="E89" t="s">
@@ -12215,7 +12229,7 @@
         <v/>
       </c>
       <c r="M89" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J89:L89)</f>
+        <f t="shared" si="1"/>
         <v>SYR</v>
       </c>
       <c r="N89" t="s">
@@ -12237,7 +12251,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:19">
+    <row r="90" spans="1:19" hidden="1">
       <c r="A90" s="2" t="str">
         <f>IF(C90="","",VLOOKUP(C90,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>USA</v>
@@ -12249,7 +12263,7 @@
       <c r="C90" t="s">
         <v>368</v>
       </c>
-      <c r="D90" t="s">
+      <c r="D90" s="7" t="s">
         <v>428</v>
       </c>
       <c r="E90" t="s">
@@ -12274,7 +12288,7 @@
         <v/>
       </c>
       <c r="M90" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J90:L90)</f>
+        <f t="shared" si="1"/>
         <v>IRN</v>
       </c>
       <c r="N90" t="s">
@@ -12296,7 +12310,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:19">
+    <row r="91" spans="1:19" hidden="1">
       <c r="A91" s="2" t="str">
         <f>IF(C91="","",VLOOKUP(C91,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>IRN</v>
@@ -12308,7 +12322,7 @@
       <c r="C91" t="s">
         <v>367</v>
       </c>
-      <c r="D91" t="s">
+      <c r="D91" s="7" t="s">
         <v>431</v>
       </c>
       <c r="F91" t="s">
@@ -12330,7 +12344,7 @@
         <v/>
       </c>
       <c r="M91" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J91:L91)</f>
+        <f t="shared" si="1"/>
         <v>USA</v>
       </c>
       <c r="N91" t="s">
@@ -12364,7 +12378,7 @@
       <c r="C92" t="s">
         <v>356</v>
       </c>
-      <c r="D92" t="s">
+      <c r="D92" s="6" t="s">
         <v>357</v>
       </c>
       <c r="E92" t="s">
@@ -12386,7 +12400,7 @@
         <v/>
       </c>
       <c r="M92" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J92:L92)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N92" t="s">
@@ -12408,7 +12422,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:19">
+    <row r="93" spans="1:19" hidden="1">
       <c r="A93" s="2" t="str">
         <f>IF(C93="","",VLOOKUP(C93,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>PAK</v>
@@ -12420,7 +12434,7 @@
       <c r="C93" t="s">
         <v>362</v>
       </c>
-      <c r="D93" t="s">
+      <c r="D93" s="7" t="s">
         <v>363</v>
       </c>
       <c r="E93" t="s">
@@ -12451,7 +12465,7 @@
         <v>USA</v>
       </c>
       <c r="M93" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J93:L93)</f>
+        <f t="shared" si="1"/>
         <v>EGY;IRN;USA</v>
       </c>
       <c r="N93" t="s">
@@ -12473,7 +12487,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:19">
+    <row r="94" spans="1:19" hidden="1">
       <c r="A94" s="2" t="str">
         <f>IF(C94="","",VLOOKUP(C94,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>VNM</v>
@@ -12485,7 +12499,7 @@
       <c r="C94" t="s">
         <v>372</v>
       </c>
-      <c r="D94" t="s">
+      <c r="D94" s="7" t="s">
         <v>373</v>
       </c>
       <c r="F94" t="s">
@@ -12504,7 +12518,7 @@
         <v/>
       </c>
       <c r="M94" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J94:L94)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N94" t="s">
@@ -12526,7 +12540,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:19">
+    <row r="95" spans="1:19" hidden="1">
       <c r="A95" s="2" t="str">
         <f>IF(C95="","",VLOOKUP(C95,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>SSD</v>
@@ -12538,7 +12552,7 @@
       <c r="C95" t="s">
         <v>403</v>
       </c>
-      <c r="D95" t="s">
+      <c r="D95" s="7" t="s">
         <v>404</v>
       </c>
       <c r="F95" t="s">
@@ -12557,7 +12571,7 @@
         <v/>
       </c>
       <c r="M95" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J95:L95)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N95" t="s">
@@ -12579,7 +12593,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:19">
+    <row r="96" spans="1:19" hidden="1">
       <c r="A96" s="2" t="str">
         <f>IF(C96="","",VLOOKUP(C96,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>IRN</v>
@@ -12591,7 +12605,7 @@
       <c r="C96" t="s">
         <v>367</v>
       </c>
-      <c r="D96" t="s">
+      <c r="D96" s="7" t="s">
         <v>422</v>
       </c>
       <c r="F96" t="s">
@@ -12613,7 +12627,7 @@
         <v/>
       </c>
       <c r="M96" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J96:L96)</f>
+        <f t="shared" si="1"/>
         <v>SAU</v>
       </c>
       <c r="N96" t="s">
@@ -12635,7 +12649,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:19">
+    <row r="97" spans="1:19" hidden="1">
       <c r="A97" s="2" t="str">
         <f>IF(C97="","",VLOOKUP(C97,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>USA</v>
@@ -12647,7 +12661,7 @@
       <c r="C97" t="s">
         <v>368</v>
       </c>
-      <c r="D97" t="s">
+      <c r="D97" s="7" t="s">
         <v>425</v>
       </c>
       <c r="E97" t="s">
@@ -12672,7 +12686,7 @@
         <v/>
       </c>
       <c r="M97" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J97:L97)</f>
+        <f t="shared" si="1"/>
         <v>IRN</v>
       </c>
       <c r="N97" t="s">
@@ -12694,7 +12708,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:19">
+    <row r="98" spans="1:19" hidden="1">
       <c r="A98" s="2" t="str">
         <f>IF(C98="","",VLOOKUP(C98,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>IRN</v>
@@ -12706,11 +12720,11 @@
       <c r="C98" t="s">
         <v>188</v>
       </c>
-      <c r="D98" t="s">
-        <v>461</v>
+      <c r="D98" s="7" t="s">
+        <v>460</v>
       </c>
       <c r="F98" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G98" t="s">
         <v>284</v>
@@ -12728,7 +12742,7 @@
         <v/>
       </c>
       <c r="M98" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J98:L98)</f>
+        <f t="shared" si="1"/>
         <v>SAU</v>
       </c>
       <c r="N98" t="s">
@@ -12762,11 +12776,11 @@
       <c r="C99" t="s">
         <v>177</v>
       </c>
-      <c r="D99" t="s">
+      <c r="D99" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="E99" t="s">
         <v>443</v>
-      </c>
-      <c r="E99" t="s">
-        <v>444</v>
       </c>
       <c r="F99" t="s">
         <v>156</v>
@@ -12790,7 +12804,7 @@
         <v/>
       </c>
       <c r="M99" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J99:L99)</f>
+        <f t="shared" si="1"/>
         <v>IRN;PAK</v>
       </c>
       <c r="N99" t="s">
@@ -12806,13 +12820,13 @@
         <v>180</v>
       </c>
       <c r="R99" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="S99">
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:19">
+    <row r="100" spans="1:19" hidden="1">
       <c r="A100" s="2" t="str">
         <f>IF(C100="","",VLOOKUP(C100,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>JPN</v>
@@ -12824,11 +12838,11 @@
       <c r="C100" t="s">
         <v>312</v>
       </c>
-      <c r="D100" t="s">
+      <c r="D100" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="E100" t="s">
         <v>449</v>
-      </c>
-      <c r="E100" t="s">
-        <v>450</v>
       </c>
       <c r="F100" t="s">
         <v>156</v>
@@ -12849,7 +12863,7 @@
         <v/>
       </c>
       <c r="M100" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J100:L100)</f>
+        <f t="shared" si="1"/>
         <v>IRN</v>
       </c>
       <c r="N100" t="s">
@@ -12865,13 +12879,13 @@
         <v>180</v>
       </c>
       <c r="R100" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="S100">
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:19">
+    <row r="101" spans="1:19" hidden="1">
       <c r="A101" s="2" t="str">
         <f>IF(C101="","",VLOOKUP(C101,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>MDG</v>
@@ -12883,11 +12897,11 @@
       <c r="C101" t="s">
         <v>401</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D101" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="E101" t="s">
         <v>451</v>
-      </c>
-      <c r="E101" t="s">
-        <v>452</v>
       </c>
       <c r="F101" t="s">
         <v>175</v>
@@ -12905,7 +12919,7 @@
         <v/>
       </c>
       <c r="M101" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J101:L101)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N101" t="s">
@@ -12921,7 +12935,7 @@
         <v>180</v>
       </c>
       <c r="R101" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="S101">
         <v>3</v>
@@ -12939,11 +12953,11 @@
       <c r="C102" t="s">
         <v>176</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D102" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="E102" t="s">
         <v>453</v>
-      </c>
-      <c r="E102" t="s">
-        <v>454</v>
       </c>
       <c r="F102" t="s">
         <v>156</v>
@@ -12970,7 +12984,7 @@
         <v>USA</v>
       </c>
       <c r="M102" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J102:L102)</f>
+        <f t="shared" si="1"/>
         <v>CHN;IRN;USA</v>
       </c>
       <c r="N102" t="s">
@@ -12986,13 +13000,13 @@
         <v>180</v>
       </c>
       <c r="R102" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="S102">
         <v>4</v>
       </c>
     </row>
-    <row r="103" spans="1:19">
+    <row r="103" spans="1:19" hidden="1">
       <c r="A103" s="2" t="str">
         <f>IF(C103="","",VLOOKUP(C103,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>MEX</v>
@@ -13004,8 +13018,8 @@
       <c r="C103" t="s">
         <v>248</v>
       </c>
-      <c r="D103" t="s">
-        <v>455</v>
+      <c r="D103" s="7" t="s">
+        <v>454</v>
       </c>
       <c r="F103" t="s">
         <v>170</v>
@@ -13023,7 +13037,7 @@
         <v/>
       </c>
       <c r="M103" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J103:L103)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N103" t="s">
@@ -13039,13 +13053,13 @@
         <v>159</v>
       </c>
       <c r="R103" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="S103">
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:19">
+    <row r="104" spans="1:19" hidden="1">
       <c r="A104" s="2" t="str">
         <f>IF(C104="","",VLOOKUP(C104,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>PRY</v>
@@ -13057,8 +13071,8 @@
       <c r="C104" t="s">
         <v>182</v>
       </c>
-      <c r="D104" t="s">
-        <v>456</v>
+      <c r="D104" s="7" t="s">
+        <v>455</v>
       </c>
       <c r="F104" t="s">
         <v>170</v>
@@ -13076,7 +13090,7 @@
         <v/>
       </c>
       <c r="M104" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J104:L104)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N104" t="s">
@@ -13092,13 +13106,13 @@
         <v>159</v>
       </c>
       <c r="R104" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="S104">
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:19">
+    <row r="105" spans="1:19" hidden="1">
       <c r="A105" s="2" t="str">
         <f>IF(C105="","",VLOOKUP(C105,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>PRK</v>
@@ -13108,13 +13122,13 @@
         <v>North Korea</v>
       </c>
       <c r="C105" t="s">
+        <v>456</v>
+      </c>
+      <c r="D105" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="D105" t="s">
-        <v>458</v>
-      </c>
       <c r="F105" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G105" t="s">
         <v>241</v>
@@ -13135,7 +13149,7 @@
         <v/>
       </c>
       <c r="M105" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J105:L105)</f>
+        <f t="shared" si="1"/>
         <v>KOR;JPN</v>
       </c>
       <c r="N105" t="s">
@@ -13151,13 +13165,13 @@
         <v>159</v>
       </c>
       <c r="R105" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="S105">
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="1:19">
+    <row r="106" spans="1:19" hidden="1">
       <c r="A106" s="2" t="str">
         <f>IF(C106="","",VLOOKUP(C106,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>AFG</v>
@@ -13169,14 +13183,14 @@
       <c r="C106" t="s">
         <v>221</v>
       </c>
-      <c r="D106" t="s">
+      <c r="D106" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="E106" t="s">
         <v>459</v>
       </c>
-      <c r="E106" t="s">
-        <v>460</v>
-      </c>
       <c r="F106" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G106" t="s">
         <v>225</v>
@@ -13197,7 +13211,7 @@
         <v/>
       </c>
       <c r="M106" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J106:L106)</f>
+        <f t="shared" si="1"/>
         <v>PAK;CHN</v>
       </c>
       <c r="N106" t="s">
@@ -13213,7 +13227,7 @@
         <v>159</v>
       </c>
       <c r="R106" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="S106">
         <v>4</v>
@@ -13231,7 +13245,7 @@
       <c r="C107" t="s">
         <v>188</v>
       </c>
-      <c r="D107" t="s">
+      <c r="D107" s="6" t="s">
         <v>438</v>
       </c>
       <c r="E107" t="s">
@@ -13256,7 +13270,7 @@
         <v/>
       </c>
       <c r="M107" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J107:L107)</f>
+        <f t="shared" si="1"/>
         <v>USA</v>
       </c>
       <c r="N107" t="s">
@@ -13272,13 +13286,13 @@
         <v>180</v>
       </c>
       <c r="R107" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="S107">
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:19">
+    <row r="108" spans="1:19" hidden="1">
       <c r="A108" s="2" t="str">
         <f>IF(C108="","",VLOOKUP(C108,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>GBR</v>
@@ -13290,14 +13304,14 @@
       <c r="C108" t="s">
         <v>193</v>
       </c>
-      <c r="D108" t="s">
+      <c r="D108" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="E108" t="s">
         <v>440</v>
       </c>
-      <c r="E108" t="s">
+      <c r="F108" t="s">
         <v>441</v>
-      </c>
-      <c r="F108" t="s">
-        <v>442</v>
       </c>
       <c r="G108" t="s">
         <v>176</v>
@@ -13315,7 +13329,7 @@
         <v/>
       </c>
       <c r="M108" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J108:L108)</f>
+        <f t="shared" si="1"/>
         <v>RUS</v>
       </c>
       <c r="N108" t="s">
@@ -13331,13 +13345,13 @@
         <v>180</v>
       </c>
       <c r="R108" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="S108">
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="1:19">
+    <row r="109" spans="1:19" hidden="1">
       <c r="A109" s="2" t="str">
         <f>IF(C109="","",VLOOKUP(C109,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>GBR</v>
@@ -13349,11 +13363,11 @@
       <c r="C109" t="s">
         <v>193</v>
       </c>
-      <c r="D109" t="s">
+      <c r="D109" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="E109" t="s">
         <v>445</v>
-      </c>
-      <c r="E109" t="s">
-        <v>446</v>
       </c>
       <c r="F109" t="s">
         <v>156</v>
@@ -13380,7 +13394,7 @@
         <v>LBN</v>
       </c>
       <c r="M109" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J109:L109)</f>
+        <f t="shared" si="1"/>
         <v>USA;ISR;LBN</v>
       </c>
       <c r="N109" t="s">
@@ -13396,7 +13410,7 @@
         <v>180</v>
       </c>
       <c r="R109" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="S109">
         <v>4</v>
@@ -13414,11 +13428,11 @@
       <c r="C110" t="s">
         <v>153</v>
       </c>
-      <c r="D110" t="s">
+      <c r="D110" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="E110" t="s">
         <v>447</v>
-      </c>
-      <c r="E110" t="s">
-        <v>448</v>
       </c>
       <c r="F110" t="s">
         <v>156</v>
@@ -13439,7 +13453,7 @@
         <v/>
       </c>
       <c r="M110" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J110:L110)</f>
+        <f t="shared" si="1"/>
         <v>LBN</v>
       </c>
       <c r="N110" t="s">
@@ -13455,7 +13469,7 @@
         <v>180</v>
       </c>
       <c r="R110" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="S110">
         <v>5</v>
@@ -13471,19 +13485,19 @@
         <v>Ecuador</v>
       </c>
       <c r="C111" t="s">
+        <v>476</v>
+      </c>
+      <c r="D111" s="6" t="s">
         <v>477</v>
       </c>
-      <c r="D111" t="s">
+      <c r="E111" t="s">
         <v>478</v>
-      </c>
-      <c r="E111" t="s">
-        <v>479</v>
       </c>
       <c r="F111" t="s">
         <v>244</v>
       </c>
       <c r="G111" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J111" s="2" t="str">
         <f>IF(G111="","",VLOOKUP(G111,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -13498,11 +13512,11 @@
         <v/>
       </c>
       <c r="M111" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J111:L111)</f>
+        <f t="shared" si="1"/>
         <v>COL</v>
       </c>
       <c r="N111" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="O111" t="s">
         <v>53</v>
@@ -13514,13 +13528,13 @@
         <v>159</v>
       </c>
       <c r="R111" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="S111">
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:19">
+    <row r="112" spans="1:19" hidden="1">
       <c r="A112" s="2" t="str">
         <f>IF(C112="","",VLOOKUP(C112,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>VEN</v>
@@ -13532,11 +13546,11 @@
       <c r="C112" t="s">
         <v>256</v>
       </c>
-      <c r="D112" t="s">
+      <c r="D112" s="7" t="s">
+        <v>482</v>
+      </c>
+      <c r="E112" t="s">
         <v>483</v>
-      </c>
-      <c r="E112" t="s">
-        <v>484</v>
       </c>
       <c r="F112" t="s">
         <v>244</v>
@@ -13554,11 +13568,11 @@
         <v/>
       </c>
       <c r="M112" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J112:L112)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N112" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="O112" t="s">
         <v>334</v>
@@ -13570,13 +13584,13 @@
         <v>180</v>
       </c>
       <c r="R112" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="S112">
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="1:19">
+    <row r="113" spans="1:19" hidden="1">
       <c r="A113" s="2" t="str">
         <f>IF(C113="","",VLOOKUP(C113,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>VEN</v>
@@ -13588,14 +13602,14 @@
       <c r="C113" t="s">
         <v>256</v>
       </c>
-      <c r="D113" t="s">
-        <v>485</v>
+      <c r="D113" s="7" t="s">
+        <v>484</v>
       </c>
       <c r="F113" t="s">
         <v>400</v>
       </c>
       <c r="G113" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="J113" s="2" t="str">
         <f>IF(G113="","",VLOOKUP(G113,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -13610,7 +13624,7 @@
         <v/>
       </c>
       <c r="M113" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J113:L113)</f>
+        <f t="shared" si="1"/>
         <v>GRD</v>
       </c>
       <c r="O113" t="s">
@@ -13623,7 +13637,7 @@
         <v>159</v>
       </c>
       <c r="R113" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="S113">
         <v>2</v>
@@ -13641,11 +13655,11 @@
       <c r="C114" t="s">
         <v>153</v>
       </c>
-      <c r="D114" t="s">
+      <c r="D114" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="E114" t="s">
         <v>493</v>
-      </c>
-      <c r="E114" t="s">
-        <v>494</v>
       </c>
       <c r="F114" t="s">
         <v>170</v>
@@ -13663,11 +13677,11 @@
         <v/>
       </c>
       <c r="M114" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J114:L114)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N114" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="O114" t="s">
         <v>79</v>
@@ -13679,13 +13693,13 @@
         <v>159</v>
       </c>
       <c r="R114" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="S114">
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:19">
+    <row r="115" spans="1:19" hidden="1">
       <c r="A115" s="2" t="str">
         <f>IF(C115="","",VLOOKUP(C115,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>ISR</v>
@@ -13697,11 +13711,11 @@
       <c r="C115" t="s">
         <v>153</v>
       </c>
-      <c r="D115" t="s">
+      <c r="D115" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="E115" t="s">
         <v>495</v>
-      </c>
-      <c r="E115" t="s">
-        <v>496</v>
       </c>
       <c r="F115" t="s">
         <v>156</v>
@@ -13722,11 +13736,11 @@
         <v/>
       </c>
       <c r="M115" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J115:L115)</f>
+        <f t="shared" si="1"/>
         <v>PSE</v>
       </c>
       <c r="N115" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="O115" t="s">
         <v>69</v>
@@ -13738,7 +13752,7 @@
         <v>159</v>
       </c>
       <c r="R115" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="S115">
         <v>4</v>
@@ -13754,13 +13768,13 @@
         <v>Brazil</v>
       </c>
       <c r="C116" t="s">
+        <v>473</v>
+      </c>
+      <c r="D116" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D116" t="s">
+      <c r="E116" t="s">
         <v>475</v>
-      </c>
-      <c r="E116" t="s">
-        <v>476</v>
       </c>
       <c r="F116" t="s">
         <v>196</v>
@@ -13781,11 +13795,11 @@
         <v/>
       </c>
       <c r="M116" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J116:L116)</f>
+        <f t="shared" si="1"/>
         <v>USA</v>
       </c>
       <c r="N116" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="O116" t="s">
         <v>53</v>
@@ -13797,13 +13811,13 @@
         <v>159</v>
       </c>
       <c r="R116" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="S116">
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:19">
+    <row r="117" spans="1:19" hidden="1">
       <c r="A117" s="2" t="str">
         <f>IF(C117="","",VLOOKUP(C117,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>VEN</v>
@@ -13815,11 +13829,11 @@
       <c r="C117" t="s">
         <v>256</v>
       </c>
-      <c r="D117" t="s">
+      <c r="D117" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="E117" t="s">
         <v>481</v>
-      </c>
-      <c r="E117" t="s">
-        <v>482</v>
       </c>
       <c r="F117" t="s">
         <v>170</v>
@@ -13837,11 +13851,11 @@
         <v/>
       </c>
       <c r="M117" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J117:L117)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N117" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="O117" t="s">
         <v>79</v>
@@ -13853,13 +13867,13 @@
         <v>159</v>
       </c>
       <c r="R117" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="S117">
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:19">
+    <row r="118" spans="1:19" hidden="1">
       <c r="A118" s="2" t="str">
         <f>IF(C118="","",VLOOKUP(C118,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>CHN</v>
@@ -13871,17 +13885,17 @@
       <c r="C118" t="s">
         <v>332</v>
       </c>
-      <c r="D118" t="s">
+      <c r="D118" s="7" t="s">
+        <v>486</v>
+      </c>
+      <c r="E118" t="s">
         <v>487</v>
-      </c>
-      <c r="E118" t="s">
-        <v>488</v>
       </c>
       <c r="F118" t="s">
         <v>400</v>
       </c>
       <c r="G118" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="J118" s="2" t="str">
         <f>IF(G118="","",VLOOKUP(G118,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -13896,11 +13910,11 @@
         <v/>
       </c>
       <c r="M118" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J118:L118)</f>
+        <f t="shared" si="1"/>
         <v>PRK</v>
       </c>
       <c r="N118" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="O118" t="s">
         <v>53</v>
@@ -13912,13 +13926,13 @@
         <v>159</v>
       </c>
       <c r="R118" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="S118">
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:19">
+    <row r="119" spans="1:19" hidden="1">
       <c r="A119" s="2" t="str">
         <f>IF(C119="","",VLOOKUP(C119,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>AUS</v>
@@ -13928,19 +13942,19 @@
         <v>Australia</v>
       </c>
       <c r="C119" t="s">
+        <v>488</v>
+      </c>
+      <c r="D119" s="7" t="s">
         <v>489</v>
       </c>
-      <c r="D119" t="s">
+      <c r="E119" t="s">
         <v>490</v>
-      </c>
-      <c r="E119" t="s">
-        <v>491</v>
       </c>
       <c r="F119" t="s">
         <v>400</v>
       </c>
       <c r="G119" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="J119" s="2" t="str">
         <f>IF(G119="","",VLOOKUP(G119,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -13955,11 +13969,11 @@
         <v/>
       </c>
       <c r="M119" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J119:L119)</f>
+        <f t="shared" si="1"/>
         <v>SGP</v>
       </c>
       <c r="N119" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="O119" t="s">
         <v>53</v>
@@ -13971,13 +13985,13 @@
         <v>159</v>
       </c>
       <c r="R119" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="S119">
         <v>3</v>
       </c>
     </row>
-    <row r="120" spans="1:19">
+    <row r="120" spans="1:19" hidden="1">
       <c r="A120" s="2" t="str">
         <f>IF(C120="","",VLOOKUP(C120,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -13999,11 +14013,11 @@
         <v/>
       </c>
       <c r="M120" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J120:L120)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="121" spans="1:19">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="121" spans="1:19" hidden="1">
       <c r="A121" s="2" t="str">
         <f>IF(C121="","",VLOOKUP(C121,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14025,11 +14039,11 @@
         <v/>
       </c>
       <c r="M121" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J121:L121)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="122" spans="1:19">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="122" spans="1:19" hidden="1">
       <c r="A122" s="2" t="str">
         <f>IF(C122="","",VLOOKUP(C122,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14051,11 +14065,11 @@
         <v/>
       </c>
       <c r="M122" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J122:L122)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="123" spans="1:19">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="123" spans="1:19" hidden="1">
       <c r="A123" s="2" t="str">
         <f>IF(C123="","",VLOOKUP(C123,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14077,11 +14091,11 @@
         <v/>
       </c>
       <c r="M123" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J123:L123)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="124" spans="1:19">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="124" spans="1:19" hidden="1">
       <c r="A124" s="2" t="str">
         <f>IF(C124="","",VLOOKUP(C124,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14103,11 +14117,11 @@
         <v/>
       </c>
       <c r="M124" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J124:L124)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="125" spans="1:19">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="125" spans="1:19" hidden="1">
       <c r="A125" s="2" t="str">
         <f>IF(C125="","",VLOOKUP(C125,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14129,11 +14143,11 @@
         <v/>
       </c>
       <c r="M125" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J125:L125)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="126" spans="1:19">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="126" spans="1:19" hidden="1">
       <c r="A126" s="2" t="str">
         <f>IF(C126="","",VLOOKUP(C126,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14155,11 +14169,11 @@
         <v/>
       </c>
       <c r="M126" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J126:L126)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="127" spans="1:19">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="127" spans="1:19" hidden="1">
       <c r="A127" s="2" t="str">
         <f>IF(C127="","",VLOOKUP(C127,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14181,11 +14195,11 @@
         <v/>
       </c>
       <c r="M127" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J127:L127)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="128" spans="1:19">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="128" spans="1:19" hidden="1">
       <c r="A128" s="2" t="str">
         <f>IF(C128="","",VLOOKUP(C128,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14207,11 +14221,11 @@
         <v/>
       </c>
       <c r="M128" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J128:L128)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="129" spans="1:13">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="129" spans="1:13" hidden="1">
       <c r="A129" s="2" t="str">
         <f>IF(C129="","",VLOOKUP(C129,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14233,11 +14247,11 @@
         <v/>
       </c>
       <c r="M129" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J129:L129)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="130" spans="1:13">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="130" spans="1:13" hidden="1">
       <c r="A130" s="2" t="str">
         <f>IF(C130="","",VLOOKUP(C130,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14259,11 +14273,11 @@
         <v/>
       </c>
       <c r="M130" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J130:L130)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="131" spans="1:13">
+        <f t="shared" ref="M130:M193" si="2">_xlfn.TEXTJOIN(";",TRUE,J130:L130)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131" spans="1:13" hidden="1">
       <c r="A131" s="2" t="str">
         <f>IF(C131="","",VLOOKUP(C131,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14285,11 +14299,11 @@
         <v/>
       </c>
       <c r="M131" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J131:L131)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="132" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="132" spans="1:13" hidden="1">
       <c r="A132" s="2" t="str">
         <f>IF(C132="","",VLOOKUP(C132,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14311,11 +14325,11 @@
         <v/>
       </c>
       <c r="M132" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J132:L132)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="133" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="133" spans="1:13" hidden="1">
       <c r="A133" s="2" t="str">
         <f>IF(C133="","",VLOOKUP(C133,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14337,11 +14351,11 @@
         <v/>
       </c>
       <c r="M133" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J133:L133)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="134" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="134" spans="1:13" hidden="1">
       <c r="A134" s="2" t="str">
         <f>IF(C134="","",VLOOKUP(C134,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14363,11 +14377,11 @@
         <v/>
       </c>
       <c r="M134" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J134:L134)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="135" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="135" spans="1:13" hidden="1">
       <c r="A135" s="2" t="str">
         <f>IF(C135="","",VLOOKUP(C135,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14389,11 +14403,11 @@
         <v/>
       </c>
       <c r="M135" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J135:L135)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="136" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="136" spans="1:13" hidden="1">
       <c r="A136" s="2" t="str">
         <f>IF(C136="","",VLOOKUP(C136,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14415,11 +14429,11 @@
         <v/>
       </c>
       <c r="M136" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J136:L136)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="137" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="137" spans="1:13" hidden="1">
       <c r="A137" s="2" t="str">
         <f>IF(C137="","",VLOOKUP(C137,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14441,11 +14455,11 @@
         <v/>
       </c>
       <c r="M137" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J137:L137)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="138" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="138" spans="1:13" hidden="1">
       <c r="A138" s="2" t="str">
         <f>IF(C138="","",VLOOKUP(C138,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14467,11 +14481,11 @@
         <v/>
       </c>
       <c r="M138" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J138:L138)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="139" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="139" spans="1:13" hidden="1">
       <c r="A139" s="2" t="str">
         <f>IF(C139="","",VLOOKUP(C139,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14493,11 +14507,11 @@
         <v/>
       </c>
       <c r="M139" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J139:L139)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="140" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="140" spans="1:13" hidden="1">
       <c r="A140" s="2" t="str">
         <f>IF(C140="","",VLOOKUP(C140,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14519,11 +14533,11 @@
         <v/>
       </c>
       <c r="M140" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J140:L140)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="141" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="141" spans="1:13" hidden="1">
       <c r="A141" s="2" t="str">
         <f>IF(C141="","",VLOOKUP(C141,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14545,11 +14559,11 @@
         <v/>
       </c>
       <c r="M141" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J141:L141)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="142" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="142" spans="1:13" hidden="1">
       <c r="A142" s="2" t="str">
         <f>IF(C142="","",VLOOKUP(C142,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14571,11 +14585,11 @@
         <v/>
       </c>
       <c r="M142" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J142:L142)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="143" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="143" spans="1:13" hidden="1">
       <c r="A143" s="2" t="str">
         <f>IF(C143="","",VLOOKUP(C143,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14597,11 +14611,11 @@
         <v/>
       </c>
       <c r="M143" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J143:L143)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="144" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="144" spans="1:13" hidden="1">
       <c r="A144" s="2" t="str">
         <f>IF(C144="","",VLOOKUP(C144,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14623,11 +14637,11 @@
         <v/>
       </c>
       <c r="M144" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J144:L144)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="145" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="145" spans="1:13" hidden="1">
       <c r="A145" s="2" t="str">
         <f>IF(C145="","",VLOOKUP(C145,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14649,11 +14663,11 @@
         <v/>
       </c>
       <c r="M145" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J145:L145)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="146" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="146" spans="1:13" hidden="1">
       <c r="A146" s="2" t="str">
         <f>IF(C146="","",VLOOKUP(C146,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14675,11 +14689,11 @@
         <v/>
       </c>
       <c r="M146" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J146:L146)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="147" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="147" spans="1:13" hidden="1">
       <c r="A147" s="2" t="str">
         <f>IF(C147="","",VLOOKUP(C147,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14701,11 +14715,11 @@
         <v/>
       </c>
       <c r="M147" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J147:L147)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="148" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="148" spans="1:13" hidden="1">
       <c r="A148" s="2" t="str">
         <f>IF(C148="","",VLOOKUP(C148,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14727,11 +14741,11 @@
         <v/>
       </c>
       <c r="M148" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J148:L148)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="149" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="149" spans="1:13" hidden="1">
       <c r="A149" s="2" t="str">
         <f>IF(C149="","",VLOOKUP(C149,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14753,11 +14767,11 @@
         <v/>
       </c>
       <c r="M149" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J149:L149)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="150" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="150" spans="1:13" hidden="1">
       <c r="A150" s="2" t="str">
         <f>IF(C150="","",VLOOKUP(C150,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14779,11 +14793,11 @@
         <v/>
       </c>
       <c r="M150" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J150:L150)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="151" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="151" spans="1:13" hidden="1">
       <c r="A151" s="2" t="str">
         <f>IF(C151="","",VLOOKUP(C151,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14805,11 +14819,11 @@
         <v/>
       </c>
       <c r="M151" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J151:L151)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="152" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="152" spans="1:13" hidden="1">
       <c r="A152" s="2" t="str">
         <f>IF(C152="","",VLOOKUP(C152,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14831,11 +14845,11 @@
         <v/>
       </c>
       <c r="M152" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J152:L152)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="153" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="153" spans="1:13" hidden="1">
       <c r="A153" s="2" t="str">
         <f>IF(C153="","",VLOOKUP(C153,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14857,11 +14871,11 @@
         <v/>
       </c>
       <c r="M153" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J153:L153)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="154" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="154" spans="1:13" hidden="1">
       <c r="A154" s="2" t="str">
         <f>IF(C154="","",VLOOKUP(C154,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14883,11 +14897,11 @@
         <v/>
       </c>
       <c r="M154" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J154:L154)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="155" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="155" spans="1:13" hidden="1">
       <c r="A155" s="2" t="str">
         <f>IF(C155="","",VLOOKUP(C155,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14909,11 +14923,11 @@
         <v/>
       </c>
       <c r="M155" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J155:L155)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="156" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="156" spans="1:13" hidden="1">
       <c r="A156" s="2" t="str">
         <f>IF(C156="","",VLOOKUP(C156,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14935,11 +14949,11 @@
         <v/>
       </c>
       <c r="M156" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J156:L156)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="157" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="157" spans="1:13" hidden="1">
       <c r="A157" s="2" t="str">
         <f>IF(C157="","",VLOOKUP(C157,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14961,11 +14975,11 @@
         <v/>
       </c>
       <c r="M157" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J157:L157)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="158" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="158" spans="1:13" hidden="1">
       <c r="A158" s="2" t="str">
         <f>IF(C158="","",VLOOKUP(C158,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14987,11 +15001,11 @@
         <v/>
       </c>
       <c r="M158" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J158:L158)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="159" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="159" spans="1:13" hidden="1">
       <c r="A159" s="2" t="str">
         <f>IF(C159="","",VLOOKUP(C159,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15013,11 +15027,11 @@
         <v/>
       </c>
       <c r="M159" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J159:L159)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="160" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="160" spans="1:13" hidden="1">
       <c r="A160" s="2" t="str">
         <f>IF(C160="","",VLOOKUP(C160,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15039,11 +15053,11 @@
         <v/>
       </c>
       <c r="M160" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J160:L160)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="161" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="161" spans="1:13" hidden="1">
       <c r="A161" s="2" t="str">
         <f>IF(C161="","",VLOOKUP(C161,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15065,11 +15079,11 @@
         <v/>
       </c>
       <c r="M161" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J161:L161)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="162" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="162" spans="1:13" hidden="1">
       <c r="A162" s="2" t="str">
         <f>IF(C162="","",VLOOKUP(C162,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15091,11 +15105,11 @@
         <v/>
       </c>
       <c r="M162" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J162:L162)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="163" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="163" spans="1:13" hidden="1">
       <c r="A163" s="2" t="str">
         <f>IF(C163="","",VLOOKUP(C163,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15117,11 +15131,11 @@
         <v/>
       </c>
       <c r="M163" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J163:L163)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="164" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="164" spans="1:13" hidden="1">
       <c r="A164" s="2" t="str">
         <f>IF(C164="","",VLOOKUP(C164,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15143,11 +15157,11 @@
         <v/>
       </c>
       <c r="M164" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J164:L164)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="165" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="165" spans="1:13" hidden="1">
       <c r="A165" s="2" t="str">
         <f>IF(C165="","",VLOOKUP(C165,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15169,11 +15183,11 @@
         <v/>
       </c>
       <c r="M165" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J165:L165)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="166" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="166" spans="1:13" hidden="1">
       <c r="A166" s="2" t="str">
         <f>IF(C166="","",VLOOKUP(C166,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15195,11 +15209,11 @@
         <v/>
       </c>
       <c r="M166" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J166:L166)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="167" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="167" spans="1:13" hidden="1">
       <c r="A167" s="2" t="str">
         <f>IF(C167="","",VLOOKUP(C167,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15221,11 +15235,11 @@
         <v/>
       </c>
       <c r="M167" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J167:L167)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="168" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="168" spans="1:13" hidden="1">
       <c r="A168" s="2" t="str">
         <f>IF(C168="","",VLOOKUP(C168,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15247,11 +15261,11 @@
         <v/>
       </c>
       <c r="M168" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J168:L168)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="169" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="169" spans="1:13" hidden="1">
       <c r="A169" s="2" t="str">
         <f>IF(C169="","",VLOOKUP(C169,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15273,11 +15287,11 @@
         <v/>
       </c>
       <c r="M169" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J169:L169)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="170" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="170" spans="1:13" hidden="1">
       <c r="A170" s="2" t="str">
         <f>IF(C170="","",VLOOKUP(C170,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15299,11 +15313,11 @@
         <v/>
       </c>
       <c r="M170" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J170:L170)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="171" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="171" spans="1:13" hidden="1">
       <c r="A171" s="2" t="str">
         <f>IF(C171="","",VLOOKUP(C171,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15325,11 +15339,11 @@
         <v/>
       </c>
       <c r="M171" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J171:L171)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="172" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="172" spans="1:13" hidden="1">
       <c r="A172" s="2" t="str">
         <f>IF(C172="","",VLOOKUP(C172,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15351,11 +15365,11 @@
         <v/>
       </c>
       <c r="M172" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J172:L172)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="173" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="173" spans="1:13" hidden="1">
       <c r="A173" s="2" t="str">
         <f>IF(C173="","",VLOOKUP(C173,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15377,11 +15391,11 @@
         <v/>
       </c>
       <c r="M173" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J173:L173)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="174" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="174" spans="1:13" hidden="1">
       <c r="A174" s="2" t="str">
         <f>IF(C174="","",VLOOKUP(C174,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15403,11 +15417,11 @@
         <v/>
       </c>
       <c r="M174" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J174:L174)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="175" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="175" spans="1:13" hidden="1">
       <c r="A175" s="2" t="str">
         <f>IF(C175="","",VLOOKUP(C175,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15429,11 +15443,11 @@
         <v/>
       </c>
       <c r="M175" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J175:L175)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="176" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="176" spans="1:13" hidden="1">
       <c r="A176" s="2" t="str">
         <f>IF(C176="","",VLOOKUP(C176,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15455,11 +15469,11 @@
         <v/>
       </c>
       <c r="M176" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J176:L176)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="177" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="177" spans="1:13" hidden="1">
       <c r="A177" s="2" t="str">
         <f>IF(C177="","",VLOOKUP(C177,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15481,11 +15495,11 @@
         <v/>
       </c>
       <c r="M177" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J177:L177)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="178" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="178" spans="1:13" hidden="1">
       <c r="A178" s="2" t="str">
         <f>IF(C178="","",VLOOKUP(C178,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15507,11 +15521,11 @@
         <v/>
       </c>
       <c r="M178" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J178:L178)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="179" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="179" spans="1:13" hidden="1">
       <c r="A179" s="2" t="str">
         <f>IF(C179="","",VLOOKUP(C179,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15533,11 +15547,11 @@
         <v/>
       </c>
       <c r="M179" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J179:L179)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="180" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="180" spans="1:13" hidden="1">
       <c r="A180" s="2" t="str">
         <f>IF(C180="","",VLOOKUP(C180,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15559,11 +15573,11 @@
         <v/>
       </c>
       <c r="M180" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J180:L180)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="181" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="181" spans="1:13" hidden="1">
       <c r="A181" s="2" t="str">
         <f>IF(C181="","",VLOOKUP(C181,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15585,11 +15599,11 @@
         <v/>
       </c>
       <c r="M181" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J181:L181)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="182" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="182" spans="1:13" hidden="1">
       <c r="A182" s="2" t="str">
         <f>IF(C182="","",VLOOKUP(C182,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15611,11 +15625,11 @@
         <v/>
       </c>
       <c r="M182" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J182:L182)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="183" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="183" spans="1:13" hidden="1">
       <c r="A183" s="2" t="str">
         <f>IF(C183="","",VLOOKUP(C183,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15637,11 +15651,11 @@
         <v/>
       </c>
       <c r="M183" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J183:L183)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="184" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="184" spans="1:13" hidden="1">
       <c r="A184" s="2" t="str">
         <f>IF(C184="","",VLOOKUP(C184,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15663,11 +15677,11 @@
         <v/>
       </c>
       <c r="M184" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J184:L184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="185" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="185" spans="1:13" hidden="1">
       <c r="A185" s="2" t="str">
         <f>IF(C185="","",VLOOKUP(C185,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15689,11 +15703,11 @@
         <v/>
       </c>
       <c r="M185" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J185:L185)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="186" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="186" spans="1:13" hidden="1">
       <c r="A186" s="2" t="str">
         <f>IF(C186="","",VLOOKUP(C186,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15715,11 +15729,11 @@
         <v/>
       </c>
       <c r="M186" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J186:L186)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="187" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="187" spans="1:13" hidden="1">
       <c r="A187" s="2" t="str">
         <f>IF(C187="","",VLOOKUP(C187,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15741,11 +15755,11 @@
         <v/>
       </c>
       <c r="M187" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J187:L187)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="188" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="188" spans="1:13" hidden="1">
       <c r="A188" s="2" t="str">
         <f>IF(C188="","",VLOOKUP(C188,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15767,11 +15781,11 @@
         <v/>
       </c>
       <c r="M188" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J188:L188)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="189" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="189" spans="1:13" hidden="1">
       <c r="A189" s="2" t="str">
         <f>IF(C189="","",VLOOKUP(C189,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15793,11 +15807,11 @@
         <v/>
       </c>
       <c r="M189" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J189:L189)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="190" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="190" spans="1:13" hidden="1">
       <c r="A190" s="2" t="str">
         <f>IF(C190="","",VLOOKUP(C190,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15819,11 +15833,11 @@
         <v/>
       </c>
       <c r="M190" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J190:L190)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="191" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="191" spans="1:13" hidden="1">
       <c r="A191" s="2" t="str">
         <f>IF(C191="","",VLOOKUP(C191,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15845,11 +15859,11 @@
         <v/>
       </c>
       <c r="M191" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J191:L191)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="192" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="192" spans="1:13" hidden="1">
       <c r="A192" s="2" t="str">
         <f>IF(C192="","",VLOOKUP(C192,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15871,11 +15885,11 @@
         <v/>
       </c>
       <c r="M192" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J192:L192)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="193" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="193" spans="1:13" hidden="1">
       <c r="A193" s="2" t="str">
         <f>IF(C193="","",VLOOKUP(C193,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15897,11 +15911,11 @@
         <v/>
       </c>
       <c r="M193" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J193:L193)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="194" spans="1:13">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="194" spans="1:13" hidden="1">
       <c r="A194" s="2" t="str">
         <f>IF(C194="","",VLOOKUP(C194,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15923,11 +15937,11 @@
         <v/>
       </c>
       <c r="M194" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J194:L194)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="195" spans="1:13">
+        <f t="shared" ref="M194:M257" si="3">_xlfn.TEXTJOIN(";",TRUE,J194:L194)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195" spans="1:13" hidden="1">
       <c r="A195" s="2" t="str">
         <f>IF(C195="","",VLOOKUP(C195,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15949,11 +15963,11 @@
         <v/>
       </c>
       <c r="M195" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J195:L195)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="196" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="196" spans="1:13" hidden="1">
       <c r="A196" s="2" t="str">
         <f>IF(C196="","",VLOOKUP(C196,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15975,11 +15989,11 @@
         <v/>
       </c>
       <c r="M196" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J196:L196)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="197" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="197" spans="1:13" hidden="1">
       <c r="A197" s="2" t="str">
         <f>IF(C197="","",VLOOKUP(C197,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16001,11 +16015,11 @@
         <v/>
       </c>
       <c r="M197" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J197:L197)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="198" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="198" spans="1:13" hidden="1">
       <c r="A198" s="2" t="str">
         <f>IF(C198="","",VLOOKUP(C198,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16027,11 +16041,11 @@
         <v/>
       </c>
       <c r="M198" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J198:L198)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="199" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="199" spans="1:13" hidden="1">
       <c r="A199" s="2" t="str">
         <f>IF(C199="","",VLOOKUP(C199,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16053,11 +16067,11 @@
         <v/>
       </c>
       <c r="M199" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J199:L199)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="200" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="200" spans="1:13" hidden="1">
       <c r="A200" s="2" t="str">
         <f>IF(C200="","",VLOOKUP(C200,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16079,11 +16093,11 @@
         <v/>
       </c>
       <c r="M200" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J200:L200)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="201" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="201" spans="1:13" hidden="1">
       <c r="A201" s="2" t="str">
         <f>IF(C201="","",VLOOKUP(C201,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16105,11 +16119,11 @@
         <v/>
       </c>
       <c r="M201" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J201:L201)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="202" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="202" spans="1:13" hidden="1">
       <c r="A202" s="2" t="str">
         <f>IF(C202="","",VLOOKUP(C202,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16131,11 +16145,11 @@
         <v/>
       </c>
       <c r="M202" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J202:L202)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="203" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="203" spans="1:13" hidden="1">
       <c r="A203" s="2" t="str">
         <f>IF(C203="","",VLOOKUP(C203,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16157,11 +16171,11 @@
         <v/>
       </c>
       <c r="M203" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J203:L203)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="204" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="204" spans="1:13" hidden="1">
       <c r="A204" s="2" t="str">
         <f>IF(C204="","",VLOOKUP(C204,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16183,11 +16197,11 @@
         <v/>
       </c>
       <c r="M204" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J204:L204)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="205" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="205" spans="1:13" hidden="1">
       <c r="A205" s="2" t="str">
         <f>IF(C205="","",VLOOKUP(C205,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16209,11 +16223,11 @@
         <v/>
       </c>
       <c r="M205" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J205:L205)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="206" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="206" spans="1:13" hidden="1">
       <c r="A206" s="2" t="str">
         <f>IF(C206="","",VLOOKUP(C206,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16235,11 +16249,11 @@
         <v/>
       </c>
       <c r="M206" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J206:L206)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="207" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="207" spans="1:13" hidden="1">
       <c r="A207" s="2" t="str">
         <f>IF(C207="","",VLOOKUP(C207,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16261,11 +16275,11 @@
         <v/>
       </c>
       <c r="M207" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J207:L207)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="208" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="208" spans="1:13" hidden="1">
       <c r="A208" s="2" t="str">
         <f>IF(C208="","",VLOOKUP(C208,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16287,11 +16301,11 @@
         <v/>
       </c>
       <c r="M208" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J208:L208)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="209" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="209" spans="1:13" hidden="1">
       <c r="A209" s="2" t="str">
         <f>IF(C209="","",VLOOKUP(C209,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16313,11 +16327,11 @@
         <v/>
       </c>
       <c r="M209" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J209:L209)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="210" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="210" spans="1:13" hidden="1">
       <c r="A210" s="2" t="str">
         <f>IF(C210="","",VLOOKUP(C210,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16339,11 +16353,11 @@
         <v/>
       </c>
       <c r="M210" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J210:L210)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="211" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="211" spans="1:13" hidden="1">
       <c r="A211" s="2" t="str">
         <f>IF(C211="","",VLOOKUP(C211,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16365,11 +16379,11 @@
         <v/>
       </c>
       <c r="M211" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J211:L211)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="212" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="212" spans="1:13" hidden="1">
       <c r="A212" s="2" t="str">
         <f>IF(C212="","",VLOOKUP(C212,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16391,11 +16405,11 @@
         <v/>
       </c>
       <c r="M212" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J212:L212)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="213" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="213" spans="1:13" hidden="1">
       <c r="A213" s="2" t="str">
         <f>IF(C213="","",VLOOKUP(C213,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16417,11 +16431,11 @@
         <v/>
       </c>
       <c r="M213" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J213:L213)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="214" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="214" spans="1:13" hidden="1">
       <c r="A214" s="2" t="str">
         <f>IF(C214="","",VLOOKUP(C214,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16443,11 +16457,11 @@
         <v/>
       </c>
       <c r="M214" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J214:L214)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="215" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="215" spans="1:13" hidden="1">
       <c r="A215" s="2" t="str">
         <f>IF(C215="","",VLOOKUP(C215,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16469,11 +16483,11 @@
         <v/>
       </c>
       <c r="M215" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J215:L215)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="216" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="216" spans="1:13" hidden="1">
       <c r="A216" s="2" t="str">
         <f>IF(C216="","",VLOOKUP(C216,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16495,11 +16509,11 @@
         <v/>
       </c>
       <c r="M216" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J216:L216)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="217" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="217" spans="1:13" hidden="1">
       <c r="A217" s="2" t="str">
         <f>IF(C217="","",VLOOKUP(C217,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16521,11 +16535,11 @@
         <v/>
       </c>
       <c r="M217" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J217:L217)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="218" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="218" spans="1:13" hidden="1">
       <c r="A218" s="2" t="str">
         <f>IF(C218="","",VLOOKUP(C218,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16547,11 +16561,11 @@
         <v/>
       </c>
       <c r="M218" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J218:L218)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="219" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="219" spans="1:13" hidden="1">
       <c r="A219" s="2" t="str">
         <f>IF(C219="","",VLOOKUP(C219,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16573,11 +16587,11 @@
         <v/>
       </c>
       <c r="M219" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J219:L219)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="220" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="220" spans="1:13" hidden="1">
       <c r="A220" s="2" t="str">
         <f>IF(C220="","",VLOOKUP(C220,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16599,11 +16613,11 @@
         <v/>
       </c>
       <c r="M220" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J220:L220)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="221" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="221" spans="1:13" hidden="1">
       <c r="A221" s="2" t="str">
         <f>IF(C221="","",VLOOKUP(C221,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16625,11 +16639,11 @@
         <v/>
       </c>
       <c r="M221" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J221:L221)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="222" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="222" spans="1:13" hidden="1">
       <c r="A222" s="2" t="str">
         <f>IF(C222="","",VLOOKUP(C222,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16651,11 +16665,11 @@
         <v/>
       </c>
       <c r="M222" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J222:L222)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="223" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="223" spans="1:13" hidden="1">
       <c r="A223" s="2" t="str">
         <f>IF(C223="","",VLOOKUP(C223,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16677,11 +16691,11 @@
         <v/>
       </c>
       <c r="M223" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J223:L223)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="224" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="224" spans="1:13" hidden="1">
       <c r="A224" s="2" t="str">
         <f>IF(C224="","",VLOOKUP(C224,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16703,11 +16717,11 @@
         <v/>
       </c>
       <c r="M224" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J224:L224)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="225" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="225" spans="1:13" hidden="1">
       <c r="A225" s="2" t="str">
         <f>IF(C225="","",VLOOKUP(C225,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16729,11 +16743,11 @@
         <v/>
       </c>
       <c r="M225" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J225:L225)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="226" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="226" spans="1:13" hidden="1">
       <c r="A226" s="2" t="str">
         <f>IF(C226="","",VLOOKUP(C226,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16755,11 +16769,11 @@
         <v/>
       </c>
       <c r="M226" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J226:L226)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="227" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="227" spans="1:13" hidden="1">
       <c r="A227" s="2" t="str">
         <f>IF(C227="","",VLOOKUP(C227,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16781,11 +16795,11 @@
         <v/>
       </c>
       <c r="M227" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J227:L227)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="228" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="228" spans="1:13" hidden="1">
       <c r="A228" s="2" t="str">
         <f>IF(C228="","",VLOOKUP(C228,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16807,11 +16821,11 @@
         <v/>
       </c>
       <c r="M228" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J228:L228)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="229" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="229" spans="1:13" hidden="1">
       <c r="A229" s="2" t="str">
         <f>IF(C229="","",VLOOKUP(C229,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16833,11 +16847,11 @@
         <v/>
       </c>
       <c r="M229" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J229:L229)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="230" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="230" spans="1:13" hidden="1">
       <c r="A230" s="2" t="str">
         <f>IF(C230="","",VLOOKUP(C230,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16859,11 +16873,11 @@
         <v/>
       </c>
       <c r="M230" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J230:L230)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="231" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="231" spans="1:13" hidden="1">
       <c r="A231" s="2" t="str">
         <f>IF(C231="","",VLOOKUP(C231,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16885,11 +16899,11 @@
         <v/>
       </c>
       <c r="M231" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J231:L231)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="232" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="232" spans="1:13" hidden="1">
       <c r="A232" s="2" t="str">
         <f>IF(C232="","",VLOOKUP(C232,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16911,11 +16925,11 @@
         <v/>
       </c>
       <c r="M232" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J232:L232)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="233" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="233" spans="1:13" hidden="1">
       <c r="A233" s="2" t="str">
         <f>IF(C233="","",VLOOKUP(C233,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16937,11 +16951,11 @@
         <v/>
       </c>
       <c r="M233" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J233:L233)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="234" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="234" spans="1:13" hidden="1">
       <c r="A234" s="2" t="str">
         <f>IF(C234="","",VLOOKUP(C234,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16963,11 +16977,11 @@
         <v/>
       </c>
       <c r="M234" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J234:L234)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="235" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="235" spans="1:13" hidden="1">
       <c r="A235" s="2" t="str">
         <f>IF(C235="","",VLOOKUP(C235,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16989,11 +17003,11 @@
         <v/>
       </c>
       <c r="M235" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J235:L235)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="236" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="236" spans="1:13" hidden="1">
       <c r="A236" s="2" t="str">
         <f>IF(C236="","",VLOOKUP(C236,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17015,11 +17029,11 @@
         <v/>
       </c>
       <c r="M236" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J236:L236)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="237" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="237" spans="1:13" hidden="1">
       <c r="A237" s="2" t="str">
         <f>IF(C237="","",VLOOKUP(C237,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17041,11 +17055,11 @@
         <v/>
       </c>
       <c r="M237" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J237:L237)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="238" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="238" spans="1:13" hidden="1">
       <c r="A238" s="2" t="str">
         <f>IF(C238="","",VLOOKUP(C238,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17067,11 +17081,11 @@
         <v/>
       </c>
       <c r="M238" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J238:L238)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="239" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="239" spans="1:13" hidden="1">
       <c r="A239" s="2" t="str">
         <f>IF(C239="","",VLOOKUP(C239,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17093,11 +17107,11 @@
         <v/>
       </c>
       <c r="M239" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J239:L239)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="240" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="240" spans="1:13" hidden="1">
       <c r="A240" s="2" t="str">
         <f>IF(C240="","",VLOOKUP(C240,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17119,11 +17133,11 @@
         <v/>
       </c>
       <c r="M240" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J240:L240)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="241" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="241" spans="1:13" hidden="1">
       <c r="A241" s="2" t="str">
         <f>IF(C241="","",VLOOKUP(C241,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17145,11 +17159,11 @@
         <v/>
       </c>
       <c r="M241" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J241:L241)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="242" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="242" spans="1:13" hidden="1">
       <c r="A242" s="2" t="str">
         <f>IF(C242="","",VLOOKUP(C242,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17171,11 +17185,11 @@
         <v/>
       </c>
       <c r="M242" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J242:L242)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="243" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="243" spans="1:13" hidden="1">
       <c r="A243" s="2" t="str">
         <f>IF(C243="","",VLOOKUP(C243,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17197,11 +17211,11 @@
         <v/>
       </c>
       <c r="M243" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J243:L243)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="244" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="244" spans="1:13" hidden="1">
       <c r="A244" s="2" t="str">
         <f>IF(C244="","",VLOOKUP(C244,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17223,11 +17237,11 @@
         <v/>
       </c>
       <c r="M244" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J244:L244)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="245" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="245" spans="1:13" hidden="1">
       <c r="A245" s="2" t="str">
         <f>IF(C245="","",VLOOKUP(C245,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17249,11 +17263,11 @@
         <v/>
       </c>
       <c r="M245" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J245:L245)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="246" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="246" spans="1:13" hidden="1">
       <c r="A246" s="2" t="str">
         <f>IF(C246="","",VLOOKUP(C246,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17275,11 +17289,11 @@
         <v/>
       </c>
       <c r="M246" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J246:L246)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="247" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="247" spans="1:13" hidden="1">
       <c r="A247" s="2" t="str">
         <f>IF(C247="","",VLOOKUP(C247,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17301,11 +17315,11 @@
         <v/>
       </c>
       <c r="M247" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J247:L247)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="248" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="248" spans="1:13" hidden="1">
       <c r="A248" s="2" t="str">
         <f>IF(C248="","",VLOOKUP(C248,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17327,11 +17341,11 @@
         <v/>
       </c>
       <c r="M248" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J248:L248)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="249" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="249" spans="1:13" hidden="1">
       <c r="A249" s="2" t="str">
         <f>IF(C249="","",VLOOKUP(C249,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17353,11 +17367,11 @@
         <v/>
       </c>
       <c r="M249" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J249:L249)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="250" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="250" spans="1:13" hidden="1">
       <c r="A250" s="2" t="str">
         <f>IF(C250="","",VLOOKUP(C250,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17379,11 +17393,11 @@
         <v/>
       </c>
       <c r="M250" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J250:L250)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="251" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="251" spans="1:13" hidden="1">
       <c r="A251" s="2" t="str">
         <f>IF(C251="","",VLOOKUP(C251,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17405,11 +17419,11 @@
         <v/>
       </c>
       <c r="M251" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J251:L251)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="252" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="252" spans="1:13" hidden="1">
       <c r="A252" s="2" t="str">
         <f>IF(C252="","",VLOOKUP(C252,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17431,11 +17445,11 @@
         <v/>
       </c>
       <c r="M252" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J252:L252)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="253" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="253" spans="1:13" hidden="1">
       <c r="A253" s="2" t="str">
         <f>IF(C253="","",VLOOKUP(C253,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17457,11 +17471,11 @@
         <v/>
       </c>
       <c r="M253" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J253:L253)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="254" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="254" spans="1:13" hidden="1">
       <c r="A254" s="2" t="str">
         <f>IF(C254="","",VLOOKUP(C254,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17483,11 +17497,11 @@
         <v/>
       </c>
       <c r="M254" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J254:L254)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="255" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="255" spans="1:13" hidden="1">
       <c r="A255" s="2" t="str">
         <f>IF(C255="","",VLOOKUP(C255,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17509,11 +17523,11 @@
         <v/>
       </c>
       <c r="M255" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J255:L255)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="256" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="256" spans="1:13" hidden="1">
       <c r="A256" s="2" t="str">
         <f>IF(C256="","",VLOOKUP(C256,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17535,11 +17549,11 @@
         <v/>
       </c>
       <c r="M256" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J256:L256)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="257" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="257" spans="1:13" hidden="1">
       <c r="A257" s="2" t="str">
         <f>IF(C257="","",VLOOKUP(C257,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17561,11 +17575,11 @@
         <v/>
       </c>
       <c r="M257" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J257:L257)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="258" spans="1:13">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="258" spans="1:13" hidden="1">
       <c r="A258" s="2" t="str">
         <f>IF(C258="","",VLOOKUP(C258,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17587,11 +17601,11 @@
         <v/>
       </c>
       <c r="M258" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J258:L258)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="259" spans="1:13">
+        <f t="shared" ref="M258:M321" si="4">_xlfn.TEXTJOIN(";",TRUE,J258:L258)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="259" spans="1:13" hidden="1">
       <c r="A259" s="2" t="str">
         <f>IF(C259="","",VLOOKUP(C259,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17613,11 +17627,11 @@
         <v/>
       </c>
       <c r="M259" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J259:L259)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="260" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="260" spans="1:13" hidden="1">
       <c r="A260" s="2" t="str">
         <f>IF(C260="","",VLOOKUP(C260,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17639,11 +17653,11 @@
         <v/>
       </c>
       <c r="M260" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J260:L260)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="261" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="261" spans="1:13" hidden="1">
       <c r="A261" s="2" t="str">
         <f>IF(C261="","",VLOOKUP(C261,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17665,11 +17679,11 @@
         <v/>
       </c>
       <c r="M261" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J261:L261)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="262" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="262" spans="1:13" hidden="1">
       <c r="A262" s="2" t="str">
         <f>IF(C262="","",VLOOKUP(C262,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17691,11 +17705,11 @@
         <v/>
       </c>
       <c r="M262" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J262:L262)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="263" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="263" spans="1:13" hidden="1">
       <c r="A263" s="2" t="str">
         <f>IF(C263="","",VLOOKUP(C263,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17717,11 +17731,11 @@
         <v/>
       </c>
       <c r="M263" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J263:L263)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="264" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="264" spans="1:13" hidden="1">
       <c r="A264" s="2" t="str">
         <f>IF(C264="","",VLOOKUP(C264,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17743,11 +17757,11 @@
         <v/>
       </c>
       <c r="M264" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J264:L264)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="265" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="265" spans="1:13" hidden="1">
       <c r="A265" s="2" t="str">
         <f>IF(C265="","",VLOOKUP(C265,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17769,11 +17783,11 @@
         <v/>
       </c>
       <c r="M265" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J265:L265)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="266" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="266" spans="1:13" hidden="1">
       <c r="A266" s="2" t="str">
         <f>IF(C266="","",VLOOKUP(C266,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17795,11 +17809,11 @@
         <v/>
       </c>
       <c r="M266" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J266:L266)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="267" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="267" spans="1:13" hidden="1">
       <c r="A267" s="2" t="str">
         <f>IF(C267="","",VLOOKUP(C267,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17821,11 +17835,11 @@
         <v/>
       </c>
       <c r="M267" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J267:L267)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="268" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="268" spans="1:13" hidden="1">
       <c r="A268" s="2" t="str">
         <f>IF(C268="","",VLOOKUP(C268,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17847,11 +17861,11 @@
         <v/>
       </c>
       <c r="M268" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J268:L268)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="269" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="269" spans="1:13" hidden="1">
       <c r="A269" s="2" t="str">
         <f>IF(C269="","",VLOOKUP(C269,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17873,11 +17887,11 @@
         <v/>
       </c>
       <c r="M269" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J269:L269)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="270" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="270" spans="1:13" hidden="1">
       <c r="A270" s="2" t="str">
         <f>IF(C270="","",VLOOKUP(C270,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17899,11 +17913,11 @@
         <v/>
       </c>
       <c r="M270" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J270:L270)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="271" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="271" spans="1:13" hidden="1">
       <c r="A271" s="2" t="str">
         <f>IF(C271="","",VLOOKUP(C271,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17925,11 +17939,11 @@
         <v/>
       </c>
       <c r="M271" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J271:L271)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="272" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="272" spans="1:13" hidden="1">
       <c r="A272" s="2" t="str">
         <f>IF(C272="","",VLOOKUP(C272,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17951,11 +17965,11 @@
         <v/>
       </c>
       <c r="M272" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J272:L272)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="273" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="273" spans="1:13" hidden="1">
       <c r="A273" s="2" t="str">
         <f>IF(C273="","",VLOOKUP(C273,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17977,11 +17991,11 @@
         <v/>
       </c>
       <c r="M273" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J273:L273)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="274" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="274" spans="1:13" hidden="1">
       <c r="A274" s="2" t="str">
         <f>IF(C274="","",VLOOKUP(C274,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18003,11 +18017,11 @@
         <v/>
       </c>
       <c r="M274" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J274:L274)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="275" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="275" spans="1:13" hidden="1">
       <c r="A275" s="2" t="str">
         <f>IF(C275="","",VLOOKUP(C275,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18029,11 +18043,11 @@
         <v/>
       </c>
       <c r="M275" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J275:L275)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="276" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="276" spans="1:13" hidden="1">
       <c r="A276" s="2" t="str">
         <f>IF(C276="","",VLOOKUP(C276,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18055,11 +18069,11 @@
         <v/>
       </c>
       <c r="M276" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J276:L276)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="277" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="277" spans="1:13" hidden="1">
       <c r="A277" s="2" t="str">
         <f>IF(C277="","",VLOOKUP(C277,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18081,11 +18095,11 @@
         <v/>
       </c>
       <c r="M277" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J277:L277)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="278" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="278" spans="1:13" hidden="1">
       <c r="A278" s="2" t="str">
         <f>IF(C278="","",VLOOKUP(C278,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18107,11 +18121,11 @@
         <v/>
       </c>
       <c r="M278" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J278:L278)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="279" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="279" spans="1:13" hidden="1">
       <c r="A279" s="2" t="str">
         <f>IF(C279="","",VLOOKUP(C279,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18133,11 +18147,11 @@
         <v/>
       </c>
       <c r="M279" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J279:L279)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="280" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="280" spans="1:13" hidden="1">
       <c r="A280" s="2" t="str">
         <f>IF(C280="","",VLOOKUP(C280,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18159,11 +18173,11 @@
         <v/>
       </c>
       <c r="M280" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J280:L280)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="281" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="281" spans="1:13" hidden="1">
       <c r="A281" s="2" t="str">
         <f>IF(C281="","",VLOOKUP(C281,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18185,11 +18199,11 @@
         <v/>
       </c>
       <c r="M281" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J281:L281)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="282" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="282" spans="1:13" hidden="1">
       <c r="A282" s="2" t="str">
         <f>IF(C282="","",VLOOKUP(C282,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18211,11 +18225,11 @@
         <v/>
       </c>
       <c r="M282" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J282:L282)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="283" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="283" spans="1:13" hidden="1">
       <c r="A283" s="2" t="str">
         <f>IF(C283="","",VLOOKUP(C283,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18237,11 +18251,11 @@
         <v/>
       </c>
       <c r="M283" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J283:L283)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="284" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="284" spans="1:13" hidden="1">
       <c r="A284" s="2" t="str">
         <f>IF(C284="","",VLOOKUP(C284,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18263,11 +18277,11 @@
         <v/>
       </c>
       <c r="M284" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J284:L284)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="285" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="285" spans="1:13" hidden="1">
       <c r="A285" s="2" t="str">
         <f>IF(C285="","",VLOOKUP(C285,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18289,11 +18303,11 @@
         <v/>
       </c>
       <c r="M285" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J285:L285)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="286" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="286" spans="1:13" hidden="1">
       <c r="A286" s="2" t="str">
         <f>IF(C286="","",VLOOKUP(C286,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18315,11 +18329,11 @@
         <v/>
       </c>
       <c r="M286" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J286:L286)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="287" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="287" spans="1:13" hidden="1">
       <c r="A287" s="2" t="str">
         <f>IF(C287="","",VLOOKUP(C287,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18341,11 +18355,11 @@
         <v/>
       </c>
       <c r="M287" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J287:L287)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="288" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="288" spans="1:13" hidden="1">
       <c r="A288" s="2" t="str">
         <f>IF(C288="","",VLOOKUP(C288,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18367,11 +18381,11 @@
         <v/>
       </c>
       <c r="M288" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J288:L288)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="289" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="289" spans="1:13" hidden="1">
       <c r="A289" s="2" t="str">
         <f>IF(C289="","",VLOOKUP(C289,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18393,11 +18407,11 @@
         <v/>
       </c>
       <c r="M289" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J289:L289)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="290" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="290" spans="1:13" hidden="1">
       <c r="A290" s="2" t="str">
         <f>IF(C290="","",VLOOKUP(C290,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18419,11 +18433,11 @@
         <v/>
       </c>
       <c r="M290" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J290:L290)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="291" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="291" spans="1:13" hidden="1">
       <c r="A291" s="2" t="str">
         <f>IF(C291="","",VLOOKUP(C291,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18445,11 +18459,11 @@
         <v/>
       </c>
       <c r="M291" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J291:L291)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="292" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="292" spans="1:13" hidden="1">
       <c r="A292" s="2" t="str">
         <f>IF(C292="","",VLOOKUP(C292,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18471,11 +18485,11 @@
         <v/>
       </c>
       <c r="M292" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J292:L292)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="293" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="293" spans="1:13" hidden="1">
       <c r="A293" s="2" t="str">
         <f>IF(C293="","",VLOOKUP(C293,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18497,11 +18511,11 @@
         <v/>
       </c>
       <c r="M293" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J293:L293)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="294" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="294" spans="1:13" hidden="1">
       <c r="A294" s="2" t="str">
         <f>IF(C294="","",VLOOKUP(C294,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18523,11 +18537,11 @@
         <v/>
       </c>
       <c r="M294" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J294:L294)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="295" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="295" spans="1:13" hidden="1">
       <c r="A295" s="2" t="str">
         <f>IF(C295="","",VLOOKUP(C295,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18549,11 +18563,11 @@
         <v/>
       </c>
       <c r="M295" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J295:L295)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="296" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="296" spans="1:13" hidden="1">
       <c r="A296" s="2" t="str">
         <f>IF(C296="","",VLOOKUP(C296,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18575,11 +18589,11 @@
         <v/>
       </c>
       <c r="M296" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J296:L296)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="297" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="297" spans="1:13" hidden="1">
       <c r="A297" s="2" t="str">
         <f>IF(C297="","",VLOOKUP(C297,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18601,11 +18615,11 @@
         <v/>
       </c>
       <c r="M297" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J297:L297)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="298" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="298" spans="1:13" hidden="1">
       <c r="A298" s="2" t="str">
         <f>IF(C298="","",VLOOKUP(C298,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18627,11 +18641,11 @@
         <v/>
       </c>
       <c r="M298" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J298:L298)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="299" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="299" spans="1:13" hidden="1">
       <c r="A299" s="2" t="str">
         <f>IF(C299="","",VLOOKUP(C299,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18653,11 +18667,11 @@
         <v/>
       </c>
       <c r="M299" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J299:L299)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="300" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="300" spans="1:13" hidden="1">
       <c r="A300" s="2" t="str">
         <f>IF(C300="","",VLOOKUP(C300,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18679,11 +18693,11 @@
         <v/>
       </c>
       <c r="M300" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J300:L300)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="301" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="301" spans="1:13" hidden="1">
       <c r="A301" s="2" t="str">
         <f>IF(C301="","",VLOOKUP(C301,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18705,11 +18719,11 @@
         <v/>
       </c>
       <c r="M301" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J301:L301)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="302" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="302" spans="1:13" hidden="1">
       <c r="A302" s="2" t="str">
         <f>IF(C302="","",VLOOKUP(C302,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18731,11 +18745,11 @@
         <v/>
       </c>
       <c r="M302" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J302:L302)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="303" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="303" spans="1:13" hidden="1">
       <c r="A303" s="2" t="str">
         <f>IF(C303="","",VLOOKUP(C303,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18757,11 +18771,11 @@
         <v/>
       </c>
       <c r="M303" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J303:L303)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="304" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="304" spans="1:13" hidden="1">
       <c r="A304" s="2" t="str">
         <f>IF(C304="","",VLOOKUP(C304,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18783,11 +18797,11 @@
         <v/>
       </c>
       <c r="M304" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J304:L304)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="305" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="305" spans="1:13" hidden="1">
       <c r="A305" s="2" t="str">
         <f>IF(C305="","",VLOOKUP(C305,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18809,11 +18823,11 @@
         <v/>
       </c>
       <c r="M305" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J305:L305)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="306" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="306" spans="1:13" hidden="1">
       <c r="A306" s="2" t="str">
         <f>IF(C306="","",VLOOKUP(C306,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18835,11 +18849,11 @@
         <v/>
       </c>
       <c r="M306" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J306:L306)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="307" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="307" spans="1:13" hidden="1">
       <c r="A307" s="2" t="str">
         <f>IF(C307="","",VLOOKUP(C307,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18861,11 +18875,11 @@
         <v/>
       </c>
       <c r="M307" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J307:L307)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="308" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="308" spans="1:13" hidden="1">
       <c r="A308" s="2" t="str">
         <f>IF(C308="","",VLOOKUP(C308,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18887,11 +18901,11 @@
         <v/>
       </c>
       <c r="M308" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J308:L308)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="309" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="309" spans="1:13" hidden="1">
       <c r="A309" s="2" t="str">
         <f>IF(C309="","",VLOOKUP(C309,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18913,11 +18927,11 @@
         <v/>
       </c>
       <c r="M309" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J309:L309)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="310" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="310" spans="1:13" hidden="1">
       <c r="A310" s="2" t="str">
         <f>IF(C310="","",VLOOKUP(C310,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18939,11 +18953,11 @@
         <v/>
       </c>
       <c r="M310" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J310:L310)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="311" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="311" spans="1:13" hidden="1">
       <c r="A311" s="2" t="str">
         <f>IF(C311="","",VLOOKUP(C311,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18965,11 +18979,11 @@
         <v/>
       </c>
       <c r="M311" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J311:L311)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="312" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="312" spans="1:13" hidden="1">
       <c r="A312" s="2" t="str">
         <f>IF(C312="","",VLOOKUP(C312,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18991,11 +19005,11 @@
         <v/>
       </c>
       <c r="M312" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J312:L312)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="313" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="313" spans="1:13" hidden="1">
       <c r="A313" s="2" t="str">
         <f>IF(C313="","",VLOOKUP(C313,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19017,11 +19031,11 @@
         <v/>
       </c>
       <c r="M313" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J313:L313)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="314" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="314" spans="1:13" hidden="1">
       <c r="A314" s="2" t="str">
         <f>IF(C314="","",VLOOKUP(C314,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19043,11 +19057,11 @@
         <v/>
       </c>
       <c r="M314" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J314:L314)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="315" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="315" spans="1:13" hidden="1">
       <c r="A315" s="2" t="str">
         <f>IF(C315="","",VLOOKUP(C315,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19069,11 +19083,11 @@
         <v/>
       </c>
       <c r="M315" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J315:L315)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="316" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="316" spans="1:13" hidden="1">
       <c r="A316" s="2" t="str">
         <f>IF(C316="","",VLOOKUP(C316,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19095,11 +19109,11 @@
         <v/>
       </c>
       <c r="M316" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J316:L316)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="317" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="317" spans="1:13" hidden="1">
       <c r="A317" s="2" t="str">
         <f>IF(C317="","",VLOOKUP(C317,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19121,11 +19135,11 @@
         <v/>
       </c>
       <c r="M317" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J317:L317)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="318" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="318" spans="1:13" hidden="1">
       <c r="A318" s="2" t="str">
         <f>IF(C318="","",VLOOKUP(C318,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19147,11 +19161,11 @@
         <v/>
       </c>
       <c r="M318" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J318:L318)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="319" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="319" spans="1:13" hidden="1">
       <c r="A319" s="2" t="str">
         <f>IF(C319="","",VLOOKUP(C319,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19173,11 +19187,11 @@
         <v/>
       </c>
       <c r="M319" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J319:L319)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="320" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="320" spans="1:13" hidden="1">
       <c r="A320" s="2" t="str">
         <f>IF(C320="","",VLOOKUP(C320,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19199,11 +19213,11 @@
         <v/>
       </c>
       <c r="M320" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J320:L320)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="321" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="321" spans="1:13" hidden="1">
       <c r="A321" s="2" t="str">
         <f>IF(C321="","",VLOOKUP(C321,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19225,11 +19239,11 @@
         <v/>
       </c>
       <c r="M321" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J321:L321)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="322" spans="1:13">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="322" spans="1:13" hidden="1">
       <c r="A322" s="2" t="str">
         <f>IF(C322="","",VLOOKUP(C322,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19251,11 +19265,11 @@
         <v/>
       </c>
       <c r="M322" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J322:L322)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="323" spans="1:13">
+        <f t="shared" ref="M322:M385" si="5">_xlfn.TEXTJOIN(";",TRUE,J322:L322)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="323" spans="1:13" hidden="1">
       <c r="A323" s="2" t="str">
         <f>IF(C323="","",VLOOKUP(C323,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19277,11 +19291,11 @@
         <v/>
       </c>
       <c r="M323" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J323:L323)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="324" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="324" spans="1:13" hidden="1">
       <c r="A324" s="2" t="str">
         <f>IF(C324="","",VLOOKUP(C324,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19303,11 +19317,11 @@
         <v/>
       </c>
       <c r="M324" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J324:L324)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="325" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="325" spans="1:13" hidden="1">
       <c r="A325" s="2" t="str">
         <f>IF(C325="","",VLOOKUP(C325,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19329,11 +19343,11 @@
         <v/>
       </c>
       <c r="M325" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J325:L325)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="326" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="326" spans="1:13" hidden="1">
       <c r="A326" s="2" t="str">
         <f>IF(C326="","",VLOOKUP(C326,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19355,11 +19369,11 @@
         <v/>
       </c>
       <c r="M326" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J326:L326)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="327" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="327" spans="1:13" hidden="1">
       <c r="A327" s="2" t="str">
         <f>IF(C327="","",VLOOKUP(C327,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19381,11 +19395,11 @@
         <v/>
       </c>
       <c r="M327" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J327:L327)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="328" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="328" spans="1:13" hidden="1">
       <c r="A328" s="2" t="str">
         <f>IF(C328="","",VLOOKUP(C328,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19407,11 +19421,11 @@
         <v/>
       </c>
       <c r="M328" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J328:L328)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="329" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="329" spans="1:13" hidden="1">
       <c r="A329" s="2" t="str">
         <f>IF(C329="","",VLOOKUP(C329,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19433,11 +19447,11 @@
         <v/>
       </c>
       <c r="M329" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J329:L329)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="330" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="330" spans="1:13" hidden="1">
       <c r="A330" s="2" t="str">
         <f>IF(C330="","",VLOOKUP(C330,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19459,11 +19473,11 @@
         <v/>
       </c>
       <c r="M330" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J330:L330)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="331" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="331" spans="1:13" hidden="1">
       <c r="A331" s="2" t="str">
         <f>IF(C331="","",VLOOKUP(C331,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19485,11 +19499,11 @@
         <v/>
       </c>
       <c r="M331" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J331:L331)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="332" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="332" spans="1:13" hidden="1">
       <c r="A332" s="2" t="str">
         <f>IF(C332="","",VLOOKUP(C332,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19511,11 +19525,11 @@
         <v/>
       </c>
       <c r="M332" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J332:L332)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="333" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="333" spans="1:13" hidden="1">
       <c r="A333" s="2" t="str">
         <f>IF(C333="","",VLOOKUP(C333,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19537,11 +19551,11 @@
         <v/>
       </c>
       <c r="M333" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J333:L333)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="334" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="334" spans="1:13" hidden="1">
       <c r="A334" s="2" t="str">
         <f>IF(C334="","",VLOOKUP(C334,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19563,11 +19577,11 @@
         <v/>
       </c>
       <c r="M334" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J334:L334)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="335" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="335" spans="1:13" hidden="1">
       <c r="A335" s="2" t="str">
         <f>IF(C335="","",VLOOKUP(C335,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19589,11 +19603,11 @@
         <v/>
       </c>
       <c r="M335" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J335:L335)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="336" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="336" spans="1:13" hidden="1">
       <c r="A336" s="2" t="str">
         <f>IF(C336="","",VLOOKUP(C336,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19615,11 +19629,11 @@
         <v/>
       </c>
       <c r="M336" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J336:L336)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="337" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="337" spans="1:13" hidden="1">
       <c r="A337" s="2" t="str">
         <f>IF(C337="","",VLOOKUP(C337,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19641,11 +19655,11 @@
         <v/>
       </c>
       <c r="M337" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J337:L337)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="338" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="338" spans="1:13" hidden="1">
       <c r="A338" s="2" t="str">
         <f>IF(C338="","",VLOOKUP(C338,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19667,11 +19681,11 @@
         <v/>
       </c>
       <c r="M338" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J338:L338)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="339" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="339" spans="1:13" hidden="1">
       <c r="A339" s="2" t="str">
         <f>IF(C339="","",VLOOKUP(C339,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19693,11 +19707,11 @@
         <v/>
       </c>
       <c r="M339" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J339:L339)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="340" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="340" spans="1:13" hidden="1">
       <c r="A340" s="2" t="str">
         <f>IF(C340="","",VLOOKUP(C340,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19719,11 +19733,11 @@
         <v/>
       </c>
       <c r="M340" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J340:L340)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="341" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="341" spans="1:13" hidden="1">
       <c r="A341" s="2" t="str">
         <f>IF(C341="","",VLOOKUP(C341,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19745,11 +19759,11 @@
         <v/>
       </c>
       <c r="M341" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J341:L341)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="342" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="342" spans="1:13" hidden="1">
       <c r="A342" s="2" t="str">
         <f>IF(C342="","",VLOOKUP(C342,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19771,11 +19785,11 @@
         <v/>
       </c>
       <c r="M342" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J342:L342)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="343" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="343" spans="1:13" hidden="1">
       <c r="A343" s="2" t="str">
         <f>IF(C343="","",VLOOKUP(C343,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19797,11 +19811,11 @@
         <v/>
       </c>
       <c r="M343" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J343:L343)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="344" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="344" spans="1:13" hidden="1">
       <c r="A344" s="2" t="str">
         <f>IF(C344="","",VLOOKUP(C344,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19823,11 +19837,11 @@
         <v/>
       </c>
       <c r="M344" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J344:L344)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="345" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="345" spans="1:13" hidden="1">
       <c r="A345" s="2" t="str">
         <f>IF(C345="","",VLOOKUP(C345,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19849,11 +19863,11 @@
         <v/>
       </c>
       <c r="M345" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J345:L345)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="346" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="346" spans="1:13" hidden="1">
       <c r="A346" s="2" t="str">
         <f>IF(C346="","",VLOOKUP(C346,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19875,11 +19889,11 @@
         <v/>
       </c>
       <c r="M346" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J346:L346)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="347" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="347" spans="1:13" hidden="1">
       <c r="A347" s="2" t="str">
         <f>IF(C347="","",VLOOKUP(C347,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19901,11 +19915,11 @@
         <v/>
       </c>
       <c r="M347" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J347:L347)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="348" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="348" spans="1:13" hidden="1">
       <c r="A348" s="2" t="str">
         <f>IF(C348="","",VLOOKUP(C348,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19927,11 +19941,11 @@
         <v/>
       </c>
       <c r="M348" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J348:L348)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="349" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="349" spans="1:13" hidden="1">
       <c r="A349" s="2" t="str">
         <f>IF(C349="","",VLOOKUP(C349,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19953,11 +19967,11 @@
         <v/>
       </c>
       <c r="M349" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J349:L349)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="350" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="350" spans="1:13" hidden="1">
       <c r="A350" s="2" t="str">
         <f>IF(C350="","",VLOOKUP(C350,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19979,11 +19993,11 @@
         <v/>
       </c>
       <c r="M350" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J350:L350)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="351" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="351" spans="1:13" hidden="1">
       <c r="A351" s="2" t="str">
         <f>IF(C351="","",VLOOKUP(C351,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20005,11 +20019,11 @@
         <v/>
       </c>
       <c r="M351" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J351:L351)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="352" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="352" spans="1:13" hidden="1">
       <c r="A352" s="2" t="str">
         <f>IF(C352="","",VLOOKUP(C352,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20031,11 +20045,11 @@
         <v/>
       </c>
       <c r="M352" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J352:L352)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="353" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="353" spans="1:13" hidden="1">
       <c r="A353" s="2" t="str">
         <f>IF(C353="","",VLOOKUP(C353,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20057,11 +20071,11 @@
         <v/>
       </c>
       <c r="M353" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J353:L353)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="354" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="354" spans="1:13" hidden="1">
       <c r="A354" s="2" t="str">
         <f>IF(C354="","",VLOOKUP(C354,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20083,11 +20097,11 @@
         <v/>
       </c>
       <c r="M354" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J354:L354)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="355" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="355" spans="1:13" hidden="1">
       <c r="A355" s="2" t="str">
         <f>IF(C355="","",VLOOKUP(C355,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20109,11 +20123,11 @@
         <v/>
       </c>
       <c r="M355" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J355:L355)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="356" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="356" spans="1:13" hidden="1">
       <c r="A356" s="2" t="str">
         <f>IF(C356="","",VLOOKUP(C356,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20135,11 +20149,11 @@
         <v/>
       </c>
       <c r="M356" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J356:L356)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="357" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="357" spans="1:13" hidden="1">
       <c r="A357" s="2" t="str">
         <f>IF(C357="","",VLOOKUP(C357,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20161,11 +20175,11 @@
         <v/>
       </c>
       <c r="M357" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J357:L357)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="358" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="358" spans="1:13" hidden="1">
       <c r="A358" s="2" t="str">
         <f>IF(C358="","",VLOOKUP(C358,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20187,11 +20201,11 @@
         <v/>
       </c>
       <c r="M358" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J358:L358)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="359" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="359" spans="1:13" hidden="1">
       <c r="A359" s="2" t="str">
         <f>IF(C359="","",VLOOKUP(C359,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20213,11 +20227,11 @@
         <v/>
       </c>
       <c r="M359" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J359:L359)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="360" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="360" spans="1:13" hidden="1">
       <c r="A360" s="2" t="str">
         <f>IF(C360="","",VLOOKUP(C360,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20239,11 +20253,11 @@
         <v/>
       </c>
       <c r="M360" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J360:L360)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="361" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="361" spans="1:13" hidden="1">
       <c r="A361" s="2" t="str">
         <f>IF(C361="","",VLOOKUP(C361,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20265,11 +20279,11 @@
         <v/>
       </c>
       <c r="M361" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J361:L361)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="362" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="362" spans="1:13" hidden="1">
       <c r="A362" s="2" t="str">
         <f>IF(C362="","",VLOOKUP(C362,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20291,11 +20305,11 @@
         <v/>
       </c>
       <c r="M362" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J362:L362)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="363" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="363" spans="1:13" hidden="1">
       <c r="A363" s="2" t="str">
         <f>IF(C363="","",VLOOKUP(C363,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20317,11 +20331,11 @@
         <v/>
       </c>
       <c r="M363" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J363:L363)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="364" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="364" spans="1:13" hidden="1">
       <c r="A364" s="2" t="str">
         <f>IF(C364="","",VLOOKUP(C364,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20343,11 +20357,11 @@
         <v/>
       </c>
       <c r="M364" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J364:L364)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="365" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="365" spans="1:13" hidden="1">
       <c r="A365" s="2" t="str">
         <f>IF(C365="","",VLOOKUP(C365,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20369,11 +20383,11 @@
         <v/>
       </c>
       <c r="M365" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J365:L365)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="366" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="366" spans="1:13" hidden="1">
       <c r="A366" s="2" t="str">
         <f>IF(C366="","",VLOOKUP(C366,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20395,11 +20409,11 @@
         <v/>
       </c>
       <c r="M366" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J366:L366)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="367" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="367" spans="1:13" hidden="1">
       <c r="A367" s="2" t="str">
         <f>IF(C367="","",VLOOKUP(C367,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20421,11 +20435,11 @@
         <v/>
       </c>
       <c r="M367" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J367:L367)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="368" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="368" spans="1:13" hidden="1">
       <c r="A368" s="2" t="str">
         <f>IF(C368="","",VLOOKUP(C368,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20447,11 +20461,11 @@
         <v/>
       </c>
       <c r="M368" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J368:L368)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="369" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="369" spans="1:13" hidden="1">
       <c r="A369" s="2" t="str">
         <f>IF(C369="","",VLOOKUP(C369,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20473,11 +20487,11 @@
         <v/>
       </c>
       <c r="M369" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J369:L369)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="370" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="370" spans="1:13" hidden="1">
       <c r="A370" s="2" t="str">
         <f>IF(C370="","",VLOOKUP(C370,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20499,11 +20513,11 @@
         <v/>
       </c>
       <c r="M370" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J370:L370)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="371" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="371" spans="1:13" hidden="1">
       <c r="A371" s="2" t="str">
         <f>IF(C371="","",VLOOKUP(C371,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20525,11 +20539,11 @@
         <v/>
       </c>
       <c r="M371" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J371:L371)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="372" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="372" spans="1:13" hidden="1">
       <c r="A372" s="2" t="str">
         <f>IF(C372="","",VLOOKUP(C372,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20551,11 +20565,11 @@
         <v/>
       </c>
       <c r="M372" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J372:L372)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="373" spans="1:13">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="373" spans="1:13" hidden="1">
       <c r="J373" s="2" t="str">
         <f>IF(G373="","",VLOOKUP(G373,[1]ISO辞書!A:B,2,FALSE))</f>
         <v/>
@@ -20569,12 +20583,15 @@
         <v/>
       </c>
       <c r="M373" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(";",TRUE,J373:L373)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S77" xr:uid="{11153815-6F7F-462F-8165-5CE05A98A928}">
+  <autoFilter ref="A1:S373" xr:uid="{11153815-6F7F-462F-8165-5CE05A98A928}">
+    <filterColumn colId="3">
+      <colorFilter dxfId="0"/>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S373">
       <sortCondition ref="P1:P77"/>
     </sortState>

--- a/public/data/データ管理用.xlsx
+++ b/public/data/データ管理用.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\world_map_project\world-map-news-app\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC9F65A-D081-4E94-8CF6-CA5AFB3AA2A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A30A0260-5C72-46F7-BB1C-CAFE8B4AE6E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1272" yWindow="828" windowWidth="21540" windowHeight="12012" xr2:uid="{17EB953A-2661-4049-9616-0D3098A3DA36}"/>
+    <workbookView xWindow="-144" yWindow="420" windowWidth="21540" windowHeight="12012" xr2:uid="{17EB953A-2661-4049-9616-0D3098A3DA36}"/>
   </bookViews>
   <sheets>
     <sheet name="events-入力用" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1237" uniqueCount="623">
   <si>
     <t>country_iso3</t>
   </si>
@@ -3240,6 +3240,849 @@
       <t>ケイコク</t>
     </rPh>
     <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ベナン</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ワダグニ財務相が94%で大統領選挙に圧勝</t>
+    <rPh sb="12" eb="17">
+      <t>ダイトウリョウセンキョ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ベナンの大統領選挙でワダグニ財務相が暫定得票94%以上の圧勝を確実にし、独立選挙委員会は90%以上の票が集計済みと報告した。野党候補が敗北は認めており、投票率は58.78%だった。</t>
+    <rPh sb="4" eb="9">
+      <t>ダイトウリョウセンキョ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>コウホ</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>ミト</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>政権継続で経済政策は安定しやすい一方、圧勝の規模は選挙の正当性や国際的評価に影響を与え、日本の対ベナン投資・協力にも不確実性をもたらす。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/africa/benins-finance-minister-wadagni-wins-presidential-election-with-94-landslide-2026-04-13/</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>スーダン</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>スーダンのダルフールでドローン攻撃、民間人死傷</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>国境なき医師団は、ダルフールでスーダン軍による５件のドローン攻撃で２人が死亡、５６人が負傷したと発表。国連やユニセフは子どもを含む民間被害の急増を警告している。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>民間人と子どもの被害増は人道危機と地域不安を深刻化させるリスクが高い。</t>
+    <rPh sb="32" eb="33">
+      <t>タカ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/africa/drone-attacks-sudan-kill-two-injure-56-msf-says-2026-04-14/</t>
+  </si>
+  <si>
+    <t>ボツワナ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ボツワナ、オマーンと資源・エネルギー協定を締結</t>
+    <rPh sb="21" eb="23">
+      <t>テイケツ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ボツワナがオマーンと複数の協定を締結。領土の約70％を対象とする鉱物探査、最低25年稼働の500MW太陽光発電所、ナミビアのウォルビスベイを含む石油貯蔵整備などを盛り込む。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>鉱物開発と再生可能エネルギー投資で収益源が多様化し、エネルギー・資源供給の安定化が進む。日本企業の資源確保や投資機会の拡大につながる可能性がある。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/sustainability/climate-energy/botswana-signs-energy-mineral-exploration-deals-with-oman-2026-04-13/</t>
+  </si>
+  <si>
+    <t>南アフリカ</t>
+    <rPh sb="0" eb="1">
+      <t>ミナミ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>南ア、ドイツと気候変動対策と鉱物資源協力で合意</t>
+    <rPh sb="9" eb="11">
+      <t>ヘンドウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>タイサク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シゲン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ゴウイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ドイツは南アフリカに対し電力網と再生エネルギーに2億ユーロの優遇気候融資を提供すると発表。両国はグリーン水素や電池のバリューチェーン向けに約2.7億ユーロの支援延長と重要鉱物での協力拡大でも合意。</t>
+    <rPh sb="4" eb="5">
+      <t>ミナミ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>サイセイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>融資と鉱物協力は南アの脱炭素と電力安定化を支援し、電池素材の供給で日本企業の調達先多様化に影響する。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/africa/south-africa-agrees-new-climate-loan-critical-minerals-cooperation-germany-visit-2026-04-13/</t>
+  </si>
+  <si>
+    <t>ナイジェリア</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ナイジェリアの市場で空爆、200人超犠牲</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ナイジェリア軍の軍用機が北東部の村の市場を空爆。少なくとも200人の死亡が報告される。攻撃はイスラム過激派追撃中に行われたと伝えられる</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>この空爆により治安悪化と深刻な人道危機が生じ、国際的批判や援助需要が高まる可能性。</t>
+    <rPh sb="2" eb="4">
+      <t>クウバク</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ショウ</t>
+    </rPh>
+    <rPh sb="37" eb="40">
+      <t>カノウセイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/africa/nigerian-airstrike-village-market-is-latest-which-civilians-have-been-killed-2026-04-13/</t>
+  </si>
+  <si>
+    <t>ナイジェリアとモロッコ、天然ガスパイプラインに合意へ</t>
+    <rPh sb="12" eb="14">
+      <t>テンネン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>両国を結ぶ天然ガスパイプラインの政府間協定が今年署名されると発表。容量は最大30bcmで、2031年に最初の供給を見込む。</t>
+    <rPh sb="51" eb="53">
+      <t>サイショ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>モロッコ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>地域のエネルギー統合が進み、国際供給網と投資環境に影響。日本企業の資源・投資機会が広がる可能性も。</t>
+    <rPh sb="44" eb="47">
+      <t>カノウセイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/sustainability/boards-policy-regulation/intergovernmental-deal-25-billion-nigeria-morocco-gas-pipeline-due-this-year-2026-04-13/</t>
+  </si>
+  <si>
+    <t>ジブチ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ジブチ大統領選挙、現職が得票率97.8%で再選</t>
+    <rPh sb="6" eb="8">
+      <t>センキョ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ゲンショク</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>トクヒョウリツ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ジブチのゲレ大統領が大統領選挙で得票率97.8%で再選、6期目に入る。議会は2025年、立候補の年齢制限を撤廃し主要野党は選挙をボイコットしていた</t>
+    <rPh sb="10" eb="13">
+      <t>ダイトウリョウ</t>
+    </rPh>
+    <rPh sb="44" eb="47">
+      <t>リッコウホ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>紅海に面する港湾と外国軍基地を有するジブチで長期政権が続くことで、地域の安全保障政策に影響が生じる。</t>
+    <rPh sb="0" eb="2">
+      <t>コウカイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>メン</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ユウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>チイキ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>ショウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/africa/djibouti-president-wins-election-with-978-vote-state-media-says-2026-04-11/</t>
+  </si>
+  <si>
+    <t>民主同盟の新党首にケープタウン市長が就任</t>
+    <rPh sb="0" eb="4">
+      <t>ミンシュドウメイ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>シントウシュ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>シチョウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>シュウニン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>民主同盟（DA）がケープタウン市長のルイス氏を新党首に選出。同氏は地方選で勢力拡大を図る考えを示した。</t>
+    <rPh sb="21" eb="22">
+      <t>ウジ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ドウシ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>与党アフリカ民族会議（ANC）の支持低下を受け、地方政局が変動する可能性。在南アの日本企業の事業環境や投資リスクに影響する。</t>
+    <rPh sb="33" eb="36">
+      <t>カノウセイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/africa/south-african-coalition-partner-da-elects-hill-lewis-leader-2026-04-12/</t>
+  </si>
+  <si>
+    <t>リビア</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>リビアにて13年ぶりに統一予算が成立</t>
+    <rPh sb="16" eb="18">
+      <t>セイリツ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>東西に分かれた二つの立法機関が約300億ドルの統一国家予算を承認。リビア中央銀行は財政安定と資源配分の一元化を期待すると発表。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>統一予算は石油収入と支出の管理を一本化し、政治的統合と地域安定を後押しする。エネルギー供給安定は日本企業の投資環境にも影響を与える。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/africa/libya-signs-first-unified-state-budget-over-decade-2026-04-11/</t>
+  </si>
+  <si>
+    <t>カナダ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>カナダ与党、補欠選挙で単独過半数確保</t>
+    <rPh sb="3" eb="5">
+      <t>ヨトウ</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>ホケツセンキョ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>カナダの与党自由党が補欠選で勝利し、下院にて単独過半数を確保。</t>
+    <rPh sb="4" eb="6">
+      <t>ヨトウ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>ジユウトウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カイン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>政権基盤が安定することで、対米貿易摩擦への対応迅速化や同国への投資拡大政策に影響が発生。</t>
+    <rPh sb="0" eb="2">
+      <t>セイケン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キバン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>アンテイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>タイベイ</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>ジンソクカ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ドウコク</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>トウシ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>カクダイ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ハッセイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/americas/canadas-carney-set-win-majority-government-special-elections-2026-04-13/</t>
+  </si>
+  <si>
+    <t>仏マクロン大統領とベネズエラ野党指導者が会談</t>
+    <rPh sb="0" eb="1">
+      <t>フツ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ダイトウリョウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヤトウ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>シドウシャ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>カイダン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>仏マクロン大統領がベネズエラ野党指導者マチャド氏と会談。ベネズエラの平和的で民主的な政権移行について協議。</t>
+    <rPh sb="0" eb="1">
+      <t>フツ</t>
+    </rPh>
+    <rPh sb="14" eb="19">
+      <t>ヤトウシドウシャ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>欧州諸国の関与表明はベネズエラ政局に国際的圧力をかけ、エネルギーや外交課題での検討加速化が期待される。</t>
+    <rPh sb="2" eb="4">
+      <t>ショコク</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ケントウ</t>
+    </rPh>
+    <rPh sb="41" eb="44">
+      <t>カソクカ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>キタイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/americas/frances-macron-hold-talks-with-venezuelan-opposition-leader-machado-2026-04-13/</t>
+  </si>
+  <si>
+    <t>北朝鮮、新型駆逐艦からミサイルを試射</t>
+    <rPh sb="0" eb="3">
+      <t>キタチョウセン</t>
+    </rPh>
+    <rPh sb="4" eb="9">
+      <t>シンガタクチクカン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>北朝鮮が日本海にて新型駆逐艦から戦略巡航ミサイルと対艦ミサイルを発射し、巡航ミサイルは2時間超飛行して目標に命中したと報じられる。</t>
+    <rPh sb="4" eb="7">
+      <t>ニホンカイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>軍事力強化は朝鮮半島の緊張を高め、日米韓の監視・抑止の強化や海上安全保証対策の協議が促進される。</t>
+    <rPh sb="27" eb="29">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ホショウ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>キョウギ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ソクシン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/asia-pacific/north-korea-tests-cruise-anti-ship-missiles-naval-destroyer-2026-04-13/</t>
+  </si>
+  <si>
+    <t>中国、米によるホルムズ海峡封鎖に懸念</t>
+    <rPh sb="3" eb="4">
+      <t>ベイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>米軍のホルムズ海峡の海上封鎖表明を受け、同海峡の封鎖は国際社会の利益に反すると中国が抑制を求める。</t>
+    <rPh sb="7" eb="9">
+      <t>カイキョウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ドウ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>チュウゴク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ホルムズ封鎖は世界の石油供給と海運に打撃を与え、日本のエネルギー安定や輸送コストにも影響を及ぼす可能性がある。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/china/china-urges-restraint-over-us-blockade-strait-hormuz-backs-talks-2026-04-13/</t>
+  </si>
+  <si>
+    <t>米豪比、南シナ海での合同軍事演習を実施</t>
+    <rPh sb="10" eb="14">
+      <t>ゴウドウグンジ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ジッシ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>アメリカ、オーストラリア、フィリピンが南シナ海で合同軍事演習を実施。連携向上が図られる。</t>
+    <rPh sb="19" eb="20">
+      <t>ミナミ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="24" eb="30">
+      <t>ゴウドウグンジエンシュウ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>レンケイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>コウジョウ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ハカ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>フィリピン</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>対中抑止と連携強化を示す演習は地域の安全保障に影響。海上輸送路の安全性が高まる一方で中国の反応も用注目。</t>
+    <rPh sb="18" eb="22">
+      <t>アンゼンホショウ</t>
+    </rPh>
+    <rPh sb="26" eb="31">
+      <t>カイジョウユソウロ</t>
+    </rPh>
+    <rPh sb="32" eb="35">
+      <t>アンゼンセイ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>イッポウ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>チュウゴク</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ハンノウ</t>
+    </rPh>
+    <rPh sb="48" eb="51">
+      <t>ヨウチュウモク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/business/aerospace-defense/us-australia-philippines-hold-second-joint-drills-south-china-sea-this-year-2026-04-13/</t>
+  </si>
+  <si>
+    <t>アメリカがホルムズ海峡封鎖を開始</t>
+    <rPh sb="9" eb="13">
+      <t>カイキョウフウサ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カイシ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>停戦協議決裂を受け、米軍がホルムズ海峡の封鎖を開始したと発表。イランは湾岸諸国の港への報復を警告し、原油は再び100ドル超へ上昇。</t>
+    <rPh sb="0" eb="2">
+      <t>テイセン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キョウギ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カイキョウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>フウサ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>カイシ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>封鎖は世界の石油供給と海運に重大影響を与え、日本のエネルギー安定や輸入コスト上昇を招く恐れがある。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/middle-east/us-blockade-iran-after-talks-fail-yield-a-deal-2026-04-13/</t>
+  </si>
+  <si>
+    <t>ポーランド</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>韓国とポーランドが連携強化を確認</t>
+    <rPh sb="11" eb="13">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>首脳会談にて両国関係を包括的戦略的パートナーシップに格上げすることが合意。防衛協力を軸に共同生産や技術移転、エネルギーや先端産業での協力拡大も確認される。</t>
+    <rPh sb="0" eb="4">
+      <t>シュノウカイダン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>防衛連携の深化は抑止力を高め、韓国の防衛産業の輸出拡大を促す。日本の安全保障や調達先にも影響を与える。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/asia-pacific/south-korea-poland-upgrade-ties-comprehensive-strategic-partnership-media-2026-04-13/</t>
+  </si>
+  <si>
+    <t>パキスタンが戦闘機をサウジアラビアへ派遣</t>
+    <rPh sb="6" eb="8">
+      <t>セントウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>両国の相互防衛協定に基づき、パキスタンの戦闘機がサウジアラビアに派遣される。イラン情勢を受けての対応と発表。</t>
+    <rPh sb="0" eb="2">
+      <t>リョウコク</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>セントウキ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ハケン</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ジョウセイ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>ハッピョウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>両国の軍事連携強化は抑止力を高める一方、地域緊張とエネルギー不安定化を招き、国際的な外交・安全保障対応を複雑化させる。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/asia-pacific/saudi-arabia-says-pakistan-sends-fighter-jets-kingdom-under-defence-pact-2026-04-11/</t>
+  </si>
+  <si>
+    <t>スペイン</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>スペインと中国の首脳会談</t>
+    <rPh sb="5" eb="7">
+      <t>チュウゴク</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>シュノウカイダン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>スペイン首相が中国を訪問、関係強化で一致し、貿易赤字是正や農産品の対中輸出拡大など経済協力を進めることで合意した。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>欧州主要国の中国接近は米中対立や貿易・安全保障政策にも波及するため、日本の対中経済戦略や同盟調整にも影響を与える。</t>
+    <rPh sb="6" eb="8">
+      <t>チュウゴク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/china/spanish-premier-chinas-xi-pledge-closer-ties-amid-crumbling-international-order-2026-04-14/</t>
+  </si>
+  <si>
+    <t>ハンガリー</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>マジャール次期首相、ハンガリー国営放送停止を指示</t>
+    <rPh sb="22" eb="24">
+      <t>シジ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>偏向報道是正のため公営メディアのニュース番組を当面停止すると発表。改革と報道の中立化を優先する意向。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/business/media-telecom/hungarys-election-winner-magyar-says-suspend-state-media-news-broadcast-2026-04-13/</t>
+  </si>
+  <si>
+    <t>ハンガリー議会選挙で政権交代へ</t>
+    <rPh sb="5" eb="9">
+      <t>ギカイセンキョ</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>セイケンコウタイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>オルバン首相が議会選挙で敗北。経済停滞への不満で親EU路線のマジャール氏率いる中道右派政党が勝利。</t>
+    <rPh sb="7" eb="11">
+      <t>ギカイセンキョ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ハイボク</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ウジ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ヒキ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>セイトウ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ショウリ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>欧州連合との関係修復や資金復帰が進めば、ウクライナ支援の拡大が見込まれる。日本の対欧・対中経済・安全保障戦略にも影響を与える。</t>
+    <rPh sb="25" eb="27">
+      <t>シエン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>カクダイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ミコ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/europe/orban-ousted-after-16-years-hungarians-flock-pro-eu-rival-2026-04-12/</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>NATO、ホルムズ封鎖に不参加を表明</t>
+    <rPh sb="16" eb="18">
+      <t>ヒョウメイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>米軍のホルムズ海峡封鎖について、NATO加盟国の英仏は参加を拒否、紛争終結後に航行再開をめざすことを提案。</t>
+    <rPh sb="0" eb="2">
+      <t>ベイグン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カイキョウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>エイフツ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>テイアン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>米欧の対立はNATOの結束を揺るがし、海上輸送と原油市場の不安が日本のエネルギー安定や輸入コストに影響を及ぼす。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/europe/nato-allies-refuse-join-trumps-strait-hormuz-blockade-2026-04-13/</t>
+  </si>
+  <si>
+    <t>ウクライナとロシアが捕虜交換を実施</t>
+    <rPh sb="10" eb="14">
+      <t>ホリョコウカン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジッシ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>UAEの仲介で両国が175名の捕虜交換を実施した。</t>
+    <rPh sb="7" eb="9">
+      <t>リョウコク</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>緊張緩和の一歩だが戦闘終結のめどはつかず。</t>
+    <rPh sb="11" eb="13">
+      <t>シュウケツ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/europe/russia-ukraine-carry-out-pow-swap-defence-ministry-says-2026-04-11/</t>
+  </si>
+  <si>
+    <t>イスラエルの情報機関にて新長官が任命される</t>
+    <rPh sb="6" eb="10">
+      <t>ジョウホウキカン</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>シンチョウカン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ニンメイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>国家諜報機関モサドの新長官が新たに承認されたとネタニヤフ首相府が発表。</t>
+    <rPh sb="14" eb="15">
+      <t>アラ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>諜報機関の長官交代は中東情勢と対テロ対応に影響を与え、日本の外交・情報連携にも波及する。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/middle-east/israel-approves-appointment-new-intelligence-agency-chief-2026-04-12/</t>
+  </si>
+  <si>
+    <t>イラク</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>イラクにて新たな大統領が選出される</t>
+    <rPh sb="5" eb="6">
+      <t>アラ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>ダイトウリョウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>センシュツ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>クルド系のアメディ氏が大統領に選出される。同氏は元環境相、愛国クルド同盟(PUK)の政治局長を務める。</t>
+    <rPh sb="9" eb="10">
+      <t>ウジ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>センシュツ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ドウシ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>首相指名が次の焦点となり、米・イランの影響力を踏まえた外交調整と政局安定が重要になる</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>https://www.reuters.com/world/middle-east/iraqi-parliament-elects-nizar-amedi-countrys-new-president-2026-04-11/</t>
   </si>
 </sst>
 </file>
@@ -3870,7 +4713,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3891,9 +4734,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3942,16 +4782,7 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="良い" xfId="6" builtinId="26" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC0E6F5"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -7048,13 +7879,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11153815-6F7F-462F-8165-5CE05A98A928}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:S373"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="2" width="0" style="2" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="34.19921875" style="7" customWidth="1"/>
-    <col min="5" max="5" width="34.19921875" customWidth="1"/>
+    <col min="4" max="5" width="34.19921875" customWidth="1"/>
     <col min="10" max="12" width="8.796875" style="2" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="8.796875" style="2"/>
     <col min="16" max="16" width="10.3984375" bestFit="1" customWidth="1"/>
@@ -7070,7 +7899,7 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
@@ -7119,7 +7948,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" hidden="1">
+    <row r="2" spans="1:19">
       <c r="A2" s="2" t="str">
         <f>IF(C2="","",VLOOKUP(C2,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>SVN</v>
@@ -7131,7 +7960,7 @@
       <c r="C2" t="s">
         <v>161</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" t="s">
         <v>162</v>
       </c>
       <c r="E2" t="s">
@@ -7175,7 +8004,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:19" hidden="1">
+    <row r="3" spans="1:19">
       <c r="A3" s="2" t="str">
         <f>IF(C3="","",VLOOKUP(C3,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>TCD</v>
@@ -7187,7 +8016,7 @@
       <c r="C3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" t="s">
         <v>20</v>
       </c>
       <c r="E3" t="s">
@@ -7234,7 +8063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:19" hidden="1">
+    <row r="4" spans="1:19">
       <c r="A4" s="2" t="str">
         <f>IF(C4="","",VLOOKUP(C4,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>CRI</v>
@@ -7246,7 +8075,7 @@
       <c r="C4" t="s">
         <v>59</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" t="s">
         <v>60</v>
       </c>
       <c r="E4" t="s">
@@ -7293,7 +8122,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:19" hidden="1">
+    <row r="5" spans="1:19">
       <c r="A5" s="2" t="str">
         <f>IF(C5="","",VLOOKUP(C5,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>CHN</v>
@@ -7305,7 +8134,7 @@
       <c r="C5" t="s">
         <v>71</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" t="s">
         <v>106</v>
       </c>
       <c r="E5" t="s">
@@ -7349,7 +8178,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:19" hidden="1">
+    <row r="6" spans="1:19">
       <c r="A6" s="2" t="str">
         <f>IF(C6="","",VLOOKUP(C6,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>ISR</v>
@@ -7361,7 +8190,7 @@
       <c r="C6" t="s">
         <v>153</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" t="s">
         <v>154</v>
       </c>
       <c r="E6" t="s">
@@ -7408,7 +8237,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:19" hidden="1">
+    <row r="7" spans="1:19">
       <c r="A7" s="2" t="str">
         <f>IF(C7="","",VLOOKUP(C7,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>ITA</v>
@@ -7420,7 +8249,7 @@
       <c r="C7" t="s">
         <v>167</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" t="s">
         <v>168</v>
       </c>
       <c r="E7" t="s">
@@ -7464,7 +8293,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:19" hidden="1">
+    <row r="8" spans="1:19">
       <c r="A8" s="2" t="str">
         <f>IF(C8="","",VLOOKUP(C8,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>JPN</v>
@@ -7476,7 +8305,7 @@
       <c r="C8" t="s">
         <v>102</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" t="s">
         <v>103</v>
       </c>
       <c r="E8" t="s">
@@ -7523,7 +8352,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:19" hidden="1">
+    <row r="9" spans="1:19">
       <c r="A9" s="2" t="str">
         <f>IF(C9="","",VLOOKUP(C9,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>ISR</v>
@@ -7535,7 +8364,7 @@
       <c r="C9" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" t="s">
         <v>131</v>
       </c>
       <c r="E9" t="s">
@@ -7582,7 +8411,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:19" hidden="1">
+    <row r="10" spans="1:19">
       <c r="A10" s="2" t="str">
         <f>IF(C10="","",VLOOKUP(C10,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>EU</v>
@@ -7594,7 +8423,7 @@
       <c r="C10" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" t="s">
         <v>147</v>
       </c>
       <c r="E10" t="s">
@@ -7638,7 +8467,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:19" hidden="1">
+    <row r="11" spans="1:19">
       <c r="A11" s="2" t="str">
         <f>IF(C11="","",VLOOKUP(C11,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>MEX</v>
@@ -7650,7 +8479,7 @@
       <c r="C11" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" t="s">
         <v>51</v>
       </c>
       <c r="E11" t="s">
@@ -7697,7 +8526,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:19" hidden="1">
+    <row r="12" spans="1:19">
       <c r="A12" s="2" t="str">
         <f>IF(C12="","",VLOOKUP(C12,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>CYP</v>
@@ -7709,7 +8538,7 @@
       <c r="C12" t="s">
         <v>117</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" t="s">
         <v>118</v>
       </c>
       <c r="E12" t="s">
@@ -7756,7 +8585,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:19" hidden="1">
+    <row r="13" spans="1:19">
       <c r="A13" s="2" t="str">
         <f>IF(C13="","",VLOOKUP(C13,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>DNK</v>
@@ -7768,7 +8597,7 @@
       <c r="C13" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" t="s">
         <v>123</v>
       </c>
       <c r="E13" t="s">
@@ -7812,7 +8641,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:19" hidden="1">
+    <row r="14" spans="1:19">
       <c r="A14" s="2" t="str">
         <f>IF(C14="","",VLOOKUP(C14,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>GBR</v>
@@ -7824,7 +8653,7 @@
       <c r="C14" t="s">
         <v>120</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" t="s">
         <v>135</v>
       </c>
       <c r="E14" t="s">
@@ -7871,7 +8700,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:19" hidden="1">
+    <row r="15" spans="1:19">
       <c r="A15" s="2" t="str">
         <f>IF(C15="","",VLOOKUP(C15,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>KEN</v>
@@ -7883,7 +8712,7 @@
       <c r="C15" t="s">
         <v>143</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" t="s">
         <v>144</v>
       </c>
       <c r="E15" t="s">
@@ -7930,7 +8759,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:19" hidden="1">
+    <row r="16" spans="1:19">
       <c r="A16" s="2" t="str">
         <f>IF(C16="","",VLOOKUP(C16,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>USA</v>
@@ -7942,7 +8771,7 @@
       <c r="C16" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" t="s">
         <v>55</v>
       </c>
       <c r="E16" t="s">
@@ -7989,7 +8818,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:19" hidden="1">
+    <row r="17" spans="1:19">
       <c r="A17" s="2" t="str">
         <f>IF(C17="","",VLOOKUP(C17,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>PAK</v>
@@ -8001,7 +8830,7 @@
       <c r="C17" t="s">
         <v>91</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" t="s">
         <v>92</v>
       </c>
       <c r="E17" t="s">
@@ -8048,7 +8877,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:19" hidden="1">
+    <row r="18" spans="1:19">
       <c r="A18" s="2" t="str">
         <f>IF(C18="","",VLOOKUP(C18,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>USA</v>
@@ -8060,7 +8889,7 @@
       <c r="C18" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" t="s">
         <v>96</v>
       </c>
       <c r="E18" t="s">
@@ -8107,7 +8936,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:19" hidden="1">
+    <row r="19" spans="1:19">
       <c r="A19" s="2" t="str">
         <f>IF(C19="","",VLOOKUP(C19,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>IRN</v>
@@ -8119,7 +8948,7 @@
       <c r="C19" t="s">
         <v>66</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" t="s">
         <v>99</v>
       </c>
       <c r="E19" t="s">
@@ -8169,7 +8998,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:19" hidden="1">
+    <row r="20" spans="1:19">
       <c r="A20" s="2" t="str">
         <f>IF(C20="","",VLOOKUP(C20,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>UKR</v>
@@ -8181,7 +9010,7 @@
       <c r="C20" t="s">
         <v>109</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" t="s">
         <v>113</v>
       </c>
       <c r="E20" t="s">
@@ -8228,7 +9057,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:19" hidden="1">
+    <row r="21" spans="1:19">
       <c r="A21" s="2" t="str">
         <f>IF(C21="","",VLOOKUP(C21,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>USA</v>
@@ -8240,7 +9069,7 @@
       <c r="C21" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" t="s">
         <v>29</v>
       </c>
       <c r="E21" t="s">
@@ -8287,7 +9116,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:19" hidden="1">
+    <row r="22" spans="1:19">
       <c r="A22" s="2" t="str">
         <f>IF(C22="","",VLOOKUP(C22,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>CAN</v>
@@ -8299,7 +9128,7 @@
       <c r="C22" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" t="s">
         <v>34</v>
       </c>
       <c r="E22" t="s">
@@ -8352,7 +9181,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:19" hidden="1">
+    <row r="23" spans="1:19">
       <c r="A23" s="2" t="str">
         <f>IF(C23="","",VLOOKUP(C23,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>EU</v>
@@ -8364,7 +9193,7 @@
       <c r="C23" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" t="s">
         <v>43</v>
       </c>
       <c r="E23" t="s">
@@ -8411,7 +9240,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:19" hidden="1">
+    <row r="24" spans="1:19">
       <c r="A24" s="2" t="str">
         <f>IF(C24="","",VLOOKUP(C24,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>CAN</v>
@@ -8423,7 +9252,7 @@
       <c r="C24" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" t="s">
         <v>47</v>
       </c>
       <c r="E24" t="s">
@@ -8476,7 +9305,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:19" hidden="1">
+    <row r="25" spans="1:19">
       <c r="A25" s="2" t="str">
         <f>IF(C25="","",VLOOKUP(C25,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>NPL</v>
@@ -8488,7 +9317,7 @@
       <c r="C25" t="s">
         <v>76</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" t="s">
         <v>77</v>
       </c>
       <c r="E25" t="s">
@@ -8532,7 +9361,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:19" hidden="1">
+    <row r="26" spans="1:19">
       <c r="A26" s="2" t="str">
         <f>IF(C26="","",VLOOKUP(C26,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>PRK</v>
@@ -8544,7 +9373,7 @@
       <c r="C26" t="s">
         <v>86</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" t="s">
         <v>87</v>
       </c>
       <c r="E26" t="s">
@@ -8591,7 +9420,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:19" hidden="1">
+    <row r="27" spans="1:19">
       <c r="A27" s="2" t="str">
         <f>IF(C27="","",VLOOKUP(C27,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>UKR</v>
@@ -8603,7 +9432,7 @@
       <c r="C27" t="s">
         <v>109</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" t="s">
         <v>110</v>
       </c>
       <c r="E27" t="s">
@@ -8650,7 +9479,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:19" hidden="1">
+    <row r="28" spans="1:19">
       <c r="A28" s="2" t="str">
         <f>IF(C28="","",VLOOKUP(C28,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>COD</v>
@@ -8662,7 +9491,7 @@
       <c r="C28" t="s">
         <v>139</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" t="s">
         <v>140</v>
       </c>
       <c r="E28" t="s">
@@ -8709,7 +9538,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:19" hidden="1">
+    <row r="29" spans="1:19">
       <c r="A29" s="2" t="str">
         <f>IF(C29="","",VLOOKUP(C29,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>CHN</v>
@@ -8721,7 +9550,7 @@
       <c r="C29" t="s">
         <v>71</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" t="s">
         <v>72</v>
       </c>
       <c r="E29" t="s">
@@ -8768,7 +9597,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:19" hidden="1">
+    <row r="30" spans="1:19">
       <c r="A30" s="2" t="str">
         <f>IF(C30="","",VLOOKUP(C30,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>IDN</v>
@@ -8780,7 +9609,7 @@
       <c r="C30" t="s">
         <v>82</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" t="s">
         <v>83</v>
       </c>
       <c r="E30" t="s">
@@ -8824,7 +9653,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:19" hidden="1">
+    <row r="31" spans="1:19">
       <c r="A31" s="2" t="str">
         <f>IF(C31="","",VLOOKUP(C31,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>UKR</v>
@@ -8836,7 +9665,7 @@
       <c r="C31" t="s">
         <v>109</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" t="s">
         <v>126</v>
       </c>
       <c r="E31" t="s">
@@ -8886,7 +9715,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:19" hidden="1">
+    <row r="32" spans="1:19">
       <c r="A32" s="2" t="str">
         <f>IF(C32="","",VLOOKUP(C32,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>NPL</v>
@@ -8898,7 +9727,7 @@
       <c r="C32" t="s">
         <v>217</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" t="s">
         <v>218</v>
       </c>
       <c r="E32" t="s">
@@ -8942,7 +9771,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:19" hidden="1">
+    <row r="33" spans="1:19">
       <c r="A33" s="2" t="str">
         <f>IF(C33="","",VLOOKUP(C33,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>YEM</v>
@@ -8954,7 +9783,7 @@
       <c r="C33" t="s">
         <v>63</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" t="s">
         <v>64</v>
       </c>
       <c r="E33" t="s">
@@ -9007,7 +9836,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:19" hidden="1">
+    <row r="34" spans="1:19">
       <c r="A34" s="2" t="str">
         <f>IF(C34="","",VLOOKUP(C34,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>UKR</v>
@@ -9019,7 +9848,7 @@
       <c r="C34" t="s">
         <v>202</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" t="s">
         <v>203</v>
       </c>
       <c r="E34" t="s">
@@ -9066,7 +9895,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:19" hidden="1">
+    <row r="35" spans="1:19">
       <c r="A35" s="2" t="str">
         <f>IF(C35="","",VLOOKUP(C35,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>EGY</v>
@@ -9078,7 +9907,7 @@
       <c r="C35" t="s">
         <v>259</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" t="s">
         <v>260</v>
       </c>
       <c r="F35" t="s">
@@ -9119,7 +9948,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:19" hidden="1">
+    <row r="36" spans="1:19">
       <c r="A36" s="2" t="str">
         <f>IF(C36="","",VLOOKUP(C36,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>CUB</v>
@@ -9131,7 +9960,7 @@
       <c r="C36" t="s">
         <v>172</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" t="s">
         <v>173</v>
       </c>
       <c r="E36" t="s">
@@ -9181,7 +10010,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:19" hidden="1">
+    <row r="37" spans="1:19">
       <c r="A37" s="2" t="str">
         <f>IF(C37="","",VLOOKUP(C37,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>LBN</v>
@@ -9193,7 +10022,7 @@
       <c r="C37" t="s">
         <v>157</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D37" t="s">
         <v>190</v>
       </c>
       <c r="E37" t="s">
@@ -9240,7 +10069,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:19" hidden="1">
+    <row r="38" spans="1:19">
       <c r="A38" s="2" t="str">
         <f>IF(C38="","",VLOOKUP(C38,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>RUS</v>
@@ -9252,7 +10081,7 @@
       <c r="C38" t="s">
         <v>176</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="D38" t="s">
         <v>207</v>
       </c>
       <c r="E38" t="s">
@@ -9299,7 +10128,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:19" hidden="1">
+    <row r="39" spans="1:19">
       <c r="A39" s="2" t="str">
         <f>IF(C39="","",VLOOKUP(C39,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>AFG</v>
@@ -9311,7 +10140,7 @@
       <c r="C39" t="s">
         <v>221</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="D39" t="s">
         <v>222</v>
       </c>
       <c r="E39" t="s">
@@ -9358,7 +10187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:19" hidden="1">
+    <row r="40" spans="1:19">
       <c r="A40" s="2" t="str">
         <f>IF(C40="","",VLOOKUP(C40,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>XKK</v>
@@ -9370,7 +10199,7 @@
       <c r="C40" t="s">
         <v>229</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="D40" t="s">
         <v>230</v>
       </c>
       <c r="E40" t="s">
@@ -9423,7 +10252,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:19" hidden="1">
+    <row r="41" spans="1:19">
       <c r="A41" s="2" t="str">
         <f>IF(C41="","",VLOOKUP(C41,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>PAK</v>
@@ -9435,7 +10264,7 @@
       <c r="C41" t="s">
         <v>225</v>
       </c>
-      <c r="D41" s="7" t="s">
+      <c r="D41" t="s">
         <v>234</v>
       </c>
       <c r="E41" t="s">
@@ -9482,7 +10311,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:19" hidden="1">
+    <row r="42" spans="1:19">
       <c r="A42" s="2" t="str">
         <f>IF(C42="","",VLOOKUP(C42,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>USA</v>
@@ -9494,7 +10323,7 @@
       <c r="C42" t="s">
         <v>177</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="D42" t="s">
         <v>254</v>
       </c>
       <c r="E42" t="s">
@@ -9541,7 +10370,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:19" hidden="1">
+    <row r="43" spans="1:19">
       <c r="A43" s="2" t="str">
         <f>IF(C43="","",VLOOKUP(C43,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>EGY</v>
@@ -9553,7 +10382,7 @@
       <c r="C43" t="s">
         <v>259</v>
       </c>
-      <c r="D43" s="7" t="s">
+      <c r="D43" t="s">
         <v>262</v>
       </c>
       <c r="F43" t="s">
@@ -9597,7 +10426,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:19" hidden="1">
+    <row r="44" spans="1:19">
       <c r="A44" s="2" t="str">
         <f>IF(C44="","",VLOOKUP(C44,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>SOM</v>
@@ -9609,7 +10438,7 @@
       <c r="C44" t="s">
         <v>266</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="D44" t="s">
         <v>267</v>
       </c>
       <c r="E44" t="s">
@@ -9653,7 +10482,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:19" hidden="1">
+    <row r="45" spans="1:19">
       <c r="A45" s="2" t="str">
         <f>IF(C45="","",VLOOKUP(C45,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>IRN</v>
@@ -9665,7 +10494,7 @@
       <c r="C45" t="s">
         <v>188</v>
       </c>
-      <c r="D45" s="7" t="s">
+      <c r="D45" t="s">
         <v>270</v>
       </c>
       <c r="E45" t="s">
@@ -9712,7 +10541,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:19" hidden="1">
+    <row r="46" spans="1:19">
       <c r="A46" s="2" t="str">
         <f>IF(C46="","",VLOOKUP(C46,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>PRY</v>
@@ -9724,7 +10553,7 @@
       <c r="C46" t="s">
         <v>182</v>
       </c>
-      <c r="D46" s="7" t="s">
+      <c r="D46" t="s">
         <v>183</v>
       </c>
       <c r="E46" t="s">
@@ -9768,7 +10597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:19" hidden="1">
+    <row r="47" spans="1:19">
       <c r="A47" s="2" t="str">
         <f>IF(C47="","",VLOOKUP(C47,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>USA</v>
@@ -9780,7 +10609,7 @@
       <c r="C47" t="s">
         <v>177</v>
       </c>
-      <c r="D47" s="7" t="s">
+      <c r="D47" t="s">
         <v>186</v>
       </c>
       <c r="E47" t="s">
@@ -9827,7 +10656,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:19" hidden="1">
+    <row r="48" spans="1:19">
       <c r="A48" s="2" t="str">
         <f>IF(C48="","",VLOOKUP(C48,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>GBR</v>
@@ -9839,7 +10668,7 @@
       <c r="C48" t="s">
         <v>193</v>
       </c>
-      <c r="D48" s="7" t="s">
+      <c r="D48" t="s">
         <v>194</v>
       </c>
       <c r="E48" t="s">
@@ -9886,7 +10715,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:19" hidden="1">
+    <row r="49" spans="1:19">
       <c r="A49" s="2" t="str">
         <f>IF(C49="","",VLOOKUP(C49,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>ISR</v>
@@ -9898,7 +10727,7 @@
       <c r="C49" t="s">
         <v>153</v>
       </c>
-      <c r="D49" s="7" t="s">
+      <c r="D49" t="s">
         <v>199</v>
       </c>
       <c r="E49" t="s">
@@ -9945,7 +10774,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:19" hidden="1">
+    <row r="50" spans="1:19">
       <c r="A50" s="2" t="str">
         <f>IF(C50="","",VLOOKUP(C50,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>ITA</v>
@@ -9957,7 +10786,7 @@
       <c r="C50" t="s">
         <v>167</v>
       </c>
-      <c r="D50" s="7" t="s">
+      <c r="D50" t="s">
         <v>210</v>
       </c>
       <c r="E50" t="s">
@@ -10004,7 +10833,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:19" hidden="1">
+    <row r="51" spans="1:19">
       <c r="A51" s="2" t="str">
         <f>IF(C51="","",VLOOKUP(C51,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>FRA</v>
@@ -10016,7 +10845,7 @@
       <c r="C51" t="s">
         <v>213</v>
       </c>
-      <c r="D51" s="7" t="s">
+      <c r="D51" t="s">
         <v>214</v>
       </c>
       <c r="E51" t="s">
@@ -10066,7 +10895,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:19" hidden="1">
+    <row r="52" spans="1:19">
       <c r="A52" s="2" t="str">
         <f>IF(C52="","",VLOOKUP(C52,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>THA</v>
@@ -10078,7 +10907,7 @@
       <c r="C52" t="s">
         <v>237</v>
       </c>
-      <c r="D52" s="7" t="s">
+      <c r="D52" t="s">
         <v>238</v>
       </c>
       <c r="E52" t="s">
@@ -10122,7 +10951,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:19" hidden="1">
+    <row r="53" spans="1:19">
       <c r="A53" s="2" t="str">
         <f>IF(C53="","",VLOOKUP(C53,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>KOR</v>
@@ -10134,7 +10963,7 @@
       <c r="C53" t="s">
         <v>241</v>
       </c>
-      <c r="D53" s="7" t="s">
+      <c r="D53" t="s">
         <v>242</v>
       </c>
       <c r="E53" t="s">
@@ -10178,7 +11007,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:19" hidden="1">
+    <row r="54" spans="1:19">
       <c r="A54" s="2" t="str">
         <f>IF(C54="","",VLOOKUP(C54,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>MNG</v>
@@ -10190,7 +11019,7 @@
       <c r="C54" t="s">
         <v>251</v>
       </c>
-      <c r="D54" s="7" t="s">
+      <c r="D54" t="s">
         <v>252</v>
       </c>
       <c r="F54" t="s">
@@ -10231,7 +11060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:19" hidden="1">
+    <row r="55" spans="1:19">
       <c r="A55" s="2" t="str">
         <f>IF(C55="","",VLOOKUP(C55,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>DEU</v>
@@ -10243,7 +11072,7 @@
       <c r="C55" t="s">
         <v>273</v>
       </c>
-      <c r="D55" s="7" t="s">
+      <c r="D55" t="s">
         <v>274</v>
       </c>
       <c r="E55" t="s">
@@ -10287,7 +11116,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:19" hidden="1">
+    <row r="56" spans="1:19">
       <c r="A56" s="2" t="str">
         <f>IF(C56="","",VLOOKUP(C56,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>SRB</v>
@@ -10299,7 +11128,7 @@
       <c r="C56" t="s">
         <v>300</v>
       </c>
-      <c r="D56" s="7" t="s">
+      <c r="D56" t="s">
         <v>301</v>
       </c>
       <c r="E56" t="s">
@@ -10343,7 +11172,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:19" hidden="1">
+    <row r="57" spans="1:19">
       <c r="A57" s="2" t="str">
         <f>IF(C57="","",VLOOKUP(C57,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>SYR</v>
@@ -10355,7 +11184,7 @@
       <c r="C57" t="s">
         <v>197</v>
       </c>
-      <c r="D57" s="7" t="s">
+      <c r="D57" t="s">
         <v>317</v>
       </c>
       <c r="E57" t="s">
@@ -10408,7 +11237,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:19" hidden="1">
+    <row r="58" spans="1:19">
       <c r="A58" s="2" t="str">
         <f>IF(C58="","",VLOOKUP(C58,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>MEX</v>
@@ -10420,7 +11249,7 @@
       <c r="C58" t="s">
         <v>248</v>
       </c>
-      <c r="D58" s="7" t="s">
+      <c r="D58" t="s">
         <v>249</v>
       </c>
       <c r="F58" t="s">
@@ -10461,7 +11290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:19" hidden="1">
+    <row r="59" spans="1:19">
       <c r="A59" s="2" t="str">
         <f>IF(C59="","",VLOOKUP(C59,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>USA</v>
@@ -10473,7 +11302,7 @@
       <c r="C59" t="s">
         <v>177</v>
       </c>
-      <c r="D59" s="7" t="s">
+      <c r="D59" t="s">
         <v>296</v>
       </c>
       <c r="E59" t="s">
@@ -10514,7 +11343,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:19" hidden="1">
+    <row r="60" spans="1:19">
       <c r="A60" s="2" t="str">
         <f>IF(C60="","",VLOOKUP(C60,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>LBN</v>
@@ -10526,7 +11355,7 @@
       <c r="C60" t="s">
         <v>157</v>
       </c>
-      <c r="D60" s="7" t="s">
+      <c r="D60" t="s">
         <v>315</v>
       </c>
       <c r="F60" t="s">
@@ -10570,7 +11399,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:19" hidden="1">
+    <row r="61" spans="1:19">
       <c r="A61" s="2" t="str">
         <f>IF(C61="","",VLOOKUP(C61,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>ARG</v>
@@ -10582,7 +11411,7 @@
       <c r="C61" t="s">
         <v>320</v>
       </c>
-      <c r="D61" s="7" t="s">
+      <c r="D61" t="s">
         <v>321</v>
       </c>
       <c r="E61" t="s">
@@ -10629,7 +11458,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:19" hidden="1">
+    <row r="62" spans="1:19">
       <c r="A62" s="2" t="str">
         <f>IF(C62="","",VLOOKUP(C62,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>EU</v>
@@ -10641,7 +11470,7 @@
       <c r="C62" t="s">
         <v>343</v>
       </c>
-      <c r="D62" s="7" t="s">
+      <c r="D62" t="s">
         <v>344</v>
       </c>
       <c r="E62" t="s">
@@ -10688,7 +11517,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:19" hidden="1">
+    <row r="63" spans="1:19">
       <c r="A63" s="2" t="str">
         <f>IF(C63="","",VLOOKUP(C63,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>TCD</v>
@@ -10700,7 +11529,7 @@
       <c r="C63" t="s">
         <v>407</v>
       </c>
-      <c r="D63" s="7" t="s">
+      <c r="D63" t="s">
         <v>408</v>
       </c>
       <c r="F63" t="s">
@@ -10744,7 +11573,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:19" hidden="1">
+    <row r="64" spans="1:19">
       <c r="A64" s="2" t="str">
         <f>IF(C64="","",VLOOKUP(C64,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>RUS</v>
@@ -10756,7 +11585,7 @@
       <c r="C64" t="s">
         <v>176</v>
       </c>
-      <c r="D64" s="7" t="s">
+      <c r="D64" t="s">
         <v>291</v>
       </c>
       <c r="F64" t="s">
@@ -10800,7 +11629,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:19" hidden="1">
+    <row r="65" spans="1:19">
       <c r="A65" s="2" t="str">
         <f>IF(C65="","",VLOOKUP(C65,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>GBR</v>
@@ -10812,7 +11641,7 @@
       <c r="C65" t="s">
         <v>193</v>
       </c>
-      <c r="D65" s="7" t="s">
+      <c r="D65" t="s">
         <v>293</v>
       </c>
       <c r="E65" t="s">
@@ -10865,7 +11694,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:19" hidden="1">
+    <row r="66" spans="1:19">
       <c r="A66" s="2" t="str">
         <f>IF(C66="","",VLOOKUP(C66,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>BFA</v>
@@ -10877,7 +11706,7 @@
       <c r="C66" t="s">
         <v>324</v>
       </c>
-      <c r="D66" s="7" t="s">
+      <c r="D66" t="s">
         <v>325</v>
       </c>
       <c r="E66" t="s">
@@ -10924,7 +11753,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:19" hidden="1">
+    <row r="67" spans="1:19">
       <c r="A67" s="2" t="str">
         <f>IF(C67="","",VLOOKUP(C67,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>COD</v>
@@ -10936,7 +11765,7 @@
       <c r="C67" t="s">
         <v>336</v>
       </c>
-      <c r="D67" s="7" t="s">
+      <c r="D67" t="s">
         <v>337</v>
       </c>
       <c r="F67" t="s">
@@ -10977,7 +11806,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:19" hidden="1">
+    <row r="68" spans="1:19">
       <c r="A68" s="2" t="str">
         <f>IF(C68="","",VLOOKUP(C68,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>USA</v>
@@ -10989,7 +11818,7 @@
       <c r="C68" t="s">
         <v>177</v>
       </c>
-      <c r="D68" s="7" t="s">
+      <c r="D68" t="s">
         <v>340</v>
       </c>
       <c r="E68" t="s">
@@ -11036,7 +11865,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:19" hidden="1">
+    <row r="69" spans="1:19">
       <c r="A69" s="2" t="str">
         <f>IF(C69="","",VLOOKUP(C69,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>NZL</v>
@@ -11048,7 +11877,7 @@
       <c r="C69" t="s">
         <v>350</v>
       </c>
-      <c r="D69" s="7" t="s">
+      <c r="D69" t="s">
         <v>351</v>
       </c>
       <c r="E69" t="s">
@@ -11095,7 +11924,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:19" hidden="1">
+    <row r="70" spans="1:19">
       <c r="A70" s="2" t="str">
         <f>IF(C70="","",VLOOKUP(C70,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>IND</v>
@@ -11107,7 +11936,7 @@
       <c r="C70" t="s">
         <v>395</v>
       </c>
-      <c r="D70" s="7" t="s">
+      <c r="D70" t="s">
         <v>396</v>
       </c>
       <c r="F70" t="s">
@@ -11154,7 +11983,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:19" hidden="1">
+    <row r="71" spans="1:19">
       <c r="A71" s="2" t="str">
         <f>IF(C71="","",VLOOKUP(C71,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>RUS</v>
@@ -11166,7 +11995,7 @@
       <c r="C71" t="s">
         <v>388</v>
       </c>
-      <c r="D71" s="7" t="s">
+      <c r="D71" t="s">
         <v>399</v>
       </c>
       <c r="F71" t="s">
@@ -11210,7 +12039,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:19" hidden="1">
+    <row r="72" spans="1:19">
       <c r="A72" s="2" t="str">
         <f>IF(C72="","",VLOOKUP(C72,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>ITA</v>
@@ -11222,7 +12051,7 @@
       <c r="C72" t="s">
         <v>167</v>
       </c>
-      <c r="D72" s="7" t="s">
+      <c r="D72" t="s">
         <v>282</v>
       </c>
       <c r="E72" t="s">
@@ -11272,7 +12101,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:19" hidden="1">
+    <row r="73" spans="1:19">
       <c r="A73" s="2" t="str">
         <f>IF(C73="","",VLOOKUP(C73,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>KOR</v>
@@ -11284,7 +12113,7 @@
       <c r="C73" t="s">
         <v>241</v>
       </c>
-      <c r="D73" s="7" t="s">
+      <c r="D73" t="s">
         <v>288</v>
       </c>
       <c r="E73" t="s">
@@ -11331,7 +12160,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:19" hidden="1">
+    <row r="74" spans="1:19">
       <c r="A74" s="2" t="str">
         <f>IF(C74="","",VLOOKUP(C74,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>RUS</v>
@@ -11343,7 +12172,7 @@
       <c r="C74" t="s">
         <v>176</v>
       </c>
-      <c r="D74" s="7" t="s">
+      <c r="D74" t="s">
         <v>309</v>
       </c>
       <c r="E74" t="s">
@@ -11390,7 +12219,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:19" hidden="1">
+    <row r="75" spans="1:19">
       <c r="A75" s="2" t="str">
         <f>IF(C75="","",VLOOKUP(C75,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>JPN</v>
@@ -11402,7 +12231,7 @@
       <c r="C75" t="s">
         <v>312</v>
       </c>
-      <c r="D75" s="7" t="s">
+      <c r="D75" t="s">
         <v>355</v>
       </c>
       <c r="F75" t="s">
@@ -11452,7 +12281,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:19" hidden="1">
+    <row r="76" spans="1:19">
       <c r="A76" s="2" t="str">
         <f>IF(C76="","",VLOOKUP(C76,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>ETH</v>
@@ -11464,7 +12293,7 @@
       <c r="C76" t="s">
         <v>329</v>
       </c>
-      <c r="D76" s="7" t="s">
+      <c r="D76" t="s">
         <v>330</v>
       </c>
       <c r="E76" t="s">
@@ -11511,7 +12340,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="1:19" hidden="1">
+    <row r="77" spans="1:19">
       <c r="A77" s="2" t="str">
         <f>IF(C77="","",VLOOKUP(C77,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>CHN</v>
@@ -11523,7 +12352,7 @@
       <c r="C77" t="s">
         <v>332</v>
       </c>
-      <c r="D77" s="7" t="s">
+      <c r="D77" t="s">
         <v>347</v>
       </c>
       <c r="E77" t="s">
@@ -11567,7 +12396,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:19" hidden="1">
+    <row r="78" spans="1:19">
       <c r="A78" s="2" t="str">
         <f>IF(C78="","",VLOOKUP(C78,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>RUS</v>
@@ -11579,7 +12408,7 @@
       <c r="C78" t="s">
         <v>388</v>
       </c>
-      <c r="D78" s="7" t="s">
+      <c r="D78" t="s">
         <v>389</v>
       </c>
       <c r="F78" t="s">
@@ -11626,7 +12455,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:19" hidden="1">
+    <row r="79" spans="1:19">
       <c r="A79" s="2" t="str">
         <f>IF(C79="","",VLOOKUP(C79,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>MMR</v>
@@ -11638,7 +12467,7 @@
       <c r="C79" t="s">
         <v>391</v>
       </c>
-      <c r="D79" s="7" t="s">
+      <c r="D79" t="s">
         <v>392</v>
       </c>
       <c r="E79" t="s">
@@ -11682,7 +12511,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:19" hidden="1">
+    <row r="80" spans="1:19">
       <c r="A80" s="2" t="str">
         <f>IF(C80="","",VLOOKUP(C80,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>AFG</v>
@@ -11694,7 +12523,7 @@
       <c r="C80" t="s">
         <v>411</v>
       </c>
-      <c r="D80" s="7" t="s">
+      <c r="D80" t="s">
         <v>412</v>
       </c>
       <c r="F80" t="s">
@@ -11735,7 +12564,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:19" hidden="1">
+    <row r="81" spans="1:19">
       <c r="A81" s="2" t="str">
         <f>IF(C81="","",VLOOKUP(C81,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>GRC</v>
@@ -11747,7 +12576,7 @@
       <c r="C81" t="s">
         <v>415</v>
       </c>
-      <c r="D81" s="7" t="s">
+      <c r="D81" t="s">
         <v>416</v>
       </c>
       <c r="F81" t="s">
@@ -11788,7 +12617,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:19" hidden="1">
+    <row r="82" spans="1:19">
       <c r="A82" s="2" t="str">
         <f>IF(C82="","",VLOOKUP(C82,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>UKR</v>
@@ -11800,7 +12629,7 @@
       <c r="C82" t="s">
         <v>202</v>
       </c>
-      <c r="D82" s="7" t="s">
+      <c r="D82" t="s">
         <v>277</v>
       </c>
       <c r="E82" t="s">
@@ -11847,7 +12676,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:19" hidden="1">
+    <row r="83" spans="1:19">
       <c r="A83" s="2" t="str">
         <f>IF(C83="","",VLOOKUP(C83,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>IRN</v>
@@ -11859,7 +12688,7 @@
       <c r="C83" t="s">
         <v>188</v>
       </c>
-      <c r="D83" s="7" t="s">
+      <c r="D83" t="s">
         <v>304</v>
       </c>
       <c r="F83" t="s">
@@ -11956,7 +12785,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="1:19" hidden="1">
+    <row r="85" spans="1:19">
       <c r="A85" s="2" t="str">
         <f>IF(C85="","",VLOOKUP(C85,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>COD</v>
@@ -11968,7 +12797,7 @@
       <c r="C85" t="s">
         <v>376</v>
       </c>
-      <c r="D85" s="7" t="s">
+      <c r="D85" t="s">
         <v>377</v>
       </c>
       <c r="E85" t="s">
@@ -12015,7 +12844,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:19" hidden="1">
+    <row r="86" spans="1:19">
       <c r="A86" s="2" t="str">
         <f>IF(C86="","",VLOOKUP(C86,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>IRN</v>
@@ -12027,7 +12856,7 @@
       <c r="C86" t="s">
         <v>367</v>
       </c>
-      <c r="D86" s="7" t="s">
+      <c r="D86" t="s">
         <v>381</v>
       </c>
       <c r="E86" t="s">
@@ -12074,7 +12903,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:19" hidden="1">
+    <row r="87" spans="1:19">
       <c r="A87" s="2" t="str">
         <f>IF(C87="","",VLOOKUP(C87,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>USA</v>
@@ -12086,7 +12915,7 @@
       <c r="C87" t="s">
         <v>368</v>
       </c>
-      <c r="D87" s="7" t="s">
+      <c r="D87" t="s">
         <v>385</v>
       </c>
       <c r="E87" t="s">
@@ -12133,7 +12962,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:19" hidden="1">
+    <row r="88" spans="1:19">
       <c r="A88" s="2" t="str">
         <f>IF(C88="","",VLOOKUP(C88,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>UKR</v>
@@ -12145,7 +12974,7 @@
       <c r="C88" t="s">
         <v>418</v>
       </c>
-      <c r="D88" s="7" t="s">
+      <c r="D88" t="s">
         <v>419</v>
       </c>
       <c r="E88" t="s">
@@ -12251,7 +13080,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:19" hidden="1">
+    <row r="90" spans="1:19">
       <c r="A90" s="2" t="str">
         <f>IF(C90="","",VLOOKUP(C90,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>USA</v>
@@ -12263,7 +13092,7 @@
       <c r="C90" t="s">
         <v>368</v>
       </c>
-      <c r="D90" s="7" t="s">
+      <c r="D90" t="s">
         <v>428</v>
       </c>
       <c r="E90" t="s">
@@ -12310,7 +13139,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:19" hidden="1">
+    <row r="91" spans="1:19">
       <c r="A91" s="2" t="str">
         <f>IF(C91="","",VLOOKUP(C91,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>IRN</v>
@@ -12322,7 +13151,7 @@
       <c r="C91" t="s">
         <v>367</v>
       </c>
-      <c r="D91" s="7" t="s">
+      <c r="D91" t="s">
         <v>431</v>
       </c>
       <c r="F91" t="s">
@@ -12422,7 +13251,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:19" hidden="1">
+    <row r="93" spans="1:19">
       <c r="A93" s="2" t="str">
         <f>IF(C93="","",VLOOKUP(C93,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>PAK</v>
@@ -12434,7 +13263,7 @@
       <c r="C93" t="s">
         <v>362</v>
       </c>
-      <c r="D93" s="7" t="s">
+      <c r="D93" t="s">
         <v>363</v>
       </c>
       <c r="E93" t="s">
@@ -12487,7 +13316,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:19" hidden="1">
+    <row r="94" spans="1:19">
       <c r="A94" s="2" t="str">
         <f>IF(C94="","",VLOOKUP(C94,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>VNM</v>
@@ -12499,7 +13328,7 @@
       <c r="C94" t="s">
         <v>372</v>
       </c>
-      <c r="D94" s="7" t="s">
+      <c r="D94" t="s">
         <v>373</v>
       </c>
       <c r="F94" t="s">
@@ -12540,7 +13369,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:19" hidden="1">
+    <row r="95" spans="1:19">
       <c r="A95" s="2" t="str">
         <f>IF(C95="","",VLOOKUP(C95,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>SSD</v>
@@ -12552,7 +13381,7 @@
       <c r="C95" t="s">
         <v>403</v>
       </c>
-      <c r="D95" s="7" t="s">
+      <c r="D95" t="s">
         <v>404</v>
       </c>
       <c r="F95" t="s">
@@ -12593,7 +13422,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:19" hidden="1">
+    <row r="96" spans="1:19">
       <c r="A96" s="2" t="str">
         <f>IF(C96="","",VLOOKUP(C96,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>IRN</v>
@@ -12605,7 +13434,7 @@
       <c r="C96" t="s">
         <v>367</v>
       </c>
-      <c r="D96" s="7" t="s">
+      <c r="D96" t="s">
         <v>422</v>
       </c>
       <c r="F96" t="s">
@@ -12649,7 +13478,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:19" hidden="1">
+    <row r="97" spans="1:19">
       <c r="A97" s="2" t="str">
         <f>IF(C97="","",VLOOKUP(C97,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>USA</v>
@@ -12661,7 +13490,7 @@
       <c r="C97" t="s">
         <v>368</v>
       </c>
-      <c r="D97" s="7" t="s">
+      <c r="D97" t="s">
         <v>425</v>
       </c>
       <c r="E97" t="s">
@@ -12708,7 +13537,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:19" hidden="1">
+    <row r="98" spans="1:19">
       <c r="A98" s="2" t="str">
         <f>IF(C98="","",VLOOKUP(C98,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>IRN</v>
@@ -12720,7 +13549,7 @@
       <c r="C98" t="s">
         <v>188</v>
       </c>
-      <c r="D98" s="7" t="s">
+      <c r="D98" t="s">
         <v>460</v>
       </c>
       <c r="F98" t="s">
@@ -12826,7 +13655,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:19" hidden="1">
+    <row r="100" spans="1:19">
       <c r="A100" s="2" t="str">
         <f>IF(C100="","",VLOOKUP(C100,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>JPN</v>
@@ -12838,7 +13667,7 @@
       <c r="C100" t="s">
         <v>312</v>
       </c>
-      <c r="D100" s="7" t="s">
+      <c r="D100" t="s">
         <v>448</v>
       </c>
       <c r="E100" t="s">
@@ -12885,7 +13714,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:19" hidden="1">
+    <row r="101" spans="1:19">
       <c r="A101" s="2" t="str">
         <f>IF(C101="","",VLOOKUP(C101,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>MDG</v>
@@ -12897,7 +13726,7 @@
       <c r="C101" t="s">
         <v>401</v>
       </c>
-      <c r="D101" s="7" t="s">
+      <c r="D101" t="s">
         <v>450</v>
       </c>
       <c r="E101" t="s">
@@ -13006,7 +13835,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="103" spans="1:19" hidden="1">
+    <row r="103" spans="1:19">
       <c r="A103" s="2" t="str">
         <f>IF(C103="","",VLOOKUP(C103,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>MEX</v>
@@ -13018,7 +13847,7 @@
       <c r="C103" t="s">
         <v>248</v>
       </c>
-      <c r="D103" s="7" t="s">
+      <c r="D103" t="s">
         <v>454</v>
       </c>
       <c r="F103" t="s">
@@ -13059,7 +13888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:19" hidden="1">
+    <row r="104" spans="1:19">
       <c r="A104" s="2" t="str">
         <f>IF(C104="","",VLOOKUP(C104,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>PRY</v>
@@ -13071,7 +13900,7 @@
       <c r="C104" t="s">
         <v>182</v>
       </c>
-      <c r="D104" s="7" t="s">
+      <c r="D104" t="s">
         <v>455</v>
       </c>
       <c r="F104" t="s">
@@ -13112,7 +13941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:19" hidden="1">
+    <row r="105" spans="1:19">
       <c r="A105" s="2" t="str">
         <f>IF(C105="","",VLOOKUP(C105,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>PRK</v>
@@ -13124,7 +13953,7 @@
       <c r="C105" t="s">
         <v>456</v>
       </c>
-      <c r="D105" s="7" t="s">
+      <c r="D105" t="s">
         <v>457</v>
       </c>
       <c r="F105" t="s">
@@ -13171,7 +14000,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="1:19" hidden="1">
+    <row r="106" spans="1:19">
       <c r="A106" s="2" t="str">
         <f>IF(C106="","",VLOOKUP(C106,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>AFG</v>
@@ -13183,7 +14012,7 @@
       <c r="C106" t="s">
         <v>221</v>
       </c>
-      <c r="D106" s="7" t="s">
+      <c r="D106" t="s">
         <v>458</v>
       </c>
       <c r="E106" t="s">
@@ -13292,7 +14121,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:19" hidden="1">
+    <row r="108" spans="1:19">
       <c r="A108" s="2" t="str">
         <f>IF(C108="","",VLOOKUP(C108,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>GBR</v>
@@ -13304,7 +14133,7 @@
       <c r="C108" t="s">
         <v>193</v>
       </c>
-      <c r="D108" s="7" t="s">
+      <c r="D108" t="s">
         <v>513</v>
       </c>
       <c r="E108" t="s">
@@ -13351,7 +14180,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="1:19" hidden="1">
+    <row r="109" spans="1:19">
       <c r="A109" s="2" t="str">
         <f>IF(C109="","",VLOOKUP(C109,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>GBR</v>
@@ -13363,7 +14192,7 @@
       <c r="C109" t="s">
         <v>193</v>
       </c>
-      <c r="D109" s="7" t="s">
+      <c r="D109" t="s">
         <v>444</v>
       </c>
       <c r="E109" t="s">
@@ -13534,7 +14363,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:19" hidden="1">
+    <row r="112" spans="1:19">
       <c r="A112" s="2" t="str">
         <f>IF(C112="","",VLOOKUP(C112,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>VEN</v>
@@ -13546,7 +14375,7 @@
       <c r="C112" t="s">
         <v>256</v>
       </c>
-      <c r="D112" s="7" t="s">
+      <c r="D112" t="s">
         <v>482</v>
       </c>
       <c r="E112" t="s">
@@ -13590,7 +14419,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="1:19" hidden="1">
+    <row r="113" spans="1:19">
       <c r="A113" s="2" t="str">
         <f>IF(C113="","",VLOOKUP(C113,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>VEN</v>
@@ -13602,7 +14431,7 @@
       <c r="C113" t="s">
         <v>256</v>
       </c>
-      <c r="D113" s="7" t="s">
+      <c r="D113" t="s">
         <v>484</v>
       </c>
       <c r="F113" t="s">
@@ -13699,7 +14528,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:19" hidden="1">
+    <row r="115" spans="1:19">
       <c r="A115" s="2" t="str">
         <f>IF(C115="","",VLOOKUP(C115,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>ISR</v>
@@ -13711,7 +14540,7 @@
       <c r="C115" t="s">
         <v>153</v>
       </c>
-      <c r="D115" s="7" t="s">
+      <c r="D115" t="s">
         <v>494</v>
       </c>
       <c r="E115" t="s">
@@ -13817,7 +14646,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:19" hidden="1">
+    <row r="117" spans="1:19">
       <c r="A117" s="2" t="str">
         <f>IF(C117="","",VLOOKUP(C117,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>VEN</v>
@@ -13829,7 +14658,7 @@
       <c r="C117" t="s">
         <v>256</v>
       </c>
-      <c r="D117" s="7" t="s">
+      <c r="D117" t="s">
         <v>480</v>
       </c>
       <c r="E117" t="s">
@@ -13873,7 +14702,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:19" hidden="1">
+    <row r="118" spans="1:19">
       <c r="A118" s="2" t="str">
         <f>IF(C118="","",VLOOKUP(C118,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>CHN</v>
@@ -13885,7 +14714,7 @@
       <c r="C118" t="s">
         <v>332</v>
       </c>
-      <c r="D118" s="7" t="s">
+      <c r="D118" t="s">
         <v>486</v>
       </c>
       <c r="E118" t="s">
@@ -13932,7 +14761,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:19" hidden="1">
+    <row r="119" spans="1:19">
       <c r="A119" s="2" t="str">
         <f>IF(C119="","",VLOOKUP(C119,[1]ISO辞書!A:C,2,FALSE))</f>
         <v>AUS</v>
@@ -13944,7 +14773,7 @@
       <c r="C119" t="s">
         <v>488</v>
       </c>
-      <c r="D119" s="7" t="s">
+      <c r="D119" t="s">
         <v>489</v>
       </c>
       <c r="E119" t="s">
@@ -13991,14 +14820,23 @@
         <v>3</v>
       </c>
     </row>
-    <row r="120" spans="1:19" hidden="1">
+    <row r="120" spans="1:19">
       <c r="A120" s="2" t="str">
         <f>IF(C120="","",VLOOKUP(C120,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>BEN</v>
       </c>
       <c r="B120" s="3" t="str">
         <f>IF(C120="","",VLOOKUP(C120,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Benin</v>
+      </c>
+      <c r="C120" t="s">
+        <v>514</v>
+      </c>
+      <c r="D120" t="s">
+        <v>515</v>
+      </c>
+      <c r="E120" t="s">
+        <v>516</v>
       </c>
       <c r="J120" s="2" t="str">
         <f>IF(G120="","",VLOOKUP(G120,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -14016,15 +14854,42 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="121" spans="1:19" hidden="1">
+      <c r="N120" t="s">
+        <v>517</v>
+      </c>
+      <c r="O120" t="s">
+        <v>79</v>
+      </c>
+      <c r="P120" s="1">
+        <v>46124</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>159</v>
+      </c>
+      <c r="R120" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="S120">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19">
       <c r="A121" s="2" t="str">
         <f>IF(C121="","",VLOOKUP(C121,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>SDN</v>
       </c>
       <c r="B121" s="3" t="str">
         <f>IF(C121="","",VLOOKUP(C121,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Sudan</v>
+      </c>
+      <c r="C121" t="s">
+        <v>519</v>
+      </c>
+      <c r="D121" t="s">
+        <v>520</v>
+      </c>
+      <c r="E121" t="s">
+        <v>521</v>
       </c>
       <c r="J121" s="2" t="str">
         <f>IF(G121="","",VLOOKUP(G121,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -14042,19 +14907,49 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="122" spans="1:19" hidden="1">
+      <c r="N121" t="s">
+        <v>522</v>
+      </c>
+      <c r="O121" t="s">
+        <v>69</v>
+      </c>
+      <c r="P121" s="1">
+        <v>46126</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>159</v>
+      </c>
+      <c r="R121" t="s">
+        <v>523</v>
+      </c>
+      <c r="S121">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:19">
       <c r="A122" s="2" t="str">
         <f>IF(C122="","",VLOOKUP(C122,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>BWA</v>
       </c>
       <c r="B122" s="3" t="str">
         <f>IF(C122="","",VLOOKUP(C122,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Botswana</v>
+      </c>
+      <c r="C122" t="s">
+        <v>524</v>
+      </c>
+      <c r="D122" t="s">
+        <v>525</v>
+      </c>
+      <c r="E122" t="s">
+        <v>526</v>
+      </c>
+      <c r="G122" t="s">
+        <v>313</v>
       </c>
       <c r="J122" s="2" t="str">
         <f>IF(G122="","",VLOOKUP(G122,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>OMN</v>
       </c>
       <c r="K122" s="2" t="str">
         <f>IF(H122="","",VLOOKUP(H122,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -14066,21 +14961,51 @@
       </c>
       <c r="M122" s="3" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="123" spans="1:19" hidden="1">
+        <v>OMN</v>
+      </c>
+      <c r="N122" t="s">
+        <v>527</v>
+      </c>
+      <c r="O122" t="s">
+        <v>53</v>
+      </c>
+      <c r="P122" s="1">
+        <v>46125</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>159</v>
+      </c>
+      <c r="R122" t="s">
+        <v>528</v>
+      </c>
+      <c r="S122">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:19">
       <c r="A123" s="2" t="str">
         <f>IF(C123="","",VLOOKUP(C123,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>ZAF</v>
       </c>
       <c r="B123" s="3" t="str">
         <f>IF(C123="","",VLOOKUP(C123,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>South Africa</v>
+      </c>
+      <c r="C123" t="s">
+        <v>529</v>
+      </c>
+      <c r="D123" t="s">
+        <v>530</v>
+      </c>
+      <c r="E123" t="s">
+        <v>531</v>
+      </c>
+      <c r="G123" t="s">
+        <v>273</v>
       </c>
       <c r="J123" s="2" t="str">
         <f>IF(G123="","",VLOOKUP(G123,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>DEU</v>
       </c>
       <c r="K123" s="2" t="str">
         <f>IF(H123="","",VLOOKUP(H123,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -14092,17 +15017,44 @@
       </c>
       <c r="M123" s="3" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="124" spans="1:19" hidden="1">
+        <v>DEU</v>
+      </c>
+      <c r="N123" t="s">
+        <v>532</v>
+      </c>
+      <c r="O123" t="s">
+        <v>53</v>
+      </c>
+      <c r="P123" s="1">
+        <v>46125</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>159</v>
+      </c>
+      <c r="R123" t="s">
+        <v>533</v>
+      </c>
+      <c r="S123">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:19">
       <c r="A124" s="2" t="str">
         <f>IF(C124="","",VLOOKUP(C124,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>NGA</v>
       </c>
       <c r="B124" s="3" t="str">
         <f>IF(C124="","",VLOOKUP(C124,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Nigeria</v>
+      </c>
+      <c r="C124" t="s">
+        <v>534</v>
+      </c>
+      <c r="D124" t="s">
+        <v>535</v>
+      </c>
+      <c r="E124" t="s">
+        <v>536</v>
       </c>
       <c r="J124" s="2" t="str">
         <f>IF(G124="","",VLOOKUP(G124,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -14120,19 +15072,49 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="125" spans="1:19" hidden="1">
+      <c r="N124" t="s">
+        <v>537</v>
+      </c>
+      <c r="O124" t="s">
+        <v>69</v>
+      </c>
+      <c r="P124" s="1">
+        <v>46125</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>159</v>
+      </c>
+      <c r="R124" t="s">
+        <v>538</v>
+      </c>
+      <c r="S124">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="125" spans="1:19">
       <c r="A125" s="2" t="str">
         <f>IF(C125="","",VLOOKUP(C125,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>NGA</v>
       </c>
       <c r="B125" s="3" t="str">
         <f>IF(C125="","",VLOOKUP(C125,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Nigeria</v>
+      </c>
+      <c r="C125" t="s">
+        <v>534</v>
+      </c>
+      <c r="D125" t="s">
+        <v>539</v>
+      </c>
+      <c r="E125" t="s">
+        <v>540</v>
+      </c>
+      <c r="G125" t="s">
+        <v>541</v>
       </c>
       <c r="J125" s="2" t="str">
         <f>IF(G125="","",VLOOKUP(G125,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>MAR</v>
       </c>
       <c r="K125" s="2" t="str">
         <f>IF(H125="","",VLOOKUP(H125,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -14144,17 +15126,44 @@
       </c>
       <c r="M125" s="3" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="126" spans="1:19" hidden="1">
+        <v>MAR</v>
+      </c>
+      <c r="N125" t="s">
+        <v>542</v>
+      </c>
+      <c r="O125" t="s">
+        <v>53</v>
+      </c>
+      <c r="P125" s="1">
+        <v>46125</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>159</v>
+      </c>
+      <c r="R125" t="s">
+        <v>543</v>
+      </c>
+      <c r="S125">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="126" spans="1:19">
       <c r="A126" s="2" t="str">
         <f>IF(C126="","",VLOOKUP(C126,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>DJI</v>
       </c>
       <c r="B126" s="3" t="str">
         <f>IF(C126="","",VLOOKUP(C126,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Djibouti</v>
+      </c>
+      <c r="C126" t="s">
+        <v>544</v>
+      </c>
+      <c r="D126" t="s">
+        <v>545</v>
+      </c>
+      <c r="E126" t="s">
+        <v>546</v>
       </c>
       <c r="J126" s="2" t="str">
         <f>IF(G126="","",VLOOKUP(G126,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -14172,15 +15181,42 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="127" spans="1:19" hidden="1">
+      <c r="N126" t="s">
+        <v>547</v>
+      </c>
+      <c r="O126" t="s">
+        <v>79</v>
+      </c>
+      <c r="P126" s="1">
+        <v>46123</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>159</v>
+      </c>
+      <c r="R126" t="s">
+        <v>548</v>
+      </c>
+      <c r="S126">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:19">
       <c r="A127" s="2" t="str">
         <f>IF(C127="","",VLOOKUP(C127,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>ZAF</v>
       </c>
       <c r="B127" s="3" t="str">
         <f>IF(C127="","",VLOOKUP(C127,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>South Africa</v>
+      </c>
+      <c r="C127" t="s">
+        <v>529</v>
+      </c>
+      <c r="D127" t="s">
+        <v>549</v>
+      </c>
+      <c r="E127" t="s">
+        <v>550</v>
       </c>
       <c r="J127" s="2" t="str">
         <f>IF(G127="","",VLOOKUP(G127,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -14198,15 +15234,42 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="128" spans="1:19" hidden="1">
+      <c r="N127" t="s">
+        <v>551</v>
+      </c>
+      <c r="O127" t="s">
+        <v>79</v>
+      </c>
+      <c r="P127" s="1">
+        <v>46124</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>159</v>
+      </c>
+      <c r="R127" t="s">
+        <v>552</v>
+      </c>
+      <c r="S127">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:19">
       <c r="A128" s="2" t="str">
         <f>IF(C128="","",VLOOKUP(C128,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>LBY</v>
       </c>
       <c r="B128" s="3" t="str">
         <f>IF(C128="","",VLOOKUP(C128,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Libya</v>
+      </c>
+      <c r="C128" t="s">
+        <v>553</v>
+      </c>
+      <c r="D128" t="s">
+        <v>554</v>
+      </c>
+      <c r="E128" t="s">
+        <v>555</v>
       </c>
       <c r="J128" s="2" t="str">
         <f>IF(G128="","",VLOOKUP(G128,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -14224,15 +15287,42 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="129" spans="1:13" hidden="1">
+      <c r="N128" t="s">
+        <v>556</v>
+      </c>
+      <c r="O128" t="s">
+        <v>79</v>
+      </c>
+      <c r="P128" s="1">
+        <v>46123</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>159</v>
+      </c>
+      <c r="R128" t="s">
+        <v>557</v>
+      </c>
+      <c r="S128">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:19">
       <c r="A129" s="2" t="str">
         <f>IF(C129="","",VLOOKUP(C129,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>CAN</v>
       </c>
       <c r="B129" s="3" t="str">
         <f>IF(C129="","",VLOOKUP(C129,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Canada</v>
+      </c>
+      <c r="C129" t="s">
+        <v>558</v>
+      </c>
+      <c r="D129" t="s">
+        <v>559</v>
+      </c>
+      <c r="E129" t="s">
+        <v>560</v>
       </c>
       <c r="J129" s="2" t="str">
         <f>IF(G129="","",VLOOKUP(G129,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -14250,19 +15340,49 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="130" spans="1:13" hidden="1">
+      <c r="N129" t="s">
+        <v>561</v>
+      </c>
+      <c r="O129" t="s">
+        <v>79</v>
+      </c>
+      <c r="P129" s="1">
+        <v>46125</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>159</v>
+      </c>
+      <c r="R129" t="s">
+        <v>562</v>
+      </c>
+      <c r="S129">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:19">
       <c r="A130" s="2" t="str">
         <f>IF(C130="","",VLOOKUP(C130,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>FRA</v>
       </c>
       <c r="B130" s="3" t="str">
         <f>IF(C130="","",VLOOKUP(C130,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>France</v>
+      </c>
+      <c r="C130" t="s">
+        <v>213</v>
+      </c>
+      <c r="D130" t="s">
+        <v>563</v>
+      </c>
+      <c r="E130" t="s">
+        <v>564</v>
+      </c>
+      <c r="G130" t="s">
+        <v>256</v>
       </c>
       <c r="J130" s="2" t="str">
         <f>IF(G130="","",VLOOKUP(G130,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>VEN</v>
       </c>
       <c r="K130" s="2" t="str">
         <f>IF(H130="","",VLOOKUP(H130,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -14273,52 +15393,121 @@
         <v/>
       </c>
       <c r="M130" s="3" t="str">
-        <f t="shared" ref="M130:M193" si="2">_xlfn.TEXTJOIN(";",TRUE,J130:L130)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="131" spans="1:13" hidden="1">
+        <f t="shared" ref="M130:M143" si="2">_xlfn.TEXTJOIN(";",TRUE,J130:L130)</f>
+        <v>VEN</v>
+      </c>
+      <c r="N130" t="s">
+        <v>565</v>
+      </c>
+      <c r="O130" t="s">
+        <v>53</v>
+      </c>
+      <c r="P130" s="1">
+        <v>46125</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>159</v>
+      </c>
+      <c r="R130" t="s">
+        <v>566</v>
+      </c>
+      <c r="S130">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:19">
       <c r="A131" s="2" t="str">
         <f>IF(C131="","",VLOOKUP(C131,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>PRK</v>
       </c>
       <c r="B131" s="3" t="str">
         <f>IF(C131="","",VLOOKUP(C131,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>North Korea</v>
+      </c>
+      <c r="C131" t="s">
+        <v>456</v>
+      </c>
+      <c r="D131" t="s">
+        <v>567</v>
+      </c>
+      <c r="E131" t="s">
+        <v>568</v>
+      </c>
+      <c r="G131" t="s">
+        <v>312</v>
+      </c>
+      <c r="H131" t="s">
+        <v>241</v>
+      </c>
+      <c r="I131" t="s">
+        <v>177</v>
       </c>
       <c r="J131" s="2" t="str">
         <f>IF(G131="","",VLOOKUP(G131,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>JPN</v>
       </c>
       <c r="K131" s="2" t="str">
         <f>IF(H131="","",VLOOKUP(H131,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>KOR</v>
       </c>
       <c r="L131" s="2" t="str">
         <f>IF(I131="","",VLOOKUP(I131,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>USA</v>
       </c>
       <c r="M131" s="3" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="132" spans="1:13" hidden="1">
+        <v>JPN;KOR;USA</v>
+      </c>
+      <c r="N131" t="s">
+        <v>569</v>
+      </c>
+      <c r="O131" t="s">
+        <v>25</v>
+      </c>
+      <c r="P131" s="1">
+        <v>46125</v>
+      </c>
+      <c r="Q131" t="s">
+        <v>159</v>
+      </c>
+      <c r="R131" t="s">
+        <v>570</v>
+      </c>
+      <c r="S131">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="132" spans="1:19">
       <c r="A132" s="2" t="str">
         <f>IF(C132="","",VLOOKUP(C132,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>CHN</v>
       </c>
       <c r="B132" s="3" t="str">
         <f>IF(C132="","",VLOOKUP(C132,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>China</v>
+      </c>
+      <c r="C132" t="s">
+        <v>332</v>
+      </c>
+      <c r="D132" t="s">
+        <v>571</v>
+      </c>
+      <c r="E132" t="s">
+        <v>572</v>
+      </c>
+      <c r="G132" t="s">
+        <v>188</v>
+      </c>
+      <c r="H132" t="s">
+        <v>177</v>
       </c>
       <c r="J132" s="2" t="str">
         <f>IF(G132="","",VLOOKUP(G132,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>IRN</v>
       </c>
       <c r="K132" s="2" t="str">
         <f>IF(H132="","",VLOOKUP(H132,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>USA</v>
       </c>
       <c r="L132" s="2" t="str">
         <f>IF(I132="","",VLOOKUP(I132,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -14326,25 +15515,58 @@
       </c>
       <c r="M132" s="3" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="133" spans="1:13" hidden="1">
+        <v>IRN;USA</v>
+      </c>
+      <c r="N132" t="s">
+        <v>573</v>
+      </c>
+      <c r="O132" t="s">
+        <v>53</v>
+      </c>
+      <c r="P132" s="1">
+        <v>46125</v>
+      </c>
+      <c r="Q132" t="s">
+        <v>159</v>
+      </c>
+      <c r="R132" t="s">
+        <v>574</v>
+      </c>
+      <c r="S132">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="133" spans="1:19">
       <c r="A133" s="2" t="str">
         <f>IF(C133="","",VLOOKUP(C133,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>USA</v>
       </c>
       <c r="B133" s="3" t="str">
         <f>IF(C133="","",VLOOKUP(C133,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>America</v>
+      </c>
+      <c r="C133" t="s">
+        <v>177</v>
+      </c>
+      <c r="D133" t="s">
+        <v>575</v>
+      </c>
+      <c r="E133" t="s">
+        <v>576</v>
+      </c>
+      <c r="G133" t="s">
+        <v>488</v>
+      </c>
+      <c r="H133" t="s">
+        <v>577</v>
       </c>
       <c r="J133" s="2" t="str">
         <f>IF(G133="","",VLOOKUP(G133,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>AUS</v>
       </c>
       <c r="K133" s="2" t="str">
         <f>IF(H133="","",VLOOKUP(H133,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>PHL</v>
       </c>
       <c r="L133" s="2" t="str">
         <f>IF(I133="","",VLOOKUP(I133,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -14352,21 +15574,51 @@
       </c>
       <c r="M133" s="3" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="134" spans="1:13" hidden="1">
+        <v>AUS;PHL</v>
+      </c>
+      <c r="N133" t="s">
+        <v>578</v>
+      </c>
+      <c r="O133" t="s">
+        <v>25</v>
+      </c>
+      <c r="P133" s="1">
+        <v>46125</v>
+      </c>
+      <c r="Q133" t="s">
+        <v>159</v>
+      </c>
+      <c r="R133" t="s">
+        <v>579</v>
+      </c>
+      <c r="S133">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:19">
       <c r="A134" s="2" t="str">
         <f>IF(C134="","",VLOOKUP(C134,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>USA</v>
       </c>
       <c r="B134" s="3" t="str">
         <f>IF(C134="","",VLOOKUP(C134,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>America</v>
+      </c>
+      <c r="C134" t="s">
+        <v>177</v>
+      </c>
+      <c r="D134" t="s">
+        <v>580</v>
+      </c>
+      <c r="E134" t="s">
+        <v>581</v>
+      </c>
+      <c r="G134" t="s">
+        <v>188</v>
       </c>
       <c r="J134" s="2" t="str">
         <f>IF(G134="","",VLOOKUP(G134,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>IRN</v>
       </c>
       <c r="K134" s="2" t="str">
         <f>IF(H134="","",VLOOKUP(H134,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -14378,21 +15630,51 @@
       </c>
       <c r="M134" s="3" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="135" spans="1:13" hidden="1">
+        <v>IRN</v>
+      </c>
+      <c r="N134" t="s">
+        <v>582</v>
+      </c>
+      <c r="O134" t="s">
+        <v>25</v>
+      </c>
+      <c r="P134" s="1">
+        <v>46125</v>
+      </c>
+      <c r="Q134" t="s">
+        <v>159</v>
+      </c>
+      <c r="R134" t="s">
+        <v>583</v>
+      </c>
+      <c r="S134">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:19">
       <c r="A135" s="2" t="str">
         <f>IF(C135="","",VLOOKUP(C135,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>POL</v>
       </c>
       <c r="B135" s="3" t="str">
         <f>IF(C135="","",VLOOKUP(C135,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Poland</v>
+      </c>
+      <c r="C135" t="s">
+        <v>584</v>
+      </c>
+      <c r="D135" t="s">
+        <v>585</v>
+      </c>
+      <c r="E135" t="s">
+        <v>586</v>
+      </c>
+      <c r="G135" t="s">
+        <v>241</v>
       </c>
       <c r="J135" s="2" t="str">
         <f>IF(G135="","",VLOOKUP(G135,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>KOR</v>
       </c>
       <c r="K135" s="2" t="str">
         <f>IF(H135="","",VLOOKUP(H135,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -14404,21 +15686,51 @@
       </c>
       <c r="M135" s="3" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="136" spans="1:13" hidden="1">
+        <v>KOR</v>
+      </c>
+      <c r="N135" t="s">
+        <v>587</v>
+      </c>
+      <c r="O135" t="s">
+        <v>53</v>
+      </c>
+      <c r="P135" s="1">
+        <v>46125</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>159</v>
+      </c>
+      <c r="R135" t="s">
+        <v>588</v>
+      </c>
+      <c r="S135">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="136" spans="1:19">
       <c r="A136" s="2" t="str">
         <f>IF(C136="","",VLOOKUP(C136,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>PAK</v>
       </c>
       <c r="B136" s="3" t="str">
         <f>IF(C136="","",VLOOKUP(C136,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Pakistan</v>
+      </c>
+      <c r="C136" t="s">
+        <v>225</v>
+      </c>
+      <c r="D136" t="s">
+        <v>589</v>
+      </c>
+      <c r="E136" t="s">
+        <v>590</v>
+      </c>
+      <c r="G136" t="s">
+        <v>284</v>
       </c>
       <c r="J136" s="2" t="str">
         <f>IF(G136="","",VLOOKUP(G136,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>SAU</v>
       </c>
       <c r="K136" s="2" t="str">
         <f>IF(H136="","",VLOOKUP(H136,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -14430,21 +15742,51 @@
       </c>
       <c r="M136" s="3" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="137" spans="1:13" hidden="1">
+        <v>SAU</v>
+      </c>
+      <c r="N136" t="s">
+        <v>591</v>
+      </c>
+      <c r="O136" t="s">
+        <v>25</v>
+      </c>
+      <c r="P136" s="1">
+        <v>46123</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>159</v>
+      </c>
+      <c r="R136" t="s">
+        <v>592</v>
+      </c>
+      <c r="S136">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:19">
       <c r="A137" s="2" t="str">
         <f>IF(C137="","",VLOOKUP(C137,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>ESP</v>
       </c>
       <c r="B137" s="3" t="str">
         <f>IF(C137="","",VLOOKUP(C137,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Spain</v>
+      </c>
+      <c r="C137" t="s">
+        <v>593</v>
+      </c>
+      <c r="D137" t="s">
+        <v>594</v>
+      </c>
+      <c r="E137" t="s">
+        <v>595</v>
+      </c>
+      <c r="G137" t="s">
+        <v>332</v>
       </c>
       <c r="J137" s="2" t="str">
         <f>IF(G137="","",VLOOKUP(G137,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>CHN</v>
       </c>
       <c r="K137" s="2" t="str">
         <f>IF(H137="","",VLOOKUP(H137,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -14456,17 +15798,44 @@
       </c>
       <c r="M137" s="3" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="138" spans="1:13" hidden="1">
+        <v>CHN</v>
+      </c>
+      <c r="N137" t="s">
+        <v>596</v>
+      </c>
+      <c r="O137" t="s">
+        <v>53</v>
+      </c>
+      <c r="P137" s="1">
+        <v>46126</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>159</v>
+      </c>
+      <c r="R137" t="s">
+        <v>597</v>
+      </c>
+      <c r="S137">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="138" spans="1:19">
       <c r="A138" s="2" t="str">
         <f>IF(C138="","",VLOOKUP(C138,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>HUN</v>
       </c>
       <c r="B138" s="3" t="str">
         <f>IF(C138="","",VLOOKUP(C138,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Hungary</v>
+      </c>
+      <c r="C138" t="s">
+        <v>598</v>
+      </c>
+      <c r="D138" t="s">
+        <v>599</v>
+      </c>
+      <c r="E138" t="s">
+        <v>600</v>
       </c>
       <c r="J138" s="2" t="str">
         <f>IF(G138="","",VLOOKUP(G138,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -14484,15 +15853,39 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-    </row>
-    <row r="139" spans="1:13" hidden="1">
+      <c r="O138" t="s">
+        <v>79</v>
+      </c>
+      <c r="P138" s="1">
+        <v>46125</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>159</v>
+      </c>
+      <c r="R138" t="s">
+        <v>601</v>
+      </c>
+      <c r="S138">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:19">
       <c r="A139" s="2" t="str">
         <f>IF(C139="","",VLOOKUP(C139,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>HUN</v>
       </c>
       <c r="B139" s="3" t="str">
         <f>IF(C139="","",VLOOKUP(C139,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Hungary</v>
+      </c>
+      <c r="C139" t="s">
+        <v>598</v>
+      </c>
+      <c r="D139" t="s">
+        <v>602</v>
+      </c>
+      <c r="E139" t="s">
+        <v>603</v>
       </c>
       <c r="J139" s="2" t="str">
         <f>IF(G139="","",VLOOKUP(G139,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -14510,45 +15903,111 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-    </row>
-    <row r="140" spans="1:13" hidden="1">
+      <c r="N139" t="s">
+        <v>604</v>
+      </c>
+      <c r="O139" t="s">
+        <v>79</v>
+      </c>
+      <c r="P139" s="1">
+        <v>46124</v>
+      </c>
+      <c r="Q139" t="s">
+        <v>159</v>
+      </c>
+      <c r="R139" t="s">
+        <v>605</v>
+      </c>
+      <c r="S139">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:19">
       <c r="A140" s="2" t="str">
         <f>IF(C140="","",VLOOKUP(C140,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>GBR</v>
       </c>
       <c r="B140" s="3" t="str">
         <f>IF(C140="","",VLOOKUP(C140,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Britain</v>
+      </c>
+      <c r="C140" t="s">
+        <v>193</v>
+      </c>
+      <c r="D140" t="s">
+        <v>606</v>
+      </c>
+      <c r="E140" t="s">
+        <v>607</v>
+      </c>
+      <c r="G140" t="s">
+        <v>177</v>
+      </c>
+      <c r="H140" t="s">
+        <v>213</v>
+      </c>
+      <c r="I140" t="s">
+        <v>188</v>
       </c>
       <c r="J140" s="2" t="str">
         <f>IF(G140="","",VLOOKUP(G140,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>USA</v>
       </c>
       <c r="K140" s="2" t="str">
         <f>IF(H140="","",VLOOKUP(H140,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>FRA</v>
       </c>
       <c r="L140" s="2" t="str">
         <f>IF(I140="","",VLOOKUP(I140,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>IRN</v>
       </c>
       <c r="M140" s="3" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="141" spans="1:13" hidden="1">
+        <v>USA;FRA;IRN</v>
+      </c>
+      <c r="N140" t="s">
+        <v>608</v>
+      </c>
+      <c r="O140" t="s">
+        <v>25</v>
+      </c>
+      <c r="P140" s="1">
+        <v>46125</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>159</v>
+      </c>
+      <c r="R140" t="s">
+        <v>609</v>
+      </c>
+      <c r="S140">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:19">
       <c r="A141" s="2" t="str">
         <f>IF(C141="","",VLOOKUP(C141,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>UKR</v>
       </c>
       <c r="B141" s="3" t="str">
         <f>IF(C141="","",VLOOKUP(C141,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Ukraine</v>
+      </c>
+      <c r="C141" t="s">
+        <v>202</v>
+      </c>
+      <c r="D141" t="s">
+        <v>610</v>
+      </c>
+      <c r="E141" t="s">
+        <v>611</v>
+      </c>
+      <c r="G141" t="s">
+        <v>176</v>
       </c>
       <c r="J141" s="2" t="str">
         <f>IF(G141="","",VLOOKUP(G141,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>RUS</v>
       </c>
       <c r="K141" s="2" t="str">
         <f>IF(H141="","",VLOOKUP(H141,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -14560,17 +16019,44 @@
       </c>
       <c r="M141" s="3" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="142" spans="1:13" hidden="1">
+        <v>RUS</v>
+      </c>
+      <c r="N141" t="s">
+        <v>612</v>
+      </c>
+      <c r="O141" t="s">
+        <v>69</v>
+      </c>
+      <c r="P141" s="1">
+        <v>46123</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>159</v>
+      </c>
+      <c r="R141" t="s">
+        <v>613</v>
+      </c>
+      <c r="S141">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:19">
       <c r="A142" s="2" t="str">
         <f>IF(C142="","",VLOOKUP(C142,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>ISR</v>
       </c>
       <c r="B142" s="3" t="str">
         <f>IF(C142="","",VLOOKUP(C142,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Israel</v>
+      </c>
+      <c r="C142" t="s">
+        <v>153</v>
+      </c>
+      <c r="D142" t="s">
+        <v>614</v>
+      </c>
+      <c r="E142" t="s">
+        <v>615</v>
       </c>
       <c r="J142" s="2" t="str">
         <f>IF(G142="","",VLOOKUP(G142,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -14588,15 +16074,42 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-    </row>
-    <row r="143" spans="1:13" hidden="1">
+      <c r="N142" t="s">
+        <v>616</v>
+      </c>
+      <c r="O142" t="s">
+        <v>79</v>
+      </c>
+      <c r="P142" s="1">
+        <v>46124</v>
+      </c>
+      <c r="Q142" t="s">
+        <v>159</v>
+      </c>
+      <c r="R142" t="s">
+        <v>617</v>
+      </c>
+      <c r="S142">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:19">
       <c r="A143" s="2" t="str">
         <f>IF(C143="","",VLOOKUP(C143,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v/>
+        <v>IRQ</v>
       </c>
       <c r="B143" s="3" t="str">
         <f>IF(C143="","",VLOOKUP(C143,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v/>
+        <v>Iraq</v>
+      </c>
+      <c r="C143" t="s">
+        <v>618</v>
+      </c>
+      <c r="D143" t="s">
+        <v>619</v>
+      </c>
+      <c r="E143" t="s">
+        <v>620</v>
       </c>
       <c r="J143" s="2" t="str">
         <f>IF(G143="","",VLOOKUP(G143,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -14614,8 +16127,26 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-    </row>
-    <row r="144" spans="1:13" hidden="1">
+      <c r="N143" t="s">
+        <v>621</v>
+      </c>
+      <c r="O143" t="s">
+        <v>79</v>
+      </c>
+      <c r="P143" s="1">
+        <v>46123</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>159</v>
+      </c>
+      <c r="R143" t="s">
+        <v>622</v>
+      </c>
+      <c r="S143">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="144" spans="1:19">
       <c r="A144" s="2" t="str">
         <f>IF(C144="","",VLOOKUP(C144,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14637,11 +16168,11 @@
         <v/>
       </c>
       <c r="M144" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="145" spans="1:13" hidden="1">
+        <f t="shared" ref="M130:M193" si="3">_xlfn.TEXTJOIN(";",TRUE,J144:L144)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145" spans="1:13">
       <c r="A145" s="2" t="str">
         <f>IF(C145="","",VLOOKUP(C145,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14663,11 +16194,11 @@
         <v/>
       </c>
       <c r="M145" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="146" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="146" spans="1:13">
       <c r="A146" s="2" t="str">
         <f>IF(C146="","",VLOOKUP(C146,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14689,11 +16220,11 @@
         <v/>
       </c>
       <c r="M146" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="147" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="147" spans="1:13">
       <c r="A147" s="2" t="str">
         <f>IF(C147="","",VLOOKUP(C147,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14715,11 +16246,11 @@
         <v/>
       </c>
       <c r="M147" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="148" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="148" spans="1:13">
       <c r="A148" s="2" t="str">
         <f>IF(C148="","",VLOOKUP(C148,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14741,11 +16272,11 @@
         <v/>
       </c>
       <c r="M148" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="149" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="149" spans="1:13">
       <c r="A149" s="2" t="str">
         <f>IF(C149="","",VLOOKUP(C149,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14767,11 +16298,11 @@
         <v/>
       </c>
       <c r="M149" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="150" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="150" spans="1:13">
       <c r="A150" s="2" t="str">
         <f>IF(C150="","",VLOOKUP(C150,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14793,11 +16324,11 @@
         <v/>
       </c>
       <c r="M150" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="151" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="151" spans="1:13">
       <c r="A151" s="2" t="str">
         <f>IF(C151="","",VLOOKUP(C151,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14819,11 +16350,11 @@
         <v/>
       </c>
       <c r="M151" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="152" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="152" spans="1:13">
       <c r="A152" s="2" t="str">
         <f>IF(C152="","",VLOOKUP(C152,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14845,11 +16376,11 @@
         <v/>
       </c>
       <c r="M152" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="153" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="153" spans="1:13">
       <c r="A153" s="2" t="str">
         <f>IF(C153="","",VLOOKUP(C153,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14871,11 +16402,11 @@
         <v/>
       </c>
       <c r="M153" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="154" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="154" spans="1:13">
       <c r="A154" s="2" t="str">
         <f>IF(C154="","",VLOOKUP(C154,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14897,11 +16428,11 @@
         <v/>
       </c>
       <c r="M154" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="155" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="155" spans="1:13">
       <c r="A155" s="2" t="str">
         <f>IF(C155="","",VLOOKUP(C155,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14923,11 +16454,11 @@
         <v/>
       </c>
       <c r="M155" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="156" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="156" spans="1:13">
       <c r="A156" s="2" t="str">
         <f>IF(C156="","",VLOOKUP(C156,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14949,11 +16480,11 @@
         <v/>
       </c>
       <c r="M156" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="157" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="157" spans="1:13">
       <c r="A157" s="2" t="str">
         <f>IF(C157="","",VLOOKUP(C157,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -14975,11 +16506,11 @@
         <v/>
       </c>
       <c r="M157" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="158" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="158" spans="1:13">
       <c r="A158" s="2" t="str">
         <f>IF(C158="","",VLOOKUP(C158,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15001,11 +16532,11 @@
         <v/>
       </c>
       <c r="M158" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="159" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="159" spans="1:13">
       <c r="A159" s="2" t="str">
         <f>IF(C159="","",VLOOKUP(C159,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15027,11 +16558,11 @@
         <v/>
       </c>
       <c r="M159" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="160" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="160" spans="1:13">
       <c r="A160" s="2" t="str">
         <f>IF(C160="","",VLOOKUP(C160,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15053,11 +16584,11 @@
         <v/>
       </c>
       <c r="M160" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="161" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="161" spans="1:13">
       <c r="A161" s="2" t="str">
         <f>IF(C161="","",VLOOKUP(C161,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15079,11 +16610,11 @@
         <v/>
       </c>
       <c r="M161" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="162" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="162" spans="1:13">
       <c r="A162" s="2" t="str">
         <f>IF(C162="","",VLOOKUP(C162,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15105,11 +16636,11 @@
         <v/>
       </c>
       <c r="M162" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="163" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="163" spans="1:13">
       <c r="A163" s="2" t="str">
         <f>IF(C163="","",VLOOKUP(C163,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15131,11 +16662,11 @@
         <v/>
       </c>
       <c r="M163" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="164" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="164" spans="1:13">
       <c r="A164" s="2" t="str">
         <f>IF(C164="","",VLOOKUP(C164,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15157,11 +16688,11 @@
         <v/>
       </c>
       <c r="M164" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="165" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="165" spans="1:13">
       <c r="A165" s="2" t="str">
         <f>IF(C165="","",VLOOKUP(C165,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15183,11 +16714,11 @@
         <v/>
       </c>
       <c r="M165" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="166" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="166" spans="1:13">
       <c r="A166" s="2" t="str">
         <f>IF(C166="","",VLOOKUP(C166,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15209,11 +16740,11 @@
         <v/>
       </c>
       <c r="M166" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="167" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="167" spans="1:13">
       <c r="A167" s="2" t="str">
         <f>IF(C167="","",VLOOKUP(C167,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15235,11 +16766,11 @@
         <v/>
       </c>
       <c r="M167" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="168" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="168" spans="1:13">
       <c r="A168" s="2" t="str">
         <f>IF(C168="","",VLOOKUP(C168,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15261,11 +16792,11 @@
         <v/>
       </c>
       <c r="M168" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="169" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="169" spans="1:13">
       <c r="A169" s="2" t="str">
         <f>IF(C169="","",VLOOKUP(C169,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15287,11 +16818,11 @@
         <v/>
       </c>
       <c r="M169" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="170" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="170" spans="1:13">
       <c r="A170" s="2" t="str">
         <f>IF(C170="","",VLOOKUP(C170,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15313,11 +16844,11 @@
         <v/>
       </c>
       <c r="M170" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="171" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="171" spans="1:13">
       <c r="A171" s="2" t="str">
         <f>IF(C171="","",VLOOKUP(C171,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15339,11 +16870,11 @@
         <v/>
       </c>
       <c r="M171" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="172" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="172" spans="1:13">
       <c r="A172" s="2" t="str">
         <f>IF(C172="","",VLOOKUP(C172,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15365,11 +16896,11 @@
         <v/>
       </c>
       <c r="M172" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="173" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="173" spans="1:13">
       <c r="A173" s="2" t="str">
         <f>IF(C173="","",VLOOKUP(C173,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15391,11 +16922,11 @@
         <v/>
       </c>
       <c r="M173" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="174" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="174" spans="1:13">
       <c r="A174" s="2" t="str">
         <f>IF(C174="","",VLOOKUP(C174,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15417,11 +16948,11 @@
         <v/>
       </c>
       <c r="M174" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="175" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="175" spans="1:13">
       <c r="A175" s="2" t="str">
         <f>IF(C175="","",VLOOKUP(C175,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15443,11 +16974,11 @@
         <v/>
       </c>
       <c r="M175" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="176" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="176" spans="1:13">
       <c r="A176" s="2" t="str">
         <f>IF(C176="","",VLOOKUP(C176,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15469,11 +17000,11 @@
         <v/>
       </c>
       <c r="M176" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="177" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="177" spans="1:13">
       <c r="A177" s="2" t="str">
         <f>IF(C177="","",VLOOKUP(C177,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15495,11 +17026,11 @@
         <v/>
       </c>
       <c r="M177" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="178" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="178" spans="1:13">
       <c r="A178" s="2" t="str">
         <f>IF(C178="","",VLOOKUP(C178,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15521,11 +17052,11 @@
         <v/>
       </c>
       <c r="M178" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="179" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="179" spans="1:13">
       <c r="A179" s="2" t="str">
         <f>IF(C179="","",VLOOKUP(C179,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15547,11 +17078,11 @@
         <v/>
       </c>
       <c r="M179" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="180" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="180" spans="1:13">
       <c r="A180" s="2" t="str">
         <f>IF(C180="","",VLOOKUP(C180,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15573,11 +17104,11 @@
         <v/>
       </c>
       <c r="M180" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="181" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="181" spans="1:13">
       <c r="A181" s="2" t="str">
         <f>IF(C181="","",VLOOKUP(C181,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15599,11 +17130,11 @@
         <v/>
       </c>
       <c r="M181" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="182" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="182" spans="1:13">
       <c r="A182" s="2" t="str">
         <f>IF(C182="","",VLOOKUP(C182,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15625,11 +17156,11 @@
         <v/>
       </c>
       <c r="M182" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="183" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="183" spans="1:13">
       <c r="A183" s="2" t="str">
         <f>IF(C183="","",VLOOKUP(C183,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15651,11 +17182,11 @@
         <v/>
       </c>
       <c r="M183" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="184" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="184" spans="1:13">
       <c r="A184" s="2" t="str">
         <f>IF(C184="","",VLOOKUP(C184,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15677,11 +17208,11 @@
         <v/>
       </c>
       <c r="M184" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="185" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="185" spans="1:13">
       <c r="A185" s="2" t="str">
         <f>IF(C185="","",VLOOKUP(C185,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15703,11 +17234,11 @@
         <v/>
       </c>
       <c r="M185" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="186" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="186" spans="1:13">
       <c r="A186" s="2" t="str">
         <f>IF(C186="","",VLOOKUP(C186,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15729,11 +17260,11 @@
         <v/>
       </c>
       <c r="M186" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="187" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="187" spans="1:13">
       <c r="A187" s="2" t="str">
         <f>IF(C187="","",VLOOKUP(C187,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15755,11 +17286,11 @@
         <v/>
       </c>
       <c r="M187" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="188" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="188" spans="1:13">
       <c r="A188" s="2" t="str">
         <f>IF(C188="","",VLOOKUP(C188,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15781,11 +17312,11 @@
         <v/>
       </c>
       <c r="M188" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="189" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="189" spans="1:13">
       <c r="A189" s="2" t="str">
         <f>IF(C189="","",VLOOKUP(C189,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15807,11 +17338,11 @@
         <v/>
       </c>
       <c r="M189" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="190" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="190" spans="1:13">
       <c r="A190" s="2" t="str">
         <f>IF(C190="","",VLOOKUP(C190,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15833,11 +17364,11 @@
         <v/>
       </c>
       <c r="M190" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="191" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="191" spans="1:13">
       <c r="A191" s="2" t="str">
         <f>IF(C191="","",VLOOKUP(C191,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15859,11 +17390,11 @@
         <v/>
       </c>
       <c r="M191" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="192" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="192" spans="1:13">
       <c r="A192" s="2" t="str">
         <f>IF(C192="","",VLOOKUP(C192,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15885,11 +17416,11 @@
         <v/>
       </c>
       <c r="M192" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="193" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="193" spans="1:13">
       <c r="A193" s="2" t="str">
         <f>IF(C193="","",VLOOKUP(C193,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15911,11 +17442,11 @@
         <v/>
       </c>
       <c r="M193" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="194" spans="1:13" hidden="1">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="194" spans="1:13">
       <c r="A194" s="2" t="str">
         <f>IF(C194="","",VLOOKUP(C194,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15937,11 +17468,11 @@
         <v/>
       </c>
       <c r="M194" s="3" t="str">
-        <f t="shared" ref="M194:M257" si="3">_xlfn.TEXTJOIN(";",TRUE,J194:L194)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="195" spans="1:13" hidden="1">
+        <f t="shared" ref="M194:M257" si="4">_xlfn.TEXTJOIN(";",TRUE,J194:L194)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195" spans="1:13">
       <c r="A195" s="2" t="str">
         <f>IF(C195="","",VLOOKUP(C195,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15963,11 +17494,11 @@
         <v/>
       </c>
       <c r="M195" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="196" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="196" spans="1:13">
       <c r="A196" s="2" t="str">
         <f>IF(C196="","",VLOOKUP(C196,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -15989,11 +17520,11 @@
         <v/>
       </c>
       <c r="M196" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="197" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="197" spans="1:13">
       <c r="A197" s="2" t="str">
         <f>IF(C197="","",VLOOKUP(C197,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16015,11 +17546,11 @@
         <v/>
       </c>
       <c r="M197" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="198" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="198" spans="1:13">
       <c r="A198" s="2" t="str">
         <f>IF(C198="","",VLOOKUP(C198,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16041,11 +17572,11 @@
         <v/>
       </c>
       <c r="M198" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="199" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="199" spans="1:13">
       <c r="A199" s="2" t="str">
         <f>IF(C199="","",VLOOKUP(C199,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16067,11 +17598,11 @@
         <v/>
       </c>
       <c r="M199" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="200" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="200" spans="1:13">
       <c r="A200" s="2" t="str">
         <f>IF(C200="","",VLOOKUP(C200,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16093,11 +17624,11 @@
         <v/>
       </c>
       <c r="M200" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="201" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="201" spans="1:13">
       <c r="A201" s="2" t="str">
         <f>IF(C201="","",VLOOKUP(C201,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16119,11 +17650,11 @@
         <v/>
       </c>
       <c r="M201" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="202" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="202" spans="1:13">
       <c r="A202" s="2" t="str">
         <f>IF(C202="","",VLOOKUP(C202,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16145,11 +17676,11 @@
         <v/>
       </c>
       <c r="M202" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="203" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="203" spans="1:13">
       <c r="A203" s="2" t="str">
         <f>IF(C203="","",VLOOKUP(C203,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16171,11 +17702,11 @@
         <v/>
       </c>
       <c r="M203" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="204" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="204" spans="1:13">
       <c r="A204" s="2" t="str">
         <f>IF(C204="","",VLOOKUP(C204,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16197,11 +17728,11 @@
         <v/>
       </c>
       <c r="M204" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="205" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="205" spans="1:13">
       <c r="A205" s="2" t="str">
         <f>IF(C205="","",VLOOKUP(C205,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16223,11 +17754,11 @@
         <v/>
       </c>
       <c r="M205" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="206" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="206" spans="1:13">
       <c r="A206" s="2" t="str">
         <f>IF(C206="","",VLOOKUP(C206,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16249,11 +17780,11 @@
         <v/>
       </c>
       <c r="M206" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="207" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="207" spans="1:13">
       <c r="A207" s="2" t="str">
         <f>IF(C207="","",VLOOKUP(C207,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16275,11 +17806,11 @@
         <v/>
       </c>
       <c r="M207" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="208" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="208" spans="1:13">
       <c r="A208" s="2" t="str">
         <f>IF(C208="","",VLOOKUP(C208,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16301,11 +17832,11 @@
         <v/>
       </c>
       <c r="M208" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="209" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="209" spans="1:13">
       <c r="A209" s="2" t="str">
         <f>IF(C209="","",VLOOKUP(C209,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16327,11 +17858,11 @@
         <v/>
       </c>
       <c r="M209" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="210" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="210" spans="1:13">
       <c r="A210" s="2" t="str">
         <f>IF(C210="","",VLOOKUP(C210,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16353,11 +17884,11 @@
         <v/>
       </c>
       <c r="M210" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="211" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="211" spans="1:13">
       <c r="A211" s="2" t="str">
         <f>IF(C211="","",VLOOKUP(C211,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16379,11 +17910,11 @@
         <v/>
       </c>
       <c r="M211" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="212" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="212" spans="1:13">
       <c r="A212" s="2" t="str">
         <f>IF(C212="","",VLOOKUP(C212,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16405,11 +17936,11 @@
         <v/>
       </c>
       <c r="M212" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="213" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="213" spans="1:13">
       <c r="A213" s="2" t="str">
         <f>IF(C213="","",VLOOKUP(C213,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16431,11 +17962,11 @@
         <v/>
       </c>
       <c r="M213" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="214" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="214" spans="1:13">
       <c r="A214" s="2" t="str">
         <f>IF(C214="","",VLOOKUP(C214,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16457,11 +17988,11 @@
         <v/>
       </c>
       <c r="M214" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="215" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="215" spans="1:13">
       <c r="A215" s="2" t="str">
         <f>IF(C215="","",VLOOKUP(C215,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16483,11 +18014,11 @@
         <v/>
       </c>
       <c r="M215" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="216" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="216" spans="1:13">
       <c r="A216" s="2" t="str">
         <f>IF(C216="","",VLOOKUP(C216,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16509,11 +18040,11 @@
         <v/>
       </c>
       <c r="M216" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="217" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="217" spans="1:13">
       <c r="A217" s="2" t="str">
         <f>IF(C217="","",VLOOKUP(C217,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16535,11 +18066,11 @@
         <v/>
       </c>
       <c r="M217" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="218" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="218" spans="1:13">
       <c r="A218" s="2" t="str">
         <f>IF(C218="","",VLOOKUP(C218,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16561,11 +18092,11 @@
         <v/>
       </c>
       <c r="M218" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="219" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="219" spans="1:13">
       <c r="A219" s="2" t="str">
         <f>IF(C219="","",VLOOKUP(C219,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16587,11 +18118,11 @@
         <v/>
       </c>
       <c r="M219" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="220" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="220" spans="1:13">
       <c r="A220" s="2" t="str">
         <f>IF(C220="","",VLOOKUP(C220,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16613,11 +18144,11 @@
         <v/>
       </c>
       <c r="M220" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="221" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="221" spans="1:13">
       <c r="A221" s="2" t="str">
         <f>IF(C221="","",VLOOKUP(C221,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16639,11 +18170,11 @@
         <v/>
       </c>
       <c r="M221" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="222" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="222" spans="1:13">
       <c r="A222" s="2" t="str">
         <f>IF(C222="","",VLOOKUP(C222,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16665,11 +18196,11 @@
         <v/>
       </c>
       <c r="M222" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="223" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="223" spans="1:13">
       <c r="A223" s="2" t="str">
         <f>IF(C223="","",VLOOKUP(C223,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16691,11 +18222,11 @@
         <v/>
       </c>
       <c r="M223" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="224" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="224" spans="1:13">
       <c r="A224" s="2" t="str">
         <f>IF(C224="","",VLOOKUP(C224,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16717,11 +18248,11 @@
         <v/>
       </c>
       <c r="M224" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="225" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="225" spans="1:13">
       <c r="A225" s="2" t="str">
         <f>IF(C225="","",VLOOKUP(C225,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16743,11 +18274,11 @@
         <v/>
       </c>
       <c r="M225" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="226" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="226" spans="1:13">
       <c r="A226" s="2" t="str">
         <f>IF(C226="","",VLOOKUP(C226,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16769,11 +18300,11 @@
         <v/>
       </c>
       <c r="M226" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="227" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="227" spans="1:13">
       <c r="A227" s="2" t="str">
         <f>IF(C227="","",VLOOKUP(C227,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16795,11 +18326,11 @@
         <v/>
       </c>
       <c r="M227" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="228" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="228" spans="1:13">
       <c r="A228" s="2" t="str">
         <f>IF(C228="","",VLOOKUP(C228,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16821,11 +18352,11 @@
         <v/>
       </c>
       <c r="M228" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="229" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="229" spans="1:13">
       <c r="A229" s="2" t="str">
         <f>IF(C229="","",VLOOKUP(C229,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16847,11 +18378,11 @@
         <v/>
       </c>
       <c r="M229" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="230" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="230" spans="1:13">
       <c r="A230" s="2" t="str">
         <f>IF(C230="","",VLOOKUP(C230,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16873,11 +18404,11 @@
         <v/>
       </c>
       <c r="M230" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="231" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="231" spans="1:13">
       <c r="A231" s="2" t="str">
         <f>IF(C231="","",VLOOKUP(C231,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16899,11 +18430,11 @@
         <v/>
       </c>
       <c r="M231" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="232" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="232" spans="1:13">
       <c r="A232" s="2" t="str">
         <f>IF(C232="","",VLOOKUP(C232,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16925,11 +18456,11 @@
         <v/>
       </c>
       <c r="M232" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="233" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="233" spans="1:13">
       <c r="A233" s="2" t="str">
         <f>IF(C233="","",VLOOKUP(C233,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16951,11 +18482,11 @@
         <v/>
       </c>
       <c r="M233" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="234" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="234" spans="1:13">
       <c r="A234" s="2" t="str">
         <f>IF(C234="","",VLOOKUP(C234,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -16977,11 +18508,11 @@
         <v/>
       </c>
       <c r="M234" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="235" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="235" spans="1:13">
       <c r="A235" s="2" t="str">
         <f>IF(C235="","",VLOOKUP(C235,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17003,11 +18534,11 @@
         <v/>
       </c>
       <c r="M235" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="236" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="236" spans="1:13">
       <c r="A236" s="2" t="str">
         <f>IF(C236="","",VLOOKUP(C236,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17029,11 +18560,11 @@
         <v/>
       </c>
       <c r="M236" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="237" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="237" spans="1:13">
       <c r="A237" s="2" t="str">
         <f>IF(C237="","",VLOOKUP(C237,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17055,11 +18586,11 @@
         <v/>
       </c>
       <c r="M237" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="238" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="238" spans="1:13">
       <c r="A238" s="2" t="str">
         <f>IF(C238="","",VLOOKUP(C238,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17081,11 +18612,11 @@
         <v/>
       </c>
       <c r="M238" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="239" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="239" spans="1:13">
       <c r="A239" s="2" t="str">
         <f>IF(C239="","",VLOOKUP(C239,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17107,11 +18638,11 @@
         <v/>
       </c>
       <c r="M239" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="240" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="240" spans="1:13">
       <c r="A240" s="2" t="str">
         <f>IF(C240="","",VLOOKUP(C240,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17133,11 +18664,11 @@
         <v/>
       </c>
       <c r="M240" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="241" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="241" spans="1:13">
       <c r="A241" s="2" t="str">
         <f>IF(C241="","",VLOOKUP(C241,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17159,11 +18690,11 @@
         <v/>
       </c>
       <c r="M241" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="242" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="242" spans="1:13">
       <c r="A242" s="2" t="str">
         <f>IF(C242="","",VLOOKUP(C242,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17185,11 +18716,11 @@
         <v/>
       </c>
       <c r="M242" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="243" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="243" spans="1:13">
       <c r="A243" s="2" t="str">
         <f>IF(C243="","",VLOOKUP(C243,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17211,11 +18742,11 @@
         <v/>
       </c>
       <c r="M243" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="244" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="244" spans="1:13">
       <c r="A244" s="2" t="str">
         <f>IF(C244="","",VLOOKUP(C244,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17237,11 +18768,11 @@
         <v/>
       </c>
       <c r="M244" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="245" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="245" spans="1:13">
       <c r="A245" s="2" t="str">
         <f>IF(C245="","",VLOOKUP(C245,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17263,11 +18794,11 @@
         <v/>
       </c>
       <c r="M245" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="246" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="246" spans="1:13">
       <c r="A246" s="2" t="str">
         <f>IF(C246="","",VLOOKUP(C246,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17289,11 +18820,11 @@
         <v/>
       </c>
       <c r="M246" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="247" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="247" spans="1:13">
       <c r="A247" s="2" t="str">
         <f>IF(C247="","",VLOOKUP(C247,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17315,11 +18846,11 @@
         <v/>
       </c>
       <c r="M247" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="248" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="248" spans="1:13">
       <c r="A248" s="2" t="str">
         <f>IF(C248="","",VLOOKUP(C248,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17341,11 +18872,11 @@
         <v/>
       </c>
       <c r="M248" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="249" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="249" spans="1:13">
       <c r="A249" s="2" t="str">
         <f>IF(C249="","",VLOOKUP(C249,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17367,11 +18898,11 @@
         <v/>
       </c>
       <c r="M249" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="250" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="250" spans="1:13">
       <c r="A250" s="2" t="str">
         <f>IF(C250="","",VLOOKUP(C250,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17393,11 +18924,11 @@
         <v/>
       </c>
       <c r="M250" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="251" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="251" spans="1:13">
       <c r="A251" s="2" t="str">
         <f>IF(C251="","",VLOOKUP(C251,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17419,11 +18950,11 @@
         <v/>
       </c>
       <c r="M251" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="252" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="252" spans="1:13">
       <c r="A252" s="2" t="str">
         <f>IF(C252="","",VLOOKUP(C252,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17445,11 +18976,11 @@
         <v/>
       </c>
       <c r="M252" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="253" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="253" spans="1:13">
       <c r="A253" s="2" t="str">
         <f>IF(C253="","",VLOOKUP(C253,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17471,11 +19002,11 @@
         <v/>
       </c>
       <c r="M253" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="254" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="254" spans="1:13">
       <c r="A254" s="2" t="str">
         <f>IF(C254="","",VLOOKUP(C254,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17497,11 +19028,11 @@
         <v/>
       </c>
       <c r="M254" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="255" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="255" spans="1:13">
       <c r="A255" s="2" t="str">
         <f>IF(C255="","",VLOOKUP(C255,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17523,11 +19054,11 @@
         <v/>
       </c>
       <c r="M255" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="256" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="256" spans="1:13">
       <c r="A256" s="2" t="str">
         <f>IF(C256="","",VLOOKUP(C256,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17549,11 +19080,11 @@
         <v/>
       </c>
       <c r="M256" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="257" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="257" spans="1:13">
       <c r="A257" s="2" t="str">
         <f>IF(C257="","",VLOOKUP(C257,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17575,11 +19106,11 @@
         <v/>
       </c>
       <c r="M257" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="258" spans="1:13" hidden="1">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="258" spans="1:13">
       <c r="A258" s="2" t="str">
         <f>IF(C258="","",VLOOKUP(C258,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17601,11 +19132,11 @@
         <v/>
       </c>
       <c r="M258" s="3" t="str">
-        <f t="shared" ref="M258:M321" si="4">_xlfn.TEXTJOIN(";",TRUE,J258:L258)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="259" spans="1:13" hidden="1">
+        <f t="shared" ref="M258:M321" si="5">_xlfn.TEXTJOIN(";",TRUE,J258:L258)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="259" spans="1:13">
       <c r="A259" s="2" t="str">
         <f>IF(C259="","",VLOOKUP(C259,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17627,11 +19158,11 @@
         <v/>
       </c>
       <c r="M259" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="260" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="260" spans="1:13">
       <c r="A260" s="2" t="str">
         <f>IF(C260="","",VLOOKUP(C260,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17653,11 +19184,11 @@
         <v/>
       </c>
       <c r="M260" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="261" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="261" spans="1:13">
       <c r="A261" s="2" t="str">
         <f>IF(C261="","",VLOOKUP(C261,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17679,11 +19210,11 @@
         <v/>
       </c>
       <c r="M261" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="262" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="262" spans="1:13">
       <c r="A262" s="2" t="str">
         <f>IF(C262="","",VLOOKUP(C262,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17705,11 +19236,11 @@
         <v/>
       </c>
       <c r="M262" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="263" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="263" spans="1:13">
       <c r="A263" s="2" t="str">
         <f>IF(C263="","",VLOOKUP(C263,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17731,11 +19262,11 @@
         <v/>
       </c>
       <c r="M263" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="264" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="264" spans="1:13">
       <c r="A264" s="2" t="str">
         <f>IF(C264="","",VLOOKUP(C264,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17757,11 +19288,11 @@
         <v/>
       </c>
       <c r="M264" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="265" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="265" spans="1:13">
       <c r="A265" s="2" t="str">
         <f>IF(C265="","",VLOOKUP(C265,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17783,11 +19314,11 @@
         <v/>
       </c>
       <c r="M265" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="266" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="266" spans="1:13">
       <c r="A266" s="2" t="str">
         <f>IF(C266="","",VLOOKUP(C266,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17809,11 +19340,11 @@
         <v/>
       </c>
       <c r="M266" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="267" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="267" spans="1:13">
       <c r="A267" s="2" t="str">
         <f>IF(C267="","",VLOOKUP(C267,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17835,11 +19366,11 @@
         <v/>
       </c>
       <c r="M267" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="268" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="268" spans="1:13">
       <c r="A268" s="2" t="str">
         <f>IF(C268="","",VLOOKUP(C268,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17861,11 +19392,11 @@
         <v/>
       </c>
       <c r="M268" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="269" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="269" spans="1:13">
       <c r="A269" s="2" t="str">
         <f>IF(C269="","",VLOOKUP(C269,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17887,11 +19418,11 @@
         <v/>
       </c>
       <c r="M269" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="270" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="270" spans="1:13">
       <c r="A270" s="2" t="str">
         <f>IF(C270="","",VLOOKUP(C270,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17913,11 +19444,11 @@
         <v/>
       </c>
       <c r="M270" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="271" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="271" spans="1:13">
       <c r="A271" s="2" t="str">
         <f>IF(C271="","",VLOOKUP(C271,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17939,11 +19470,11 @@
         <v/>
       </c>
       <c r="M271" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="272" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="272" spans="1:13">
       <c r="A272" s="2" t="str">
         <f>IF(C272="","",VLOOKUP(C272,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17965,11 +19496,11 @@
         <v/>
       </c>
       <c r="M272" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="273" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="273" spans="1:13">
       <c r="A273" s="2" t="str">
         <f>IF(C273="","",VLOOKUP(C273,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -17991,11 +19522,11 @@
         <v/>
       </c>
       <c r="M273" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="274" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="274" spans="1:13">
       <c r="A274" s="2" t="str">
         <f>IF(C274="","",VLOOKUP(C274,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18017,11 +19548,11 @@
         <v/>
       </c>
       <c r="M274" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="275" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="275" spans="1:13">
       <c r="A275" s="2" t="str">
         <f>IF(C275="","",VLOOKUP(C275,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18043,11 +19574,11 @@
         <v/>
       </c>
       <c r="M275" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="276" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="276" spans="1:13">
       <c r="A276" s="2" t="str">
         <f>IF(C276="","",VLOOKUP(C276,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18069,11 +19600,11 @@
         <v/>
       </c>
       <c r="M276" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="277" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="277" spans="1:13">
       <c r="A277" s="2" t="str">
         <f>IF(C277="","",VLOOKUP(C277,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18095,11 +19626,11 @@
         <v/>
       </c>
       <c r="M277" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="278" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="278" spans="1:13">
       <c r="A278" s="2" t="str">
         <f>IF(C278="","",VLOOKUP(C278,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18121,11 +19652,11 @@
         <v/>
       </c>
       <c r="M278" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="279" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="279" spans="1:13">
       <c r="A279" s="2" t="str">
         <f>IF(C279="","",VLOOKUP(C279,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18147,11 +19678,11 @@
         <v/>
       </c>
       <c r="M279" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="280" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="280" spans="1:13">
       <c r="A280" s="2" t="str">
         <f>IF(C280="","",VLOOKUP(C280,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18173,11 +19704,11 @@
         <v/>
       </c>
       <c r="M280" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="281" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="281" spans="1:13">
       <c r="A281" s="2" t="str">
         <f>IF(C281="","",VLOOKUP(C281,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18199,11 +19730,11 @@
         <v/>
       </c>
       <c r="M281" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="282" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="282" spans="1:13">
       <c r="A282" s="2" t="str">
         <f>IF(C282="","",VLOOKUP(C282,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18225,11 +19756,11 @@
         <v/>
       </c>
       <c r="M282" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="283" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="283" spans="1:13">
       <c r="A283" s="2" t="str">
         <f>IF(C283="","",VLOOKUP(C283,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18251,11 +19782,11 @@
         <v/>
       </c>
       <c r="M283" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="284" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="284" spans="1:13">
       <c r="A284" s="2" t="str">
         <f>IF(C284="","",VLOOKUP(C284,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18277,11 +19808,11 @@
         <v/>
       </c>
       <c r="M284" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="285" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="285" spans="1:13">
       <c r="A285" s="2" t="str">
         <f>IF(C285="","",VLOOKUP(C285,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18303,11 +19834,11 @@
         <v/>
       </c>
       <c r="M285" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="286" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="286" spans="1:13">
       <c r="A286" s="2" t="str">
         <f>IF(C286="","",VLOOKUP(C286,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18329,11 +19860,11 @@
         <v/>
       </c>
       <c r="M286" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="287" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="287" spans="1:13">
       <c r="A287" s="2" t="str">
         <f>IF(C287="","",VLOOKUP(C287,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18355,11 +19886,11 @@
         <v/>
       </c>
       <c r="M287" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="288" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="288" spans="1:13">
       <c r="A288" s="2" t="str">
         <f>IF(C288="","",VLOOKUP(C288,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18381,11 +19912,11 @@
         <v/>
       </c>
       <c r="M288" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="289" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="289" spans="1:13">
       <c r="A289" s="2" t="str">
         <f>IF(C289="","",VLOOKUP(C289,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18407,11 +19938,11 @@
         <v/>
       </c>
       <c r="M289" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="290" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="290" spans="1:13">
       <c r="A290" s="2" t="str">
         <f>IF(C290="","",VLOOKUP(C290,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18433,11 +19964,11 @@
         <v/>
       </c>
       <c r="M290" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="291" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="291" spans="1:13">
       <c r="A291" s="2" t="str">
         <f>IF(C291="","",VLOOKUP(C291,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18459,11 +19990,11 @@
         <v/>
       </c>
       <c r="M291" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="292" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="292" spans="1:13">
       <c r="A292" s="2" t="str">
         <f>IF(C292="","",VLOOKUP(C292,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18485,11 +20016,11 @@
         <v/>
       </c>
       <c r="M292" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="293" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="293" spans="1:13">
       <c r="A293" s="2" t="str">
         <f>IF(C293="","",VLOOKUP(C293,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18511,11 +20042,11 @@
         <v/>
       </c>
       <c r="M293" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="294" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="294" spans="1:13">
       <c r="A294" s="2" t="str">
         <f>IF(C294="","",VLOOKUP(C294,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18537,11 +20068,11 @@
         <v/>
       </c>
       <c r="M294" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="295" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="295" spans="1:13">
       <c r="A295" s="2" t="str">
         <f>IF(C295="","",VLOOKUP(C295,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18563,11 +20094,11 @@
         <v/>
       </c>
       <c r="M295" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="296" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="296" spans="1:13">
       <c r="A296" s="2" t="str">
         <f>IF(C296="","",VLOOKUP(C296,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18589,11 +20120,11 @@
         <v/>
       </c>
       <c r="M296" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="297" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="297" spans="1:13">
       <c r="A297" s="2" t="str">
         <f>IF(C297="","",VLOOKUP(C297,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18615,11 +20146,11 @@
         <v/>
       </c>
       <c r="M297" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="298" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="298" spans="1:13">
       <c r="A298" s="2" t="str">
         <f>IF(C298="","",VLOOKUP(C298,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18641,11 +20172,11 @@
         <v/>
       </c>
       <c r="M298" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="299" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="299" spans="1:13">
       <c r="A299" s="2" t="str">
         <f>IF(C299="","",VLOOKUP(C299,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18667,11 +20198,11 @@
         <v/>
       </c>
       <c r="M299" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="300" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="300" spans="1:13">
       <c r="A300" s="2" t="str">
         <f>IF(C300="","",VLOOKUP(C300,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18693,11 +20224,11 @@
         <v/>
       </c>
       <c r="M300" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="301" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="301" spans="1:13">
       <c r="A301" s="2" t="str">
         <f>IF(C301="","",VLOOKUP(C301,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18719,11 +20250,11 @@
         <v/>
       </c>
       <c r="M301" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="302" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="302" spans="1:13">
       <c r="A302" s="2" t="str">
         <f>IF(C302="","",VLOOKUP(C302,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18745,11 +20276,11 @@
         <v/>
       </c>
       <c r="M302" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="303" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="303" spans="1:13">
       <c r="A303" s="2" t="str">
         <f>IF(C303="","",VLOOKUP(C303,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18771,11 +20302,11 @@
         <v/>
       </c>
       <c r="M303" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="304" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="304" spans="1:13">
       <c r="A304" s="2" t="str">
         <f>IF(C304="","",VLOOKUP(C304,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18797,11 +20328,11 @@
         <v/>
       </c>
       <c r="M304" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="305" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="305" spans="1:13">
       <c r="A305" s="2" t="str">
         <f>IF(C305="","",VLOOKUP(C305,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18823,11 +20354,11 @@
         <v/>
       </c>
       <c r="M305" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="306" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="306" spans="1:13">
       <c r="A306" s="2" t="str">
         <f>IF(C306="","",VLOOKUP(C306,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18849,11 +20380,11 @@
         <v/>
       </c>
       <c r="M306" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="307" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="307" spans="1:13">
       <c r="A307" s="2" t="str">
         <f>IF(C307="","",VLOOKUP(C307,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18875,11 +20406,11 @@
         <v/>
       </c>
       <c r="M307" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="308" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="308" spans="1:13">
       <c r="A308" s="2" t="str">
         <f>IF(C308="","",VLOOKUP(C308,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18901,11 +20432,11 @@
         <v/>
       </c>
       <c r="M308" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="309" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="309" spans="1:13">
       <c r="A309" s="2" t="str">
         <f>IF(C309="","",VLOOKUP(C309,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18927,11 +20458,11 @@
         <v/>
       </c>
       <c r="M309" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="310" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="310" spans="1:13">
       <c r="A310" s="2" t="str">
         <f>IF(C310="","",VLOOKUP(C310,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18953,11 +20484,11 @@
         <v/>
       </c>
       <c r="M310" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="311" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="311" spans="1:13">
       <c r="A311" s="2" t="str">
         <f>IF(C311="","",VLOOKUP(C311,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -18979,11 +20510,11 @@
         <v/>
       </c>
       <c r="M311" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="312" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="312" spans="1:13">
       <c r="A312" s="2" t="str">
         <f>IF(C312="","",VLOOKUP(C312,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19005,11 +20536,11 @@
         <v/>
       </c>
       <c r="M312" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="313" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="313" spans="1:13">
       <c r="A313" s="2" t="str">
         <f>IF(C313="","",VLOOKUP(C313,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19031,11 +20562,11 @@
         <v/>
       </c>
       <c r="M313" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="314" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="314" spans="1:13">
       <c r="A314" s="2" t="str">
         <f>IF(C314="","",VLOOKUP(C314,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19057,11 +20588,11 @@
         <v/>
       </c>
       <c r="M314" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="315" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="315" spans="1:13">
       <c r="A315" s="2" t="str">
         <f>IF(C315="","",VLOOKUP(C315,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19083,11 +20614,11 @@
         <v/>
       </c>
       <c r="M315" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="316" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="316" spans="1:13">
       <c r="A316" s="2" t="str">
         <f>IF(C316="","",VLOOKUP(C316,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19109,11 +20640,11 @@
         <v/>
       </c>
       <c r="M316" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="317" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="317" spans="1:13">
       <c r="A317" s="2" t="str">
         <f>IF(C317="","",VLOOKUP(C317,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19135,11 +20666,11 @@
         <v/>
       </c>
       <c r="M317" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="318" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="318" spans="1:13">
       <c r="A318" s="2" t="str">
         <f>IF(C318="","",VLOOKUP(C318,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19161,11 +20692,11 @@
         <v/>
       </c>
       <c r="M318" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="319" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="319" spans="1:13">
       <c r="A319" s="2" t="str">
         <f>IF(C319="","",VLOOKUP(C319,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19187,11 +20718,11 @@
         <v/>
       </c>
       <c r="M319" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="320" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="320" spans="1:13">
       <c r="A320" s="2" t="str">
         <f>IF(C320="","",VLOOKUP(C320,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19213,11 +20744,11 @@
         <v/>
       </c>
       <c r="M320" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="321" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="321" spans="1:13">
       <c r="A321" s="2" t="str">
         <f>IF(C321="","",VLOOKUP(C321,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19239,11 +20770,11 @@
         <v/>
       </c>
       <c r="M321" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="322" spans="1:13" hidden="1">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="322" spans="1:13">
       <c r="A322" s="2" t="str">
         <f>IF(C322="","",VLOOKUP(C322,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19265,11 +20796,11 @@
         <v/>
       </c>
       <c r="M322" s="3" t="str">
-        <f t="shared" ref="M322:M385" si="5">_xlfn.TEXTJOIN(";",TRUE,J322:L322)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="323" spans="1:13" hidden="1">
+        <f t="shared" ref="M322:M373" si="6">_xlfn.TEXTJOIN(";",TRUE,J322:L322)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="323" spans="1:13">
       <c r="A323" s="2" t="str">
         <f>IF(C323="","",VLOOKUP(C323,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19291,11 +20822,11 @@
         <v/>
       </c>
       <c r="M323" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="324" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="324" spans="1:13">
       <c r="A324" s="2" t="str">
         <f>IF(C324="","",VLOOKUP(C324,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19317,11 +20848,11 @@
         <v/>
       </c>
       <c r="M324" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="325" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="325" spans="1:13">
       <c r="A325" s="2" t="str">
         <f>IF(C325="","",VLOOKUP(C325,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19343,11 +20874,11 @@
         <v/>
       </c>
       <c r="M325" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="326" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="326" spans="1:13">
       <c r="A326" s="2" t="str">
         <f>IF(C326="","",VLOOKUP(C326,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19369,11 +20900,11 @@
         <v/>
       </c>
       <c r="M326" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="327" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="327" spans="1:13">
       <c r="A327" s="2" t="str">
         <f>IF(C327="","",VLOOKUP(C327,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19395,11 +20926,11 @@
         <v/>
       </c>
       <c r="M327" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="328" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="328" spans="1:13">
       <c r="A328" s="2" t="str">
         <f>IF(C328="","",VLOOKUP(C328,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19421,11 +20952,11 @@
         <v/>
       </c>
       <c r="M328" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="329" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="329" spans="1:13">
       <c r="A329" s="2" t="str">
         <f>IF(C329="","",VLOOKUP(C329,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19447,11 +20978,11 @@
         <v/>
       </c>
       <c r="M329" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="330" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="330" spans="1:13">
       <c r="A330" s="2" t="str">
         <f>IF(C330="","",VLOOKUP(C330,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19473,11 +21004,11 @@
         <v/>
       </c>
       <c r="M330" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="331" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="331" spans="1:13">
       <c r="A331" s="2" t="str">
         <f>IF(C331="","",VLOOKUP(C331,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19499,11 +21030,11 @@
         <v/>
       </c>
       <c r="M331" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="332" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="332" spans="1:13">
       <c r="A332" s="2" t="str">
         <f>IF(C332="","",VLOOKUP(C332,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19525,11 +21056,11 @@
         <v/>
       </c>
       <c r="M332" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="333" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="333" spans="1:13">
       <c r="A333" s="2" t="str">
         <f>IF(C333="","",VLOOKUP(C333,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19551,11 +21082,11 @@
         <v/>
       </c>
       <c r="M333" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="334" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="334" spans="1:13">
       <c r="A334" s="2" t="str">
         <f>IF(C334="","",VLOOKUP(C334,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19577,11 +21108,11 @@
         <v/>
       </c>
       <c r="M334" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="335" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="335" spans="1:13">
       <c r="A335" s="2" t="str">
         <f>IF(C335="","",VLOOKUP(C335,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19603,11 +21134,11 @@
         <v/>
       </c>
       <c r="M335" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="336" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="336" spans="1:13">
       <c r="A336" s="2" t="str">
         <f>IF(C336="","",VLOOKUP(C336,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19629,11 +21160,11 @@
         <v/>
       </c>
       <c r="M336" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="337" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="337" spans="1:13">
       <c r="A337" s="2" t="str">
         <f>IF(C337="","",VLOOKUP(C337,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19655,11 +21186,11 @@
         <v/>
       </c>
       <c r="M337" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="338" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="338" spans="1:13">
       <c r="A338" s="2" t="str">
         <f>IF(C338="","",VLOOKUP(C338,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19681,11 +21212,11 @@
         <v/>
       </c>
       <c r="M338" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="339" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="339" spans="1:13">
       <c r="A339" s="2" t="str">
         <f>IF(C339="","",VLOOKUP(C339,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19707,11 +21238,11 @@
         <v/>
       </c>
       <c r="M339" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="340" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="340" spans="1:13">
       <c r="A340" s="2" t="str">
         <f>IF(C340="","",VLOOKUP(C340,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19733,11 +21264,11 @@
         <v/>
       </c>
       <c r="M340" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="341" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="341" spans="1:13">
       <c r="A341" s="2" t="str">
         <f>IF(C341="","",VLOOKUP(C341,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19759,11 +21290,11 @@
         <v/>
       </c>
       <c r="M341" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="342" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="342" spans="1:13">
       <c r="A342" s="2" t="str">
         <f>IF(C342="","",VLOOKUP(C342,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19785,11 +21316,11 @@
         <v/>
       </c>
       <c r="M342" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="343" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="343" spans="1:13">
       <c r="A343" s="2" t="str">
         <f>IF(C343="","",VLOOKUP(C343,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19811,11 +21342,11 @@
         <v/>
       </c>
       <c r="M343" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="344" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="344" spans="1:13">
       <c r="A344" s="2" t="str">
         <f>IF(C344="","",VLOOKUP(C344,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19837,11 +21368,11 @@
         <v/>
       </c>
       <c r="M344" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="345" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="345" spans="1:13">
       <c r="A345" s="2" t="str">
         <f>IF(C345="","",VLOOKUP(C345,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19863,11 +21394,11 @@
         <v/>
       </c>
       <c r="M345" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="346" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="346" spans="1:13">
       <c r="A346" s="2" t="str">
         <f>IF(C346="","",VLOOKUP(C346,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19889,11 +21420,11 @@
         <v/>
       </c>
       <c r="M346" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="347" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="347" spans="1:13">
       <c r="A347" s="2" t="str">
         <f>IF(C347="","",VLOOKUP(C347,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19915,11 +21446,11 @@
         <v/>
       </c>
       <c r="M347" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="348" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="348" spans="1:13">
       <c r="A348" s="2" t="str">
         <f>IF(C348="","",VLOOKUP(C348,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19941,11 +21472,11 @@
         <v/>
       </c>
       <c r="M348" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="349" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="349" spans="1:13">
       <c r="A349" s="2" t="str">
         <f>IF(C349="","",VLOOKUP(C349,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19967,11 +21498,11 @@
         <v/>
       </c>
       <c r="M349" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="350" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="350" spans="1:13">
       <c r="A350" s="2" t="str">
         <f>IF(C350="","",VLOOKUP(C350,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -19993,11 +21524,11 @@
         <v/>
       </c>
       <c r="M350" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="351" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="351" spans="1:13">
       <c r="A351" s="2" t="str">
         <f>IF(C351="","",VLOOKUP(C351,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20019,11 +21550,11 @@
         <v/>
       </c>
       <c r="M351" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="352" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="352" spans="1:13">
       <c r="A352" s="2" t="str">
         <f>IF(C352="","",VLOOKUP(C352,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20045,11 +21576,11 @@
         <v/>
       </c>
       <c r="M352" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="353" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="353" spans="1:13">
       <c r="A353" s="2" t="str">
         <f>IF(C353="","",VLOOKUP(C353,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20071,11 +21602,11 @@
         <v/>
       </c>
       <c r="M353" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="354" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="354" spans="1:13">
       <c r="A354" s="2" t="str">
         <f>IF(C354="","",VLOOKUP(C354,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20097,11 +21628,11 @@
         <v/>
       </c>
       <c r="M354" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="355" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="355" spans="1:13">
       <c r="A355" s="2" t="str">
         <f>IF(C355="","",VLOOKUP(C355,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20123,11 +21654,11 @@
         <v/>
       </c>
       <c r="M355" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="356" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="356" spans="1:13">
       <c r="A356" s="2" t="str">
         <f>IF(C356="","",VLOOKUP(C356,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20149,11 +21680,11 @@
         <v/>
       </c>
       <c r="M356" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="357" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="357" spans="1:13">
       <c r="A357" s="2" t="str">
         <f>IF(C357="","",VLOOKUP(C357,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20175,11 +21706,11 @@
         <v/>
       </c>
       <c r="M357" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="358" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="358" spans="1:13">
       <c r="A358" s="2" t="str">
         <f>IF(C358="","",VLOOKUP(C358,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20201,11 +21732,11 @@
         <v/>
       </c>
       <c r="M358" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="359" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="359" spans="1:13">
       <c r="A359" s="2" t="str">
         <f>IF(C359="","",VLOOKUP(C359,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20227,11 +21758,11 @@
         <v/>
       </c>
       <c r="M359" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="360" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="360" spans="1:13">
       <c r="A360" s="2" t="str">
         <f>IF(C360="","",VLOOKUP(C360,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20253,11 +21784,11 @@
         <v/>
       </c>
       <c r="M360" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="361" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="361" spans="1:13">
       <c r="A361" s="2" t="str">
         <f>IF(C361="","",VLOOKUP(C361,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20279,11 +21810,11 @@
         <v/>
       </c>
       <c r="M361" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="362" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="362" spans="1:13">
       <c r="A362" s="2" t="str">
         <f>IF(C362="","",VLOOKUP(C362,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20305,11 +21836,11 @@
         <v/>
       </c>
       <c r="M362" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="363" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="363" spans="1:13">
       <c r="A363" s="2" t="str">
         <f>IF(C363="","",VLOOKUP(C363,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20331,11 +21862,11 @@
         <v/>
       </c>
       <c r="M363" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="364" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="364" spans="1:13">
       <c r="A364" s="2" t="str">
         <f>IF(C364="","",VLOOKUP(C364,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20357,11 +21888,11 @@
         <v/>
       </c>
       <c r="M364" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="365" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="365" spans="1:13">
       <c r="A365" s="2" t="str">
         <f>IF(C365="","",VLOOKUP(C365,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20383,11 +21914,11 @@
         <v/>
       </c>
       <c r="M365" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="366" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="366" spans="1:13">
       <c r="A366" s="2" t="str">
         <f>IF(C366="","",VLOOKUP(C366,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20409,11 +21940,11 @@
         <v/>
       </c>
       <c r="M366" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="367" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="367" spans="1:13">
       <c r="A367" s="2" t="str">
         <f>IF(C367="","",VLOOKUP(C367,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20435,11 +21966,11 @@
         <v/>
       </c>
       <c r="M367" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="368" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="368" spans="1:13">
       <c r="A368" s="2" t="str">
         <f>IF(C368="","",VLOOKUP(C368,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20461,11 +21992,11 @@
         <v/>
       </c>
       <c r="M368" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="369" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="369" spans="1:13">
       <c r="A369" s="2" t="str">
         <f>IF(C369="","",VLOOKUP(C369,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20487,11 +22018,11 @@
         <v/>
       </c>
       <c r="M369" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="370" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="370" spans="1:13">
       <c r="A370" s="2" t="str">
         <f>IF(C370="","",VLOOKUP(C370,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20513,11 +22044,11 @@
         <v/>
       </c>
       <c r="M370" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="371" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="371" spans="1:13">
       <c r="A371" s="2" t="str">
         <f>IF(C371="","",VLOOKUP(C371,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20539,11 +22070,11 @@
         <v/>
       </c>
       <c r="M371" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="372" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="372" spans="1:13">
       <c r="A372" s="2" t="str">
         <f>IF(C372="","",VLOOKUP(C372,[1]ISO辞書!A:C,2,FALSE))</f>
         <v/>
@@ -20565,11 +22096,11 @@
         <v/>
       </c>
       <c r="M372" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="373" spans="1:13" hidden="1">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="373" spans="1:13">
       <c r="J373" s="2" t="str">
         <f>IF(G373="","",VLOOKUP(G373,[1]ISO辞書!A:B,2,FALSE))</f>
         <v/>
@@ -20583,15 +22114,12 @@
         <v/>
       </c>
       <c r="M373" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:S373" xr:uid="{11153815-6F7F-462F-8165-5CE05A98A928}">
-    <filterColumn colId="3">
-      <colorFilter dxfId="0"/>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S373">
       <sortCondition ref="P1:P77"/>
     </sortState>
@@ -20603,6 +22131,7 @@
     <hyperlink ref="R46" r:id="rId3" xr:uid="{CAB2C613-E685-436C-AA62-7678804484F9}"/>
     <hyperlink ref="R47" r:id="rId4" xr:uid="{B735F61B-7109-4112-8AD5-8A0DE0EE4130}"/>
     <hyperlink ref="R58" r:id="rId5" xr:uid="{26955398-EA42-49E0-8883-3400EA7BDFE3}"/>
+    <hyperlink ref="R120" r:id="rId6" xr:uid="{7A7EACA8-130A-4B97-AD1E-F8E11AE4B691}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/データ管理用.xlsx
+++ b/public/data/データ管理用.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\world_map_project\world-map-news-app\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C960F63D-BDA5-47CF-AF80-FD9DF769F7B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3234AB1F-7AD8-4062-8B7B-D109A71E0BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29430" yWindow="1785" windowWidth="20595" windowHeight="9540" xr2:uid="{17EB953A-2661-4049-9616-0D3098A3DA36}"/>
+    <workbookView xWindow="35625" yWindow="1080" windowWidth="20595" windowHeight="12855" xr2:uid="{17EB953A-2661-4049-9616-0D3098A3DA36}"/>
   </bookViews>
   <sheets>
     <sheet name="events-入力用" sheetId="1" r:id="rId1"/>
@@ -9061,7 +9061,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -9250,6 +9250,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -9501,7 +9507,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -9540,6 +9546,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -12690,7 +12705,11 @@
   <cols>
     <col min="1" max="2" width="8.796875" style="2" customWidth="1"/>
     <col min="4" max="5" width="34.19921875" customWidth="1"/>
-    <col min="13" max="15" width="8.796875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="8.796875" style="13"/>
+    <col min="8" max="8" width="8.796875" customWidth="1"/>
+    <col min="9" max="9" width="8.796875" style="13"/>
+    <col min="10" max="12" width="0" hidden="1" customWidth="1"/>
+    <col min="13" max="15" width="8.796875" style="2" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="8.796875" style="2"/>
     <col min="19" max="19" width="10.3984375" bestFit="1" customWidth="1"/>
   </cols>
@@ -12714,13 +12733,13 @@
       <c r="F1" t="s">
         <v>866</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="13" t="s">
         <v>867</v>
       </c>
       <c r="H1" t="s">
         <v>868</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="13" t="s">
         <v>5</v>
       </c>
       <c r="J1" t="s">
@@ -12794,7 +12813,7 @@
         <v/>
       </c>
       <c r="P2" s="3" t="str">
-        <f t="shared" ref="P2:P65" si="0">_xlfn.TEXTJOIN(";",TRUE,M2:O2)</f>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M2:O2)</f>
         <v/>
       </c>
       <c r="Q2" t="s">
@@ -12850,7 +12869,7 @@
         <v/>
       </c>
       <c r="P3" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M3:O3)</f>
         <v>SDN</v>
       </c>
       <c r="Q3" t="s">
@@ -12906,7 +12925,7 @@
         <v/>
       </c>
       <c r="P4" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M4:O4)</f>
         <v>USA</v>
       </c>
       <c r="Q4" t="s">
@@ -12959,7 +12978,7 @@
         <v/>
       </c>
       <c r="P5" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M5:O5)</f>
         <v/>
       </c>
       <c r="Q5" t="s">
@@ -13015,7 +13034,7 @@
         <v/>
       </c>
       <c r="P6" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M6:O6)</f>
         <v>LBN</v>
       </c>
       <c r="Q6" s="6" t="s">
@@ -13068,7 +13087,7 @@
         <v/>
       </c>
       <c r="P7" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M7:O7)</f>
         <v/>
       </c>
       <c r="Q7" t="s">
@@ -13124,7 +13143,7 @@
         <v/>
       </c>
       <c r="P8" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M8:O8)</f>
         <v>CHN</v>
       </c>
       <c r="Q8" t="s">
@@ -13180,7 +13199,7 @@
         <v/>
       </c>
       <c r="P9" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M9:O9)</f>
         <v>LBN</v>
       </c>
       <c r="Q9" t="s">
@@ -13236,7 +13255,7 @@
         <v/>
       </c>
       <c r="P10" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M10:O10)</f>
         <v>AUS</v>
       </c>
       <c r="Q10" t="s">
@@ -13292,7 +13311,7 @@
         <v/>
       </c>
       <c r="P11" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M11:O11)</f>
         <v>CUB</v>
       </c>
       <c r="R11" t="s">
@@ -13345,7 +13364,7 @@
         <v/>
       </c>
       <c r="P12" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M12:O12)</f>
         <v>GBR</v>
       </c>
       <c r="Q12" t="s">
@@ -13398,7 +13417,7 @@
         <v/>
       </c>
       <c r="P13" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M13:O13)</f>
         <v/>
       </c>
       <c r="Q13" t="s">
@@ -13454,7 +13473,7 @@
         <v/>
       </c>
       <c r="P14" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M14:O14)</f>
         <v>TUR</v>
       </c>
       <c r="Q14" t="s">
@@ -13510,7 +13529,7 @@
         <v/>
       </c>
       <c r="P15" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M15:O15)</f>
         <v>CHN</v>
       </c>
       <c r="Q15" t="s">
@@ -13566,7 +13585,7 @@
         <v/>
       </c>
       <c r="P16" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M16:O16)</f>
         <v>VEN</v>
       </c>
       <c r="Q16" t="s">
@@ -13622,7 +13641,7 @@
         <v/>
       </c>
       <c r="P17" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M17:O17)</f>
         <v>AFG</v>
       </c>
       <c r="Q17" t="s">
@@ -13678,7 +13697,7 @@
         <v/>
       </c>
       <c r="P18" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M18:O18)</f>
         <v>IRN</v>
       </c>
       <c r="Q18" t="s">
@@ -13737,7 +13756,7 @@
         <v/>
       </c>
       <c r="P19" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M19:O19)</f>
         <v>USA;PAK</v>
       </c>
       <c r="Q19" t="s">
@@ -13793,7 +13812,7 @@
         <v/>
       </c>
       <c r="P20" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M20:O20)</f>
         <v>RUS</v>
       </c>
       <c r="Q20" t="s">
@@ -13849,7 +13868,7 @@
         <v/>
       </c>
       <c r="P21" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M21:O21)</f>
         <v>CUB</v>
       </c>
       <c r="Q21" t="s">
@@ -13911,7 +13930,7 @@
         <v>PRY</v>
       </c>
       <c r="P22" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M22:O22)</f>
         <v>BRA;ARG;PRY</v>
       </c>
       <c r="Q22" t="s">
@@ -13967,7 +13986,7 @@
         <v/>
       </c>
       <c r="P23" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M23:O23)</f>
         <v>CPTPP</v>
       </c>
       <c r="Q23" t="s">
@@ -14020,7 +14039,7 @@
         <v/>
       </c>
       <c r="P24" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M24:O24)</f>
         <v/>
       </c>
       <c r="Q24" t="s">
@@ -14076,7 +14095,7 @@
         <v/>
       </c>
       <c r="P25" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M25:O25)</f>
         <v>BLR</v>
       </c>
       <c r="Q25" t="s">
@@ -14132,7 +14151,7 @@
         <v/>
       </c>
       <c r="P26" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M26:O26)</f>
         <v>SAU</v>
       </c>
       <c r="Q26" t="s">
@@ -14188,7 +14207,7 @@
         <v/>
       </c>
       <c r="P27" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M27:O27)</f>
         <v>CHN</v>
       </c>
       <c r="Q27" t="s">
@@ -14244,7 +14263,7 @@
         <v/>
       </c>
       <c r="P28" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M28:O28)</f>
         <v>PHL</v>
       </c>
       <c r="Q28" t="s">
@@ -14297,7 +14316,7 @@
         <v/>
       </c>
       <c r="P29" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M29:O29)</f>
         <v/>
       </c>
       <c r="Q29" t="s">
@@ -14356,7 +14375,7 @@
         <v/>
       </c>
       <c r="P30" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M30:O30)</f>
         <v>ARE;QAT</v>
       </c>
       <c r="Q30" t="s">
@@ -14409,7 +14428,7 @@
         <v/>
       </c>
       <c r="P31" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M31:O31)</f>
         <v/>
       </c>
       <c r="R31" t="s">
@@ -14468,7 +14487,7 @@
         <v>ISR</v>
       </c>
       <c r="P32" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M32:O32)</f>
         <v>IRN;USA;ISR</v>
       </c>
       <c r="Q32" t="s">
@@ -14524,7 +14543,7 @@
         <v/>
       </c>
       <c r="P33" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M33:O33)</f>
         <v>JOR</v>
       </c>
       <c r="Q33" t="s">
@@ -14577,7 +14596,7 @@
         <v/>
       </c>
       <c r="P34" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M34:O34)</f>
         <v/>
       </c>
       <c r="Q34" t="s">
@@ -14636,7 +14655,7 @@
         <v/>
       </c>
       <c r="P35" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M35:O35)</f>
         <v>RUS;USA</v>
       </c>
       <c r="Q35" t="s">
@@ -14692,7 +14711,7 @@
         <v/>
       </c>
       <c r="P36" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M36:O36)</f>
         <v>ISR</v>
       </c>
       <c r="Q36" t="s">
@@ -14748,7 +14767,7 @@
         <v/>
       </c>
       <c r="P37" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M37:O37)</f>
         <v>GBR</v>
       </c>
       <c r="Q37" t="s">
@@ -14804,7 +14823,7 @@
         <v/>
       </c>
       <c r="P38" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M38:O38)</f>
         <v>PAK</v>
       </c>
       <c r="R38" t="s">
@@ -14863,7 +14882,7 @@
         <v>PSE</v>
       </c>
       <c r="P39" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M39:O39)</f>
         <v>USA;ISR;PSE</v>
       </c>
       <c r="R39" t="s">
@@ -14916,7 +14935,7 @@
         <v/>
       </c>
       <c r="P40" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M40:O40)</f>
         <v>AFG</v>
       </c>
       <c r="Q40" t="s">
@@ -14972,7 +14991,7 @@
         <v/>
       </c>
       <c r="P41" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M41:O41)</f>
         <v>VEN</v>
       </c>
       <c r="Q41" t="s">
@@ -15028,7 +15047,7 @@
         <v/>
       </c>
       <c r="P42" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M42:O42)</f>
         <v>CYP</v>
       </c>
       <c r="Q42" t="s">
@@ -15081,7 +15100,7 @@
         <v/>
       </c>
       <c r="P43" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M43:O43)</f>
         <v/>
       </c>
       <c r="Q43" t="s">
@@ -15137,7 +15156,7 @@
         <v/>
       </c>
       <c r="P44" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M44:O44)</f>
         <v>ISR</v>
       </c>
       <c r="Q44" t="s">
@@ -15190,7 +15209,7 @@
         <v/>
       </c>
       <c r="P45" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M45:O45)</f>
         <v/>
       </c>
       <c r="R45" t="s">
@@ -15243,7 +15262,7 @@
         <v/>
       </c>
       <c r="P46" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M46:O46)</f>
         <v>IRN</v>
       </c>
       <c r="Q46" t="s">
@@ -15299,7 +15318,7 @@
         <v/>
       </c>
       <c r="P47" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M47:O47)</f>
         <v>SYR</v>
       </c>
       <c r="Q47" t="s">
@@ -15355,7 +15374,7 @@
         <v/>
       </c>
       <c r="P48" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M48:O48)</f>
         <v>LBN</v>
       </c>
       <c r="Q48" t="s">
@@ -15411,7 +15430,7 @@
         <v/>
       </c>
       <c r="P49" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M49:O49)</f>
         <v>USA</v>
       </c>
       <c r="Q49" t="s">
@@ -15470,7 +15489,7 @@
         <v/>
       </c>
       <c r="P50" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M50:O50)</f>
         <v>ISR;USA</v>
       </c>
       <c r="Q50" t="s">
@@ -15523,7 +15542,7 @@
         <v/>
       </c>
       <c r="P51" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M51:O51)</f>
         <v/>
       </c>
       <c r="Q51" t="s">
@@ -15576,7 +15595,7 @@
         <v/>
       </c>
       <c r="P52" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M52:O52)</f>
         <v/>
       </c>
       <c r="Q52" t="s">
@@ -15629,7 +15648,7 @@
         <v/>
       </c>
       <c r="P53" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M53:O53)</f>
         <v/>
       </c>
       <c r="Q53" t="s">
@@ -15682,7 +15701,7 @@
         <v/>
       </c>
       <c r="P54" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M54:O54)</f>
         <v/>
       </c>
       <c r="Q54" t="s">
@@ -15735,7 +15754,7 @@
         <v/>
       </c>
       <c r="P55" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M55:O55)</f>
         <v/>
       </c>
       <c r="Q55" t="s">
@@ -15797,7 +15816,7 @@
         <v>ISR</v>
       </c>
       <c r="P56" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M56:O56)</f>
         <v>IRN;USA;ISR</v>
       </c>
       <c r="Q56" t="s">
@@ -15850,7 +15869,7 @@
         <v/>
       </c>
       <c r="P57" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M57:O57)</f>
         <v/>
       </c>
       <c r="Q57" t="s">
@@ -15903,7 +15922,7 @@
         <v/>
       </c>
       <c r="P58" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M58:O58)</f>
         <v>ISR</v>
       </c>
       <c r="Q58" t="s">
@@ -15959,7 +15978,7 @@
         <v/>
       </c>
       <c r="P59" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M59:O59)</f>
         <v>IRN</v>
       </c>
       <c r="Q59" t="s">
@@ -16015,7 +16034,7 @@
         <v/>
       </c>
       <c r="P60" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M60:O60)</f>
         <v>CUB</v>
       </c>
       <c r="Q60" t="s">
@@ -16071,7 +16090,7 @@
         <v/>
       </c>
       <c r="P61" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M61:O61)</f>
         <v>HTI</v>
       </c>
       <c r="R61" t="s">
@@ -16124,7 +16143,7 @@
         <v/>
       </c>
       <c r="P62" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M62:O62)</f>
         <v>UKR</v>
       </c>
       <c r="R62" t="s">
@@ -16183,7 +16202,7 @@
         <v>ARE</v>
       </c>
       <c r="P63" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M63:O63)</f>
         <v>DEU;FRA;ARE</v>
       </c>
       <c r="Q63" t="s">
@@ -16239,7 +16258,7 @@
         <v/>
       </c>
       <c r="P64" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M64:O64)</f>
         <v>MLI</v>
       </c>
       <c r="Q64" t="s">
@@ -16292,7 +16311,7 @@
         <v/>
       </c>
       <c r="P65" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M65:O65)</f>
         <v/>
       </c>
       <c r="Q65" t="s">
@@ -16348,7 +16367,7 @@
         <v/>
       </c>
       <c r="P66" s="3" t="str">
-        <f t="shared" ref="P66:P129" si="1">_xlfn.TEXTJOIN(";",TRUE,M66:O66)</f>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M66:O66)</f>
         <v>VEN</v>
       </c>
       <c r="Q66" t="s">
@@ -16404,7 +16423,7 @@
         <v/>
       </c>
       <c r="P67" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M67:O67)</f>
         <v>COK</v>
       </c>
       <c r="Q67" t="s">
@@ -16463,7 +16482,7 @@
         <v/>
       </c>
       <c r="P68" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M68:O68)</f>
         <v>GBR;IRN</v>
       </c>
       <c r="Q68" t="s">
@@ -16519,7 +16538,7 @@
         <v/>
       </c>
       <c r="P69" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M69:O69)</f>
         <v>MDG</v>
       </c>
       <c r="Q69" t="s">
@@ -16581,7 +16600,7 @@
         <v>ARE</v>
       </c>
       <c r="P70" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M70:O70)</f>
         <v>SAU;QAT;ARE</v>
       </c>
       <c r="Q70" t="s">
@@ -16637,7 +16656,7 @@
         <v/>
       </c>
       <c r="P71" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M71:O71)</f>
         <v>FRA</v>
       </c>
       <c r="R71" t="s">
@@ -16690,7 +16709,7 @@
         <v/>
       </c>
       <c r="P72" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M72:O72)</f>
         <v>TUR</v>
       </c>
       <c r="Q72" t="s">
@@ -16752,7 +16771,7 @@
         <v>IRN</v>
       </c>
       <c r="P73" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M73:O73)</f>
         <v>FRA;OMN;IRN</v>
       </c>
       <c r="Q73" t="s">
@@ -16808,7 +16827,7 @@
         <v/>
       </c>
       <c r="P74" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M74:O74)</f>
         <v>CHN</v>
       </c>
       <c r="Q74" t="s">
@@ -16861,7 +16880,7 @@
         <v/>
       </c>
       <c r="P75" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M75:O75)</f>
         <v/>
       </c>
       <c r="Q75" t="s">
@@ -16917,7 +16936,7 @@
         <v/>
       </c>
       <c r="P76" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M76:O76)</f>
         <v>IRN;USA</v>
       </c>
       <c r="Q76" t="s">
@@ -16970,7 +16989,7 @@
         <v/>
       </c>
       <c r="P77" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M77:O77)</f>
         <v/>
       </c>
       <c r="Q77" t="s">
@@ -17023,7 +17042,7 @@
         <v/>
       </c>
       <c r="P78" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M78:O78)</f>
         <v/>
       </c>
       <c r="R78" t="s">
@@ -17073,7 +17092,7 @@
         <v/>
       </c>
       <c r="P79" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M79:O79)</f>
         <v/>
       </c>
       <c r="R79" t="s">
@@ -17126,7 +17145,7 @@
         <v/>
       </c>
       <c r="P80" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M80:O80)</f>
         <v>TUR</v>
       </c>
       <c r="Q80" t="s">
@@ -17179,7 +17198,7 @@
         <v/>
       </c>
       <c r="P81" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M81:O81)</f>
         <v/>
       </c>
       <c r="Q81" t="s">
@@ -17235,7 +17254,7 @@
         <v/>
       </c>
       <c r="P82" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M82:O82)</f>
         <v>IRN</v>
       </c>
       <c r="Q82" t="s">
@@ -17291,7 +17310,7 @@
         <v/>
       </c>
       <c r="P83" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M83:O83)</f>
         <v>USA</v>
       </c>
       <c r="R83" t="s">
@@ -17344,7 +17363,7 @@
         <v/>
       </c>
       <c r="P84" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M84:O84)</f>
         <v>ARE</v>
       </c>
       <c r="Q84" t="s">
@@ -17400,7 +17419,7 @@
         <v/>
       </c>
       <c r="P85" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M85:O85)</f>
         <v>IRN</v>
       </c>
       <c r="Q85" t="s">
@@ -17456,7 +17475,7 @@
         <v/>
       </c>
       <c r="P86" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M86:O86)</f>
         <v>RUS</v>
       </c>
       <c r="R86" t="s">
@@ -17509,7 +17528,7 @@
         <v/>
       </c>
       <c r="P87" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M87:O87)</f>
         <v>SYR</v>
       </c>
       <c r="Q87" t="s">
@@ -17565,7 +17584,7 @@
         <v/>
       </c>
       <c r="P88" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M88:O88)</f>
         <v>IRN</v>
       </c>
       <c r="Q88" t="s">
@@ -17621,7 +17640,7 @@
         <v/>
       </c>
       <c r="P89" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M89:O89)</f>
         <v>USA</v>
       </c>
       <c r="Q89" t="s">
@@ -17674,7 +17693,7 @@
         <v/>
       </c>
       <c r="P90" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M90:O90)</f>
         <v/>
       </c>
       <c r="Q90" t="s">
@@ -17736,7 +17755,7 @@
         <v>USA</v>
       </c>
       <c r="P91" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M91:O91)</f>
         <v>EGY;IRN;USA</v>
       </c>
       <c r="Q91" t="s">
@@ -17789,7 +17808,7 @@
         <v/>
       </c>
       <c r="P92" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M92:O92)</f>
         <v/>
       </c>
       <c r="Q92" t="s">
@@ -17842,7 +17861,7 @@
         <v/>
       </c>
       <c r="P93" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M93:O93)</f>
         <v/>
       </c>
       <c r="Q93" t="s">
@@ -17898,7 +17917,7 @@
         <v/>
       </c>
       <c r="P94" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M94:O94)</f>
         <v>SAU</v>
       </c>
       <c r="Q94" t="s">
@@ -17954,7 +17973,7 @@
         <v/>
       </c>
       <c r="P95" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M95:O95)</f>
         <v>IRN</v>
       </c>
       <c r="Q95" t="s">
@@ -18013,7 +18032,7 @@
         <v/>
       </c>
       <c r="P96" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M96:O96)</f>
         <v>IRN;PAK</v>
       </c>
       <c r="Q96" t="s">
@@ -18069,7 +18088,7 @@
         <v/>
       </c>
       <c r="P97" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M97:O97)</f>
         <v>IRN</v>
       </c>
       <c r="Q97" t="s">
@@ -18122,7 +18141,7 @@
         <v/>
       </c>
       <c r="P98" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M98:O98)</f>
         <v/>
       </c>
       <c r="Q98" t="s">
@@ -18184,7 +18203,7 @@
         <v>USA</v>
       </c>
       <c r="P99" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M99:O99)</f>
         <v>CHN;IRN;USA</v>
       </c>
       <c r="Q99" t="s">
@@ -18237,7 +18256,7 @@
         <v/>
       </c>
       <c r="P100" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M100:O100)</f>
         <v/>
       </c>
       <c r="Q100" t="s">
@@ -18290,7 +18309,7 @@
         <v/>
       </c>
       <c r="P101" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M101:O101)</f>
         <v/>
       </c>
       <c r="R101" t="s">
@@ -18346,7 +18365,7 @@
         <v/>
       </c>
       <c r="P102" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M102:O102)</f>
         <v>KOR;JPN</v>
       </c>
       <c r="Q102" t="s">
@@ -18405,7 +18424,7 @@
         <v/>
       </c>
       <c r="P103" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M103:O103)</f>
         <v>PAK;CHN</v>
       </c>
       <c r="Q103" t="s">
@@ -18461,7 +18480,7 @@
         <v/>
       </c>
       <c r="P104" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M104:O104)</f>
         <v>USA</v>
       </c>
       <c r="Q104" t="s">
@@ -18517,7 +18536,7 @@
         <v/>
       </c>
       <c r="P105" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M105:O105)</f>
         <v>RUS</v>
       </c>
       <c r="Q105" t="s">
@@ -18579,7 +18598,7 @@
         <v>LBN</v>
       </c>
       <c r="P106" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M106:O106)</f>
         <v>USA;ISR;LBN</v>
       </c>
       <c r="Q106" t="s">
@@ -18635,7 +18654,7 @@
         <v/>
       </c>
       <c r="P107" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M107:O107)</f>
         <v>LBN</v>
       </c>
       <c r="Q107" t="s">
@@ -18691,7 +18710,7 @@
         <v/>
       </c>
       <c r="P108" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M108:O108)</f>
         <v>COL</v>
       </c>
       <c r="Q108" t="s">
@@ -18744,7 +18763,7 @@
         <v/>
       </c>
       <c r="P109" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M109:O109)</f>
         <v/>
       </c>
       <c r="Q109" t="s">
@@ -18797,7 +18816,7 @@
         <v/>
       </c>
       <c r="P110" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M110:O110)</f>
         <v>GRD</v>
       </c>
       <c r="R110" t="s">
@@ -18847,7 +18866,7 @@
         <v/>
       </c>
       <c r="P111" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M111:O111)</f>
         <v/>
       </c>
       <c r="Q111" t="s">
@@ -18903,7 +18922,7 @@
         <v/>
       </c>
       <c r="P112" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M112:O112)</f>
         <v>PSE</v>
       </c>
       <c r="Q112" t="s">
@@ -18959,7 +18978,7 @@
         <v/>
       </c>
       <c r="P113" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M113:O113)</f>
         <v>USA</v>
       </c>
       <c r="Q113" t="s">
@@ -19012,7 +19031,7 @@
         <v/>
       </c>
       <c r="P114" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M114:O114)</f>
         <v/>
       </c>
       <c r="Q114" t="s">
@@ -19068,7 +19087,7 @@
         <v/>
       </c>
       <c r="P115" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M115:O115)</f>
         <v>PRK</v>
       </c>
       <c r="Q115" t="s">
@@ -19124,7 +19143,7 @@
         <v/>
       </c>
       <c r="P116" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M116:O116)</f>
         <v>SGP</v>
       </c>
       <c r="Q116" t="s">
@@ -19177,7 +19196,7 @@
         <v/>
       </c>
       <c r="P117" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M117:O117)</f>
         <v/>
       </c>
       <c r="Q117" t="s">
@@ -19230,7 +19249,7 @@
         <v/>
       </c>
       <c r="P118" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M118:O118)</f>
         <v/>
       </c>
       <c r="Q118" t="s">
@@ -19286,7 +19305,7 @@
         <v/>
       </c>
       <c r="P119" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M119:O119)</f>
         <v>SAU</v>
       </c>
       <c r="Q119" t="s">
@@ -19342,7 +19361,7 @@
         <v/>
       </c>
       <c r="P120" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M120:O120)</f>
         <v>RUS</v>
       </c>
       <c r="Q120" t="s">
@@ -19395,7 +19414,7 @@
         <v/>
       </c>
       <c r="P121" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M121:O121)</f>
         <v/>
       </c>
       <c r="Q121" t="s">
@@ -19448,7 +19467,7 @@
         <v/>
       </c>
       <c r="P122" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M122:O122)</f>
         <v/>
       </c>
       <c r="Q122" t="s">
@@ -19501,7 +19520,7 @@
         <v/>
       </c>
       <c r="P123" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M123:O123)</f>
         <v/>
       </c>
       <c r="Q123" t="s">
@@ -19554,7 +19573,7 @@
         <v/>
       </c>
       <c r="P124" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M124:O124)</f>
         <v/>
       </c>
       <c r="Q124" t="s">
@@ -19607,7 +19626,7 @@
         <v/>
       </c>
       <c r="P125" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M125:O125)</f>
         <v/>
       </c>
       <c r="Q125" t="s">
@@ -19663,7 +19682,7 @@
         <v/>
       </c>
       <c r="P126" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M126:O126)</f>
         <v>OMN</v>
       </c>
       <c r="Q126" t="s">
@@ -19719,7 +19738,7 @@
         <v/>
       </c>
       <c r="P127" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M127:O127)</f>
         <v>DEU</v>
       </c>
       <c r="Q127" t="s">
@@ -19772,7 +19791,7 @@
         <v/>
       </c>
       <c r="P128" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M128:O128)</f>
         <v/>
       </c>
       <c r="Q128" t="s">
@@ -19828,7 +19847,7 @@
         <v/>
       </c>
       <c r="P129" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M129:O129)</f>
         <v>MAR</v>
       </c>
       <c r="Q129" t="s">
@@ -19881,7 +19900,7 @@
         <v/>
       </c>
       <c r="P130" s="3" t="str">
-        <f t="shared" ref="P130:P193" si="2">_xlfn.TEXTJOIN(";",TRUE,M130:O130)</f>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M130:O130)</f>
         <v/>
       </c>
       <c r="Q130" t="s">
@@ -19937,7 +19956,7 @@
         <v/>
       </c>
       <c r="P131" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M131:O131)</f>
         <v>VEN</v>
       </c>
       <c r="Q131" t="s">
@@ -19999,7 +20018,7 @@
         <v>USA</v>
       </c>
       <c r="P132" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M132:O132)</f>
         <v>JPN;KOR;USA</v>
       </c>
       <c r="Q132" t="s">
@@ -20058,7 +20077,7 @@
         <v/>
       </c>
       <c r="P133" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M133:O133)</f>
         <v>IRN;USA</v>
       </c>
       <c r="Q133" t="s">
@@ -20117,7 +20136,7 @@
         <v/>
       </c>
       <c r="P134" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M134:O134)</f>
         <v>AUS;PHL</v>
       </c>
       <c r="Q134" t="s">
@@ -20173,7 +20192,7 @@
         <v/>
       </c>
       <c r="P135" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M135:O135)</f>
         <v>IRN</v>
       </c>
       <c r="Q135" t="s">
@@ -20229,7 +20248,7 @@
         <v/>
       </c>
       <c r="P136" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M136:O136)</f>
         <v>KOR</v>
       </c>
       <c r="Q136" t="s">
@@ -20282,7 +20301,7 @@
         <v/>
       </c>
       <c r="P137" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M137:O137)</f>
         <v/>
       </c>
       <c r="R137" t="s">
@@ -20341,7 +20360,7 @@
         <v>IRN</v>
       </c>
       <c r="P138" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M138:O138)</f>
         <v>USA;FRA;IRN</v>
       </c>
       <c r="Q138" t="s">
@@ -20394,7 +20413,7 @@
         <v/>
       </c>
       <c r="P139" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M139:O139)</f>
         <v/>
       </c>
       <c r="Q139" t="s">
@@ -20450,7 +20469,7 @@
         <v/>
       </c>
       <c r="P140" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M140:O140)</f>
         <v>CHN</v>
       </c>
       <c r="Q140" t="s">
@@ -20509,7 +20528,7 @@
         <v/>
       </c>
       <c r="P141" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M141:O141)</f>
         <v>GBR;MUS</v>
       </c>
       <c r="Q141" t="s">
@@ -20565,7 +20584,7 @@
         <v/>
       </c>
       <c r="P142" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M142:O142)</f>
         <v>USA</v>
       </c>
       <c r="Q142" t="s">
@@ -20621,7 +20640,7 @@
         <v/>
       </c>
       <c r="P143" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M143:O143)</f>
         <v>USA</v>
       </c>
       <c r="Q143" t="s">
@@ -20677,7 +20696,7 @@
         <v/>
       </c>
       <c r="P144" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M144:O144)</f>
         <v>ISR</v>
       </c>
       <c r="Q144" t="s">
@@ -20733,7 +20752,7 @@
         <v/>
       </c>
       <c r="P145" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M145:O145)</f>
         <v>UKR</v>
       </c>
       <c r="Q145" t="s">
@@ -20786,7 +20805,7 @@
         <v/>
       </c>
       <c r="P146" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M146:O146)</f>
         <v/>
       </c>
       <c r="Q146" t="s">
@@ -20839,7 +20858,7 @@
         <v/>
       </c>
       <c r="P147" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M147:O147)</f>
         <v/>
       </c>
       <c r="Q147" t="s">
@@ -20892,7 +20911,7 @@
         <v/>
       </c>
       <c r="P148" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M148:O148)</f>
         <v/>
       </c>
       <c r="Q148" t="s">
@@ -20945,7 +20964,7 @@
         <v/>
       </c>
       <c r="P149" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M149:O149)</f>
         <v/>
       </c>
       <c r="Q149" t="s">
@@ -21001,7 +21020,7 @@
         <v/>
       </c>
       <c r="P150" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M150:O150)</f>
         <v>ISR</v>
       </c>
       <c r="Q150" t="s">
@@ -21057,7 +21076,7 @@
         <v/>
       </c>
       <c r="P151" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M151:O151)</f>
         <v>AUS</v>
       </c>
       <c r="Q151" t="s">
@@ -21110,7 +21129,7 @@
         <v/>
       </c>
       <c r="P152" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M152:O152)</f>
         <v/>
       </c>
       <c r="R152" t="s">
@@ -21169,7 +21188,7 @@
         <v>LBN</v>
       </c>
       <c r="P153" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M153:O153)</f>
         <v>USA;ISR;LBN</v>
       </c>
       <c r="Q153" t="s">
@@ -21222,7 +21241,7 @@
         <v/>
       </c>
       <c r="P154" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M154:O154)</f>
         <v/>
       </c>
       <c r="Q154" t="s">
@@ -21284,7 +21303,7 @@
         <v>IRN</v>
       </c>
       <c r="P155" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M155:O155)</f>
         <v>USA;LBN;IRN</v>
       </c>
       <c r="Q155" t="s">
@@ -21340,7 +21359,7 @@
         <v/>
       </c>
       <c r="P156" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M156:O156)</f>
         <v>BRA</v>
       </c>
       <c r="Q156" t="s">
@@ -21393,7 +21412,7 @@
         <v/>
       </c>
       <c r="P157" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M157:O157)</f>
         <v/>
       </c>
       <c r="Q157" t="s">
@@ -21446,7 +21465,7 @@
         <v/>
       </c>
       <c r="P158" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M158:O158)</f>
         <v/>
       </c>
       <c r="Q158" t="s">
@@ -21499,7 +21518,7 @@
         <v/>
       </c>
       <c r="P159" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M159:O159)</f>
         <v/>
       </c>
       <c r="Q159" t="s">
@@ -21552,7 +21571,7 @@
         <v/>
       </c>
       <c r="P160" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M160:O160)</f>
         <v/>
       </c>
       <c r="Q160" t="s">
@@ -21611,7 +21630,7 @@
         <v/>
       </c>
       <c r="P161" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M161:O161)</f>
         <v>JPN;KOR</v>
       </c>
       <c r="Q161" t="s">
@@ -21667,7 +21686,7 @@
         <v/>
       </c>
       <c r="P162" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M162:O162)</f>
         <v>TKM</v>
       </c>
       <c r="Q162" t="s">
@@ -21723,7 +21742,7 @@
         <v/>
       </c>
       <c r="P163" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M163:O163)</f>
         <v>ESP</v>
       </c>
       <c r="Q163" t="s">
@@ -21785,7 +21804,7 @@
         <v>MEX</v>
       </c>
       <c r="P164" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M164:O164)</f>
         <v>CUB;ESP;MEX</v>
       </c>
       <c r="Q164" t="s">
@@ -21841,7 +21860,7 @@
         <v/>
       </c>
       <c r="P165" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M165:O165)</f>
         <v>AUS</v>
       </c>
       <c r="Q165" t="s">
@@ -21897,7 +21916,7 @@
         <v/>
       </c>
       <c r="P166" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M166:O166)</f>
         <v>NIC</v>
       </c>
       <c r="Q166" t="s">
@@ -21956,7 +21975,7 @@
         <v/>
       </c>
       <c r="P167" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M167:O167)</f>
         <v>JPN;KOR</v>
       </c>
       <c r="Q167" t="s">
@@ -22012,7 +22031,7 @@
         <v/>
       </c>
       <c r="P168" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M168:O168)</f>
         <v>IRN</v>
       </c>
       <c r="Q168" s="7" t="s">
@@ -22046,7 +22065,7 @@
       <c r="C169" t="s">
         <v>243</v>
       </c>
-      <c r="D169" t="s">
+      <c r="D169" s="14" t="s">
         <v>815</v>
       </c>
       <c r="E169" t="s">
@@ -22065,7 +22084,7 @@
         <v/>
       </c>
       <c r="P169" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M169:O169)</f>
         <v/>
       </c>
       <c r="Q169" t="s">
@@ -22121,7 +22140,7 @@
         <v/>
       </c>
       <c r="P170" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M170:O170)</f>
         <v>SYR</v>
       </c>
       <c r="Q170" t="s">
@@ -22177,7 +22196,7 @@
         <v/>
       </c>
       <c r="P171" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M171:O171)</f>
         <v>SYR</v>
       </c>
       <c r="Q171" t="s">
@@ -22233,7 +22252,7 @@
         <v/>
       </c>
       <c r="P172" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M172:O172)</f>
         <v>SAU</v>
       </c>
       <c r="Q172" t="s">
@@ -22267,7 +22286,7 @@
       <c r="C173" t="s">
         <v>825</v>
       </c>
-      <c r="D173" t="s">
+      <c r="D173" s="14" t="s">
         <v>826</v>
       </c>
       <c r="E173" t="s">
@@ -22289,7 +22308,7 @@
         <v/>
       </c>
       <c r="P173" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M173:O173)</f>
         <v>EU</v>
       </c>
       <c r="Q173" t="s">
@@ -22342,7 +22361,7 @@
         <v/>
       </c>
       <c r="P174" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M174:O174)</f>
         <v/>
       </c>
       <c r="Q174" t="s">
@@ -22398,7 +22417,7 @@
         <v/>
       </c>
       <c r="P175" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M175:O175)</f>
         <v>USA</v>
       </c>
       <c r="Q175" t="s">
@@ -22454,7 +22473,7 @@
         <v/>
       </c>
       <c r="P176" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M176:O176)</f>
         <v>BRA</v>
       </c>
       <c r="Q176" t="s">
@@ -22488,7 +22507,7 @@
       <c r="C177" t="s">
         <v>229</v>
       </c>
-      <c r="D177" t="s">
+      <c r="D177" s="14" t="s">
         <v>834</v>
       </c>
       <c r="E177" t="s">
@@ -22510,7 +22529,7 @@
         <v/>
       </c>
       <c r="P177" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M177:O177)</f>
         <v>MEX</v>
       </c>
       <c r="Q177" t="s">
@@ -22566,7 +22585,7 @@
         <v/>
       </c>
       <c r="P178" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M178:O178)</f>
         <v>CHN</v>
       </c>
       <c r="Q178" t="s">
@@ -22591,62 +22610,66 @@
     <row r="179" spans="1:22">
       <c r="A179" s="2" t="str">
         <f>IF(C179="","",VLOOKUP(C179,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>USA</v>
+        <v>LBN</v>
       </c>
       <c r="B179" s="3" t="str">
         <f>IF(C179="","",VLOOKUP(C179,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>America</v>
+        <v>Lebanon</v>
       </c>
       <c r="C179" s="8" t="s">
-        <v>869</v>
+        <v>934</v>
       </c>
       <c r="D179" s="8" t="s">
-        <v>870</v>
+        <v>940</v>
       </c>
       <c r="E179" s="8" t="s">
-        <v>871</v>
+        <v>941</v>
       </c>
       <c r="F179" s="8" t="s">
-        <v>872</v>
+        <v>942</v>
       </c>
       <c r="G179" s="9"/>
       <c r="H179" s="8" t="s">
-        <v>873</v>
+        <v>943</v>
       </c>
       <c r="I179" s="9"/>
-      <c r="J179" s="8"/>
-      <c r="K179" s="8"/>
+      <c r="J179" s="8" t="s">
+        <v>935</v>
+      </c>
+      <c r="K179" s="8" t="s">
+        <v>869</v>
+      </c>
       <c r="L179" s="8"/>
       <c r="M179" s="2" t="str">
         <f>IF(J179="","",VLOOKUP(J179,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>ISR</v>
       </c>
       <c r="N179" s="2" t="str">
         <f>IF(K179="","",VLOOKUP(K179,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>USA</v>
       </c>
       <c r="O179" s="2" t="str">
         <f>IF(L179="","",VLOOKUP(L179,[1]ISO辞書!A:B,2,FALSE))</f>
         <v/>
       </c>
       <c r="P179" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M179:O179)</f>
+        <v>ISR;USA</v>
       </c>
       <c r="Q179" s="8" t="s">
-        <v>993</v>
+        <v>1023</v>
       </c>
       <c r="R179" s="8" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="S179" s="10">
-        <v>46138</v>
+        <v>46133</v>
       </c>
       <c r="T179" s="8" t="s">
-        <v>994</v>
-      </c>
-      <c r="U179" s="11" t="s">
-        <v>995</v>
+        <v>1015</v>
+      </c>
+      <c r="U179" s="8" t="s">
+        <v>1024</v>
       </c>
       <c r="V179" s="8">
         <v>4</v>
@@ -22655,103 +22678,99 @@
     <row r="180" spans="1:22">
       <c r="A180" s="2" t="str">
         <f>IF(C180="","",VLOOKUP(C180,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>USA</v>
+        <v>NGA</v>
       </c>
       <c r="B180" s="3" t="str">
         <f>IF(C180="","",VLOOKUP(C180,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>America</v>
+        <v>Nigeria</v>
       </c>
       <c r="C180" s="8" t="s">
-        <v>869</v>
+        <v>944</v>
       </c>
       <c r="D180" s="8" t="s">
-        <v>874</v>
+        <v>945</v>
       </c>
       <c r="E180" s="8" t="s">
-        <v>875</v>
+        <v>946</v>
       </c>
       <c r="F180" s="8" t="s">
-        <v>876</v>
+        <v>947</v>
       </c>
       <c r="G180" s="9"/>
-      <c r="H180" s="8" t="s">
-        <v>877</v>
-      </c>
+      <c r="H180" s="8"/>
       <c r="I180" s="9"/>
-      <c r="J180" s="8" t="s">
-        <v>878</v>
-      </c>
-      <c r="K180" s="8" t="s">
-        <v>879</v>
-      </c>
+      <c r="J180" s="8"/>
+      <c r="K180" s="8"/>
       <c r="L180" s="8"/>
       <c r="M180" s="2" t="str">
         <f>IF(J180="","",VLOOKUP(J180,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>IRN</v>
+        <v/>
       </c>
       <c r="N180" s="2" t="str">
         <f>IF(K180="","",VLOOKUP(K180,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>PAK</v>
+        <v/>
       </c>
       <c r="O180" s="2" t="str">
         <f>IF(L180="","",VLOOKUP(L180,[1]ISO辞書!A:B,2,FALSE))</f>
         <v/>
       </c>
       <c r="P180" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>IRN;PAK</v>
-      </c>
-      <c r="Q180" s="12" t="s">
-        <v>996</v>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M180:O180)</f>
+        <v/>
+      </c>
+      <c r="Q180" s="8" t="s">
+        <v>1025</v>
       </c>
       <c r="R180" s="8" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="S180" s="10">
-        <v>46137</v>
+        <v>46133</v>
       </c>
       <c r="T180" s="8" t="s">
-        <v>994</v>
+        <v>1015</v>
       </c>
       <c r="U180" s="8" t="s">
-        <v>997</v>
+        <v>1026</v>
       </c>
       <c r="V180" s="8">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181" spans="1:22">
       <c r="A181" s="2" t="str">
         <f>IF(C181="","",VLOOKUP(C181,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>USA</v>
+        <v>EU</v>
       </c>
       <c r="B181" s="3" t="str">
         <f>IF(C181="","",VLOOKUP(C181,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>America</v>
+        <v>EU</v>
       </c>
       <c r="C181" s="8" t="s">
-        <v>869</v>
+        <v>983</v>
       </c>
       <c r="D181" s="8" t="s">
-        <v>880</v>
+        <v>984</v>
       </c>
       <c r="E181" s="8" t="s">
-        <v>881</v>
+        <v>985</v>
       </c>
       <c r="F181" s="8" t="s">
-        <v>882</v>
+        <v>986</v>
       </c>
       <c r="G181" s="9"/>
       <c r="H181" s="8" t="s">
-        <v>883</v>
+        <v>987</v>
       </c>
       <c r="I181" s="9"/>
-      <c r="J181" s="8"/>
+      <c r="J181" s="8" t="s">
+        <v>919</v>
+      </c>
       <c r="K181" s="8"/>
       <c r="L181" s="8"/>
       <c r="M181" s="2" t="str">
         <f>IF(J181="","",VLOOKUP(J181,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>RUS</v>
       </c>
       <c r="N181" s="2" t="str">
         <f>IF(K181="","",VLOOKUP(K181,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -22762,62 +22781,60 @@
         <v/>
       </c>
       <c r="P181" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M181:O181)</f>
+        <v>RUS</v>
       </c>
       <c r="Q181" s="8" t="s">
-        <v>998</v>
+        <v>1041</v>
       </c>
       <c r="R181" s="8" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="S181" s="10">
-        <v>46137</v>
+        <v>46133</v>
       </c>
       <c r="T181" s="8" t="s">
-        <v>994</v>
+        <v>1015</v>
       </c>
       <c r="U181" s="8" t="s">
-        <v>999</v>
+        <v>1042</v>
       </c>
       <c r="V181" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182" spans="1:22">
       <c r="A182" s="2" t="str">
         <f>IF(C182="","",VLOOKUP(C182,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>USA</v>
+        <v>JPN</v>
       </c>
       <c r="B182" s="3" t="str">
         <f>IF(C182="","",VLOOKUP(C182,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>America</v>
+        <v>Japan</v>
       </c>
       <c r="C182" s="8" t="s">
-        <v>869</v>
-      </c>
-      <c r="D182" s="8" t="s">
-        <v>884</v>
+        <v>988</v>
+      </c>
+      <c r="D182" s="15" t="s">
+        <v>989</v>
       </c>
       <c r="E182" s="8" t="s">
-        <v>885</v>
+        <v>990</v>
       </c>
       <c r="F182" s="8" t="s">
-        <v>886</v>
+        <v>991</v>
       </c>
       <c r="G182" s="9"/>
       <c r="H182" s="8" t="s">
-        <v>887</v>
+        <v>992</v>
       </c>
       <c r="I182" s="9"/>
-      <c r="J182" s="8" t="s">
-        <v>878</v>
-      </c>
+      <c r="J182" s="8"/>
       <c r="K182" s="8"/>
       <c r="L182" s="8"/>
       <c r="M182" s="2" t="str">
         <f>IF(J182="","",VLOOKUP(J182,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>IRN</v>
+        <v/>
       </c>
       <c r="N182" s="2" t="str">
         <f>IF(K182="","",VLOOKUP(K182,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -22828,23 +22845,23 @@
         <v/>
       </c>
       <c r="P182" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>IRN</v>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M182:O182)</f>
+        <v/>
       </c>
       <c r="Q182" s="8" t="s">
-        <v>1000</v>
+        <v>1043</v>
       </c>
       <c r="R182" s="8" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="S182" s="10">
-        <v>46138</v>
+        <v>46133</v>
       </c>
       <c r="T182" s="8" t="s">
-        <v>994</v>
+        <v>1015</v>
       </c>
       <c r="U182" s="8" t="s">
-        <v>1001</v>
+        <v>1044</v>
       </c>
       <c r="V182" s="8">
         <v>5</v>
@@ -22853,37 +22870,37 @@
     <row r="183" spans="1:22">
       <c r="A183" s="2" t="str">
         <f>IF(C183="","",VLOOKUP(C183,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>CHN</v>
+        <v>IRN</v>
       </c>
       <c r="B183" s="3" t="str">
         <f>IF(C183="","",VLOOKUP(C183,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>China</v>
+        <v>Iran</v>
       </c>
       <c r="C183" s="8" t="s">
-        <v>888</v>
+        <v>878</v>
       </c>
       <c r="D183" s="8" t="s">
-        <v>889</v>
+        <v>936</v>
       </c>
       <c r="E183" s="8" t="s">
-        <v>890</v>
+        <v>937</v>
       </c>
       <c r="F183" s="8" t="s">
-        <v>891</v>
+        <v>938</v>
       </c>
       <c r="G183" s="9"/>
       <c r="H183" s="8" t="s">
-        <v>892</v>
+        <v>939</v>
       </c>
       <c r="I183" s="9"/>
       <c r="J183" s="8" t="s">
-        <v>893</v>
+        <v>869</v>
       </c>
       <c r="K183" s="8"/>
       <c r="L183" s="8"/>
       <c r="M183" s="2" t="str">
         <f>IF(J183="","",VLOOKUP(J183,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>MMR</v>
+        <v>USA</v>
       </c>
       <c r="N183" s="2" t="str">
         <f>IF(K183="","",VLOOKUP(K183,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -22894,62 +22911,62 @@
         <v/>
       </c>
       <c r="P183" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>MMR</v>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M183:O183)</f>
+        <v>USA</v>
       </c>
       <c r="Q183" s="8" t="s">
-        <v>1002</v>
+        <v>1021</v>
       </c>
       <c r="R183" s="8" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="S183" s="10">
-        <v>46137</v>
+        <v>46134</v>
       </c>
       <c r="T183" s="8" t="s">
-        <v>994</v>
+        <v>1015</v>
       </c>
       <c r="U183" s="8" t="s">
-        <v>1003</v>
+        <v>1022</v>
       </c>
       <c r="V183" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="184" spans="1:22">
       <c r="A184" s="2" t="str">
         <f>IF(C184="","",VLOOKUP(C184,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>FRA</v>
+        <v>BRA</v>
       </c>
       <c r="B184" s="3" t="str">
         <f>IF(C184="","",VLOOKUP(C184,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>France</v>
+        <v>Brazil</v>
       </c>
       <c r="C184" s="8" t="s">
-        <v>894</v>
+        <v>948</v>
       </c>
       <c r="D184" s="8" t="s">
-        <v>895</v>
+        <v>949</v>
       </c>
       <c r="E184" s="8" t="s">
-        <v>896</v>
+        <v>950</v>
       </c>
       <c r="F184" s="8" t="s">
-        <v>897</v>
+        <v>951</v>
       </c>
       <c r="G184" s="9"/>
       <c r="H184" s="8" t="s">
-        <v>898</v>
+        <v>952</v>
       </c>
       <c r="I184" s="9"/>
       <c r="J184" s="8" t="s">
-        <v>899</v>
+        <v>869</v>
       </c>
       <c r="K184" s="8"/>
       <c r="L184" s="8"/>
       <c r="M184" s="2" t="str">
         <f>IF(J184="","",VLOOKUP(J184,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>GRC</v>
+        <v>USA</v>
       </c>
       <c r="N184" s="2" t="str">
         <f>IF(K184="","",VLOOKUP(K184,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -22960,60 +22977,62 @@
         <v/>
       </c>
       <c r="P184" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>GRC</v>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M184:O184)</f>
+        <v>USA</v>
       </c>
       <c r="Q184" s="8" t="s">
-        <v>1004</v>
+        <v>1027</v>
       </c>
       <c r="R184" s="8" t="s">
         <v>43</v>
       </c>
       <c r="S184" s="10">
-        <v>46137</v>
+        <v>46134</v>
       </c>
       <c r="T184" s="8" t="s">
-        <v>994</v>
+        <v>1015</v>
       </c>
       <c r="U184" s="8" t="s">
-        <v>1005</v>
+        <v>1028</v>
       </c>
       <c r="V184" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185" spans="1:22">
       <c r="A185" s="2" t="str">
         <f>IF(C185="","",VLOOKUP(C185,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>MLI</v>
+        <v>USA</v>
       </c>
       <c r="B185" s="3" t="str">
         <f>IF(C185="","",VLOOKUP(C185,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Mali</v>
+        <v>America</v>
       </c>
       <c r="C185" s="8" t="s">
-        <v>900</v>
+        <v>869</v>
       </c>
       <c r="D185" s="8" t="s">
-        <v>901</v>
+        <v>978</v>
       </c>
       <c r="E185" s="8" t="s">
-        <v>902</v>
+        <v>979</v>
       </c>
       <c r="F185" s="8" t="s">
-        <v>903</v>
+        <v>980</v>
       </c>
       <c r="G185" s="9"/>
       <c r="H185" s="8" t="s">
-        <v>904</v>
+        <v>981</v>
       </c>
       <c r="I185" s="9"/>
-      <c r="J185" s="8"/>
+      <c r="J185" s="8" t="s">
+        <v>982</v>
+      </c>
       <c r="K185" s="8"/>
       <c r="L185" s="8"/>
       <c r="M185" s="2" t="str">
         <f>IF(J185="","",VLOOKUP(J185,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>NLD</v>
       </c>
       <c r="N185" s="2" t="str">
         <f>IF(K185="","",VLOOKUP(K185,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -23024,23 +23043,23 @@
         <v/>
       </c>
       <c r="P185" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M185:O185)</f>
+        <v>NLD</v>
       </c>
       <c r="Q185" s="8" t="s">
-        <v>1006</v>
+        <v>1039</v>
       </c>
       <c r="R185" s="8" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="S185" s="10">
-        <v>46137</v>
+        <v>46134</v>
       </c>
       <c r="T185" s="8" t="s">
-        <v>994</v>
+        <v>1015</v>
       </c>
       <c r="U185" s="8" t="s">
-        <v>1007</v>
+        <v>1040</v>
       </c>
       <c r="V185" s="8">
         <v>3</v>
@@ -23049,37 +23068,35 @@
     <row r="186" spans="1:22">
       <c r="A186" s="2" t="str">
         <f>IF(C186="","",VLOOKUP(C186,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>USA</v>
+        <v>TUR</v>
       </c>
       <c r="B186" s="3" t="str">
         <f>IF(C186="","",VLOOKUP(C186,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>America</v>
+        <v>Türkiye</v>
       </c>
       <c r="C186" s="8" t="s">
-        <v>869</v>
+        <v>925</v>
       </c>
       <c r="D186" s="8" t="s">
-        <v>905</v>
+        <v>926</v>
       </c>
       <c r="E186" s="8" t="s">
-        <v>906</v>
+        <v>927</v>
       </c>
       <c r="F186" s="8" t="s">
-        <v>907</v>
+        <v>928</v>
       </c>
       <c r="G186" s="9"/>
       <c r="H186" s="8" t="s">
-        <v>908</v>
+        <v>929</v>
       </c>
       <c r="I186" s="9"/>
-      <c r="J186" s="8" t="s">
-        <v>888</v>
-      </c>
+      <c r="J186" s="8"/>
       <c r="K186" s="8"/>
       <c r="L186" s="8"/>
       <c r="M186" s="2" t="str">
         <f>IF(J186="","",VLOOKUP(J186,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>CHN</v>
+        <v/>
       </c>
       <c r="N186" s="2" t="str">
         <f>IF(K186="","",VLOOKUP(K186,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -23090,126 +23107,128 @@
         <v/>
       </c>
       <c r="P186" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>CHN</v>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M186:O186)</f>
+        <v/>
       </c>
       <c r="Q186" s="8" t="s">
-        <v>1008</v>
+        <v>1017</v>
       </c>
       <c r="R186" s="8" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="S186" s="10">
-        <v>46136</v>
+        <v>46135</v>
       </c>
       <c r="T186" s="8" t="s">
-        <v>994</v>
-      </c>
-      <c r="U186" s="5" t="s">
-        <v>1009</v>
+        <v>1015</v>
+      </c>
+      <c r="U186" s="8" t="s">
+        <v>1018</v>
       </c>
       <c r="V186" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187" spans="1:22">
       <c r="A187" s="2" t="str">
         <f>IF(C187="","",VLOOKUP(C187,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>GBR</v>
+        <v>USA</v>
       </c>
       <c r="B187" s="3" t="str">
         <f>IF(C187="","",VLOOKUP(C187,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Britain</v>
+        <v>America</v>
       </c>
       <c r="C187" s="8" t="s">
-        <v>909</v>
-      </c>
-      <c r="D187" s="8" t="s">
-        <v>910</v>
+        <v>869</v>
+      </c>
+      <c r="D187" s="15" t="s">
+        <v>930</v>
       </c>
       <c r="E187" s="8" t="s">
-        <v>911</v>
+        <v>931</v>
       </c>
       <c r="F187" s="8" t="s">
-        <v>912</v>
+        <v>932</v>
       </c>
       <c r="G187" s="9"/>
       <c r="H187" s="8" t="s">
-        <v>913</v>
+        <v>933</v>
       </c>
       <c r="I187" s="9"/>
-      <c r="J187" s="8"/>
-      <c r="K187" s="8"/>
+      <c r="J187" s="8" t="s">
+        <v>934</v>
+      </c>
+      <c r="K187" s="8" t="s">
+        <v>935</v>
+      </c>
       <c r="L187" s="8"/>
       <c r="M187" s="2" t="str">
         <f>IF(J187="","",VLOOKUP(J187,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>LBN</v>
       </c>
       <c r="N187" s="2" t="str">
         <f>IF(K187="","",VLOOKUP(K187,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>ISR</v>
       </c>
       <c r="O187" s="2" t="str">
         <f>IF(L187="","",VLOOKUP(L187,[1]ISO辞書!A:B,2,FALSE))</f>
         <v/>
       </c>
       <c r="P187" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M187:O187)</f>
+        <v>LBN;ISR</v>
       </c>
       <c r="Q187" s="8" t="s">
-        <v>1010</v>
+        <v>1019</v>
       </c>
       <c r="R187" s="8" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="S187" s="10">
-        <v>46136</v>
+        <v>46135</v>
       </c>
       <c r="T187" s="8" t="s">
-        <v>994</v>
+        <v>1015</v>
       </c>
       <c r="U187" s="8" t="s">
-        <v>1011</v>
+        <v>1020</v>
       </c>
       <c r="V187" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:22">
       <c r="A188" s="2" t="str">
         <f>IF(C188="","",VLOOKUP(C188,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>UKR</v>
+        <v>PHL</v>
       </c>
       <c r="B188" s="3" t="str">
         <f>IF(C188="","",VLOOKUP(C188,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Ukraine</v>
+        <v>Philippines</v>
       </c>
       <c r="C188" s="8" t="s">
-        <v>914</v>
-      </c>
-      <c r="D188" s="8" t="s">
-        <v>915</v>
+        <v>957</v>
+      </c>
+      <c r="D188" s="15" t="s">
+        <v>958</v>
       </c>
       <c r="E188" s="8" t="s">
-        <v>916</v>
+        <v>959</v>
       </c>
       <c r="F188" s="8" t="s">
-        <v>917</v>
+        <v>960</v>
       </c>
       <c r="G188" s="9"/>
       <c r="H188" s="8" t="s">
-        <v>918</v>
+        <v>961</v>
       </c>
       <c r="I188" s="9"/>
-      <c r="J188" s="8" t="s">
-        <v>919</v>
-      </c>
+      <c r="J188" s="8"/>
       <c r="K188" s="8"/>
       <c r="L188" s="8"/>
       <c r="M188" s="2" t="str">
         <f>IF(J188="","",VLOOKUP(J188,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>RUS</v>
+        <v/>
       </c>
       <c r="N188" s="2" t="str">
         <f>IF(K188="","",VLOOKUP(K188,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -23220,62 +23239,62 @@
         <v/>
       </c>
       <c r="P188" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>RUS</v>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M188:O188)</f>
+        <v/>
       </c>
       <c r="Q188" s="8" t="s">
-        <v>1012</v>
+        <v>1031</v>
       </c>
       <c r="R188" s="8" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="S188" s="10">
-        <v>46136</v>
+        <v>46135</v>
       </c>
       <c r="T188" s="8" t="s">
-        <v>994</v>
+        <v>1015</v>
       </c>
       <c r="U188" s="8" t="s">
-        <v>1013</v>
+        <v>1032</v>
       </c>
       <c r="V188" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189" spans="1:22">
       <c r="A189" s="2" t="str">
         <f>IF(C189="","",VLOOKUP(C189,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>QAT</v>
+        <v>KOR</v>
       </c>
       <c r="B189" s="3" t="str">
         <f>IF(C189="","",VLOOKUP(C189,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Qatar</v>
+        <v>Korea</v>
       </c>
       <c r="C189" s="8" t="s">
-        <v>920</v>
+        <v>962</v>
       </c>
       <c r="D189" s="8" t="s">
-        <v>921</v>
+        <v>963</v>
       </c>
       <c r="E189" s="8" t="s">
-        <v>922</v>
+        <v>964</v>
       </c>
       <c r="F189" s="8" t="s">
-        <v>923</v>
+        <v>965</v>
       </c>
       <c r="G189" s="9"/>
       <c r="H189" s="8" t="s">
-        <v>924</v>
+        <v>966</v>
       </c>
       <c r="I189" s="9"/>
       <c r="J189" s="8" t="s">
-        <v>869</v>
+        <v>967</v>
       </c>
       <c r="K189" s="8"/>
       <c r="L189" s="8"/>
       <c r="M189" s="2" t="str">
         <f>IF(J189="","",VLOOKUP(J189,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>USA</v>
+        <v>VNM</v>
       </c>
       <c r="N189" s="2" t="str">
         <f>IF(K189="","",VLOOKUP(K189,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -23286,23 +23305,23 @@
         <v/>
       </c>
       <c r="P189" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>USA</v>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M189:O189)</f>
+        <v>VNM</v>
       </c>
       <c r="Q189" s="8" t="s">
-        <v>1014</v>
+        <v>1033</v>
       </c>
       <c r="R189" s="8" t="s">
         <v>43</v>
       </c>
       <c r="S189" s="10">
-        <v>46136</v>
+        <v>46135</v>
       </c>
       <c r="T189" s="8" t="s">
         <v>1015</v>
       </c>
       <c r="U189" s="8" t="s">
-        <v>1016</v>
+        <v>1034</v>
       </c>
       <c r="V189" s="8">
         <v>3</v>
@@ -23311,35 +23330,37 @@
     <row r="190" spans="1:22">
       <c r="A190" s="2" t="str">
         <f>IF(C190="","",VLOOKUP(C190,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>TUR</v>
+        <v>USA</v>
       </c>
       <c r="B190" s="3" t="str">
         <f>IF(C190="","",VLOOKUP(C190,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Türkiye</v>
+        <v>America</v>
       </c>
       <c r="C190" s="8" t="s">
-        <v>925</v>
+        <v>869</v>
       </c>
       <c r="D190" s="8" t="s">
-        <v>926</v>
+        <v>905</v>
       </c>
       <c r="E190" s="8" t="s">
-        <v>927</v>
+        <v>906</v>
       </c>
       <c r="F190" s="8" t="s">
-        <v>928</v>
+        <v>907</v>
       </c>
       <c r="G190" s="9"/>
       <c r="H190" s="8" t="s">
-        <v>929</v>
+        <v>908</v>
       </c>
       <c r="I190" s="9"/>
-      <c r="J190" s="8"/>
+      <c r="J190" s="8" t="s">
+        <v>888</v>
+      </c>
       <c r="K190" s="8"/>
       <c r="L190" s="8"/>
       <c r="M190" s="2" t="str">
         <f>IF(J190="","",VLOOKUP(J190,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>CHN</v>
       </c>
       <c r="N190" s="2" t="str">
         <f>IF(K190="","",VLOOKUP(K190,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -23350,130 +23371,126 @@
         <v/>
       </c>
       <c r="P190" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M190:O190)</f>
+        <v>CHN</v>
       </c>
       <c r="Q190" s="8" t="s">
-        <v>1017</v>
+        <v>1008</v>
       </c>
       <c r="R190" s="8" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="S190" s="10">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="T190" s="8" t="s">
-        <v>1015</v>
-      </c>
-      <c r="U190" s="8" t="s">
-        <v>1018</v>
+        <v>994</v>
+      </c>
+      <c r="U190" s="5" t="s">
+        <v>1009</v>
       </c>
       <c r="V190" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="191" spans="1:22">
       <c r="A191" s="2" t="str">
         <f>IF(C191="","",VLOOKUP(C191,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>USA</v>
+        <v>GBR</v>
       </c>
       <c r="B191" s="3" t="str">
         <f>IF(C191="","",VLOOKUP(C191,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>America</v>
+        <v>Britain</v>
       </c>
       <c r="C191" s="8" t="s">
-        <v>869</v>
+        <v>909</v>
       </c>
       <c r="D191" s="8" t="s">
-        <v>930</v>
+        <v>910</v>
       </c>
       <c r="E191" s="8" t="s">
-        <v>931</v>
+        <v>911</v>
       </c>
       <c r="F191" s="8" t="s">
-        <v>932</v>
+        <v>912</v>
       </c>
       <c r="G191" s="9"/>
       <c r="H191" s="8" t="s">
-        <v>933</v>
+        <v>913</v>
       </c>
       <c r="I191" s="9"/>
-      <c r="J191" s="8" t="s">
-        <v>934</v>
-      </c>
-      <c r="K191" s="8" t="s">
-        <v>935</v>
-      </c>
+      <c r="J191" s="8"/>
+      <c r="K191" s="8"/>
       <c r="L191" s="8"/>
       <c r="M191" s="2" t="str">
         <f>IF(J191="","",VLOOKUP(J191,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>LBN</v>
+        <v/>
       </c>
       <c r="N191" s="2" t="str">
         <f>IF(K191="","",VLOOKUP(K191,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>ISR</v>
+        <v/>
       </c>
       <c r="O191" s="2" t="str">
         <f>IF(L191="","",VLOOKUP(L191,[1]ISO辞書!A:B,2,FALSE))</f>
         <v/>
       </c>
       <c r="P191" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>LBN;ISR</v>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M191:O191)</f>
+        <v/>
       </c>
       <c r="Q191" s="8" t="s">
-        <v>1019</v>
+        <v>1010</v>
       </c>
       <c r="R191" s="8" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="S191" s="10">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="T191" s="8" t="s">
-        <v>1015</v>
+        <v>994</v>
       </c>
       <c r="U191" s="8" t="s">
-        <v>1020</v>
+        <v>1011</v>
       </c>
       <c r="V191" s="8">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="192" spans="1:22">
       <c r="A192" s="2" t="str">
         <f>IF(C192="","",VLOOKUP(C192,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>IRN</v>
+        <v>UKR</v>
       </c>
       <c r="B192" s="3" t="str">
         <f>IF(C192="","",VLOOKUP(C192,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Iran</v>
+        <v>Ukraine</v>
       </c>
       <c r="C192" s="8" t="s">
-        <v>878</v>
+        <v>914</v>
       </c>
       <c r="D192" s="8" t="s">
-        <v>936</v>
+        <v>915</v>
       </c>
       <c r="E192" s="8" t="s">
-        <v>937</v>
+        <v>916</v>
       </c>
       <c r="F192" s="8" t="s">
-        <v>938</v>
+        <v>917</v>
       </c>
       <c r="G192" s="9"/>
       <c r="H192" s="8" t="s">
-        <v>939</v>
+        <v>918</v>
       </c>
       <c r="I192" s="9"/>
       <c r="J192" s="8" t="s">
-        <v>869</v>
+        <v>919</v>
       </c>
       <c r="K192" s="8"/>
       <c r="L192" s="8"/>
       <c r="M192" s="2" t="str">
         <f>IF(J192="","",VLOOKUP(J192,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>USA</v>
+        <v>RUS</v>
       </c>
       <c r="N192" s="2" t="str">
         <f>IF(K192="","",VLOOKUP(K192,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -23484,126 +23501,128 @@
         <v/>
       </c>
       <c r="P192" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>USA</v>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M192:O192)</f>
+        <v>RUS</v>
       </c>
       <c r="Q192" s="8" t="s">
-        <v>1021</v>
+        <v>1012</v>
       </c>
       <c r="R192" s="8" t="s">
         <v>55</v>
       </c>
       <c r="S192" s="10">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="T192" s="8" t="s">
-        <v>1015</v>
+        <v>994</v>
       </c>
       <c r="U192" s="8" t="s">
-        <v>1022</v>
+        <v>1013</v>
       </c>
       <c r="V192" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="193" spans="1:22">
       <c r="A193" s="2" t="str">
         <f>IF(C193="","",VLOOKUP(C193,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>LBN</v>
+        <v>QAT</v>
       </c>
       <c r="B193" s="3" t="str">
         <f>IF(C193="","",VLOOKUP(C193,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Lebanon</v>
+        <v>Qatar</v>
       </c>
       <c r="C193" s="8" t="s">
-        <v>934</v>
+        <v>920</v>
       </c>
       <c r="D193" s="8" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="E193" s="8" t="s">
-        <v>941</v>
+        <v>922</v>
       </c>
       <c r="F193" s="8" t="s">
-        <v>942</v>
+        <v>923</v>
       </c>
       <c r="G193" s="9"/>
       <c r="H193" s="8" t="s">
-        <v>943</v>
+        <v>924</v>
       </c>
       <c r="I193" s="9"/>
       <c r="J193" s="8" t="s">
-        <v>935</v>
-      </c>
-      <c r="K193" s="8" t="s">
         <v>869</v>
       </c>
+      <c r="K193" s="8"/>
       <c r="L193" s="8"/>
       <c r="M193" s="2" t="str">
         <f>IF(J193="","",VLOOKUP(J193,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>ISR</v>
+        <v>USA</v>
       </c>
       <c r="N193" s="2" t="str">
         <f>IF(K193="","",VLOOKUP(K193,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>USA</v>
+        <v/>
       </c>
       <c r="O193" s="2" t="str">
         <f>IF(L193="","",VLOOKUP(L193,[1]ISO辞書!A:B,2,FALSE))</f>
         <v/>
       </c>
       <c r="P193" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>ISR;USA</v>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M193:O193)</f>
+        <v>USA</v>
       </c>
       <c r="Q193" s="8" t="s">
-        <v>1023</v>
+        <v>1014</v>
       </c>
       <c r="R193" s="8" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="S193" s="10">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="T193" s="8" t="s">
         <v>1015</v>
       </c>
       <c r="U193" s="8" t="s">
-        <v>1024</v>
+        <v>1016</v>
       </c>
       <c r="V193" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="194" spans="1:22">
       <c r="A194" s="2" t="str">
         <f>IF(C194="","",VLOOKUP(C194,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>NGA</v>
+        <v>UKR</v>
       </c>
       <c r="B194" s="3" t="str">
         <f>IF(C194="","",VLOOKUP(C194,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Nigeria</v>
+        <v>Ukraine</v>
       </c>
       <c r="C194" s="8" t="s">
-        <v>944</v>
+        <v>914</v>
       </c>
       <c r="D194" s="8" t="s">
-        <v>945</v>
+        <v>973</v>
       </c>
       <c r="E194" s="8" t="s">
-        <v>946</v>
+        <v>974</v>
       </c>
       <c r="F194" s="8" t="s">
-        <v>947</v>
+        <v>975</v>
       </c>
       <c r="G194" s="9"/>
-      <c r="H194" s="8"/>
+      <c r="H194" s="8" t="s">
+        <v>976</v>
+      </c>
       <c r="I194" s="9"/>
-      <c r="J194" s="8"/>
+      <c r="J194" s="8" t="s">
+        <v>977</v>
+      </c>
       <c r="K194" s="8"/>
       <c r="L194" s="8"/>
       <c r="M194" s="2" t="str">
         <f>IF(J194="","",VLOOKUP(J194,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>SAU</v>
       </c>
       <c r="N194" s="2" t="str">
         <f>IF(K194="","",VLOOKUP(K194,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -23614,126 +23633,128 @@
         <v/>
       </c>
       <c r="P194" s="3" t="str">
-        <f t="shared" ref="P194:P257" si="3">_xlfn.TEXTJOIN(";",TRUE,M194:O194)</f>
-        <v/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M194:O194)</f>
+        <v>SAU</v>
       </c>
       <c r="Q194" s="8" t="s">
-        <v>1025</v>
+        <v>1037</v>
       </c>
       <c r="R194" s="8" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="S194" s="10">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="T194" s="8" t="s">
         <v>1015</v>
       </c>
       <c r="U194" s="8" t="s">
-        <v>1026</v>
+        <v>1038</v>
       </c>
       <c r="V194" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="195" spans="1:22">
       <c r="A195" s="2" t="str">
         <f>IF(C195="","",VLOOKUP(C195,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>BRA</v>
+        <v>USA</v>
       </c>
       <c r="B195" s="3" t="str">
         <f>IF(C195="","",VLOOKUP(C195,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Brazil</v>
+        <v>America</v>
       </c>
       <c r="C195" s="8" t="s">
-        <v>948</v>
-      </c>
-      <c r="D195" s="8" t="s">
-        <v>949</v>
+        <v>869</v>
+      </c>
+      <c r="D195" s="15" t="s">
+        <v>874</v>
       </c>
       <c r="E195" s="8" t="s">
-        <v>950</v>
+        <v>875</v>
       </c>
       <c r="F195" s="8" t="s">
-        <v>951</v>
+        <v>876</v>
       </c>
       <c r="G195" s="9"/>
       <c r="H195" s="8" t="s">
-        <v>952</v>
+        <v>877</v>
       </c>
       <c r="I195" s="9"/>
       <c r="J195" s="8" t="s">
-        <v>869</v>
-      </c>
-      <c r="K195" s="8"/>
+        <v>878</v>
+      </c>
+      <c r="K195" s="8" t="s">
+        <v>879</v>
+      </c>
       <c r="L195" s="8"/>
       <c r="M195" s="2" t="str">
         <f>IF(J195="","",VLOOKUP(J195,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>USA</v>
+        <v>IRN</v>
       </c>
       <c r="N195" s="2" t="str">
         <f>IF(K195="","",VLOOKUP(K195,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>PAK</v>
       </c>
       <c r="O195" s="2" t="str">
         <f>IF(L195="","",VLOOKUP(L195,[1]ISO辞書!A:B,2,FALSE))</f>
         <v/>
       </c>
       <c r="P195" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>USA</v>
-      </c>
-      <c r="Q195" s="8" t="s">
-        <v>1027</v>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M195:O195)</f>
+        <v>IRN;PAK</v>
+      </c>
+      <c r="Q195" s="12" t="s">
+        <v>996</v>
       </c>
       <c r="R195" s="8" t="s">
         <v>43</v>
       </c>
       <c r="S195" s="10">
-        <v>46134</v>
+        <v>46137</v>
       </c>
       <c r="T195" s="8" t="s">
-        <v>1015</v>
+        <v>994</v>
       </c>
       <c r="U195" s="8" t="s">
-        <v>1028</v>
+        <v>997</v>
       </c>
       <c r="V195" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="196" spans="1:22">
       <c r="A196" s="2" t="str">
         <f>IF(C196="","",VLOOKUP(C196,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>RUS</v>
+        <v>USA</v>
       </c>
       <c r="B196" s="3" t="str">
         <f>IF(C196="","",VLOOKUP(C196,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Russian Federation</v>
+        <v>America</v>
       </c>
       <c r="C196" s="8" t="s">
-        <v>919</v>
-      </c>
-      <c r="D196" s="8" t="s">
-        <v>953</v>
+        <v>869</v>
+      </c>
+      <c r="D196" s="15" t="s">
+        <v>880</v>
       </c>
       <c r="E196" s="8" t="s">
-        <v>954</v>
+        <v>881</v>
       </c>
       <c r="F196" s="8" t="s">
-        <v>955</v>
+        <v>882</v>
       </c>
       <c r="G196" s="9"/>
-      <c r="H196" s="8"/>
+      <c r="H196" s="8" t="s">
+        <v>883</v>
+      </c>
       <c r="I196" s="9"/>
-      <c r="J196" s="8" t="s">
-        <v>956</v>
-      </c>
+      <c r="J196" s="8"/>
       <c r="K196" s="8"/>
       <c r="L196" s="8"/>
       <c r="M196" s="2" t="str">
         <f>IF(J196="","",VLOOKUP(J196,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>PRK</v>
+        <v/>
       </c>
       <c r="N196" s="2" t="str">
         <f>IF(K196="","",VLOOKUP(K196,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -23744,60 +23765,62 @@
         <v/>
       </c>
       <c r="P196" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>PRK</v>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M196:O196)</f>
+        <v/>
       </c>
       <c r="Q196" s="8" t="s">
-        <v>1029</v>
+        <v>998</v>
       </c>
       <c r="R196" s="8" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="S196" s="10">
         <v>46137</v>
       </c>
       <c r="T196" s="8" t="s">
-        <v>1015</v>
+        <v>994</v>
       </c>
       <c r="U196" s="8" t="s">
-        <v>1030</v>
+        <v>999</v>
       </c>
       <c r="V196" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="197" spans="1:22">
       <c r="A197" s="2" t="str">
         <f>IF(C197="","",VLOOKUP(C197,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>PHL</v>
+        <v>CHN</v>
       </c>
       <c r="B197" s="3" t="str">
         <f>IF(C197="","",VLOOKUP(C197,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Philippines</v>
+        <v>China</v>
       </c>
       <c r="C197" s="8" t="s">
-        <v>957</v>
+        <v>888</v>
       </c>
       <c r="D197" s="8" t="s">
-        <v>958</v>
+        <v>889</v>
       </c>
       <c r="E197" s="8" t="s">
-        <v>959</v>
+        <v>890</v>
       </c>
       <c r="F197" s="8" t="s">
-        <v>960</v>
+        <v>891</v>
       </c>
       <c r="G197" s="9"/>
       <c r="H197" s="8" t="s">
-        <v>961</v>
+        <v>892</v>
       </c>
       <c r="I197" s="9"/>
-      <c r="J197" s="8"/>
+      <c r="J197" s="8" t="s">
+        <v>893</v>
+      </c>
       <c r="K197" s="8"/>
       <c r="L197" s="8"/>
       <c r="M197" s="2" t="str">
         <f>IF(J197="","",VLOOKUP(J197,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>MMR</v>
       </c>
       <c r="N197" s="2" t="str">
         <f>IF(K197="","",VLOOKUP(K197,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -23808,23 +23831,23 @@
         <v/>
       </c>
       <c r="P197" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M197:O197)</f>
+        <v>MMR</v>
       </c>
       <c r="Q197" s="8" t="s">
-        <v>1031</v>
+        <v>1002</v>
       </c>
       <c r="R197" s="8" t="s">
         <v>43</v>
       </c>
       <c r="S197" s="10">
-        <v>46135</v>
+        <v>46137</v>
       </c>
       <c r="T197" s="8" t="s">
-        <v>1015</v>
+        <v>994</v>
       </c>
       <c r="U197" s="8" t="s">
-        <v>1032</v>
+        <v>1003</v>
       </c>
       <c r="V197" s="8">
         <v>3</v>
@@ -23833,37 +23856,37 @@
     <row r="198" spans="1:22">
       <c r="A198" s="2" t="str">
         <f>IF(C198="","",VLOOKUP(C198,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>KOR</v>
+        <v>FRA</v>
       </c>
       <c r="B198" s="3" t="str">
         <f>IF(C198="","",VLOOKUP(C198,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Korea</v>
+        <v>France</v>
       </c>
       <c r="C198" s="8" t="s">
-        <v>962</v>
+        <v>894</v>
       </c>
       <c r="D198" s="8" t="s">
-        <v>963</v>
+        <v>895</v>
       </c>
       <c r="E198" s="8" t="s">
-        <v>964</v>
+        <v>896</v>
       </c>
       <c r="F198" s="8" t="s">
-        <v>965</v>
+        <v>897</v>
       </c>
       <c r="G198" s="9"/>
       <c r="H198" s="8" t="s">
-        <v>966</v>
+        <v>898</v>
       </c>
       <c r="I198" s="9"/>
       <c r="J198" s="8" t="s">
-        <v>967</v>
+        <v>899</v>
       </c>
       <c r="K198" s="8"/>
       <c r="L198" s="8"/>
       <c r="M198" s="2" t="str">
         <f>IF(J198="","",VLOOKUP(J198,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>VNM</v>
+        <v>GRC</v>
       </c>
       <c r="N198" s="2" t="str">
         <f>IF(K198="","",VLOOKUP(K198,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -23874,52 +23897,52 @@
         <v/>
       </c>
       <c r="P198" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>VNM</v>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M198:O198)</f>
+        <v>GRC</v>
       </c>
       <c r="Q198" s="8" t="s">
-        <v>1033</v>
+        <v>1004</v>
       </c>
       <c r="R198" s="8" t="s">
         <v>43</v>
       </c>
       <c r="S198" s="10">
-        <v>46135</v>
+        <v>46137</v>
       </c>
       <c r="T198" s="8" t="s">
-        <v>1015</v>
+        <v>994</v>
       </c>
       <c r="U198" s="8" t="s">
-        <v>1034</v>
+        <v>1005</v>
       </c>
       <c r="V198" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="199" spans="1:22">
       <c r="A199" s="2" t="str">
         <f>IF(C199="","",VLOOKUP(C199,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>DEU</v>
+        <v>MLI</v>
       </c>
       <c r="B199" s="3" t="str">
         <f>IF(C199="","",VLOOKUP(C199,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Germany</v>
+        <v>Mali</v>
       </c>
       <c r="C199" s="8" t="s">
-        <v>968</v>
-      </c>
-      <c r="D199" s="8" t="s">
-        <v>969</v>
+        <v>900</v>
+      </c>
+      <c r="D199" s="15" t="s">
+        <v>901</v>
       </c>
       <c r="E199" s="8" t="s">
-        <v>970</v>
+        <v>902</v>
       </c>
       <c r="F199" s="8" t="s">
-        <v>971</v>
+        <v>903</v>
       </c>
       <c r="G199" s="9"/>
       <c r="H199" s="8" t="s">
-        <v>972</v>
+        <v>904</v>
       </c>
       <c r="I199" s="9"/>
       <c r="J199" s="8"/>
@@ -23938,62 +23961,60 @@
         <v/>
       </c>
       <c r="P199" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M199:O199)</f>
         <v/>
       </c>
       <c r="Q199" s="8" t="s">
-        <v>1035</v>
+        <v>1006</v>
       </c>
       <c r="R199" s="8" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="S199" s="10">
         <v>46137</v>
       </c>
       <c r="T199" s="8" t="s">
-        <v>1015</v>
+        <v>994</v>
       </c>
       <c r="U199" s="8" t="s">
-        <v>1036</v>
+        <v>1007</v>
       </c>
       <c r="V199" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="200" spans="1:22">
       <c r="A200" s="2" t="str">
         <f>IF(C200="","",VLOOKUP(C200,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>UKR</v>
+        <v>RUS</v>
       </c>
       <c r="B200" s="3" t="str">
         <f>IF(C200="","",VLOOKUP(C200,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Ukraine</v>
+        <v>Russian Federation</v>
       </c>
       <c r="C200" s="8" t="s">
-        <v>914</v>
+        <v>919</v>
       </c>
       <c r="D200" s="8" t="s">
-        <v>973</v>
+        <v>953</v>
       </c>
       <c r="E200" s="8" t="s">
-        <v>974</v>
+        <v>954</v>
       </c>
       <c r="F200" s="8" t="s">
-        <v>975</v>
+        <v>955</v>
       </c>
       <c r="G200" s="9"/>
-      <c r="H200" s="8" t="s">
-        <v>976</v>
-      </c>
+      <c r="H200" s="8"/>
       <c r="I200" s="9"/>
       <c r="J200" s="8" t="s">
-        <v>977</v>
+        <v>956</v>
       </c>
       <c r="K200" s="8"/>
       <c r="L200" s="8"/>
       <c r="M200" s="2" t="str">
         <f>IF(J200="","",VLOOKUP(J200,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>SAU</v>
+        <v>PRK</v>
       </c>
       <c r="N200" s="2" t="str">
         <f>IF(K200="","",VLOOKUP(K200,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -24004,62 +24025,60 @@
         <v/>
       </c>
       <c r="P200" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>SAU</v>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M200:O200)</f>
+        <v>PRK</v>
       </c>
       <c r="Q200" s="8" t="s">
-        <v>1037</v>
+        <v>1029</v>
       </c>
       <c r="R200" s="8" t="s">
         <v>43</v>
       </c>
       <c r="S200" s="10">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="T200" s="8" t="s">
         <v>1015</v>
       </c>
       <c r="U200" s="8" t="s">
-        <v>1038</v>
+        <v>1030</v>
       </c>
       <c r="V200" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201" spans="1:22">
       <c r="A201" s="2" t="str">
         <f>IF(C201="","",VLOOKUP(C201,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>USA</v>
+        <v>DEU</v>
       </c>
       <c r="B201" s="3" t="str">
         <f>IF(C201="","",VLOOKUP(C201,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>America</v>
+        <v>Germany</v>
       </c>
       <c r="C201" s="8" t="s">
-        <v>869</v>
+        <v>968</v>
       </c>
       <c r="D201" s="8" t="s">
-        <v>978</v>
+        <v>969</v>
       </c>
       <c r="E201" s="8" t="s">
-        <v>979</v>
+        <v>970</v>
       </c>
       <c r="F201" s="8" t="s">
-        <v>980</v>
+        <v>971</v>
       </c>
       <c r="G201" s="9"/>
       <c r="H201" s="8" t="s">
-        <v>981</v>
+        <v>972</v>
       </c>
       <c r="I201" s="9"/>
-      <c r="J201" s="8" t="s">
-        <v>982</v>
-      </c>
+      <c r="J201" s="8"/>
       <c r="K201" s="8"/>
       <c r="L201" s="8"/>
       <c r="M201" s="2" t="str">
         <f>IF(J201="","",VLOOKUP(J201,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>NLD</v>
+        <v/>
       </c>
       <c r="N201" s="2" t="str">
         <f>IF(K201="","",VLOOKUP(K201,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -24070,62 +24089,60 @@
         <v/>
       </c>
       <c r="P201" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>NLD</v>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M201:O201)</f>
+        <v/>
       </c>
       <c r="Q201" s="8" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
       <c r="R201" s="8" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="S201" s="10">
-        <v>46134</v>
+        <v>46137</v>
       </c>
       <c r="T201" s="8" t="s">
         <v>1015</v>
       </c>
       <c r="U201" s="8" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="V201" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="202" spans="1:22">
       <c r="A202" s="2" t="str">
         <f>IF(C202="","",VLOOKUP(C202,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>EU</v>
+        <v>USA</v>
       </c>
       <c r="B202" s="3" t="str">
         <f>IF(C202="","",VLOOKUP(C202,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>EU</v>
+        <v>America</v>
       </c>
       <c r="C202" s="8" t="s">
-        <v>983</v>
+        <v>869</v>
       </c>
       <c r="D202" s="8" t="s">
-        <v>984</v>
+        <v>870</v>
       </c>
       <c r="E202" s="8" t="s">
-        <v>985</v>
+        <v>871</v>
       </c>
       <c r="F202" s="8" t="s">
-        <v>986</v>
+        <v>872</v>
       </c>
       <c r="G202" s="9"/>
       <c r="H202" s="8" t="s">
-        <v>987</v>
+        <v>873</v>
       </c>
       <c r="I202" s="9"/>
-      <c r="J202" s="8" t="s">
-        <v>919</v>
-      </c>
+      <c r="J202" s="8"/>
       <c r="K202" s="8"/>
       <c r="L202" s="8"/>
       <c r="M202" s="2" t="str">
         <f>IF(J202="","",VLOOKUP(J202,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v>RUS</v>
+        <v/>
       </c>
       <c r="N202" s="2" t="str">
         <f>IF(K202="","",VLOOKUP(K202,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -24136,60 +24153,62 @@
         <v/>
       </c>
       <c r="P202" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>RUS</v>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M202:O202)</f>
+        <v/>
       </c>
       <c r="Q202" s="8" t="s">
-        <v>1041</v>
+        <v>993</v>
       </c>
       <c r="R202" s="8" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="S202" s="10">
-        <v>46133</v>
+        <v>46138</v>
       </c>
       <c r="T202" s="8" t="s">
-        <v>1015</v>
-      </c>
-      <c r="U202" s="8" t="s">
-        <v>1042</v>
+        <v>994</v>
+      </c>
+      <c r="U202" s="11" t="s">
+        <v>995</v>
       </c>
       <c r="V202" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="203" spans="1:22">
       <c r="A203" s="2" t="str">
         <f>IF(C203="","",VLOOKUP(C203,[1]ISO辞書!A:C,2,FALSE))</f>
-        <v>JPN</v>
+        <v>USA</v>
       </c>
       <c r="B203" s="3" t="str">
         <f>IF(C203="","",VLOOKUP(C203,[1]ISO辞書!A:C,3,FALSE))</f>
-        <v>Japan</v>
+        <v>America</v>
       </c>
       <c r="C203" s="8" t="s">
-        <v>988</v>
+        <v>869</v>
       </c>
       <c r="D203" s="8" t="s">
-        <v>989</v>
+        <v>884</v>
       </c>
       <c r="E203" s="8" t="s">
-        <v>990</v>
+        <v>885</v>
       </c>
       <c r="F203" s="8" t="s">
-        <v>991</v>
+        <v>886</v>
       </c>
       <c r="G203" s="9"/>
       <c r="H203" s="8" t="s">
-        <v>992</v>
+        <v>887</v>
       </c>
       <c r="I203" s="9"/>
-      <c r="J203" s="8"/>
+      <c r="J203" s="8" t="s">
+        <v>878</v>
+      </c>
       <c r="K203" s="8"/>
       <c r="L203" s="8"/>
       <c r="M203" s="2" t="str">
         <f>IF(J203="","",VLOOKUP(J203,[1]ISO辞書!A:B,2,FALSE))</f>
-        <v/>
+        <v>IRN</v>
       </c>
       <c r="N203" s="2" t="str">
         <f>IF(K203="","",VLOOKUP(K203,[1]ISO辞書!A:B,2,FALSE))</f>
@@ -24200,23 +24219,23 @@
         <v/>
       </c>
       <c r="P203" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M203:O203)</f>
+        <v>IRN</v>
       </c>
       <c r="Q203" s="8" t="s">
-        <v>1043</v>
+        <v>1000</v>
       </c>
       <c r="R203" s="8" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="S203" s="10">
-        <v>46133</v>
+        <v>46138</v>
       </c>
       <c r="T203" s="8" t="s">
-        <v>1015</v>
+        <v>994</v>
       </c>
       <c r="U203" s="8" t="s">
-        <v>1044</v>
+        <v>1001</v>
       </c>
       <c r="V203" s="8">
         <v>5</v>
@@ -24244,7 +24263,7 @@
         <v/>
       </c>
       <c r="P204" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M204:O204)</f>
         <v/>
       </c>
     </row>
@@ -24270,7 +24289,7 @@
         <v/>
       </c>
       <c r="P205" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M205:O205)</f>
         <v/>
       </c>
     </row>
@@ -24296,7 +24315,7 @@
         <v/>
       </c>
       <c r="P206" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M206:O206)</f>
         <v/>
       </c>
     </row>
@@ -24322,7 +24341,7 @@
         <v/>
       </c>
       <c r="P207" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M207:O207)</f>
         <v/>
       </c>
     </row>
@@ -24348,7 +24367,7 @@
         <v/>
       </c>
       <c r="P208" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M208:O208)</f>
         <v/>
       </c>
     </row>
@@ -24374,7 +24393,7 @@
         <v/>
       </c>
       <c r="P209" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M209:O209)</f>
         <v/>
       </c>
     </row>
@@ -24400,7 +24419,7 @@
         <v/>
       </c>
       <c r="P210" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M210:O210)</f>
         <v/>
       </c>
     </row>
@@ -24426,7 +24445,7 @@
         <v/>
       </c>
       <c r="P211" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M211:O211)</f>
         <v/>
       </c>
     </row>
@@ -24452,7 +24471,7 @@
         <v/>
       </c>
       <c r="P212" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M212:O212)</f>
         <v/>
       </c>
     </row>
@@ -24478,7 +24497,7 @@
         <v/>
       </c>
       <c r="P213" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M213:O213)</f>
         <v/>
       </c>
     </row>
@@ -24504,7 +24523,7 @@
         <v/>
       </c>
       <c r="P214" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M214:O214)</f>
         <v/>
       </c>
     </row>
@@ -24530,7 +24549,7 @@
         <v/>
       </c>
       <c r="P215" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M215:O215)</f>
         <v/>
       </c>
     </row>
@@ -24556,7 +24575,7 @@
         <v/>
       </c>
       <c r="P216" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M216:O216)</f>
         <v/>
       </c>
     </row>
@@ -24582,7 +24601,7 @@
         <v/>
       </c>
       <c r="P217" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M217:O217)</f>
         <v/>
       </c>
     </row>
@@ -24608,7 +24627,7 @@
         <v/>
       </c>
       <c r="P218" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M218:O218)</f>
         <v/>
       </c>
     </row>
@@ -24634,7 +24653,7 @@
         <v/>
       </c>
       <c r="P219" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M219:O219)</f>
         <v/>
       </c>
     </row>
@@ -24660,7 +24679,7 @@
         <v/>
       </c>
       <c r="P220" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M220:O220)</f>
         <v/>
       </c>
     </row>
@@ -24686,7 +24705,7 @@
         <v/>
       </c>
       <c r="P221" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M221:O221)</f>
         <v/>
       </c>
     </row>
@@ -24712,7 +24731,7 @@
         <v/>
       </c>
       <c r="P222" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M222:O222)</f>
         <v/>
       </c>
     </row>
@@ -24738,7 +24757,7 @@
         <v/>
       </c>
       <c r="P223" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M223:O223)</f>
         <v/>
       </c>
     </row>
@@ -24764,7 +24783,7 @@
         <v/>
       </c>
       <c r="P224" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M224:O224)</f>
         <v/>
       </c>
     </row>
@@ -24790,7 +24809,7 @@
         <v/>
       </c>
       <c r="P225" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M225:O225)</f>
         <v/>
       </c>
     </row>
@@ -24816,7 +24835,7 @@
         <v/>
       </c>
       <c r="P226" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M226:O226)</f>
         <v/>
       </c>
     </row>
@@ -24842,7 +24861,7 @@
         <v/>
       </c>
       <c r="P227" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M227:O227)</f>
         <v/>
       </c>
     </row>
@@ -24868,7 +24887,7 @@
         <v/>
       </c>
       <c r="P228" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M228:O228)</f>
         <v/>
       </c>
     </row>
@@ -24894,7 +24913,7 @@
         <v/>
       </c>
       <c r="P229" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M229:O229)</f>
         <v/>
       </c>
     </row>
@@ -24920,7 +24939,7 @@
         <v/>
       </c>
       <c r="P230" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M230:O230)</f>
         <v/>
       </c>
     </row>
@@ -24946,7 +24965,7 @@
         <v/>
       </c>
       <c r="P231" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M231:O231)</f>
         <v/>
       </c>
     </row>
@@ -24972,7 +24991,7 @@
         <v/>
       </c>
       <c r="P232" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M232:O232)</f>
         <v/>
       </c>
     </row>
@@ -24998,7 +25017,7 @@
         <v/>
       </c>
       <c r="P233" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M233:O233)</f>
         <v/>
       </c>
     </row>
@@ -25024,7 +25043,7 @@
         <v/>
       </c>
       <c r="P234" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M234:O234)</f>
         <v/>
       </c>
     </row>
@@ -25050,7 +25069,7 @@
         <v/>
       </c>
       <c r="P235" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M235:O235)</f>
         <v/>
       </c>
     </row>
@@ -25076,7 +25095,7 @@
         <v/>
       </c>
       <c r="P236" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M236:O236)</f>
         <v/>
       </c>
     </row>
@@ -25102,7 +25121,7 @@
         <v/>
       </c>
       <c r="P237" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M237:O237)</f>
         <v/>
       </c>
     </row>
@@ -25128,7 +25147,7 @@
         <v/>
       </c>
       <c r="P238" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M238:O238)</f>
         <v/>
       </c>
     </row>
@@ -25154,7 +25173,7 @@
         <v/>
       </c>
       <c r="P239" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M239:O239)</f>
         <v/>
       </c>
     </row>
@@ -25180,7 +25199,7 @@
         <v/>
       </c>
       <c r="P240" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M240:O240)</f>
         <v/>
       </c>
     </row>
@@ -25206,7 +25225,7 @@
         <v/>
       </c>
       <c r="P241" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M241:O241)</f>
         <v/>
       </c>
     </row>
@@ -25232,7 +25251,7 @@
         <v/>
       </c>
       <c r="P242" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M242:O242)</f>
         <v/>
       </c>
     </row>
@@ -25258,7 +25277,7 @@
         <v/>
       </c>
       <c r="P243" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M243:O243)</f>
         <v/>
       </c>
     </row>
@@ -25284,7 +25303,7 @@
         <v/>
       </c>
       <c r="P244" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M244:O244)</f>
         <v/>
       </c>
     </row>
@@ -25310,7 +25329,7 @@
         <v/>
       </c>
       <c r="P245" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M245:O245)</f>
         <v/>
       </c>
     </row>
@@ -25336,7 +25355,7 @@
         <v/>
       </c>
       <c r="P246" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M246:O246)</f>
         <v/>
       </c>
     </row>
@@ -25362,7 +25381,7 @@
         <v/>
       </c>
       <c r="P247" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M247:O247)</f>
         <v/>
       </c>
     </row>
@@ -25388,7 +25407,7 @@
         <v/>
       </c>
       <c r="P248" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M248:O248)</f>
         <v/>
       </c>
     </row>
@@ -25414,7 +25433,7 @@
         <v/>
       </c>
       <c r="P249" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M249:O249)</f>
         <v/>
       </c>
     </row>
@@ -25440,7 +25459,7 @@
         <v/>
       </c>
       <c r="P250" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M250:O250)</f>
         <v/>
       </c>
     </row>
@@ -25466,7 +25485,7 @@
         <v/>
       </c>
       <c r="P251" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M251:O251)</f>
         <v/>
       </c>
     </row>
@@ -25492,7 +25511,7 @@
         <v/>
       </c>
       <c r="P252" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M252:O252)</f>
         <v/>
       </c>
     </row>
@@ -25518,7 +25537,7 @@
         <v/>
       </c>
       <c r="P253" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M253:O253)</f>
         <v/>
       </c>
     </row>
@@ -25544,7 +25563,7 @@
         <v/>
       </c>
       <c r="P254" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M254:O254)</f>
         <v/>
       </c>
     </row>
@@ -25570,7 +25589,7 @@
         <v/>
       </c>
       <c r="P255" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M255:O255)</f>
         <v/>
       </c>
     </row>
@@ -25596,7 +25615,7 @@
         <v/>
       </c>
       <c r="P256" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M256:O256)</f>
         <v/>
       </c>
     </row>
@@ -25622,7 +25641,7 @@
         <v/>
       </c>
       <c r="P257" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M257:O257)</f>
         <v/>
       </c>
     </row>
@@ -25648,7 +25667,7 @@
         <v/>
       </c>
       <c r="P258" s="3" t="str">
-        <f t="shared" ref="P258:P321" si="4">_xlfn.TEXTJOIN(";",TRUE,M258:O258)</f>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M258:O258)</f>
         <v/>
       </c>
     </row>
@@ -25674,7 +25693,7 @@
         <v/>
       </c>
       <c r="P259" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M259:O259)</f>
         <v/>
       </c>
     </row>
@@ -25700,7 +25719,7 @@
         <v/>
       </c>
       <c r="P260" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M260:O260)</f>
         <v/>
       </c>
     </row>
@@ -25726,7 +25745,7 @@
         <v/>
       </c>
       <c r="P261" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M261:O261)</f>
         <v/>
       </c>
     </row>
@@ -25752,7 +25771,7 @@
         <v/>
       </c>
       <c r="P262" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M262:O262)</f>
         <v/>
       </c>
     </row>
@@ -25778,7 +25797,7 @@
         <v/>
       </c>
       <c r="P263" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M263:O263)</f>
         <v/>
       </c>
     </row>
@@ -25804,7 +25823,7 @@
         <v/>
       </c>
       <c r="P264" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M264:O264)</f>
         <v/>
       </c>
     </row>
@@ -25830,7 +25849,7 @@
         <v/>
       </c>
       <c r="P265" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M265:O265)</f>
         <v/>
       </c>
     </row>
@@ -25856,7 +25875,7 @@
         <v/>
       </c>
       <c r="P266" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M266:O266)</f>
         <v/>
       </c>
     </row>
@@ -25882,7 +25901,7 @@
         <v/>
       </c>
       <c r="P267" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M267:O267)</f>
         <v/>
       </c>
     </row>
@@ -25908,7 +25927,7 @@
         <v/>
       </c>
       <c r="P268" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M268:O268)</f>
         <v/>
       </c>
     </row>
@@ -25934,7 +25953,7 @@
         <v/>
       </c>
       <c r="P269" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M269:O269)</f>
         <v/>
       </c>
     </row>
@@ -25960,7 +25979,7 @@
         <v/>
       </c>
       <c r="P270" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M270:O270)</f>
         <v/>
       </c>
     </row>
@@ -25986,7 +26005,7 @@
         <v/>
       </c>
       <c r="P271" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M271:O271)</f>
         <v/>
       </c>
     </row>
@@ -26012,7 +26031,7 @@
         <v/>
       </c>
       <c r="P272" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M272:O272)</f>
         <v/>
       </c>
     </row>
@@ -26038,7 +26057,7 @@
         <v/>
       </c>
       <c r="P273" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M273:O273)</f>
         <v/>
       </c>
     </row>
@@ -26064,7 +26083,7 @@
         <v/>
       </c>
       <c r="P274" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M274:O274)</f>
         <v/>
       </c>
     </row>
@@ -26090,7 +26109,7 @@
         <v/>
       </c>
       <c r="P275" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M275:O275)</f>
         <v/>
       </c>
     </row>
@@ -26116,7 +26135,7 @@
         <v/>
       </c>
       <c r="P276" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M276:O276)</f>
         <v/>
       </c>
     </row>
@@ -26142,7 +26161,7 @@
         <v/>
       </c>
       <c r="P277" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M277:O277)</f>
         <v/>
       </c>
     </row>
@@ -26168,7 +26187,7 @@
         <v/>
       </c>
       <c r="P278" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M278:O278)</f>
         <v/>
       </c>
     </row>
@@ -26194,7 +26213,7 @@
         <v/>
       </c>
       <c r="P279" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M279:O279)</f>
         <v/>
       </c>
     </row>
@@ -26220,7 +26239,7 @@
         <v/>
       </c>
       <c r="P280" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M280:O280)</f>
         <v/>
       </c>
     </row>
@@ -26246,7 +26265,7 @@
         <v/>
       </c>
       <c r="P281" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M281:O281)</f>
         <v/>
       </c>
     </row>
@@ -26272,7 +26291,7 @@
         <v/>
       </c>
       <c r="P282" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M282:O282)</f>
         <v/>
       </c>
     </row>
@@ -26298,7 +26317,7 @@
         <v/>
       </c>
       <c r="P283" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M283:O283)</f>
         <v/>
       </c>
     </row>
@@ -26324,7 +26343,7 @@
         <v/>
       </c>
       <c r="P284" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M284:O284)</f>
         <v/>
       </c>
     </row>
@@ -26350,7 +26369,7 @@
         <v/>
       </c>
       <c r="P285" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M285:O285)</f>
         <v/>
       </c>
     </row>
@@ -26376,7 +26395,7 @@
         <v/>
       </c>
       <c r="P286" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M286:O286)</f>
         <v/>
       </c>
     </row>
@@ -26402,7 +26421,7 @@
         <v/>
       </c>
       <c r="P287" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M287:O287)</f>
         <v/>
       </c>
     </row>
@@ -26428,7 +26447,7 @@
         <v/>
       </c>
       <c r="P288" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M288:O288)</f>
         <v/>
       </c>
     </row>
@@ -26454,7 +26473,7 @@
         <v/>
       </c>
       <c r="P289" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M289:O289)</f>
         <v/>
       </c>
     </row>
@@ -26480,7 +26499,7 @@
         <v/>
       </c>
       <c r="P290" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M290:O290)</f>
         <v/>
       </c>
     </row>
@@ -26506,7 +26525,7 @@
         <v/>
       </c>
       <c r="P291" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M291:O291)</f>
         <v/>
       </c>
     </row>
@@ -26532,7 +26551,7 @@
         <v/>
       </c>
       <c r="P292" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M292:O292)</f>
         <v/>
       </c>
     </row>
@@ -26558,7 +26577,7 @@
         <v/>
       </c>
       <c r="P293" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M293:O293)</f>
         <v/>
       </c>
     </row>
@@ -26584,7 +26603,7 @@
         <v/>
       </c>
       <c r="P294" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M294:O294)</f>
         <v/>
       </c>
     </row>
@@ -26610,7 +26629,7 @@
         <v/>
       </c>
       <c r="P295" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M295:O295)</f>
         <v/>
       </c>
     </row>
@@ -26636,7 +26655,7 @@
         <v/>
       </c>
       <c r="P296" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M296:O296)</f>
         <v/>
       </c>
     </row>
@@ -26662,7 +26681,7 @@
         <v/>
       </c>
       <c r="P297" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M297:O297)</f>
         <v/>
       </c>
     </row>
@@ -26688,7 +26707,7 @@
         <v/>
       </c>
       <c r="P298" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M298:O298)</f>
         <v/>
       </c>
     </row>
@@ -26714,7 +26733,7 @@
         <v/>
       </c>
       <c r="P299" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M299:O299)</f>
         <v/>
       </c>
     </row>
@@ -26740,7 +26759,7 @@
         <v/>
       </c>
       <c r="P300" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M300:O300)</f>
         <v/>
       </c>
     </row>
@@ -26766,7 +26785,7 @@
         <v/>
       </c>
       <c r="P301" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M301:O301)</f>
         <v/>
       </c>
     </row>
@@ -26792,7 +26811,7 @@
         <v/>
       </c>
       <c r="P302" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M302:O302)</f>
         <v/>
       </c>
     </row>
@@ -26818,7 +26837,7 @@
         <v/>
       </c>
       <c r="P303" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M303:O303)</f>
         <v/>
       </c>
     </row>
@@ -26844,7 +26863,7 @@
         <v/>
       </c>
       <c r="P304" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M304:O304)</f>
         <v/>
       </c>
     </row>
@@ -26870,7 +26889,7 @@
         <v/>
       </c>
       <c r="P305" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M305:O305)</f>
         <v/>
       </c>
     </row>
@@ -26896,7 +26915,7 @@
         <v/>
       </c>
       <c r="P306" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M306:O306)</f>
         <v/>
       </c>
     </row>
@@ -26922,7 +26941,7 @@
         <v/>
       </c>
       <c r="P307" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M307:O307)</f>
         <v/>
       </c>
     </row>
@@ -26948,7 +26967,7 @@
         <v/>
       </c>
       <c r="P308" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M308:O308)</f>
         <v/>
       </c>
     </row>
@@ -26974,7 +26993,7 @@
         <v/>
       </c>
       <c r="P309" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M309:O309)</f>
         <v/>
       </c>
     </row>
@@ -27000,7 +27019,7 @@
         <v/>
       </c>
       <c r="P310" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M310:O310)</f>
         <v/>
       </c>
     </row>
@@ -27026,7 +27045,7 @@
         <v/>
       </c>
       <c r="P311" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M311:O311)</f>
         <v/>
       </c>
     </row>
@@ -27052,7 +27071,7 @@
         <v/>
       </c>
       <c r="P312" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M312:O312)</f>
         <v/>
       </c>
     </row>
@@ -27078,7 +27097,7 @@
         <v/>
       </c>
       <c r="P313" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M313:O313)</f>
         <v/>
       </c>
     </row>
@@ -27104,7 +27123,7 @@
         <v/>
       </c>
       <c r="P314" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M314:O314)</f>
         <v/>
       </c>
     </row>
@@ -27130,7 +27149,7 @@
         <v/>
       </c>
       <c r="P315" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M315:O315)</f>
         <v/>
       </c>
     </row>
@@ -27156,7 +27175,7 @@
         <v/>
       </c>
       <c r="P316" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M316:O316)</f>
         <v/>
       </c>
     </row>
@@ -27182,7 +27201,7 @@
         <v/>
       </c>
       <c r="P317" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M317:O317)</f>
         <v/>
       </c>
     </row>
@@ -27208,7 +27227,7 @@
         <v/>
       </c>
       <c r="P318" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M318:O318)</f>
         <v/>
       </c>
     </row>
@@ -27234,7 +27253,7 @@
         <v/>
       </c>
       <c r="P319" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M319:O319)</f>
         <v/>
       </c>
     </row>
@@ -27260,7 +27279,7 @@
         <v/>
       </c>
       <c r="P320" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M320:O320)</f>
         <v/>
       </c>
     </row>
@@ -27286,7 +27305,7 @@
         <v/>
       </c>
       <c r="P321" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M321:O321)</f>
         <v/>
       </c>
     </row>
@@ -27312,7 +27331,7 @@
         <v/>
       </c>
       <c r="P322" s="3" t="str">
-        <f t="shared" ref="P322:P370" si="5">_xlfn.TEXTJOIN(";",TRUE,M322:O322)</f>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M322:O322)</f>
         <v/>
       </c>
     </row>
@@ -27338,7 +27357,7 @@
         <v/>
       </c>
       <c r="P323" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M323:O323)</f>
         <v/>
       </c>
     </row>
@@ -27364,7 +27383,7 @@
         <v/>
       </c>
       <c r="P324" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M324:O324)</f>
         <v/>
       </c>
     </row>
@@ -27390,7 +27409,7 @@
         <v/>
       </c>
       <c r="P325" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M325:O325)</f>
         <v/>
       </c>
     </row>
@@ -27416,7 +27435,7 @@
         <v/>
       </c>
       <c r="P326" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M326:O326)</f>
         <v/>
       </c>
     </row>
@@ -27442,7 +27461,7 @@
         <v/>
       </c>
       <c r="P327" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M327:O327)</f>
         <v/>
       </c>
     </row>
@@ -27468,7 +27487,7 @@
         <v/>
       </c>
       <c r="P328" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M328:O328)</f>
         <v/>
       </c>
     </row>
@@ -27494,7 +27513,7 @@
         <v/>
       </c>
       <c r="P329" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M329:O329)</f>
         <v/>
       </c>
     </row>
@@ -27520,7 +27539,7 @@
         <v/>
       </c>
       <c r="P330" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M330:O330)</f>
         <v/>
       </c>
     </row>
@@ -27546,7 +27565,7 @@
         <v/>
       </c>
       <c r="P331" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M331:O331)</f>
         <v/>
       </c>
     </row>
@@ -27572,7 +27591,7 @@
         <v/>
       </c>
       <c r="P332" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M332:O332)</f>
         <v/>
       </c>
     </row>
@@ -27598,7 +27617,7 @@
         <v/>
       </c>
       <c r="P333" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M333:O333)</f>
         <v/>
       </c>
     </row>
@@ -27624,7 +27643,7 @@
         <v/>
       </c>
       <c r="P334" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M334:O334)</f>
         <v/>
       </c>
     </row>
@@ -27650,7 +27669,7 @@
         <v/>
       </c>
       <c r="P335" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M335:O335)</f>
         <v/>
       </c>
     </row>
@@ -27676,7 +27695,7 @@
         <v/>
       </c>
       <c r="P336" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M336:O336)</f>
         <v/>
       </c>
     </row>
@@ -27702,7 +27721,7 @@
         <v/>
       </c>
       <c r="P337" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M337:O337)</f>
         <v/>
       </c>
     </row>
@@ -27728,7 +27747,7 @@
         <v/>
       </c>
       <c r="P338" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M338:O338)</f>
         <v/>
       </c>
     </row>
@@ -27754,7 +27773,7 @@
         <v/>
       </c>
       <c r="P339" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M339:O339)</f>
         <v/>
       </c>
     </row>
@@ -27780,7 +27799,7 @@
         <v/>
       </c>
       <c r="P340" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M340:O340)</f>
         <v/>
       </c>
     </row>
@@ -27806,7 +27825,7 @@
         <v/>
       </c>
       <c r="P341" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M341:O341)</f>
         <v/>
       </c>
     </row>
@@ -27832,7 +27851,7 @@
         <v/>
       </c>
       <c r="P342" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M342:O342)</f>
         <v/>
       </c>
     </row>
@@ -27858,7 +27877,7 @@
         <v/>
       </c>
       <c r="P343" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M343:O343)</f>
         <v/>
       </c>
     </row>
@@ -27884,7 +27903,7 @@
         <v/>
       </c>
       <c r="P344" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M344:O344)</f>
         <v/>
       </c>
     </row>
@@ -27910,7 +27929,7 @@
         <v/>
       </c>
       <c r="P345" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M345:O345)</f>
         <v/>
       </c>
     </row>
@@ -27936,7 +27955,7 @@
         <v/>
       </c>
       <c r="P346" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M346:O346)</f>
         <v/>
       </c>
     </row>
@@ -27962,7 +27981,7 @@
         <v/>
       </c>
       <c r="P347" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M347:O347)</f>
         <v/>
       </c>
     </row>
@@ -27988,7 +28007,7 @@
         <v/>
       </c>
       <c r="P348" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M348:O348)</f>
         <v/>
       </c>
     </row>
@@ -28014,7 +28033,7 @@
         <v/>
       </c>
       <c r="P349" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M349:O349)</f>
         <v/>
       </c>
     </row>
@@ -28040,7 +28059,7 @@
         <v/>
       </c>
       <c r="P350" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M350:O350)</f>
         <v/>
       </c>
     </row>
@@ -28066,7 +28085,7 @@
         <v/>
       </c>
       <c r="P351" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M351:O351)</f>
         <v/>
       </c>
     </row>
@@ -28092,7 +28111,7 @@
         <v/>
       </c>
       <c r="P352" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M352:O352)</f>
         <v/>
       </c>
     </row>
@@ -28118,7 +28137,7 @@
         <v/>
       </c>
       <c r="P353" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M353:O353)</f>
         <v/>
       </c>
     </row>
@@ -28144,7 +28163,7 @@
         <v/>
       </c>
       <c r="P354" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M354:O354)</f>
         <v/>
       </c>
     </row>
@@ -28170,7 +28189,7 @@
         <v/>
       </c>
       <c r="P355" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M355:O355)</f>
         <v/>
       </c>
     </row>
@@ -28196,7 +28215,7 @@
         <v/>
       </c>
       <c r="P356" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M356:O356)</f>
         <v/>
       </c>
     </row>
@@ -28222,7 +28241,7 @@
         <v/>
       </c>
       <c r="P357" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M357:O357)</f>
         <v/>
       </c>
     </row>
@@ -28248,7 +28267,7 @@
         <v/>
       </c>
       <c r="P358" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M358:O358)</f>
         <v/>
       </c>
     </row>
@@ -28274,7 +28293,7 @@
         <v/>
       </c>
       <c r="P359" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M359:O359)</f>
         <v/>
       </c>
     </row>
@@ -28300,7 +28319,7 @@
         <v/>
       </c>
       <c r="P360" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M360:O360)</f>
         <v/>
       </c>
     </row>
@@ -28326,7 +28345,7 @@
         <v/>
       </c>
       <c r="P361" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M361:O361)</f>
         <v/>
       </c>
     </row>
@@ -28352,7 +28371,7 @@
         <v/>
       </c>
       <c r="P362" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M362:O362)</f>
         <v/>
       </c>
     </row>
@@ -28378,7 +28397,7 @@
         <v/>
       </c>
       <c r="P363" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M363:O363)</f>
         <v/>
       </c>
     </row>
@@ -28404,7 +28423,7 @@
         <v/>
       </c>
       <c r="P364" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M364:O364)</f>
         <v/>
       </c>
     </row>
@@ -28430,7 +28449,7 @@
         <v/>
       </c>
       <c r="P365" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M365:O365)</f>
         <v/>
       </c>
     </row>
@@ -28456,7 +28475,7 @@
         <v/>
       </c>
       <c r="P366" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M366:O366)</f>
         <v/>
       </c>
     </row>
@@ -28482,7 +28501,7 @@
         <v/>
       </c>
       <c r="P367" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M367:O367)</f>
         <v/>
       </c>
     </row>
@@ -28508,7 +28527,7 @@
         <v/>
       </c>
       <c r="P368" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M368:O368)</f>
         <v/>
       </c>
     </row>
@@ -28534,7 +28553,7 @@
         <v/>
       </c>
       <c r="P369" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M369:O369)</f>
         <v/>
       </c>
     </row>
@@ -28552,7 +28571,7 @@
         <v/>
       </c>
       <c r="P370" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f>_xlfn.TEXTJOIN(";",TRUE,M370:O370)</f>
         <v/>
       </c>
     </row>
@@ -28569,7 +28588,7 @@
     <hyperlink ref="U45" r:id="rId3" xr:uid="{CAB2C613-E685-436C-AA62-7678804484F9}"/>
     <hyperlink ref="U46" r:id="rId4" xr:uid="{B735F61B-7109-4112-8AD5-8A0DE0EE4130}"/>
     <hyperlink ref="U122" r:id="rId5" xr:uid="{7A7EACA8-130A-4B97-AD1E-F8E11AE4B691}"/>
-    <hyperlink ref="U186" r:id="rId6" xr:uid="{AC5420A9-A336-40E2-8D12-313E09D20CCB}"/>
+    <hyperlink ref="U190" r:id="rId6" xr:uid="{AC5420A9-A336-40E2-8D12-313E09D20CCB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
